--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newfoundland &amp; Labrador" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Newfoundland &amp; Labrador" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Michelin Deposit</t>
+          <t>Copper Creek BV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>013J/12/U  001</t>
+          <t>012H/16/Cu 040</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>44</v>
       </c>
       <c r="V2" t="n">
-        <v>54.58562</v>
+        <v>49.91887</v>
       </c>
       <c r="W2" t="n">
-        <v>-59.98056</v>
+        <v>-56.20986</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rainbow Deposit</t>
+          <t>Horseshoe Zone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>013J/12/U  008</t>
+          <t>002E/02/Au 039</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,23 +688,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>54.56417</v>
+        <v>49.01341</v>
       </c>
       <c r="W3" t="n">
-        <v>-59.99369</v>
+        <v>-54.81741</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jacques Lake</t>
+          <t>Viking Gold-Thor Trend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>013J/12/U  018</t>
+          <t>012H/10/Au 011</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -760,23 +760,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U4" t="n">
         <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>54.71754</v>
+        <v>49.69447</v>
       </c>
       <c r="W4" t="n">
-        <v>-59.59268</v>
+        <v>-56.99193</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Road Zone</t>
+          <t>PW Zone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>012H/15/Au 011</t>
+          <t>011O/10/Au 011</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -841,14 +841,14 @@
         <v>44</v>
       </c>
       <c r="V5" t="n">
-        <v>49.88465</v>
+        <v>47.74631</v>
       </c>
       <c r="W5" t="n">
-        <v>-56.83885</v>
+        <v>-58.94364</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apsy Zone</t>
+          <t>Deep Fox</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>012H/15/Au 014</t>
+          <t>003D/05/Ree007</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>44</v>
       </c>
       <c r="V6" t="n">
-        <v>49.89471</v>
+        <v>52.3805</v>
       </c>
       <c r="W6" t="n">
-        <v>-56.82917</v>
+        <v>-55.64987</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deer Cove Main Zone</t>
+          <t>Mart Lake Graphite</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>012I/01/Au 001</t>
+          <t>023B/14/Gf 001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>44</v>
       </c>
       <c r="V7" t="n">
-        <v>50.01619</v>
+        <v>52.8283</v>
       </c>
       <c r="W7" t="n">
-        <v>-56.04389</v>
+        <v>-67.01484000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Turners Ridge</t>
+          <t>Rainbow Deposit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>012H/11/Pb 001</t>
+          <t>013J/12/U  008</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U8" t="n">
         <v>44</v>
       </c>
       <c r="V8" t="n">
-        <v>49.59029</v>
+        <v>54.56417</v>
       </c>
       <c r="W8" t="n">
-        <v>-57.00443</v>
+        <v>-59.99369</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mann #1</t>
+          <t>Michelin Deposit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>013L/01/Be 001</t>
+          <t>013J/12/U  001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Niobium, Uranium, Zinc, Beryllium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>44</v>
       </c>
       <c r="V9" t="n">
-        <v>54.23929</v>
+        <v>54.58562</v>
       </c>
       <c r="W9" t="n">
-        <v>-62.3924</v>
+        <v>-59.98056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Two Tom Lake</t>
+          <t>Deer Cove Main Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>013L/01/REE001</t>
+          <t>012I/01/Au 001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>54.21359</v>
+        <v>50.01619</v>
       </c>
       <c r="W10" t="n">
-        <v>-62.14192</v>
+        <v>-56.04389</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nash Lake (Main Zone)</t>
+          <t>Apsy Zone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>013J/13/U  006</t>
+          <t>012H/15/Au 014</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1273,14 +1273,14 @@
         <v>44</v>
       </c>
       <c r="V11" t="n">
-        <v>54.91032</v>
+        <v>49.89471</v>
       </c>
       <c r="W11" t="n">
-        <v>-59.62004</v>
+        <v>-56.82917</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
         </is>
       </c>
     </row>
@@ -1290,24 +1290,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inda Lake</t>
+          <t>Road Zone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>013J/13/U  009</t>
+          <t>012H/15/Au 011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Uranium</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>44</v>
       </c>
       <c r="V12" t="n">
-        <v>54.92456</v>
+        <v>49.88465</v>
       </c>
       <c r="W12" t="n">
-        <v>-59.5807</v>
+        <v>-56.83885</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gear Lake</t>
+          <t>Jacques Lake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>013J/13/U  010</t>
+          <t>013J/12/U  018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1417,14 +1417,14 @@
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>54.94329</v>
+        <v>54.71754</v>
       </c>
       <c r="W13" t="n">
-        <v>-59.54386</v>
+        <v>-59.59268</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
         </is>
       </c>
     </row>
@@ -1434,24 +1434,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kitts</t>
+          <t>Turners Ridge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>013J/14/U  001</t>
+          <t>012H/11/Pb 001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>44</v>
       </c>
       <c r="V14" t="n">
-        <v>54.99779</v>
+        <v>49.59029</v>
       </c>
       <c r="W14" t="n">
-        <v>-59.4872</v>
+        <v>-57.00443</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H Brook Showing</t>
+          <t>Kitts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>011O/15/Au 004</t>
+          <t>013J/14/U  001</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U16" t="n">
         <v>44</v>
       </c>
       <c r="V16" t="n">
-        <v>47.7624</v>
+        <v>54.99779</v>
       </c>
       <c r="W16" t="n">
-        <v>-58.91357</v>
+        <v>-59.4872</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit #4 Zone</t>
+          <t>Gear Lake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>011O/15/Au 001</t>
+          <t>013J/13/U  010</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>44</v>
       </c>
       <c r="V17" t="n">
-        <v>47.76081</v>
+        <v>54.94329</v>
       </c>
       <c r="W17" t="n">
-        <v>-58.91872</v>
+        <v>-59.54386</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
         </is>
       </c>
     </row>
@@ -1722,24 +1722,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit 41 Zone</t>
+          <t>Inda Lake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>011O/15/Au 002</t>
+          <t>013J/13/U  009</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Molybdenum, Copper, Uranium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1777,14 +1777,14 @@
         <v>44</v>
       </c>
       <c r="V18" t="n">
-        <v>47.75858</v>
+        <v>54.92456</v>
       </c>
       <c r="W18" t="n">
-        <v>-58.92331</v>
+        <v>-59.5807</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>51 Zone</t>
+          <t>Nash Lake (Main Zone)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>011O/15/Au 003</t>
+          <t>013J/13/U  006</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>44</v>
       </c>
       <c r="V19" t="n">
-        <v>47.75077</v>
+        <v>54.91032</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.93823</v>
+        <v>-59.62004</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>H Brook Showing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>011O/15/Au 004</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>44</v>
       </c>
       <c r="V20" t="n">
-        <v>48.69485</v>
+        <v>47.7624</v>
       </c>
       <c r="W20" t="n">
-        <v>-58.68177</v>
+        <v>-58.91357</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Keats</t>
+          <t>51 Zone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>002D/15/Au 010</t>
+          <t>011O/15/Au 003</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>44</v>
       </c>
       <c r="V21" t="n">
-        <v>48.97891</v>
+        <v>47.75077</v>
       </c>
       <c r="W21" t="n">
-        <v>-54.8402</v>
+        <v>-58.93823</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Point Leamington Deposit</t>
+          <t>Cape Ray Gold Deposit 41 Zone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>002E/05/Zn 001</t>
+          <t>011O/15/Au 002</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead, Zinc</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>44</v>
       </c>
       <c r="V22" t="n">
-        <v>49.27672</v>
+        <v>47.75858</v>
       </c>
       <c r="W22" t="n">
-        <v>-55.63152</v>
+        <v>-58.92331</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bull Road Showing</t>
+          <t>Cape Ray Gold Deposit #4 Zone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>002E/12/Zn 007</t>
+          <t>011O/15/Au 001</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Antimony, Zinc</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>44</v>
       </c>
       <c r="V23" t="n">
-        <v>49.51431</v>
+        <v>47.76081</v>
       </c>
       <c r="W23" t="n">
-        <v>-55.7118</v>
+        <v>-58.91872</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2154,24 +2154,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Windowglass Hill - Main Zone</t>
+          <t>Two Tom Lake</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>011O/10/Au 001</t>
+          <t>013L/01/REE001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>44</v>
       </c>
       <c r="V24" t="n">
-        <v>47.74279</v>
+        <v>54.21359</v>
       </c>
       <c r="W24" t="n">
-        <v>-58.95727</v>
+        <v>-62.14192</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Far Eastern Deeps</t>
+          <t>Mann #1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>014D/08/Ni 013</t>
+          <t>013L/01/Be 001</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Niobium, Uranium, Zinc, Beryllium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>44</v>
       </c>
       <c r="V25" t="n">
-        <v>56.32109</v>
+        <v>54.23929</v>
       </c>
       <c r="W25" t="n">
-        <v>-62.06064</v>
+        <v>-62.3924</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
         </is>
       </c>
     </row>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ackley City</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>001M/11/Mo 002</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Molybdenum</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2353,14 +2353,14 @@
         <v>44</v>
       </c>
       <c r="V26" t="n">
-        <v>47.69347</v>
+        <v>48.69485</v>
       </c>
       <c r="W26" t="n">
-        <v>-55.20716</v>
+        <v>-58.68177</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -2370,24 +2370,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Strickland - Copper Zone</t>
+          <t>Keats</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>011O/16/Cu 001</t>
+          <t>002D/15/Au 010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>44</v>
       </c>
       <c r="V27" t="n">
-        <v>47.80365</v>
+        <v>48.97891</v>
       </c>
       <c r="W27" t="n">
-        <v>-58.30275</v>
+        <v>-54.8402</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
         </is>
       </c>
     </row>
@@ -2442,24 +2442,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Two Time</t>
+          <t>Bull Road Showing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>013K/11/U  005</t>
+          <t>002E/12/Zn 007</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper, Silver, Lead, Antimony, Zinc</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2497,14 +2497,14 @@
         <v>44</v>
       </c>
       <c r="V28" t="n">
-        <v>54.56554</v>
+        <v>49.51431</v>
       </c>
       <c r="W28" t="n">
-        <v>-61.17152</v>
+        <v>-55.7118</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2514,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Voisey's Bay, South Eastern Deeps</t>
+          <t>Point Leamington Deposit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>014D/08/Ni 017</t>
+          <t>002E/05/Zn 001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Silver, Copper, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>44</v>
       </c>
       <c r="V29" t="n">
-        <v>56.31756</v>
+        <v>49.27672</v>
       </c>
       <c r="W29" t="n">
-        <v>-62.06953</v>
+        <v>-55.63152</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Voisey's Bay, North Eastern Deeps</t>
+          <t>Windowglass Hill - Main Zone</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>014D/08/Ni 011</t>
+          <t>011O/10/Au 001</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2641,14 +2641,14 @@
         <v>44</v>
       </c>
       <c r="V30" t="n">
-        <v>56.32929</v>
+        <v>47.74279</v>
       </c>
       <c r="W30" t="n">
-        <v>-62.07733</v>
+        <v>-58.95727</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2730,24 +2730,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moran Lake C-Zone</t>
+          <t>Voisey's Bay, North Eastern Deeps</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>013K/07/U  002</t>
+          <t>014D/08/Ni 011</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2785,14 +2785,14 @@
         <v>44</v>
       </c>
       <c r="V32" t="n">
-        <v>54.47908</v>
+        <v>56.32929</v>
       </c>
       <c r="W32" t="n">
-        <v>-60.9581</v>
+        <v>-62.07733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Voisey's Bay, South Eastern Deeps</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>013K/07/U  007</t>
+          <t>014D/08/Ni 017</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Vanadium, Uranium</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2857,14 +2857,14 @@
         <v>44</v>
       </c>
       <c r="V33" t="n">
-        <v>54.46751</v>
+        <v>56.31756</v>
       </c>
       <c r="W33" t="n">
-        <v>-60.98105</v>
+        <v>-62.06953</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
         </is>
       </c>
     </row>
@@ -2874,24 +2874,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jaclyn Main - Golden Promise</t>
+          <t>Two Time</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>012A/16/Au 002</t>
+          <t>013K/11/U  005</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2929,14 +2929,14 @@
         <v>44</v>
       </c>
       <c r="V34" t="n">
-        <v>48.90572</v>
+        <v>54.56554</v>
       </c>
       <c r="W34" t="n">
-        <v>-56.15002</v>
+        <v>-61.17152</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Strickland - Main Zone</t>
+          <t>Area 1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>011O/16/Zn 001</t>
+          <t>013K/07/U  007</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Gold, Zinc</t>
+          <t>Copper, Vanadium, Uranium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>44</v>
       </c>
       <c r="V35" t="n">
-        <v>47.80818</v>
+        <v>54.46751</v>
       </c>
       <c r="W35" t="n">
-        <v>-58.29993</v>
+        <v>-60.98105</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Strickland - Silver Hill Zone</t>
+          <t>Moran Lake C-Zone</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>011O/16/Zn 002</t>
+          <t>013K/07/U  002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>44</v>
       </c>
       <c r="V36" t="n">
-        <v>47.81</v>
+        <v>54.47908</v>
       </c>
       <c r="W36" t="n">
-        <v>-58.2985</v>
+        <v>-60.9581</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
         </is>
       </c>
     </row>
@@ -3090,24 +3090,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Moly Brook</t>
+          <t>Grey River Tungsten</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>011P/11/Mo 001</t>
+          <t>011P/11/W  001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,14 +3145,14 @@
         <v>44</v>
       </c>
       <c r="V37" t="n">
-        <v>47.61683</v>
+        <v>47.59343</v>
       </c>
       <c r="W37" t="n">
-        <v>-57.1034</v>
+        <v>-57.10342</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3162,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Grey River Tungsten</t>
+          <t>Moly Brook</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>011P/11/W  001</t>
+          <t>011P/11/Mo 001</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3217,14 +3217,14 @@
         <v>44</v>
       </c>
       <c r="V38" t="n">
-        <v>47.59343</v>
+        <v>47.61683</v>
       </c>
       <c r="W38" t="n">
-        <v>-57.10342</v>
+        <v>-57.1034</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Springer's Hill-Main Showing</t>
+          <t>Strickland - Silver Hill Zone</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>012B/16/Cr 002</t>
+          <t>011O/16/Zn 002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>44</v>
       </c>
       <c r="V39" t="n">
-        <v>48.7927</v>
+        <v>47.81</v>
       </c>
       <c r="W39" t="n">
-        <v>-58.44526</v>
+        <v>-58.2985</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -3306,24 +3306,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Saddle Zone</t>
+          <t>Strickland - Main Zone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>002E/02/Au 038</t>
+          <t>011O/16/Zn 001</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Copper, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U40" t="n">
         <v>44</v>
       </c>
       <c r="V40" t="n">
-        <v>49.00899</v>
+        <v>47.80818</v>
       </c>
       <c r="W40" t="n">
-        <v>-54.81554</v>
+        <v>-58.29993</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Keats South</t>
+          <t>Jaclyn Main - Golden Promise</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>002D/15/Au 060</t>
+          <t>012A/16/Au 002</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>44</v>
       </c>
       <c r="V41" t="n">
-        <v>48.97791</v>
+        <v>48.90572</v>
       </c>
       <c r="W41" t="n">
-        <v>-54.84407</v>
+        <v>-56.15002</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viking Gold-Thor Trend</t>
+          <t>Strickland - Copper Zone</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>012H/10/Au 011</t>
+          <t>011O/16/Cu 001</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3496,23 +3496,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
         <v>44</v>
       </c>
       <c r="V42" t="n">
-        <v>49.69447</v>
+        <v>47.80365</v>
       </c>
       <c r="W42" t="n">
-        <v>-56.99193</v>
+        <v>-58.30275</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Horseshoe Zone</t>
+          <t>Ackley City</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>002E/02/Au 039</t>
+          <t>001M/11/Mo 002</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>44</v>
       </c>
       <c r="V43" t="n">
-        <v>49.01341</v>
+        <v>47.69347</v>
       </c>
       <c r="W43" t="n">
-        <v>-54.81741</v>
+        <v>-55.20716</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
         </is>
       </c>
     </row>
@@ -3594,24 +3594,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Copper Creek BV</t>
+          <t>Voisey's Bay, Far Eastern Deeps</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>012H/16/Cu 040</t>
+          <t>014D/08/Ni 013</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>44</v>
       </c>
       <c r="V44" t="n">
-        <v>49.91887</v>
+        <v>56.32109</v>
       </c>
       <c r="W44" t="n">
-        <v>-56.20986</v>
+        <v>-62.06064</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deep Fox</t>
+          <t>Springer's Hill-Main Showing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>003D/05/Ree007</t>
+          <t>012B/16/Cr 002</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>44</v>
       </c>
       <c r="V45" t="n">
-        <v>52.3805</v>
+        <v>48.7927</v>
       </c>
       <c r="W45" t="n">
-        <v>-55.64987</v>
+        <v>-58.44526</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PW Zone</t>
+          <t>Keats South</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>011O/10/Au 011</t>
+          <t>002D/15/Au 060</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>44</v>
       </c>
       <c r="V46" t="n">
-        <v>47.74631</v>
+        <v>48.97791</v>
       </c>
       <c r="W46" t="n">
-        <v>-58.94364</v>
+        <v>-54.84407</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mart Lake Graphite</t>
+          <t>Saddle Zone</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>023B/14/Gf 001</t>
+          <t>002E/02/Au 038</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3856,23 +3856,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U47" t="n">
         <v>44</v>
       </c>
       <c r="V47" t="n">
-        <v>52.8283</v>
+        <v>49.00899</v>
       </c>
       <c r="W47" t="n">
-        <v>-67.01484000000001</v>
+        <v>-54.81554</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Foxtrot</t>
+          <t>Lewis Brook Mine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>003D/05/Ree001</t>
+          <t>012B/15/Asb001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>37</v>
       </c>
       <c r="V48" t="n">
-        <v>52.40035</v>
+        <v>48.77071</v>
       </c>
       <c r="W48" t="n">
-        <v>-55.82418</v>
+        <v>-58.56548</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deer Cove Talc Zone</t>
+          <t>Beaver Dam</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>012I/01/Tlc001</t>
+          <t>012H/15/Au 018</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Magnesium, Talc</t>
+          <t>Arsenic, Gold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4009,14 +4009,14 @@
         <v>37</v>
       </c>
       <c r="V49" t="n">
-        <v>50.01534</v>
+        <v>49.86141</v>
       </c>
       <c r="W49" t="n">
-        <v>-56.04949</v>
+        <v>-56.85295</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Beaver Dam</t>
+          <t>Strange Lake</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>012H/15/Au 018</t>
+          <t>024A/08/Ree001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Arsenic, Gold</t>
+          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>49.86141</v>
+        <v>56.31656</v>
       </c>
       <c r="W50" t="n">
-        <v>-56.85295</v>
+        <v>-64.12678</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Strange Lake</t>
+          <t>Norsk South Block</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>024A/08/Ree001</t>
+          <t>012B/10/Dol004</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>56.31656</v>
+        <v>48.52445</v>
       </c>
       <c r="W51" t="n">
-        <v>-64.12678</v>
+        <v>-58.99684</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Norsk North Block</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>012B/10/Dol003</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4225,14 +4225,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>48.39536</v>
+        <v>48.53397</v>
       </c>
       <c r="W52" t="n">
-        <v>-58.42046</v>
+        <v>-58.9773</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Porcupine Strand North Beach</t>
+          <t>Round Pond Deposit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>013I/03/Ti 001</t>
+          <t>012P/08/Zn 015</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
+          <t>Fluorine, Lead, Zinc</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>54.03818</v>
+        <v>51.25735</v>
       </c>
       <c r="W53" t="n">
-        <v>-57.31912</v>
+        <v>-56.26701</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4386,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Round Pond Deposit</t>
+          <t>Porcupine Strand North Beach</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>012P/08/Zn 015</t>
+          <t>013I/03/Ti 001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fluorine, Lead, Zinc</t>
+          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4441,14 +4441,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>51.25735</v>
+        <v>54.03818</v>
       </c>
       <c r="W55" t="n">
-        <v>-56.26701</v>
+        <v>-57.31912</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Norsk South Block</t>
+          <t>Deer Cove Talc Zone</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>012B/10/Dol004</t>
+          <t>012I/01/Tlc001</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Magnesium, Talc</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>48.52445</v>
+        <v>50.01534</v>
       </c>
       <c r="W56" t="n">
-        <v>-58.99684</v>
+        <v>-56.04949</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Norsk North Block</t>
+          <t>Foxtrot</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>012B/10/Dol003</t>
+          <t>003D/05/Ree001</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>48.53397</v>
+        <v>52.40035</v>
       </c>
       <c r="W57" t="n">
-        <v>-58.9773</v>
+        <v>-55.82418</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lewis Brook Mine</t>
+          <t>Sheep Brook</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>012B/15/Asb001</t>
+          <t>012B/08/Gyp001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>48.77071</v>
+        <v>48.39536</v>
       </c>
       <c r="W60" t="n">
-        <v>-58.56548</v>
+        <v>-58.42046</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Voisey's Bay, Ovoid</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>014D/08/Ni 001</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>47.4063</v>
+        <v>56.33134</v>
       </c>
       <c r="W61" t="n">
-        <v>-52.70699</v>
+        <v>-62.09706</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>York Harbour Mine</t>
+          <t>AGS Vein</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>012G/01/Cu 002</t>
+          <t>001L/14/Fl 013</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
+          <t>Zinc, Lead, Copper, Fluorine</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>49.05208</v>
+        <v>46.91489</v>
       </c>
       <c r="W62" t="n">
-        <v>-58.30769</v>
+        <v>-55.48584</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
         </is>
       </c>
     </row>
@@ -4962,24 +4962,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sleepy Hollow</t>
+          <t>Blow-Me-Down Chromite #1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>002E/12/Cu 031</t>
+          <t>012G/01/Cr 001</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5008,23 +5008,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T63" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U63" t="n">
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>49.59747</v>
+        <v>49.01096</v>
       </c>
       <c r="W63" t="n">
-        <v>-55.94735</v>
+        <v>-58.24371</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -5034,24 +5034,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Miles Cove Mine</t>
+          <t>Goose Cove</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>002E/12/Cu 012</t>
+          <t>002M/05/Cu 001</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Zinc, Nickel, Iron, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>49.53936</v>
+        <v>51.31009</v>
       </c>
       <c r="W64" t="n">
-        <v>-55.79062</v>
+        <v>-55.62342</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Goose Cove</t>
+          <t>York Harbour Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>002M/05/Cu 001</t>
+          <t>012G/01/Cu 002</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zinc, Nickel, Iron, Copper</t>
+          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>51.31009</v>
+        <v>49.05208</v>
       </c>
       <c r="W65" t="n">
-        <v>-55.62342</v>
+        <v>-58.30769</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -5178,24 +5178,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blow-Me-Down Chromite #1</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>012G/01/Cr 001</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>49.01096</v>
+        <v>50.27283</v>
       </c>
       <c r="W66" t="n">
-        <v>-58.24371</v>
+        <v>-57.46448</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Ovoid</t>
+          <t>Terra Nova Mine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>014D/08/Ni 001</t>
+          <t>012H/16/Cu 004</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>56.33134</v>
+        <v>49.92133</v>
       </c>
       <c r="W67" t="n">
-        <v>-62.09706</v>
+        <v>-56.22896</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-G Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>012I/06/Zn 007</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>50.29448</v>
+        <v>50.31118</v>
       </c>
       <c r="W68" t="n">
-        <v>-57.44714</v>
+        <v>-57.43009</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-Q Zone</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 016</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>50.27283</v>
+        <v>50.29741</v>
       </c>
       <c r="W69" t="n">
-        <v>-57.46448</v>
+        <v>-57.48016</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Browning Mine</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012H/10/Au 001</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>50.31118</v>
+        <v>49.71799</v>
       </c>
       <c r="W70" t="n">
-        <v>-57.43009</v>
+        <v>-56.92565</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5538,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-H Zone</t>
+          <t>Goldenville</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>012I/06/Zn 008</t>
+          <t>012H/16/Au 033</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper, Iron, Gold</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5584,23 +5584,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T71" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U71" t="n">
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>50.29179</v>
+        <v>49.99193</v>
       </c>
       <c r="W71" t="n">
-        <v>-57.44599</v>
+        <v>-56.05735</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-J Zone</t>
+          <t>Stog'er Tight</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>012I/06/Zn 009</t>
+          <t>012H/16/Au 041</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5665,14 +5665,14 @@
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>50.30247</v>
+        <v>49.9661</v>
       </c>
       <c r="W72" t="n">
-        <v>-57.47459</v>
+        <v>-56.07765</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-K Zone</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>012I/06/Zn 010</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5737,14 +5737,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>50.2935</v>
+        <v>49.19579</v>
       </c>
       <c r="W73" t="n">
-        <v>-57.46875</v>
+        <v>-57.84974</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -5754,24 +5754,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-L Zone</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>012I/06/Zn 011</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lead, Dolomite, Zinc</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5809,14 +5809,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>50.27686</v>
+        <v>52.961</v>
       </c>
       <c r="W74" t="n">
-        <v>-57.46788</v>
+        <v>-66.81446</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5826,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-M Zone</t>
+          <t>Daniel's Harbour Mine-J Zone</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>012I/06/Zn 012</t>
+          <t>012I/06/Zn 009</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>50.29514</v>
+        <v>50.30247</v>
       </c>
       <c r="W75" t="n">
-        <v>-57.44013</v>
+        <v>-57.47459</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-N Zone</t>
+          <t>Daniel's Harbour Mine-L Zone</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>012I/06/Zn 013</t>
+          <t>012I/06/Zn 011</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Lead, Dolomite, Zinc</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>50.29873</v>
+        <v>50.27686</v>
       </c>
       <c r="W76" t="n">
-        <v>-57.48691</v>
+        <v>-57.46788</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
         </is>
       </c>
     </row>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Terra Nova Mine</t>
+          <t>Daniel's Harbour Mine-N Zone</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>012H/16/Cu 004</t>
+          <t>012I/06/Zn 013</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>49.92133</v>
+        <v>50.29873</v>
       </c>
       <c r="W77" t="n">
-        <v>-56.22896</v>
+        <v>-57.48691</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6042,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Goldenville</t>
+          <t>Daniel's Harbour Mine-F Zone</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>012H/16/Au 033</t>
+          <t>012I/06/Zn 006</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Copper, Iron, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6088,23 +6088,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U78" t="n">
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>49.99193</v>
+        <v>50.29437</v>
       </c>
       <c r="W78" t="n">
-        <v>-56.05735</v>
+        <v>-57.45374</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
         </is>
       </c>
     </row>
@@ -6114,24 +6114,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Stog'er Tight</t>
+          <t>Daniel's Harbour Mine-E Zone</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>012H/16/Au 041</t>
+          <t>012I/06/Zn 005</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>49.9661</v>
+        <v>50.31067</v>
       </c>
       <c r="W79" t="n">
-        <v>-56.07765</v>
+        <v>-57.44799</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-B Zone</t>
+          <t>Daniel's Harbour Mine-C Zone</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>012I/06/Zn 002</t>
+          <t>012I/06/Zn 003</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6241,14 +6241,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>50.2975</v>
+        <v>50.30435</v>
       </c>
       <c r="W80" t="n">
-        <v>-57.45784</v>
+        <v>-57.45355</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
         </is>
       </c>
     </row>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-E Zone</t>
+          <t>Daniel's Harbour Mine-D Zone</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>012I/06/Zn 005</t>
+          <t>012I/06/Zn 004</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6313,14 +6313,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>50.31067</v>
+        <v>50.30795</v>
       </c>
       <c r="W81" t="n">
-        <v>-57.44799</v>
+        <v>-57.45218</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-C Zone</t>
+          <t>Daniel's Harbour Mine-B Zone</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>012I/06/Zn 003</t>
+          <t>012I/06/Zn 002</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6385,14 +6385,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>50.30435</v>
+        <v>50.2975</v>
       </c>
       <c r="W82" t="n">
-        <v>-57.45355</v>
+        <v>-57.45784</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -6402,12 +6402,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-D Zone</t>
+          <t>Daniel's Harbour Mine-H Zone</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>012I/06/Zn 004</t>
+          <t>012I/06/Zn 008</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6457,14 +6457,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>50.30795</v>
+        <v>50.29179</v>
       </c>
       <c r="W83" t="n">
-        <v>-57.45218</v>
+        <v>-57.44599</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pilley's Island Mine</t>
+          <t>Daniel's Harbour Mine-G Zone</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>002E/12/Cu 001</t>
+          <t>012I/06/Zn 007</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6529,14 +6529,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>49.50863</v>
+        <v>50.29448</v>
       </c>
       <c r="W84" t="n">
-        <v>-55.71872</v>
+        <v>-57.44714</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AGS Vein</t>
+          <t>Daniel's Harbour Mine-M Zone</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>001L/14/Fl 013</t>
+          <t>012I/06/Zn 012</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6601,14 +6601,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>46.91489</v>
+        <v>50.29514</v>
       </c>
       <c r="W85" t="n">
-        <v>-55.48584</v>
+        <v>-57.44013</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
         </is>
       </c>
     </row>
@@ -6618,24 +6618,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nugget Pond</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>002E/13/Au 001</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6673,14 +6673,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>49.84502</v>
+        <v>49.45488</v>
       </c>
       <c r="W86" t="n">
-        <v>-55.77536</v>
+        <v>-55.49811</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -6690,24 +6690,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bishop North</t>
+          <t>Stoneyhouse</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>012B/08/Fe 001</t>
+          <t>001M/01/Cu 001</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6745,14 +6745,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>48.40317</v>
+        <v>47.0541</v>
       </c>
       <c r="W87" t="n">
-        <v>-58.3315</v>
+        <v>-54.11056</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -6762,24 +6762,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Upper Drill Brook Mine</t>
+          <t>Indian Head Mine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>012B/09/Fe 002</t>
+          <t>012B/10/Fe 001</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>48.53533</v>
+        <v>48.52416</v>
       </c>
       <c r="W88" t="n">
-        <v>-58.48601</v>
+        <v>-58.5148</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6834,24 +6834,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Tilt Cove/East Mine/Upper Dump</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>002E/13/Au 028</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Silver, Nickel, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>48.5353</v>
+        <v>49.88512</v>
       </c>
       <c r="W89" t="n">
-        <v>-58.48804</v>
+        <v>-55.62192</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
         </is>
       </c>
     </row>
@@ -6906,12 +6906,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Betts Cove Mine</t>
+          <t>Tilt Cove Mine</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>002E/13/Cu 002</t>
+          <t>002E/13/Cu 001</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Gold, Nickel, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>49.81179</v>
+        <v>49.88214</v>
       </c>
       <c r="W90" t="n">
-        <v>-55.80608</v>
+        <v>-55.62813</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tilt Cove Mine</t>
+          <t>Stewart Mine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>002E/13/Cu 001</t>
+          <t>002E/10/Au 001</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Silver, Zinc, Copper</t>
+          <t>Silver, Antimony, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>49.88214</v>
+        <v>49.58065</v>
       </c>
       <c r="W91" t="n">
-        <v>-55.62813</v>
+        <v>-54.85442</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -7050,24 +7050,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tilt Cove/East Mine/Upper Dump</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>002E/13/Au 028</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Zinc, Gold</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7105,14 +7105,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>49.88512</v>
+        <v>48.5353</v>
       </c>
       <c r="W92" t="n">
-        <v>-55.62192</v>
+        <v>-58.48804</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cross Cove</t>
+          <t>Pine Cove</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>002E/10/Sb 001</t>
+          <t>012H/16/Au 023</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>49.57534</v>
+        <v>49.96066</v>
       </c>
       <c r="W93" t="n">
-        <v>-54.86876</v>
+        <v>-56.13074</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
         </is>
       </c>
     </row>
@@ -7194,24 +7194,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Stoneyhouse</t>
+          <t>Bishop South</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>001M/01/Cu 001</t>
+          <t>012B/08/Fe 002</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7249,14 +7249,14 @@
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>47.0541</v>
+        <v>48.39996</v>
       </c>
       <c r="W94" t="n">
-        <v>-54.11056</v>
+        <v>-58.33683</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7266,24 +7266,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Bishop North</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>012B/08/Fe 001</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7321,14 +7321,14 @@
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>49.45488</v>
+        <v>48.40317</v>
       </c>
       <c r="W95" t="n">
-        <v>-55.49811</v>
+        <v>-58.3315</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -7338,24 +7338,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Argyle</t>
+          <t>Upper Drill Brook Mine</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>012H/16/Au 083</t>
+          <t>012B/09/Fe 002</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7393,14 +7393,14 @@
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>49.97838</v>
+        <v>48.53533</v>
       </c>
       <c r="W96" t="n">
-        <v>-56.05952</v>
+        <v>-58.48601</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7410,24 +7410,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Turk's Gut</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/11/Cu 001</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7465,14 +7465,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>47.4438</v>
+        <v>47.50226</v>
       </c>
       <c r="W97" t="n">
-        <v>-54.4169</v>
+        <v>-53.20074</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Turk's Gut</t>
+          <t>Cross Cove</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>001N/11/Cu 001</t>
+          <t>002E/10/Sb 001</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>47.50226</v>
+        <v>49.57534</v>
       </c>
       <c r="W98" t="n">
-        <v>-53.20074</v>
+        <v>-54.86876</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-A Zone</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>012I/06/Zn 001</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>50.29576</v>
+        <v>47.4438</v>
       </c>
       <c r="W99" t="n">
-        <v>-57.46512</v>
+        <v>-54.4169</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7626,24 +7626,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>La Manche</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>001N/12/Pb 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Barium, Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>35</v>
       </c>
       <c r="V100" t="n">
-        <v>47.6889</v>
+        <v>47.4063</v>
       </c>
       <c r="W100" t="n">
-        <v>-53.93901</v>
+        <v>-52.70699</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -7770,24 +7770,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hope Brook</t>
+          <t>Miles Cove Mine</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>011O/09/Au 003</t>
+          <t>002E/12/Cu 012</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7825,14 +7825,14 @@
         <v>35</v>
       </c>
       <c r="V102" t="n">
-        <v>47.73806</v>
+        <v>49.53936</v>
       </c>
       <c r="W102" t="n">
-        <v>-58.09531</v>
+        <v>-55.79062</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>Pilley's Island Mine</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>002E/12/Cu 001</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>35</v>
       </c>
       <c r="V103" t="n">
-        <v>52.961</v>
+        <v>49.50863</v>
       </c>
       <c r="W103" t="n">
-        <v>-66.81446</v>
+        <v>-55.71872</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7914,24 +7914,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ming West</t>
+          <t>Hope Brook</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>012H/16/Cu 029</t>
+          <t>011O/09/Au 003</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7960,23 +7960,23 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U104" t="n">
         <v>35</v>
       </c>
       <c r="V104" t="n">
-        <v>49.9148</v>
+        <v>47.73806</v>
       </c>
       <c r="W104" t="n">
-        <v>-56.08996</v>
+        <v>-58.09531</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -7986,24 +7986,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>La Manche</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>001N/12/Pb 001</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Zinc, Silver, Barium, Lead</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8041,14 +8041,14 @@
         <v>35</v>
       </c>
       <c r="V105" t="n">
-        <v>49.19579</v>
+        <v>47.6889</v>
       </c>
       <c r="W105" t="n">
-        <v>-57.84974</v>
+        <v>-53.93901</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -8058,24 +8058,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-Q Zone</t>
+          <t>Sleepy Hollow</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>012I/06/Zn 016</t>
+          <t>002E/12/Cu 031</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8113,14 +8113,14 @@
         <v>35</v>
       </c>
       <c r="V106" t="n">
-        <v>50.29741</v>
+        <v>49.59747</v>
       </c>
       <c r="W106" t="n">
-        <v>-57.48016</v>
+        <v>-55.94735</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
         </is>
       </c>
     </row>
@@ -8130,24 +8130,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Browning Mine</t>
+          <t>Ming West</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>012H/10/Au 001</t>
+          <t>012H/16/Cu 029</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8176,23 +8176,23 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T107" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U107" t="n">
         <v>35</v>
       </c>
       <c r="V107" t="n">
-        <v>49.71799</v>
+        <v>49.9148</v>
       </c>
       <c r="W107" t="n">
-        <v>-56.92565</v>
+        <v>-56.08996</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
         </is>
       </c>
     </row>
@@ -8202,24 +8202,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Pine Cove</t>
+          <t>Daniel's Harbour Mine-A Zone</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>012H/16/Au 023</t>
+          <t>012I/06/Zn 001</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8257,14 +8257,14 @@
         <v>35</v>
       </c>
       <c r="V108" t="n">
-        <v>49.96066</v>
+        <v>50.29576</v>
       </c>
       <c r="W108" t="n">
-        <v>-56.13074</v>
+        <v>-57.46512</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bishop South</t>
+          <t>Argyle</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>012B/08/Fe 002</t>
+          <t>012H/16/Au 083</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>35</v>
       </c>
       <c r="V109" t="n">
-        <v>48.39996</v>
+        <v>49.97838</v>
       </c>
       <c r="W109" t="n">
-        <v>-58.33683</v>
+        <v>-56.05952</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
         </is>
       </c>
     </row>
@@ -8346,24 +8346,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-F Zone</t>
+          <t>Daniel's Harbour Mine-K Zone</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>012I/06/Zn 006</t>
+          <t>012I/06/Zn 010</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>35</v>
       </c>
       <c r="V110" t="n">
-        <v>50.29437</v>
+        <v>50.2935</v>
       </c>
       <c r="W110" t="n">
-        <v>-57.45374</v>
+        <v>-57.46875</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
         </is>
       </c>
     </row>
@@ -8418,24 +8418,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Stewart Mine</t>
+          <t>Betts Cove Mine</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>002E/10/Au 001</t>
+          <t>002E/13/Cu 002</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Silver, Antimony, Copper, Zinc, Gold</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>35</v>
       </c>
       <c r="V111" t="n">
-        <v>49.58065</v>
+        <v>49.81179</v>
       </c>
       <c r="W111" t="n">
-        <v>-54.85442</v>
+        <v>-55.80608</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -8490,24 +8490,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Indian Head Mine</t>
+          <t>Nugget Pond</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>012B/10/Fe 001</t>
+          <t>002E/13/Au 001</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>35</v>
       </c>
       <c r="V112" t="n">
-        <v>48.52416</v>
+        <v>49.84502</v>
       </c>
       <c r="W112" t="n">
-        <v>-58.5148</v>
+        <v>-55.77536</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -8562,24 +8562,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Goethite Bay North</t>
+          <t>Timmins No 8</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>023G/02/Fe 041</t>
+          <t>023J/14/Fe 026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8617,14 +8617,14 @@
         <v>31</v>
       </c>
       <c r="V113" t="n">
-        <v>53.18717</v>
+        <v>54.89589</v>
       </c>
       <c r="W113" t="n">
-        <v>-66.74445</v>
+        <v>-67.07944000000001</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
         </is>
       </c>
     </row>
@@ -8634,24 +8634,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ruth Lake No 2</t>
+          <t>Timmins No 5</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>023J/15/Fe 011</t>
+          <t>023J/14/Fe 024</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>31</v>
       </c>
       <c r="V114" t="n">
-        <v>54.79747</v>
+        <v>54.86384</v>
       </c>
       <c r="W114" t="n">
-        <v>-66.87487</v>
+        <v>-67.09327</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Block 103 - Greenbush Zone</t>
+          <t>Mile 2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>023J/14/Fe 043</t>
+          <t>023B/15/Fe 011</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -8761,14 +8761,14 @@
         <v>31</v>
       </c>
       <c r="V115" t="n">
-        <v>54.97234</v>
+        <v>52.97907</v>
       </c>
       <c r="W115" t="n">
-        <v>-67.25158</v>
+        <v>-66.88907</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Elizabeth No. 2</t>
+          <t>Wabush No. 1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>023J/15/Fe 032</t>
+          <t>023B/15/Fe 002</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>31</v>
       </c>
       <c r="V116" t="n">
-        <v>54.77182</v>
+        <v>52.9599</v>
       </c>
       <c r="W116" t="n">
-        <v>-66.88666000000001</v>
+        <v>-66.9704</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lorraine No. 4</t>
+          <t>Julienne Lake</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>023G/02/Fe 008</t>
+          <t>023G/02/Fe 009</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8905,14 +8905,14 @@
         <v>31</v>
       </c>
       <c r="V117" t="n">
-        <v>53.08316</v>
+        <v>53.13733</v>
       </c>
       <c r="W117" t="n">
-        <v>-66.87726000000001</v>
+        <v>-66.78360000000001</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Elizabeth No. 1</t>
+          <t>Joyce Lake</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>023J/15/Fe 031</t>
+          <t>023J/15/Fe 030</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -8977,14 +8977,14 @@
         <v>31</v>
       </c>
       <c r="V118" t="n">
-        <v>54.78743</v>
+        <v>54.8993</v>
       </c>
       <c r="W118" t="n">
-        <v>-66.90081000000001</v>
+        <v>-66.53366</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
         </is>
       </c>
     </row>
@@ -8994,24 +8994,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wabush No. 7</t>
+          <t>Attikamagen Deposit</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>023G/02/Fe 007</t>
+          <t>023J/16/Fe 001</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9049,14 +9049,14 @@
         <v>31</v>
       </c>
       <c r="V119" t="n">
-        <v>53.02512</v>
+        <v>54.80989</v>
       </c>
       <c r="W119" t="n">
-        <v>-66.90531</v>
+        <v>-66.47658</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Knob Lake 1</t>
+          <t>Goethite Bay North</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>023J/15/Fe 013</t>
+          <t>023G/02/Fe 041</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9121,14 +9121,14 @@
         <v>31</v>
       </c>
       <c r="V120" t="n">
-        <v>54.7766</v>
+        <v>53.18717</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.80589000000001</v>
+        <v>-66.74445</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
         </is>
       </c>
     </row>
@@ -9138,24 +9138,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Howse</t>
+          <t>Wabush No. 6</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>023J/14/Fe 028</t>
+          <t>023G/02/Fe 006</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9193,14 +9193,14 @@
         <v>31</v>
       </c>
       <c r="V121" t="n">
-        <v>54.9089</v>
+        <v>53.01798</v>
       </c>
       <c r="W121" t="n">
-        <v>-67.14075</v>
+        <v>-66.89297999999999</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9210,24 +9210,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ferriman No 7</t>
+          <t>Canning</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>023J/15/Fe 014</t>
+          <t>023B/15/Fe 007</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9265,14 +9265,14 @@
         <v>31</v>
       </c>
       <c r="V122" t="n">
-        <v>54.81281</v>
+        <v>52.9469</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.94580999999999</v>
+        <v>-66.95802999999999</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9282,24 +9282,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Duley No. 1</t>
+          <t>Timmins No 7</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>023B/14/Fe 001</t>
+          <t>023J/14/Fe 025</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9337,14 +9337,14 @@
         <v>31</v>
       </c>
       <c r="V123" t="n">
-        <v>52.87237</v>
+        <v>54.89246</v>
       </c>
       <c r="W123" t="n">
-        <v>-67.05874</v>
+        <v>-67.07259000000001</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Kivivic No 3</t>
+          <t>Ferriman No 7</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>023O/03/Fe 003</t>
+          <t>023J/15/Fe 014</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9409,14 +9409,14 @@
         <v>31</v>
       </c>
       <c r="V124" t="n">
-        <v>55.05061</v>
+        <v>54.81281</v>
       </c>
       <c r="W124" t="n">
-        <v>-67.26130000000001</v>
+        <v>-66.94580999999999</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
         </is>
       </c>
     </row>
@@ -9426,24 +9426,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sawyer Lake</t>
+          <t>Wabush No. 4</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>023I/05/Fe 001</t>
+          <t>023B/15/Fe 004</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9481,14 +9481,14 @@
         <v>31</v>
       </c>
       <c r="V125" t="n">
-        <v>54.45206</v>
+        <v>52.95373</v>
       </c>
       <c r="W125" t="n">
-        <v>-65.98627</v>
+        <v>-66.94092000000001</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -9498,24 +9498,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ruth Lake No 8</t>
+          <t>Block 103 - Greenbush Zone</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>023J/15/Fe 009</t>
+          <t>023J/14/Fe 043</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9553,14 +9553,14 @@
         <v>31</v>
       </c>
       <c r="V126" t="n">
-        <v>54.78104</v>
+        <v>54.97234</v>
       </c>
       <c r="W126" t="n">
-        <v>-66.86577</v>
+        <v>-67.25158</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
         </is>
       </c>
     </row>
@@ -9570,12 +9570,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Attikamagen Deposit</t>
+          <t>Howells River North</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>023J/16/Fe 001</t>
+          <t>023O/03/Fe 007</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -9625,14 +9625,14 @@
         <v>31</v>
       </c>
       <c r="V127" t="n">
-        <v>54.80989</v>
+        <v>55.01179</v>
       </c>
       <c r="W127" t="n">
-        <v>-66.47658</v>
+        <v>-67.37214</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Joyce Lake</t>
+          <t>Duley No. 2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>023J/15/Fe 030</t>
+          <t>023B/15/Fe 008</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>31</v>
       </c>
       <c r="V128" t="n">
-        <v>54.8993</v>
+        <v>52.87214</v>
       </c>
       <c r="W128" t="n">
-        <v>-66.53366</v>
+        <v>-66.99635000000001</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -9714,12 +9714,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Howells Lake</t>
+          <t>Elizabeth No. 1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>023O/03/Fe 006</t>
+          <t>023J/15/Fe 031</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -9769,14 +9769,14 @@
         <v>31</v>
       </c>
       <c r="V129" t="n">
-        <v>55.06346</v>
+        <v>54.78743</v>
       </c>
       <c r="W129" t="n">
-        <v>-67.40528</v>
+        <v>-66.90081000000001</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9786,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Howells River North</t>
+          <t>Howells Lake</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>023O/03/Fe 007</t>
+          <t>023O/03/Fe 006</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9841,14 +9841,14 @@
         <v>31</v>
       </c>
       <c r="V130" t="n">
-        <v>55.01179</v>
+        <v>55.06346</v>
       </c>
       <c r="W130" t="n">
-        <v>-67.37214</v>
+        <v>-67.40528</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Wabush No. 6</t>
+          <t>Wabush No. 7</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>023G/02/Fe 006</t>
+          <t>023G/02/Fe 007</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9913,14 +9913,14 @@
         <v>31</v>
       </c>
       <c r="V131" t="n">
-        <v>53.01798</v>
+        <v>53.02512</v>
       </c>
       <c r="W131" t="n">
-        <v>-66.89297999999999</v>
+        <v>-66.90531</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Julienne Lake</t>
+          <t>Lorraine No. 4</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>023G/02/Fe 009</t>
+          <t>023G/02/Fe 008</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9985,14 +9985,14 @@
         <v>31</v>
       </c>
       <c r="V132" t="n">
-        <v>53.13733</v>
+        <v>53.08316</v>
       </c>
       <c r="W132" t="n">
-        <v>-66.78360000000001</v>
+        <v>-66.87726000000001</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Duley No. 2</t>
+          <t>Wabush No. 8</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>023B/15/Fe 008</t>
+          <t>023B/15/Fe 005</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -10057,14 +10057,14 @@
         <v>31</v>
       </c>
       <c r="V133" t="n">
-        <v>52.87214</v>
+        <v>52.9791</v>
       </c>
       <c r="W133" t="n">
-        <v>-66.99635000000001</v>
+        <v>-66.90604999999999</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Canning</t>
+          <t>Houston 2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>023B/15/Fe 007</t>
+          <t>023J/10/Fe 009</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10129,14 +10129,14 @@
         <v>31</v>
       </c>
       <c r="V134" t="n">
-        <v>52.9469</v>
+        <v>54.71245</v>
       </c>
       <c r="W134" t="n">
-        <v>-66.95802999999999</v>
+        <v>-66.66257</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10146,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Timmins No 7</t>
+          <t>Houston 3</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>023J/14/Fe 025</t>
+          <t>023J/10/Fe 010</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10201,14 +10201,14 @@
         <v>31</v>
       </c>
       <c r="V135" t="n">
-        <v>54.89246</v>
+        <v>54.69887</v>
       </c>
       <c r="W135" t="n">
-        <v>-67.07259000000001</v>
+        <v>-66.64483</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mile 2</t>
+          <t>Kivivic No 3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>023B/15/Fe 011</t>
+          <t>023O/03/Fe 003</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -10273,14 +10273,14 @@
         <v>31</v>
       </c>
       <c r="V136" t="n">
-        <v>52.97907</v>
+        <v>55.05061</v>
       </c>
       <c r="W136" t="n">
-        <v>-66.88907</v>
+        <v>-67.26130000000001</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Wabush No. 8</t>
+          <t>Kivivic No 4</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>023B/15/Fe 005</t>
+          <t>023O/03/Fe 004</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>31</v>
       </c>
       <c r="V137" t="n">
-        <v>52.9791</v>
+        <v>55.04865</v>
       </c>
       <c r="W137" t="n">
-        <v>-66.90604999999999</v>
+        <v>-67.28158000000001</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -10362,24 +10362,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Wabush No. 4</t>
+          <t>Kivivic No 5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>023B/15/Fe 004</t>
+          <t>023O/03/Fe 005</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>31</v>
       </c>
       <c r="V138" t="n">
-        <v>52.95373</v>
+        <v>55.06664</v>
       </c>
       <c r="W138" t="n">
-        <v>-66.94092000000001</v>
+        <v>-67.29537000000001</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10434,24 +10434,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Timmins No 8</t>
+          <t>Duley No. 1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>023J/14/Fe 026</t>
+          <t>023B/14/Fe 001</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>31</v>
       </c>
       <c r="V139" t="n">
-        <v>54.89589</v>
+        <v>52.87237</v>
       </c>
       <c r="W139" t="n">
-        <v>-67.07944000000001</v>
+        <v>-67.05874</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10506,24 +10506,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Timmins No 5</t>
+          <t>Mills Lake</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>023J/14/Fe 024</t>
+          <t>023B/14/Fe 002</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>31</v>
       </c>
       <c r="V140" t="n">
-        <v>54.86384</v>
+        <v>52.79808</v>
       </c>
       <c r="W140" t="n">
-        <v>-67.09327</v>
+        <v>-67.00413</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -10578,24 +10578,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sheps Lake</t>
+          <t>Howells River West Zone A</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>023J/11/Fe 001</t>
+          <t>023J/14/Fe 001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10633,14 +10633,14 @@
         <v>31</v>
       </c>
       <c r="V141" t="n">
-        <v>54.73475</v>
+        <v>54.90958</v>
       </c>
       <c r="W141" t="n">
-        <v>-67.06362</v>
+        <v>-67.26052</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Neal 1</t>
+          <t>Houston 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>023B/14/Fe 008</t>
+          <t>023J/10/Fe 008</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10705,14 +10705,14 @@
         <v>31</v>
       </c>
       <c r="V142" t="n">
-        <v>52.95013</v>
+        <v>54.70748</v>
       </c>
       <c r="W142" t="n">
-        <v>-67.15191</v>
+        <v>-66.65615</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10722,24 +10722,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Redmond 5</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>023B/14/Fe 028</t>
+          <t>023J/10/Fe 005</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10777,14 +10777,14 @@
         <v>31</v>
       </c>
       <c r="V143" t="n">
-        <v>52.94868</v>
+        <v>54.70854</v>
       </c>
       <c r="W143" t="n">
-        <v>-67.01146</v>
+        <v>-66.79174999999999</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sawyer Lake</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>023B/14/Fe 020</t>
+          <t>023I/05/Fe 001</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>31</v>
       </c>
       <c r="V144" t="n">
-        <v>52.83351</v>
+        <v>54.45206</v>
       </c>
       <c r="W144" t="n">
-        <v>-67.0311</v>
+        <v>-65.98627</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10938,24 +10938,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Howells River West Zone A</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>023J/14/Fe 001</t>
+          <t>023B/14/Fe 020</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>31</v>
       </c>
       <c r="V146" t="n">
-        <v>54.90958</v>
+        <v>52.83351</v>
       </c>
       <c r="W146" t="n">
-        <v>-67.26052</v>
+        <v>-67.0311</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
         </is>
       </c>
     </row>
@@ -11010,24 +11010,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Wabush No. 1</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>023B/15/Fe 002</t>
+          <t>023B/14/Fe 028</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11065,14 +11065,14 @@
         <v>31</v>
       </c>
       <c r="V147" t="n">
-        <v>52.9599</v>
+        <v>52.94868</v>
       </c>
       <c r="W147" t="n">
-        <v>-66.9704</v>
+        <v>-67.01146</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Redmond 5</t>
+          <t>Sheps Lake</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>023J/10/Fe 005</t>
+          <t>023J/11/Fe 001</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11137,14 +11137,14 @@
         <v>31</v>
       </c>
       <c r="V148" t="n">
-        <v>54.70854</v>
+        <v>54.73475</v>
       </c>
       <c r="W148" t="n">
-        <v>-66.79174999999999</v>
+        <v>-67.06362</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Mills Lake</t>
+          <t>Neal 1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>023B/14/Fe 002</t>
+          <t>023B/14/Fe 008</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -11209,14 +11209,14 @@
         <v>31</v>
       </c>
       <c r="V149" t="n">
-        <v>52.79808</v>
+        <v>52.95013</v>
       </c>
       <c r="W149" t="n">
-        <v>-67.00413</v>
+        <v>-67.15191</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Houston 1</t>
+          <t>Ruth Lake No 8</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>023J/10/Fe 008</t>
+          <t>023J/15/Fe 009</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11281,14 +11281,14 @@
         <v>31</v>
       </c>
       <c r="V150" t="n">
-        <v>54.70748</v>
+        <v>54.78104</v>
       </c>
       <c r="W150" t="n">
-        <v>-66.65615</v>
+        <v>-66.86577</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Houston 3</t>
+          <t>Ruth Lake No 2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>023J/10/Fe 010</t>
+          <t>023J/15/Fe 011</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11353,14 +11353,14 @@
         <v>31</v>
       </c>
       <c r="V151" t="n">
-        <v>54.69887</v>
+        <v>54.79747</v>
       </c>
       <c r="W151" t="n">
-        <v>-66.64483</v>
+        <v>-66.87487</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -11370,24 +11370,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Houston 2</t>
+          <t>Elizabeth No. 2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>023J/10/Fe 009</t>
+          <t>023J/15/Fe 032</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11425,14 +11425,14 @@
         <v>31</v>
       </c>
       <c r="V152" t="n">
-        <v>54.71245</v>
+        <v>54.77182</v>
       </c>
       <c r="W152" t="n">
-        <v>-66.66257</v>
+        <v>-66.88666000000001</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
         </is>
       </c>
     </row>
@@ -11442,24 +11442,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Kivivic No 4</t>
+          <t>Knob Lake 1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>023O/03/Fe 004</t>
+          <t>023J/15/Fe 013</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11497,14 +11497,14 @@
         <v>31</v>
       </c>
       <c r="V153" t="n">
-        <v>55.04865</v>
+        <v>54.7766</v>
       </c>
       <c r="W153" t="n">
-        <v>-67.28158000000001</v>
+        <v>-66.80589000000001</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11514,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Kivivic No 5</t>
+          <t>Howse</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>023O/03/Fe 005</t>
+          <t>023J/14/Fe 028</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11569,14 +11569,14 @@
         <v>31</v>
       </c>
       <c r="V154" t="n">
-        <v>55.06664</v>
+        <v>54.9089</v>
       </c>
       <c r="W154" t="n">
-        <v>-67.29537000000001</v>
+        <v>-67.14075</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Mine Hill</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>001N/07/Pph004</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Pyrophyllite</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11641,14 +11641,14 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>53.40462</v>
+        <v>47.48</v>
       </c>
       <c r="W155" t="n">
-        <v>-65.08734</v>
+        <v>-52.95479</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Parsons Pond No 3</t>
+          <t>Iron Springs Mine</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>012H/13/Btm003</t>
+          <t>001L/14/Fl 008</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11785,14 +11785,14 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>49.97912</v>
+        <v>46.88701</v>
       </c>
       <c r="W157" t="n">
-        <v>-57.64547</v>
+        <v>-55.421</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Parsons Pond No 2</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>012H/13/Btm002</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11857,14 +11857,14 @@
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>49.97421</v>
+        <v>48.56074</v>
       </c>
       <c r="W158" t="n">
-        <v>-57.60538</v>
+        <v>-58.8161</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Parsons Pond No 4</t>
+          <t>Hares Ears Vein</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>012H/13/Btm004</t>
+          <t>001L/14/Fl 007</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11920,23 +11920,23 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T159" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U159" t="n">
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>49.99787</v>
+        <v>46.88814</v>
       </c>
       <c r="W159" t="n">
-        <v>-57.63818</v>
+        <v>-55.41178</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Middle Arm Brook</t>
+          <t>Collier Point</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>012H/16/Vir001</t>
+          <t>001N/12/Ba 001</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Virginite</t>
+          <t>Barium</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12001,14 +12001,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>49.80048</v>
+        <v>47.59126</v>
       </c>
       <c r="W160" t="n">
-        <v>-56.31995</v>
+        <v>-53.69011</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lord &amp; Lady Gulch Mine</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>001L/14/Fl 005</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12073,14 +12073,14 @@
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>46.87554</v>
+        <v>48.30663</v>
       </c>
       <c r="W161" t="n">
-        <v>-55.4111</v>
+        <v>-58.68165</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Baie Verte Mine</t>
+          <t>Parsons Pond Cart Track</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>012H/16/Asb008</t>
+          <t>012I/04/Btm001</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Magnesium, Asbestos</t>
+          <t>Oil Shale</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12136,23 +12136,23 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T162" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U162" t="n">
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>49.97974</v>
+        <v>50.00564</v>
       </c>
       <c r="W162" t="n">
-        <v>-56.19399</v>
+        <v>-57.63187</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -12162,12 +12162,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Black Duck Mine</t>
+          <t>Baie Verte Mine</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>001L/14/Fl 010</t>
+          <t>012H/16/Asb008</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Magnesium, Asbestos</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12217,14 +12217,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>46.93201</v>
+        <v>49.97974</v>
       </c>
       <c r="W163" t="n">
-        <v>-55.38881</v>
+        <v>-56.19399</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Borney Lake</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>002D/14/Stn001</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12289,14 +12289,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>48.30663</v>
+        <v>48.9264</v>
       </c>
       <c r="W164" t="n">
-        <v>-58.68165</v>
+        <v>-55.44535</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Southern Cross Veins</t>
+          <t>Doctors Pond Veins</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>001L/14/Fl 020</t>
+          <t>001L/14/Fl 036</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12361,14 +12361,14 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>46.88974</v>
+        <v>46.92769</v>
       </c>
       <c r="W165" t="n">
-        <v>-55.42958</v>
+        <v>-55.37593</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tarefare Mine</t>
+          <t>Parsons Pond No 3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>001L/14/Fl 006</t>
+          <t>012H/13/Btm003</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12433,14 +12433,14 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>46.8912</v>
+        <v>49.97912</v>
       </c>
       <c r="W166" t="n">
-        <v>-55.43112</v>
+        <v>-57.64547</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Tarefare Mine</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>001L/14/Fl 006</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12505,14 +12505,14 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>53.469</v>
+        <v>46.8912</v>
       </c>
       <c r="W167" t="n">
-        <v>-64.91218000000001</v>
+        <v>-55.43112</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
         </is>
       </c>
     </row>
@@ -12522,12 +12522,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mine Hill</t>
+          <t>Blue Beach Mine</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>001N/07/Pph004</t>
+          <t>001L/14/Fl 001</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pyrophyllite</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12577,14 +12577,14 @@
         <v>30</v>
       </c>
       <c r="V168" t="n">
-        <v>47.48</v>
+        <v>46.91553</v>
       </c>
       <c r="W168" t="n">
-        <v>-52.95479</v>
+        <v>-55.40729</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
         </is>
       </c>
     </row>
@@ -12594,12 +12594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Black Duck Mine</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>001L/14/Fl 010</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12649,14 +12649,14 @@
         <v>30</v>
       </c>
       <c r="V169" t="n">
-        <v>48.56074</v>
+        <v>46.93201</v>
       </c>
       <c r="W169" t="n">
-        <v>-58.8161</v>
+        <v>-55.38881</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Collier Point</t>
+          <t>Southern Cross Veins</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>001N/12/Ba 001</t>
+          <t>001L/14/Fl 020</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Barium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12721,14 +12721,14 @@
         <v>30</v>
       </c>
       <c r="V170" t="n">
-        <v>47.59126</v>
+        <v>46.88974</v>
       </c>
       <c r="W170" t="n">
-        <v>-53.69011</v>
+        <v>-55.42958</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
         </is>
       </c>
     </row>
@@ -12738,12 +12738,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Parsons Pond Cart Track</t>
+          <t>Lord &amp; Lady Gulch Mine</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>012I/04/Btm001</t>
+          <t>001L/14/Fl 005</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Oil Shale</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12784,23 +12784,23 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T171" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U171" t="n">
         <v>30</v>
       </c>
       <c r="V171" t="n">
-        <v>50.00564</v>
+        <v>46.87554</v>
       </c>
       <c r="W171" t="n">
-        <v>-57.63187</v>
+        <v>-55.4111</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Doctors Pond Veins</t>
+          <t>Scrape Vein</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>001L/14/Fl 036</t>
+          <t>001L/14/Fl 035</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -12865,14 +12865,14 @@
         <v>30</v>
       </c>
       <c r="V172" t="n">
-        <v>46.92769</v>
+        <v>46.92547</v>
       </c>
       <c r="W172" t="n">
-        <v>-55.37593</v>
+        <v>-55.37193</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Little Salt Cove</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>001L/14/Fl 016</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12937,14 +12937,14 @@
         <v>30</v>
       </c>
       <c r="V173" t="n">
-        <v>46.87654</v>
+        <v>53.40462</v>
       </c>
       <c r="W173" t="n">
-        <v>-55.43141</v>
+        <v>-65.08734</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12954,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Scrape Vein</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>001L/14/Fl 035</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13009,14 +13009,14 @@
         <v>30</v>
       </c>
       <c r="V174" t="n">
-        <v>46.92547</v>
+        <v>48.50411</v>
       </c>
       <c r="W174" t="n">
-        <v>-55.37193</v>
+        <v>-58.53451</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Director Mine</t>
+          <t>Bluff Head Mine</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>001L/14/Fl 009</t>
+          <t>012B/15/Cr 001</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Asbestos, Chromium</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13081,14 +13081,14 @@
         <v>30</v>
       </c>
       <c r="V175" t="n">
-        <v>46.90681</v>
+        <v>48.77717</v>
       </c>
       <c r="W175" t="n">
-        <v>-55.42107</v>
+        <v>-58.59931</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Iron Springs Mine</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>001L/14/Fl 008</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13153,14 +13153,14 @@
         <v>30</v>
       </c>
       <c r="V176" t="n">
-        <v>46.88701</v>
+        <v>53.469</v>
       </c>
       <c r="W176" t="n">
-        <v>-55.421</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Borney Lake</t>
+          <t>Director Mine</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>002D/14/Stn001</t>
+          <t>001L/14/Fl 009</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13225,14 +13225,14 @@
         <v>30</v>
       </c>
       <c r="V177" t="n">
-        <v>48.9264</v>
+        <v>46.90681</v>
       </c>
       <c r="W177" t="n">
-        <v>-55.44535</v>
+        <v>-55.42107</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Bluff Head Mine</t>
+          <t>Little Salt Cove</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>012B/15/Cr 001</t>
+          <t>001L/14/Fl 016</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Asbestos, Chromium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13297,14 +13297,14 @@
         <v>30</v>
       </c>
       <c r="V178" t="n">
-        <v>48.77717</v>
+        <v>46.87654</v>
       </c>
       <c r="W178" t="n">
-        <v>-58.59931</v>
+        <v>-55.43141</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
         </is>
       </c>
     </row>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Middle Arm Brook</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>012H/16/Vir001</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Virginite</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13441,14 +13441,14 @@
         <v>30</v>
       </c>
       <c r="V180" t="n">
-        <v>48.50411</v>
+        <v>49.80048</v>
       </c>
       <c r="W180" t="n">
-        <v>-58.53451</v>
+        <v>-56.31995</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
         </is>
       </c>
     </row>
@@ -13458,12 +13458,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Blue Beach Mine</t>
+          <t>Parsons Pond No 2</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>001L/14/Fl 001</t>
+          <t>012H/13/Btm002</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13513,14 +13513,14 @@
         <v>30</v>
       </c>
       <c r="V181" t="n">
-        <v>46.91553</v>
+        <v>49.97421</v>
       </c>
       <c r="W181" t="n">
-        <v>-55.40729</v>
+        <v>-57.60538</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
         </is>
       </c>
     </row>
@@ -13530,12 +13530,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hares Ears Vein</t>
+          <t>Parsons Pond No 1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>001L/14/Fl 007</t>
+          <t>012H/13/Btm001</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13576,23 +13576,23 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T182" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U182" t="n">
         <v>30</v>
       </c>
       <c r="V182" t="n">
-        <v>46.88814</v>
+        <v>49.99228</v>
       </c>
       <c r="W182" t="n">
-        <v>-55.41178</v>
+        <v>-57.58928</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Parsons Pond No 1</t>
+          <t>Parsons Pond No 4</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>012H/13/Btm001</t>
+          <t>012H/13/Btm004</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13648,23 +13648,23 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T183" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U183" t="n">
         <v>30</v>
       </c>
       <c r="V183" t="n">
-        <v>49.99228</v>
+        <v>49.99787</v>
       </c>
       <c r="W183" t="n">
-        <v>-57.58928</v>
+        <v>-57.63818</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
         </is>
       </c>
     </row>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Little Bay Mine</t>
+          <t>Grey Copper Mine</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>002E/12/Cu 030</t>
+          <t>002E/11/Cu 001</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Iron, Gold, Copper</t>
+          <t>Iron, Copper</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13729,14 +13729,14 @@
         <v>26</v>
       </c>
       <c r="V184" t="n">
-        <v>49.5961</v>
+        <v>49.5173</v>
       </c>
       <c r="W184" t="n">
-        <v>-55.94531</v>
+        <v>-55.2721</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Fleming No 3</t>
+          <t>Scotia Formation</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>023J/14/Fe 022</t>
+          <t>001N/10/Fe 002</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13801,14 +13801,14 @@
         <v>26</v>
       </c>
       <c r="V185" t="n">
-        <v>54.85836</v>
+        <v>47.64169</v>
       </c>
       <c r="W185" t="n">
-        <v>-67.03167999999999</v>
+        <v>-52.97639</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Timmins No 2</t>
+          <t>Gull Island Formation</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>023J/14/Fe 019</t>
+          <t>001N/10/Fe 003</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -13873,14 +13873,14 @@
         <v>26</v>
       </c>
       <c r="V186" t="n">
-        <v>54.89421</v>
+        <v>47.65193</v>
       </c>
       <c r="W186" t="n">
-        <v>-67.08716</v>
+        <v>-52.95654</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Timmins No 4</t>
+          <t>Redmond No 2</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>023J/14/Fe 023</t>
+          <t>023J/10/Fe 002</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13945,14 +13945,14 @@
         <v>26</v>
       </c>
       <c r="V187" t="n">
-        <v>54.89884</v>
+        <v>54.69738</v>
       </c>
       <c r="W187" t="n">
-        <v>-67.10881000000001</v>
+        <v>-66.77224</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -13962,24 +13962,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Little Bay Mine</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>002E/12/Cu 030</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron, Gold, Copper</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14017,14 +14017,14 @@
         <v>26</v>
       </c>
       <c r="V188" t="n">
-        <v>47.53392</v>
+        <v>49.5961</v>
       </c>
       <c r="W188" t="n">
-        <v>-53.18293</v>
+        <v>-55.94531</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -14034,24 +14034,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dominion Formation</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>001N/10/Fe 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14089,14 +14089,14 @@
         <v>26</v>
       </c>
       <c r="V189" t="n">
-        <v>47.64164</v>
+        <v>49.50376</v>
       </c>
       <c r="W189" t="n">
-        <v>-52.95309</v>
+        <v>-55.21553</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14106,24 +14106,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Redmond No 2</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>023J/10/Fe 002</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14161,14 +14161,14 @@
         <v>26</v>
       </c>
       <c r="V190" t="n">
-        <v>54.69738</v>
+        <v>47.53392</v>
       </c>
       <c r="W190" t="n">
-        <v>-66.77224</v>
+        <v>-53.18293</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Gull Island Formation</t>
+          <t>Dominion Formation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>001N/10/Fe 003</t>
+          <t>001N/10/Fe 001</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -14233,14 +14233,14 @@
         <v>26</v>
       </c>
       <c r="V191" t="n">
-        <v>47.65193</v>
+        <v>47.64164</v>
       </c>
       <c r="W191" t="n">
-        <v>-52.95654</v>
+        <v>-52.95309</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14250,12 +14250,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Scotia Formation</t>
+          <t>Cliff Mine</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>001N/10/Fe 002</t>
+          <t>012B/09/Fe 001</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -14305,14 +14305,14 @@
         <v>26</v>
       </c>
       <c r="V192" t="n">
-        <v>47.64169</v>
+        <v>48.54434</v>
       </c>
       <c r="W192" t="n">
-        <v>-52.97639</v>
+        <v>-58.49915</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Timmins No 1</t>
+          <t>Skindles Mine</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>023J/14/Fe 018</t>
+          <t>012B/09/Fe 004</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14377,14 +14377,14 @@
         <v>26</v>
       </c>
       <c r="V193" t="n">
-        <v>54.88449</v>
+        <v>48.54069</v>
       </c>
       <c r="W193" t="n">
-        <v>-67.08575</v>
+        <v>-58.48888</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14394,24 +14394,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Timmins No 6</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>023J/14/Fe 021</t>
+          <t>023J/15/Fe 010</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14449,14 +14449,14 @@
         <v>26</v>
       </c>
       <c r="V194" t="n">
-        <v>54.90148</v>
+        <v>54.77437</v>
       </c>
       <c r="W194" t="n">
-        <v>-67.09757999999999</v>
+        <v>-66.82881</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14466,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Skindles Mine</t>
+          <t>Ruth Lake No 7</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>012B/09/Fe 004</t>
+          <t>023J/15/Fe 006</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
         <v>26</v>
       </c>
       <c r="V195" t="n">
-        <v>48.54069</v>
+        <v>54.80557</v>
       </c>
       <c r="W195" t="n">
-        <v>-58.48888</v>
+        <v>-66.90618000000001</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -14538,24 +14538,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Cliff Mine</t>
+          <t>Ruth Lake No 5</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>012B/09/Fe 001</t>
+          <t>023J/15/Fe 007</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14593,14 +14593,14 @@
         <v>26</v>
       </c>
       <c r="V196" t="n">
-        <v>48.54434</v>
+        <v>54.80503</v>
       </c>
       <c r="W196" t="n">
-        <v>-58.49915</v>
+        <v>-66.88023</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -14610,24 +14610,24 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Grey Copper Mine</t>
+          <t>Ruth Lake No 6</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>002E/11/Cu 001</t>
+          <t>023J/15/Fe 008</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Iron, Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14665,14 +14665,14 @@
         <v>26</v>
       </c>
       <c r="V197" t="n">
-        <v>49.5173</v>
+        <v>54.80104</v>
       </c>
       <c r="W197" t="n">
-        <v>-55.2721</v>
+        <v>-66.87327999999999</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -14682,24 +14682,24 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Ruth Lake No 9</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>023J/15/Fe 005</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14737,14 +14737,14 @@
         <v>26</v>
       </c>
       <c r="V198" t="n">
-        <v>49.50376</v>
+        <v>54.80033</v>
       </c>
       <c r="W198" t="n">
-        <v>-55.21553</v>
+        <v>-66.89447</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14754,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Smallwood Mine</t>
+          <t>Ruth Lake No 1</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>023G/02/Fe 001</t>
+          <t>023J/15/Fe 002</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14809,14 +14809,14 @@
         <v>26</v>
       </c>
       <c r="V199" t="n">
-        <v>53.03718</v>
+        <v>54.79145</v>
       </c>
       <c r="W199" t="n">
-        <v>-66.93694000000001</v>
+        <v>-66.85449</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14826,24 +14826,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Wishart No 2 (Wishart Mine)</t>
+          <t>Wishart No 1 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>023J/15/Fe 004</t>
+          <t>023J/15/Fe 003</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14881,14 +14881,14 @@
         <v>26</v>
       </c>
       <c r="V200" t="n">
-        <v>54.7654</v>
+        <v>54.76166</v>
       </c>
       <c r="W200" t="n">
-        <v>-66.9067</v>
+        <v>-66.88793</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lorraine Mine</t>
+          <t>Wishart No 2 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>023G/02/Fe 004</t>
+          <t>023J/15/Fe 004</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14953,14 +14953,14 @@
         <v>26</v>
       </c>
       <c r="V201" t="n">
-        <v>53.06833</v>
+        <v>54.7654</v>
       </c>
       <c r="W201" t="n">
-        <v>-66.94949</v>
+        <v>-66.9067</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14970,12 +14970,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ruth Lake No 1</t>
+          <t>Ruth Lake No 3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>023J/15/Fe 002</t>
+          <t>023J/15/Fe 001</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
         <v>26</v>
       </c>
       <c r="V202" t="n">
-        <v>54.79145</v>
+        <v>54.80404</v>
       </c>
       <c r="W202" t="n">
-        <v>-66.85449</v>
+        <v>-66.87016</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15042,12 +15042,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Ruth Lake No 3</t>
+          <t>Smallwood Mine</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>023J/15/Fe 001</t>
+          <t>023G/02/Fe 001</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -15097,14 +15097,14 @@
         <v>26</v>
       </c>
       <c r="V203" t="n">
-        <v>54.80404</v>
+        <v>53.03718</v>
       </c>
       <c r="W203" t="n">
-        <v>-66.87016</v>
+        <v>-66.93694000000001</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15114,24 +15114,24 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Wishart No 1 (Wishart Mine)</t>
+          <t>Lorraine Mine</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>023J/15/Fe 003</t>
+          <t>023G/02/Fe 004</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -15169,14 +15169,14 @@
         <v>26</v>
       </c>
       <c r="V204" t="n">
-        <v>54.76166</v>
+        <v>53.06833</v>
       </c>
       <c r="W204" t="n">
-        <v>-66.88793</v>
+        <v>-66.94949</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ruth Lake No 9</t>
+          <t>Fleming No 3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>023J/15/Fe 005</t>
+          <t>023J/14/Fe 022</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -15241,14 +15241,14 @@
         <v>26</v>
       </c>
       <c r="V205" t="n">
-        <v>54.80033</v>
+        <v>54.85836</v>
       </c>
       <c r="W205" t="n">
-        <v>-66.89447</v>
+        <v>-67.03167999999999</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
         </is>
       </c>
     </row>
@@ -15258,24 +15258,24 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ruth Lake No 5</t>
+          <t>Timmins No 1</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>023J/15/Fe 007</t>
+          <t>023J/14/Fe 018</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -15313,14 +15313,14 @@
         <v>26</v>
       </c>
       <c r="V206" t="n">
-        <v>54.80503</v>
+        <v>54.88449</v>
       </c>
       <c r="W206" t="n">
-        <v>-66.88023</v>
+        <v>-67.08575</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15330,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Ruth Lake No 7</t>
+          <t>Timmins No 4</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>023J/15/Fe 006</t>
+          <t>023J/14/Fe 023</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15385,14 +15385,14 @@
         <v>26</v>
       </c>
       <c r="V207" t="n">
-        <v>54.80557</v>
+        <v>54.89884</v>
       </c>
       <c r="W207" t="n">
-        <v>-66.90618000000001</v>
+        <v>-67.10881000000001</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
         </is>
       </c>
     </row>
@@ -15402,24 +15402,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ruth Lake No 6</t>
+          <t>Timmins No 2</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>023J/15/Fe 008</t>
+          <t>023J/14/Fe 019</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15457,14 +15457,14 @@
         <v>26</v>
       </c>
       <c r="V208" t="n">
-        <v>54.80104</v>
+        <v>54.89421</v>
       </c>
       <c r="W208" t="n">
-        <v>-66.87327999999999</v>
+        <v>-67.08716</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
         </is>
       </c>
     </row>
@@ -15474,24 +15474,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Timmins No 6</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>023J/15/Fe 010</t>
+          <t>023J/14/Fe 021</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15529,14 +15529,14 @@
         <v>26</v>
       </c>
       <c r="V209" t="n">
-        <v>54.77437</v>
+        <v>54.90148</v>
       </c>
       <c r="W209" t="n">
-        <v>-66.82881</v>
+        <v>-67.09757999999999</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
         </is>
       </c>
     </row>
@@ -15618,24 +15618,24 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Ming Footwall Deposit</t>
+          <t>Whalesback Mine</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>012H/16/Cu 030</t>
+          <t>012H/09/Cu 001</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Copper</t>
+          <t>Zinc, Titanium, Copper</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -15664,23 +15664,23 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T211" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U211" t="n">
         <v>19</v>
       </c>
       <c r="V211" t="n">
-        <v>49.91174</v>
+        <v>49.59682</v>
       </c>
       <c r="W211" t="n">
-        <v>-56.08642</v>
+        <v>-56.00604</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F09%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -15690,24 +15690,24 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ming Mine</t>
+          <t>Ming Footwall Deposit</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>012H/16/Cu 010</t>
+          <t>012H/16/Cu 030</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -15745,14 +15745,14 @@
         <v>19</v>
       </c>
       <c r="V212" t="n">
-        <v>49.9128</v>
+        <v>49.91174</v>
       </c>
       <c r="W212" t="n">
-        <v>-56.08313</v>
+        <v>-56.08642</v>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -15762,24 +15762,24 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Whalesback Mine</t>
+          <t>Ming Mine</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>012H/09/Cu 001</t>
+          <t>012H/16/Cu 010</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Zinc, Titanium, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -15808,23 +15808,23 @@
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T213" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U213" t="n">
         <v>19</v>
       </c>
       <c r="V213" t="n">
-        <v>49.59682</v>
+        <v>49.9128</v>
       </c>
       <c r="W213" t="n">
-        <v>-56.00604</v>
+        <v>-56.08313</v>
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F09%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20010</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X215"/>
+  <dimension ref="A1:X214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Copper Creek BV</t>
+          <t>Michelin Deposit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>012H/16/Cu 040</t>
+          <t>013J/12/U  001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>44</v>
       </c>
       <c r="V2" t="n">
-        <v>49.91887</v>
+        <v>54.58562</v>
       </c>
       <c r="W2" t="n">
-        <v>-56.20986</v>
+        <v>-59.98056</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Horseshoe Zone</t>
+          <t>Rainbow Deposit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>002E/02/Au 039</t>
+          <t>013J/12/U  008</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,23 +688,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>49.01341</v>
+        <v>54.56417</v>
       </c>
       <c r="W3" t="n">
-        <v>-54.81741</v>
+        <v>-59.99369</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viking Gold-Thor Trend</t>
+          <t>Jacques Lake</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012H/10/Au 011</t>
+          <t>013J/12/U  018</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -760,23 +760,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>49.69447</v>
+        <v>54.71754</v>
       </c>
       <c r="W4" t="n">
-        <v>-56.99193</v>
+        <v>-59.59268</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PW Zone</t>
+          <t>Road Zone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>011O/10/Au 011</t>
+          <t>012H/15/Au 011</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -841,14 +841,14 @@
         <v>44</v>
       </c>
       <c r="V5" t="n">
-        <v>47.74631</v>
+        <v>49.88465</v>
       </c>
       <c r="W5" t="n">
-        <v>-58.94364</v>
+        <v>-56.83885</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deep Fox</t>
+          <t>Apsy Zone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>003D/05/Ree007</t>
+          <t>012H/15/Au 014</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>44</v>
       </c>
       <c r="V6" t="n">
-        <v>52.3805</v>
+        <v>49.89471</v>
       </c>
       <c r="W6" t="n">
-        <v>-55.64987</v>
+        <v>-56.82917</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mart Lake Graphite</t>
+          <t>Deer Cove Main Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>023B/14/Gf 001</t>
+          <t>012I/01/Au 001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>44</v>
       </c>
       <c r="V7" t="n">
-        <v>52.8283</v>
+        <v>50.01619</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.01484000000001</v>
+        <v>-56.04389</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rainbow Deposit</t>
+          <t>Turners Ridge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>013J/12/U  008</t>
+          <t>012H/11/Pb 001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
         <v>44</v>
       </c>
       <c r="V8" t="n">
-        <v>54.56417</v>
+        <v>49.59029</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.99369</v>
+        <v>-57.00443</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michelin Deposit</t>
+          <t>Mann #1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>013J/12/U  001</t>
+          <t>013L/01/Be 001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Niobium, Uranium, Zinc, Beryllium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>44</v>
       </c>
       <c r="V9" t="n">
-        <v>54.58562</v>
+        <v>54.23929</v>
       </c>
       <c r="W9" t="n">
-        <v>-59.98056</v>
+        <v>-62.3924</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deer Cove Main Zone</t>
+          <t>Two Tom Lake</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>012I/01/Au 001</t>
+          <t>013L/01/REE001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>50.01619</v>
+        <v>54.21359</v>
       </c>
       <c r="W10" t="n">
-        <v>-56.04389</v>
+        <v>-62.14192</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apsy Zone</t>
+          <t>Nash Lake (Main Zone)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>012H/15/Au 014</t>
+          <t>013J/13/U  006</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1273,14 +1273,14 @@
         <v>44</v>
       </c>
       <c r="V11" t="n">
-        <v>49.89471</v>
+        <v>54.91032</v>
       </c>
       <c r="W11" t="n">
-        <v>-56.82917</v>
+        <v>-59.62004</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
         </is>
       </c>
     </row>
@@ -1290,24 +1290,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Road Zone</t>
+          <t>Inda Lake</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012H/15/Au 011</t>
+          <t>013J/13/U  009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Molybdenum, Copper, Uranium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>44</v>
       </c>
       <c r="V12" t="n">
-        <v>49.88465</v>
+        <v>54.92456</v>
       </c>
       <c r="W12" t="n">
-        <v>-56.83885</v>
+        <v>-59.5807</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jacques Lake</t>
+          <t>Gear Lake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>013J/12/U  018</t>
+          <t>013J/13/U  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1417,14 +1417,14 @@
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>54.71754</v>
+        <v>54.94329</v>
       </c>
       <c r="W13" t="n">
-        <v>-59.59268</v>
+        <v>-59.54386</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
         </is>
       </c>
     </row>
@@ -1434,24 +1434,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Turners Ridge</t>
+          <t>Kitts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>012H/11/Pb 001</t>
+          <t>013J/14/U  001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>44</v>
       </c>
       <c r="V14" t="n">
-        <v>49.59029</v>
+        <v>54.99779</v>
       </c>
       <c r="W14" t="n">
-        <v>-57.00443</v>
+        <v>-59.4872</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kitts</t>
+          <t>H Brook Showing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>013J/14/U  001</t>
+          <t>011O/15/Au 004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>44</v>
       </c>
       <c r="V16" t="n">
-        <v>54.99779</v>
+        <v>47.7624</v>
       </c>
       <c r="W16" t="n">
-        <v>-59.4872</v>
+        <v>-58.91357</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gear Lake</t>
+          <t>Cape Ray Gold Deposit #4 Zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>013J/13/U  010</t>
+          <t>011O/15/Au 001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>44</v>
       </c>
       <c r="V17" t="n">
-        <v>54.94329</v>
+        <v>47.76081</v>
       </c>
       <c r="W17" t="n">
-        <v>-59.54386</v>
+        <v>-58.91872</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -1722,24 +1722,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inda Lake</t>
+          <t>Cape Ray Gold Deposit 41 Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>013J/13/U  009</t>
+          <t>011O/15/Au 002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1777,14 +1777,14 @@
         <v>44</v>
       </c>
       <c r="V18" t="n">
-        <v>54.92456</v>
+        <v>47.75858</v>
       </c>
       <c r="W18" t="n">
-        <v>-59.5807</v>
+        <v>-58.92331</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nash Lake (Main Zone)</t>
+          <t>51 Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>013J/13/U  006</t>
+          <t>011O/15/Au 003</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>44</v>
       </c>
       <c r="V19" t="n">
-        <v>54.91032</v>
+        <v>47.75077</v>
       </c>
       <c r="W19" t="n">
-        <v>-59.62004</v>
+        <v>-58.93823</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H Brook Showing</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>011O/15/Au 004</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>44</v>
       </c>
       <c r="V20" t="n">
-        <v>47.7624</v>
+        <v>48.69485</v>
       </c>
       <c r="W20" t="n">
-        <v>-58.91357</v>
+        <v>-58.68177</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>51 Zone</t>
+          <t>Keats</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>011O/15/Au 003</t>
+          <t>002D/15/Au 010</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>44</v>
       </c>
       <c r="V21" t="n">
-        <v>47.75077</v>
+        <v>48.97891</v>
       </c>
       <c r="W21" t="n">
-        <v>-58.93823</v>
+        <v>-54.8402</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit 41 Zone</t>
+          <t>Point Leamington Deposit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>011O/15/Au 002</t>
+          <t>002E/05/Zn 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Silver, Copper, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>44</v>
       </c>
       <c r="V22" t="n">
-        <v>47.75858</v>
+        <v>49.27672</v>
       </c>
       <c r="W22" t="n">
-        <v>-58.92331</v>
+        <v>-55.63152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit #4 Zone</t>
+          <t>Bull Road Showing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>011O/15/Au 001</t>
+          <t>002E/12/Zn 007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Copper, Silver, Lead, Antimony, Zinc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>44</v>
       </c>
       <c r="V23" t="n">
-        <v>47.76081</v>
+        <v>49.51431</v>
       </c>
       <c r="W23" t="n">
-        <v>-58.91872</v>
+        <v>-55.7118</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -2154,24 +2154,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Two Tom Lake</t>
+          <t>Windowglass Hill - Main Zone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>013L/01/REE001</t>
+          <t>011O/10/Au 001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Copper, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>44</v>
       </c>
       <c r="V24" t="n">
-        <v>54.21359</v>
+        <v>47.74279</v>
       </c>
       <c r="W24" t="n">
-        <v>-62.14192</v>
+        <v>-58.95727</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mann #1</t>
+          <t>Voisey's Bay, Far Eastern Deeps</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>013L/01/Be 001</t>
+          <t>014D/08/Ni 013</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Niobium, Uranium, Zinc, Beryllium</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>44</v>
       </c>
       <c r="V25" t="n">
-        <v>54.23929</v>
+        <v>56.32109</v>
       </c>
       <c r="W25" t="n">
-        <v>-62.3924</v>
+        <v>-62.06064</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
         </is>
       </c>
     </row>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Ackley City</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>001M/11/Mo 002</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Zinc, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2353,14 +2353,14 @@
         <v>44</v>
       </c>
       <c r="V26" t="n">
-        <v>48.69485</v>
+        <v>47.69347</v>
       </c>
       <c r="W26" t="n">
-        <v>-58.68177</v>
+        <v>-55.20716</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
         </is>
       </c>
     </row>
@@ -2370,24 +2370,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Keats</t>
+          <t>Strickland - Copper Zone</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>002D/15/Au 010</t>
+          <t>011O/16/Cu 001</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>44</v>
       </c>
       <c r="V27" t="n">
-        <v>48.97891</v>
+        <v>47.80365</v>
       </c>
       <c r="W27" t="n">
-        <v>-54.8402</v>
+        <v>-58.30275</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -2442,24 +2442,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bull Road Showing</t>
+          <t>Two Time</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>002E/12/Zn 007</t>
+          <t>013K/11/U  005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Antimony, Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2497,14 +2497,14 @@
         <v>44</v>
       </c>
       <c r="V28" t="n">
-        <v>49.51431</v>
+        <v>54.56554</v>
       </c>
       <c r="W28" t="n">
-        <v>-55.7118</v>
+        <v>-61.17152</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2514,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Point Leamington Deposit</t>
+          <t>Voisey's Bay, South Eastern Deeps</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>002E/05/Zn 001</t>
+          <t>014D/08/Ni 017</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead, Zinc</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>44</v>
       </c>
       <c r="V29" t="n">
-        <v>49.27672</v>
+        <v>56.31756</v>
       </c>
       <c r="W29" t="n">
-        <v>-55.63152</v>
+        <v>-62.06953</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Windowglass Hill - Main Zone</t>
+          <t>Voisey's Bay, North Eastern Deeps</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>011O/10/Au 001</t>
+          <t>014D/08/Ni 011</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2641,14 +2641,14 @@
         <v>44</v>
       </c>
       <c r="V30" t="n">
-        <v>47.74279</v>
+        <v>56.32929</v>
       </c>
       <c r="W30" t="n">
-        <v>-58.95727</v>
+        <v>-62.07733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
         </is>
       </c>
     </row>
@@ -2730,24 +2730,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Voisey's Bay, North Eastern Deeps</t>
+          <t>Moran Lake C-Zone</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>014D/08/Ni 011</t>
+          <t>013K/07/U  002</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2785,14 +2785,14 @@
         <v>44</v>
       </c>
       <c r="V32" t="n">
-        <v>56.32929</v>
+        <v>54.47908</v>
       </c>
       <c r="W32" t="n">
-        <v>-62.07733</v>
+        <v>-60.9581</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Voisey's Bay, South Eastern Deeps</t>
+          <t>Area 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>014D/08/Ni 017</t>
+          <t>013K/07/U  007</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Vanadium, Uranium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2857,14 +2857,14 @@
         <v>44</v>
       </c>
       <c r="V33" t="n">
-        <v>56.31756</v>
+        <v>54.46751</v>
       </c>
       <c r="W33" t="n">
-        <v>-62.06953</v>
+        <v>-60.98105</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
         </is>
       </c>
     </row>
@@ -2874,24 +2874,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Two Time</t>
+          <t>Jaclyn Main - Golden Promise</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>013K/11/U  005</t>
+          <t>012A/16/Au 002</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2929,14 +2929,14 @@
         <v>44</v>
       </c>
       <c r="V34" t="n">
-        <v>54.56554</v>
+        <v>48.90572</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.17152</v>
+        <v>-56.15002</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Strickland - Main Zone</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>013K/07/U  007</t>
+          <t>011O/16/Zn 001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Vanadium, Uranium</t>
+          <t>Lead, Copper, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>44</v>
       </c>
       <c r="V35" t="n">
-        <v>54.46751</v>
+        <v>47.80818</v>
       </c>
       <c r="W35" t="n">
-        <v>-60.98105</v>
+        <v>-58.29993</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Moran Lake C-Zone</t>
+          <t>Strickland - Silver Hill Zone</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>013K/07/U  002</t>
+          <t>011O/16/Zn 002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>44</v>
       </c>
       <c r="V36" t="n">
-        <v>54.47908</v>
+        <v>47.81</v>
       </c>
       <c r="W36" t="n">
-        <v>-60.9581</v>
+        <v>-58.2985</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -3090,24 +3090,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grey River Tungsten</t>
+          <t>Moly Brook</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>011P/11/W  001</t>
+          <t>011P/11/Mo 001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,14 +3145,14 @@
         <v>44</v>
       </c>
       <c r="V37" t="n">
-        <v>47.59343</v>
+        <v>47.61683</v>
       </c>
       <c r="W37" t="n">
-        <v>-57.10342</v>
+        <v>-57.1034</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3162,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Moly Brook</t>
+          <t>Grey River Tungsten</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>011P/11/Mo 001</t>
+          <t>011P/11/W  001</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3217,14 +3217,14 @@
         <v>44</v>
       </c>
       <c r="V38" t="n">
-        <v>47.61683</v>
+        <v>47.59343</v>
       </c>
       <c r="W38" t="n">
-        <v>-57.1034</v>
+        <v>-57.10342</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Strickland - Silver Hill Zone</t>
+          <t>Springer's Hill-Main Showing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>011O/16/Zn 002</t>
+          <t>012B/16/Cr 002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>44</v>
       </c>
       <c r="V39" t="n">
-        <v>47.81</v>
+        <v>48.7927</v>
       </c>
       <c r="W39" t="n">
-        <v>-58.2985</v>
+        <v>-58.44526</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
         </is>
       </c>
     </row>
@@ -3306,24 +3306,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Strickland - Main Zone</t>
+          <t>Saddle Zone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>011O/16/Zn 001</t>
+          <t>002E/02/Au 038</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Gold, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U40" t="n">
         <v>44</v>
       </c>
       <c r="V40" t="n">
-        <v>47.80818</v>
+        <v>49.00899</v>
       </c>
       <c r="W40" t="n">
-        <v>-58.29993</v>
+        <v>-54.81554</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
         </is>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jaclyn Main - Golden Promise</t>
+          <t>Keats South</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>012A/16/Au 002</t>
+          <t>002D/15/Au 060</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>44</v>
       </c>
       <c r="V41" t="n">
-        <v>48.90572</v>
+        <v>48.97791</v>
       </c>
       <c r="W41" t="n">
-        <v>-56.15002</v>
+        <v>-54.84407</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Strickland - Copper Zone</t>
+          <t>Viking Gold-Thor Trend</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>011O/16/Cu 001</t>
+          <t>012H/10/Au 011</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3496,23 +3496,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U42" t="n">
         <v>44</v>
       </c>
       <c r="V42" t="n">
-        <v>47.80365</v>
+        <v>49.69447</v>
       </c>
       <c r="W42" t="n">
-        <v>-58.30275</v>
+        <v>-56.99193</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ackley City</t>
+          <t>Horseshoe Zone</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>001M/11/Mo 002</t>
+          <t>002E/02/Au 039</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>44</v>
       </c>
       <c r="V43" t="n">
-        <v>47.69347</v>
+        <v>49.01341</v>
       </c>
       <c r="W43" t="n">
-        <v>-55.20716</v>
+        <v>-54.81741</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
         </is>
       </c>
     </row>
@@ -3594,24 +3594,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Far Eastern Deeps</t>
+          <t>Copper Creek BV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>014D/08/Ni 013</t>
+          <t>012H/16/Cu 040</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>44</v>
       </c>
       <c r="V44" t="n">
-        <v>56.32109</v>
+        <v>49.91887</v>
       </c>
       <c r="W44" t="n">
-        <v>-62.06064</v>
+        <v>-56.20986</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Springer's Hill-Main Showing</t>
+          <t>Deep Fox</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>012B/16/Cr 002</t>
+          <t>003D/05/Ree007</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>44</v>
       </c>
       <c r="V45" t="n">
-        <v>48.7927</v>
+        <v>52.3805</v>
       </c>
       <c r="W45" t="n">
-        <v>-58.44526</v>
+        <v>-55.64987</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Keats South</t>
+          <t>PW Zone</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>002D/15/Au 060</t>
+          <t>011O/10/Au 011</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>44</v>
       </c>
       <c r="V46" t="n">
-        <v>48.97791</v>
+        <v>47.74631</v>
       </c>
       <c r="W46" t="n">
-        <v>-54.84407</v>
+        <v>-58.94364</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saddle Zone</t>
+          <t>Mart Lake Graphite</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>002E/02/Au 038</t>
+          <t>023B/14/Gf 001</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Graphite</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3856,23 +3856,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
         <v>44</v>
       </c>
       <c r="V47" t="n">
-        <v>49.00899</v>
+        <v>52.8283</v>
       </c>
       <c r="W47" t="n">
-        <v>-54.81554</v>
+        <v>-67.01484000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lewis Brook Mine</t>
+          <t>Foxtrot</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>012B/15/Asb001</t>
+          <t>003D/05/Ree001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>37</v>
       </c>
       <c r="V48" t="n">
-        <v>48.77071</v>
+        <v>52.40035</v>
       </c>
       <c r="W48" t="n">
-        <v>-58.56548</v>
+        <v>-55.82418</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Beaver Dam</t>
+          <t>Deer Cove Talc Zone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>012H/15/Au 018</t>
+          <t>012I/01/Tlc001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Arsenic, Gold</t>
+          <t>Magnesium, Talc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4009,14 +4009,14 @@
         <v>37</v>
       </c>
       <c r="V49" t="n">
-        <v>49.86141</v>
+        <v>50.01534</v>
       </c>
       <c r="W49" t="n">
-        <v>-56.85295</v>
+        <v>-56.04949</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Strange Lake</t>
+          <t>Beaver Dam</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>024A/08/Ree001</t>
+          <t>012H/15/Au 018</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
+          <t>Arsenic, Gold</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>56.31656</v>
+        <v>49.86141</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.12678</v>
+        <v>-56.85295</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Norsk South Block</t>
+          <t>Strange Lake</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>012B/10/Dol004</t>
+          <t>024A/08/Ree001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>48.52445</v>
+        <v>56.31656</v>
       </c>
       <c r="W51" t="n">
-        <v>-58.99684</v>
+        <v>-64.12678</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Norsk North Block</t>
+          <t>Sheep Brook</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>012B/10/Dol003</t>
+          <t>012B/08/Gyp001</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4225,14 +4225,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>48.53397</v>
+        <v>48.39536</v>
       </c>
       <c r="W52" t="n">
-        <v>-58.9773</v>
+        <v>-58.42046</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Round Pond Deposit</t>
+          <t>Porcupine Strand North Beach</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012P/08/Zn 015</t>
+          <t>013I/03/Ti 001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fluorine, Lead, Zinc</t>
+          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>51.25735</v>
+        <v>54.03818</v>
       </c>
       <c r="W53" t="n">
-        <v>-56.26701</v>
+        <v>-57.31912</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4386,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Porcupine Strand North Beach</t>
+          <t>Round Pond Deposit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>013I/03/Ti 001</t>
+          <t>012P/08/Zn 015</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
+          <t>Fluorine, Lead, Zinc</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4441,14 +4441,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>54.03818</v>
+        <v>51.25735</v>
       </c>
       <c r="W55" t="n">
-        <v>-57.31912</v>
+        <v>-56.26701</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deer Cove Talc Zone</t>
+          <t>Norsk South Block</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>012I/01/Tlc001</t>
+          <t>012B/10/Dol004</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Magnesium, Talc</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>50.01534</v>
+        <v>48.52445</v>
       </c>
       <c r="W56" t="n">
-        <v>-56.04949</v>
+        <v>-58.99684</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Foxtrot</t>
+          <t>Norsk North Block</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>003D/05/Ree001</t>
+          <t>012B/10/Dol003</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>52.40035</v>
+        <v>48.53397</v>
       </c>
       <c r="W57" t="n">
-        <v>-55.82418</v>
+        <v>-58.9773</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Lewis Brook Mine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>012B/15/Asb001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>48.39536</v>
+        <v>48.77071</v>
       </c>
       <c r="W60" t="n">
-        <v>-58.42046</v>
+        <v>-58.56548</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Ovoid</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>014D/08/Ni 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>56.33134</v>
+        <v>47.4063</v>
       </c>
       <c r="W61" t="n">
-        <v>-62.09706</v>
+        <v>-52.70699</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGS Vein</t>
+          <t>York Harbour Mine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>001L/14/Fl 013</t>
+          <t>012G/01/Cu 002</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Fluorine</t>
+          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>46.91489</v>
+        <v>49.05208</v>
       </c>
       <c r="W62" t="n">
-        <v>-55.48584</v>
+        <v>-58.30769</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -4962,24 +4962,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blow-Me-Down Chromite #1</t>
+          <t>Sleepy Hollow</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>012G/01/Cr 001</t>
+          <t>002E/12/Cu 031</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5008,23 +5008,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T63" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U63" t="n">
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>49.01096</v>
+        <v>49.59747</v>
       </c>
       <c r="W63" t="n">
-        <v>-58.24371</v>
+        <v>-55.94735</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
         </is>
       </c>
     </row>
@@ -5034,24 +5034,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Goose Cove</t>
+          <t>Miles Cove Mine</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>002M/05/Cu 001</t>
+          <t>002E/12/Cu 012</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zinc, Nickel, Iron, Copper</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>51.31009</v>
+        <v>49.53936</v>
       </c>
       <c r="W64" t="n">
-        <v>-55.62342</v>
+        <v>-55.79062</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>York Harbour Mine</t>
+          <t>Goose Cove</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>012G/01/Cu 002</t>
+          <t>002M/05/Cu 001</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
+          <t>Zinc, Nickel, Iron, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>49.05208</v>
+        <v>51.31009</v>
       </c>
       <c r="W65" t="n">
-        <v>-58.30769</v>
+        <v>-55.62342</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5178,24 +5178,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Blow-Me-Down Chromite #1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012G/01/Cr 001</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U66" t="n">
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>50.27283</v>
+        <v>49.01096</v>
       </c>
       <c r="W66" t="n">
-        <v>-57.46448</v>
+        <v>-58.24371</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Terra Nova Mine</t>
+          <t>Voisey's Bay, Ovoid</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>012H/16/Cu 004</t>
+          <t>014D/08/Ni 001</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>49.92133</v>
+        <v>56.33134</v>
       </c>
       <c r="W67" t="n">
-        <v>-56.22896</v>
+        <v>-62.09706</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-G Zone</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 007</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>50.31118</v>
+        <v>50.29448</v>
       </c>
       <c r="W68" t="n">
-        <v>-57.43009</v>
+        <v>-57.44714</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-Q Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>012I/06/Zn 016</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>50.29741</v>
+        <v>50.27283</v>
       </c>
       <c r="W69" t="n">
-        <v>-57.48016</v>
+        <v>-57.46448</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Browning Mine</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>012H/10/Au 001</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>49.71799</v>
+        <v>50.31118</v>
       </c>
       <c r="W70" t="n">
-        <v>-56.92565</v>
+        <v>-57.43009</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5538,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Goldenville</t>
+          <t>Daniel's Harbour Mine-H Zone</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>012H/16/Au 033</t>
+          <t>012I/06/Zn 008</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper, Iron, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5584,23 +5584,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>49.99193</v>
+        <v>50.29179</v>
       </c>
       <c r="W71" t="n">
-        <v>-56.05735</v>
+        <v>-57.44599</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stog'er Tight</t>
+          <t>Daniel's Harbour Mine-J Zone</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>012H/16/Au 041</t>
+          <t>012I/06/Zn 009</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5665,14 +5665,14 @@
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>49.9661</v>
+        <v>50.30247</v>
       </c>
       <c r="W72" t="n">
-        <v>-56.07765</v>
+        <v>-57.47459</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>Daniel's Harbour Mine-K Zone</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>012I/06/Zn 010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5737,14 +5737,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>49.19579</v>
+        <v>50.2935</v>
       </c>
       <c r="W73" t="n">
-        <v>-57.84974</v>
+        <v>-57.46875</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
         </is>
       </c>
     </row>
@@ -5754,24 +5754,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>Daniel's Harbour Mine-L Zone</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>012I/06/Zn 011</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Lead, Dolomite, Zinc</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5809,14 +5809,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>52.961</v>
+        <v>50.27686</v>
       </c>
       <c r="W74" t="n">
-        <v>-66.81446</v>
+        <v>-57.46788</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5826,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-J Zone</t>
+          <t>Daniel's Harbour Mine-M Zone</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>012I/06/Zn 009</t>
+          <t>012I/06/Zn 012</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>50.30247</v>
+        <v>50.29514</v>
       </c>
       <c r="W75" t="n">
-        <v>-57.47459</v>
+        <v>-57.44013</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-L Zone</t>
+          <t>Daniel's Harbour Mine-N Zone</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>012I/06/Zn 011</t>
+          <t>012I/06/Zn 013</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lead, Dolomite, Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>50.27686</v>
+        <v>50.29873</v>
       </c>
       <c r="W76" t="n">
-        <v>-57.46788</v>
+        <v>-57.48691</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
         </is>
       </c>
     </row>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-N Zone</t>
+          <t>Terra Nova Mine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>012I/06/Zn 013</t>
+          <t>012H/16/Cu 004</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>50.29873</v>
+        <v>49.92133</v>
       </c>
       <c r="W77" t="n">
-        <v>-57.48691</v>
+        <v>-56.22896</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6042,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-F Zone</t>
+          <t>Goldenville</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>012I/06/Zn 006</t>
+          <t>012H/16/Au 033</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper, Iron, Gold</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6088,23 +6088,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T78" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U78" t="n">
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>50.29437</v>
+        <v>49.99193</v>
       </c>
       <c r="W78" t="n">
-        <v>-57.45374</v>
+        <v>-56.05735</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
         </is>
       </c>
     </row>
@@ -6114,24 +6114,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-E Zone</t>
+          <t>Stog'er Tight</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>012I/06/Zn 005</t>
+          <t>012H/16/Au 041</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>50.31067</v>
+        <v>49.9661</v>
       </c>
       <c r="W79" t="n">
-        <v>-57.44799</v>
+        <v>-56.07765</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-C Zone</t>
+          <t>Daniel's Harbour Mine-B Zone</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>012I/06/Zn 003</t>
+          <t>012I/06/Zn 002</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6241,14 +6241,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>50.30435</v>
+        <v>50.2975</v>
       </c>
       <c r="W80" t="n">
-        <v>-57.45355</v>
+        <v>-57.45784</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-D Zone</t>
+          <t>Daniel's Harbour Mine-E Zone</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>012I/06/Zn 004</t>
+          <t>012I/06/Zn 005</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6313,14 +6313,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>50.30795</v>
+        <v>50.31067</v>
       </c>
       <c r="W81" t="n">
-        <v>-57.45218</v>
+        <v>-57.44799</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-B Zone</t>
+          <t>Daniel's Harbour Mine-C Zone</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>012I/06/Zn 002</t>
+          <t>012I/06/Zn 003</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6385,14 +6385,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>50.2975</v>
+        <v>50.30435</v>
       </c>
       <c r="W82" t="n">
-        <v>-57.45784</v>
+        <v>-57.45355</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
         </is>
       </c>
     </row>
@@ -6402,12 +6402,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-H Zone</t>
+          <t>Daniel's Harbour Mine-D Zone</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>012I/06/Zn 008</t>
+          <t>012I/06/Zn 004</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6457,14 +6457,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>50.29179</v>
+        <v>50.30795</v>
       </c>
       <c r="W83" t="n">
-        <v>-57.44599</v>
+        <v>-57.45218</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-G Zone</t>
+          <t>Pilley's Island Mine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>012I/06/Zn 007</t>
+          <t>002E/12/Cu 001</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6529,14 +6529,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>50.29448</v>
+        <v>49.50863</v>
       </c>
       <c r="W84" t="n">
-        <v>-57.44714</v>
+        <v>-55.71872</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-M Zone</t>
+          <t>AGS Vein</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>012I/06/Zn 012</t>
+          <t>001L/14/Fl 013</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc, Lead, Copper, Fluorine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6601,14 +6601,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>50.29514</v>
+        <v>46.91489</v>
       </c>
       <c r="W85" t="n">
-        <v>-57.44013</v>
+        <v>-55.48584</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
         </is>
       </c>
     </row>
@@ -6618,24 +6618,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Nugget Pond</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>002E/13/Au 001</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6673,14 +6673,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>49.45488</v>
+        <v>49.84502</v>
       </c>
       <c r="W86" t="n">
-        <v>-55.49811</v>
+        <v>-55.77536</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -6690,24 +6690,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stoneyhouse</t>
+          <t>Bishop North</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>001M/01/Cu 001</t>
+          <t>012B/08/Fe 001</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6745,14 +6745,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>47.0541</v>
+        <v>48.40317</v>
       </c>
       <c r="W87" t="n">
-        <v>-54.11056</v>
+        <v>-58.3315</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6762,24 +6762,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Indian Head Mine</t>
+          <t>Upper Drill Brook Mine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>012B/10/Fe 001</t>
+          <t>012B/09/Fe 002</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>48.52416</v>
+        <v>48.53533</v>
       </c>
       <c r="W88" t="n">
-        <v>-58.5148</v>
+        <v>-58.48601</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -6834,24 +6834,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tilt Cove/East Mine/Upper Dump</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>002E/13/Au 028</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Zinc, Gold</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>49.88512</v>
+        <v>48.5353</v>
       </c>
       <c r="W89" t="n">
-        <v>-55.62192</v>
+        <v>-58.48804</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -6906,12 +6906,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tilt Cove Mine</t>
+          <t>Betts Cove Mine</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>002E/13/Cu 001</t>
+          <t>002E/13/Cu 002</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Silver, Zinc, Copper</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>49.88214</v>
+        <v>49.81179</v>
       </c>
       <c r="W90" t="n">
-        <v>-55.62813</v>
+        <v>-55.80608</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Stewart Mine</t>
+          <t>Tilt Cove Mine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>002E/10/Au 001</t>
+          <t>002E/13/Cu 001</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Silver, Antimony, Copper, Zinc, Gold</t>
+          <t>Gold, Nickel, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>49.58065</v>
+        <v>49.88214</v>
       </c>
       <c r="W91" t="n">
-        <v>-54.85442</v>
+        <v>-55.62813</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7050,24 +7050,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Tilt Cove/East Mine/Upper Dump</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>002E/13/Au 028</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Silver, Nickel, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7105,14 +7105,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>48.5353</v>
+        <v>49.88512</v>
       </c>
       <c r="W92" t="n">
-        <v>-58.48804</v>
+        <v>-55.62192</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
         </is>
       </c>
     </row>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pine Cove</t>
+          <t>Cross Cove</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>012H/16/Au 023</t>
+          <t>002E/10/Sb 001</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>49.96066</v>
+        <v>49.57534</v>
       </c>
       <c r="W93" t="n">
-        <v>-56.13074</v>
+        <v>-54.86876</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
         </is>
       </c>
     </row>
@@ -7194,24 +7194,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bishop South</t>
+          <t>Stoneyhouse</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>012B/08/Fe 002</t>
+          <t>001M/01/Cu 001</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7249,14 +7249,14 @@
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>48.39996</v>
+        <v>47.0541</v>
       </c>
       <c r="W94" t="n">
-        <v>-58.33683</v>
+        <v>-54.11056</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7266,24 +7266,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bishop North</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>012B/08/Fe 001</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7321,14 +7321,14 @@
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>48.40317</v>
+        <v>49.45488</v>
       </c>
       <c r="W95" t="n">
-        <v>-58.3315</v>
+        <v>-55.49811</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -7338,24 +7338,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Upper Drill Brook Mine</t>
+          <t>Argyle</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>012B/09/Fe 002</t>
+          <t>012H/16/Au 083</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7393,14 +7393,14 @@
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>48.53533</v>
+        <v>49.97838</v>
       </c>
       <c r="W96" t="n">
-        <v>-58.48601</v>
+        <v>-56.05952</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
         </is>
       </c>
     </row>
@@ -7410,24 +7410,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Turk's Gut</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>001N/11/Cu 001</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7465,14 +7465,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>47.50226</v>
+        <v>47.4438</v>
       </c>
       <c r="W97" t="n">
-        <v>-53.20074</v>
+        <v>-54.4169</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cross Cove</t>
+          <t>Turk's Gut</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>002E/10/Sb 001</t>
+          <t>001N/11/Cu 001</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>49.57534</v>
+        <v>47.50226</v>
       </c>
       <c r="W98" t="n">
-        <v>-54.86876</v>
+        <v>-53.20074</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Daniel's Harbour Mine-A Zone</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>012I/06/Zn 001</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>47.4438</v>
+        <v>50.29576</v>
       </c>
       <c r="W99" t="n">
-        <v>-54.4169</v>
+        <v>-57.46512</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -7626,24 +7626,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>La Manche</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001N/12/Pb 001</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Silver, Barium, Lead</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>35</v>
       </c>
       <c r="V100" t="n">
-        <v>47.4063</v>
+        <v>47.6889</v>
       </c>
       <c r="W100" t="n">
-        <v>-52.70699</v>
+        <v>-53.93901</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -7770,24 +7770,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Miles Cove Mine</t>
+          <t>Hope Brook</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>002E/12/Cu 012</t>
+          <t>011O/09/Au 003</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7825,14 +7825,14 @@
         <v>35</v>
       </c>
       <c r="V102" t="n">
-        <v>49.53936</v>
+        <v>47.73806</v>
       </c>
       <c r="W102" t="n">
-        <v>-55.79062</v>
+        <v>-58.09531</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Pilley's Island Mine</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>002E/12/Cu 001</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>35</v>
       </c>
       <c r="V103" t="n">
-        <v>49.50863</v>
+        <v>52.961</v>
       </c>
       <c r="W103" t="n">
-        <v>-55.71872</v>
+        <v>-66.81446</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -7914,24 +7914,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hope Brook</t>
+          <t>Ming West</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>011O/09/Au 003</t>
+          <t>012H/16/Cu 029</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7960,23 +7960,23 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T104" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U104" t="n">
         <v>35</v>
       </c>
       <c r="V104" t="n">
-        <v>47.73806</v>
+        <v>49.9148</v>
       </c>
       <c r="W104" t="n">
-        <v>-58.09531</v>
+        <v>-56.08996</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
         </is>
       </c>
     </row>
@@ -7986,24 +7986,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>La Manche</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>001N/12/Pb 001</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Barium, Lead</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8041,14 +8041,14 @@
         <v>35</v>
       </c>
       <c r="V105" t="n">
-        <v>47.6889</v>
+        <v>49.19579</v>
       </c>
       <c r="W105" t="n">
-        <v>-53.93901</v>
+        <v>-57.84974</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -8058,24 +8058,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sleepy Hollow</t>
+          <t>Daniel's Harbour Mine-Q Zone</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>002E/12/Cu 031</t>
+          <t>012I/06/Zn 016</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8113,14 +8113,14 @@
         <v>35</v>
       </c>
       <c r="V106" t="n">
-        <v>49.59747</v>
+        <v>50.29741</v>
       </c>
       <c r="W106" t="n">
-        <v>-55.94735</v>
+        <v>-57.48016</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
         </is>
       </c>
     </row>
@@ -8130,24 +8130,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ming West</t>
+          <t>Browning Mine</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>012H/16/Cu 029</t>
+          <t>012H/10/Au 001</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8176,23 +8176,23 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T107" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U107" t="n">
         <v>35</v>
       </c>
       <c r="V107" t="n">
-        <v>49.9148</v>
+        <v>49.71799</v>
       </c>
       <c r="W107" t="n">
-        <v>-56.08996</v>
+        <v>-56.92565</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -8202,24 +8202,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-A Zone</t>
+          <t>Pine Cove</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>012I/06/Zn 001</t>
+          <t>012H/16/Au 023</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8257,14 +8257,14 @@
         <v>35</v>
       </c>
       <c r="V108" t="n">
-        <v>50.29576</v>
+        <v>49.96066</v>
       </c>
       <c r="W108" t="n">
-        <v>-57.46512</v>
+        <v>-56.13074</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Argyle</t>
+          <t>Bishop South</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>012H/16/Au 083</t>
+          <t>012B/08/Fe 002</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>35</v>
       </c>
       <c r="V109" t="n">
-        <v>49.97838</v>
+        <v>48.39996</v>
       </c>
       <c r="W109" t="n">
-        <v>-56.05952</v>
+        <v>-58.33683</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -8346,24 +8346,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-K Zone</t>
+          <t>Daniel's Harbour Mine-F Zone</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>012I/06/Zn 010</t>
+          <t>012I/06/Zn 006</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>35</v>
       </c>
       <c r="V110" t="n">
-        <v>50.2935</v>
+        <v>50.29437</v>
       </c>
       <c r="W110" t="n">
-        <v>-57.46875</v>
+        <v>-57.45374</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
         </is>
       </c>
     </row>
@@ -8418,24 +8418,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Betts Cove Mine</t>
+          <t>Stewart Mine</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>002E/13/Cu 002</t>
+          <t>002E/10/Au 001</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Silver, Antimony, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>35</v>
       </c>
       <c r="V111" t="n">
-        <v>49.81179</v>
+        <v>49.58065</v>
       </c>
       <c r="W111" t="n">
-        <v>-55.80608</v>
+        <v>-54.85442</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -8490,24 +8490,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nugget Pond</t>
+          <t>Indian Head Mine</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>002E/13/Au 001</t>
+          <t>012B/10/Fe 001</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>35</v>
       </c>
       <c r="V112" t="n">
-        <v>49.84502</v>
+        <v>48.52416</v>
       </c>
       <c r="W112" t="n">
-        <v>-55.77536</v>
+        <v>-58.5148</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8562,24 +8562,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timmins No 8</t>
+          <t>Goethite Bay North</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>023J/14/Fe 026</t>
+          <t>023G/02/Fe 041</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8617,14 +8617,14 @@
         <v>31</v>
       </c>
       <c r="V113" t="n">
-        <v>54.89589</v>
+        <v>53.18717</v>
       </c>
       <c r="W113" t="n">
-        <v>-67.07944000000001</v>
+        <v>-66.74445</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
         </is>
       </c>
     </row>
@@ -8634,24 +8634,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timmins No 5</t>
+          <t>Ruth Lake No 2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>023J/14/Fe 024</t>
+          <t>023J/15/Fe 011</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>31</v>
       </c>
       <c r="V114" t="n">
-        <v>54.86384</v>
+        <v>54.79747</v>
       </c>
       <c r="W114" t="n">
-        <v>-67.09327</v>
+        <v>-66.87487</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mile 2</t>
+          <t>Block 103 - Greenbush Zone</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>023B/15/Fe 011</t>
+          <t>023J/14/Fe 043</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -8761,14 +8761,14 @@
         <v>31</v>
       </c>
       <c r="V115" t="n">
-        <v>52.97907</v>
+        <v>54.97234</v>
       </c>
       <c r="W115" t="n">
-        <v>-66.88907</v>
+        <v>-67.25158</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wabush No. 1</t>
+          <t>Elizabeth No. 2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>023B/15/Fe 002</t>
+          <t>023J/15/Fe 032</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>31</v>
       </c>
       <c r="V116" t="n">
-        <v>52.9599</v>
+        <v>54.77182</v>
       </c>
       <c r="W116" t="n">
-        <v>-66.9704</v>
+        <v>-66.88666000000001</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Julienne Lake</t>
+          <t>Lorraine No. 4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>023G/02/Fe 009</t>
+          <t>023G/02/Fe 008</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8905,14 +8905,14 @@
         <v>31</v>
       </c>
       <c r="V117" t="n">
-        <v>53.13733</v>
+        <v>53.08316</v>
       </c>
       <c r="W117" t="n">
-        <v>-66.78360000000001</v>
+        <v>-66.87726000000001</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Joyce Lake</t>
+          <t>Elizabeth No. 1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>023J/15/Fe 030</t>
+          <t>023J/15/Fe 031</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -8977,14 +8977,14 @@
         <v>31</v>
       </c>
       <c r="V118" t="n">
-        <v>54.8993</v>
+        <v>54.78743</v>
       </c>
       <c r="W118" t="n">
-        <v>-66.53366</v>
+        <v>-66.90081000000001</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
         </is>
       </c>
     </row>
@@ -8994,24 +8994,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Attikamagen Deposit</t>
+          <t>Wabush No. 7</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>023J/16/Fe 001</t>
+          <t>023G/02/Fe 007</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9049,14 +9049,14 @@
         <v>31</v>
       </c>
       <c r="V119" t="n">
-        <v>54.80989</v>
+        <v>53.02512</v>
       </c>
       <c r="W119" t="n">
-        <v>-66.47658</v>
+        <v>-66.90531</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Goethite Bay North</t>
+          <t>Knob Lake 1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>023G/02/Fe 041</t>
+          <t>023J/15/Fe 013</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9121,14 +9121,14 @@
         <v>31</v>
       </c>
       <c r="V120" t="n">
-        <v>53.18717</v>
+        <v>54.7766</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.74445</v>
+        <v>-66.80589000000001</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
         </is>
       </c>
     </row>
@@ -9138,24 +9138,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Wabush No. 6</t>
+          <t>Howse</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>023G/02/Fe 006</t>
+          <t>023J/14/Fe 028</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9193,14 +9193,14 @@
         <v>31</v>
       </c>
       <c r="V121" t="n">
-        <v>53.01798</v>
+        <v>54.9089</v>
       </c>
       <c r="W121" t="n">
-        <v>-66.89297999999999</v>
+        <v>-67.14075</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -9210,24 +9210,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Canning</t>
+          <t>Ferriman No 7</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>023B/15/Fe 007</t>
+          <t>023J/15/Fe 014</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9265,14 +9265,14 @@
         <v>31</v>
       </c>
       <c r="V122" t="n">
-        <v>52.9469</v>
+        <v>54.81281</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.95802999999999</v>
+        <v>-66.94580999999999</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
         </is>
       </c>
     </row>
@@ -9282,24 +9282,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timmins No 7</t>
+          <t>Duley No. 1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>023J/14/Fe 025</t>
+          <t>023B/14/Fe 001</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9337,14 +9337,14 @@
         <v>31</v>
       </c>
       <c r="V123" t="n">
-        <v>54.89246</v>
+        <v>52.87237</v>
       </c>
       <c r="W123" t="n">
-        <v>-67.07259000000001</v>
+        <v>-67.05874</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ferriman No 7</t>
+          <t>Kivivic No 3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>023J/15/Fe 014</t>
+          <t>023O/03/Fe 003</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9409,14 +9409,14 @@
         <v>31</v>
       </c>
       <c r="V124" t="n">
-        <v>54.81281</v>
+        <v>55.05061</v>
       </c>
       <c r="W124" t="n">
-        <v>-66.94580999999999</v>
+        <v>-67.26130000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -9426,24 +9426,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Wabush No. 4</t>
+          <t>Sawyer Lake</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>023B/15/Fe 004</t>
+          <t>023I/05/Fe 001</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9481,14 +9481,14 @@
         <v>31</v>
       </c>
       <c r="V125" t="n">
-        <v>52.95373</v>
+        <v>54.45206</v>
       </c>
       <c r="W125" t="n">
-        <v>-66.94092000000001</v>
+        <v>-65.98627</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9498,24 +9498,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Block 103 - Greenbush Zone</t>
+          <t>Ruth Lake No 8</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>023J/14/Fe 043</t>
+          <t>023J/15/Fe 009</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9553,14 +9553,14 @@
         <v>31</v>
       </c>
       <c r="V126" t="n">
-        <v>54.97234</v>
+        <v>54.78104</v>
       </c>
       <c r="W126" t="n">
-        <v>-67.25158</v>
+        <v>-66.86577</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9570,12 +9570,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Howells River North</t>
+          <t>Attikamagen Deposit</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>023O/03/Fe 007</t>
+          <t>023J/16/Fe 001</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -9625,14 +9625,14 @@
         <v>31</v>
       </c>
       <c r="V127" t="n">
-        <v>55.01179</v>
+        <v>54.80989</v>
       </c>
       <c r="W127" t="n">
-        <v>-67.37214</v>
+        <v>-66.47658</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Duley No. 2</t>
+          <t>Joyce Lake</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>023B/15/Fe 008</t>
+          <t>023J/15/Fe 030</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>31</v>
       </c>
       <c r="V128" t="n">
-        <v>52.87214</v>
+        <v>54.8993</v>
       </c>
       <c r="W128" t="n">
-        <v>-66.99635000000001</v>
+        <v>-66.53366</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
         </is>
       </c>
     </row>
@@ -9714,12 +9714,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Elizabeth No. 1</t>
+          <t>Howells Lake</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>023J/15/Fe 031</t>
+          <t>023O/03/Fe 006</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -9769,14 +9769,14 @@
         <v>31</v>
       </c>
       <c r="V129" t="n">
-        <v>54.78743</v>
+        <v>55.06346</v>
       </c>
       <c r="W129" t="n">
-        <v>-66.90081000000001</v>
+        <v>-67.40528</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9786,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Howells Lake</t>
+          <t>Howells River North</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>023O/03/Fe 006</t>
+          <t>023O/03/Fe 007</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9841,14 +9841,14 @@
         <v>31</v>
       </c>
       <c r="V130" t="n">
-        <v>55.06346</v>
+        <v>55.01179</v>
       </c>
       <c r="W130" t="n">
-        <v>-67.40528</v>
+        <v>-67.37214</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Wabush No. 7</t>
+          <t>Wabush No. 6</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>023G/02/Fe 007</t>
+          <t>023G/02/Fe 006</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9913,14 +9913,14 @@
         <v>31</v>
       </c>
       <c r="V131" t="n">
-        <v>53.02512</v>
+        <v>53.01798</v>
       </c>
       <c r="W131" t="n">
-        <v>-66.90531</v>
+        <v>-66.89297999999999</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lorraine No. 4</t>
+          <t>Julienne Lake</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>023G/02/Fe 008</t>
+          <t>023G/02/Fe 009</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9985,14 +9985,14 @@
         <v>31</v>
       </c>
       <c r="V132" t="n">
-        <v>53.08316</v>
+        <v>53.13733</v>
       </c>
       <c r="W132" t="n">
-        <v>-66.87726000000001</v>
+        <v>-66.78360000000001</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wabush No. 8</t>
+          <t>Duley No. 2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>023B/15/Fe 005</t>
+          <t>023B/15/Fe 008</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -10057,14 +10057,14 @@
         <v>31</v>
       </c>
       <c r="V133" t="n">
-        <v>52.9791</v>
+        <v>52.87214</v>
       </c>
       <c r="W133" t="n">
-        <v>-66.90604999999999</v>
+        <v>-66.99635000000001</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Houston 2</t>
+          <t>Canning</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>023J/10/Fe 009</t>
+          <t>023B/15/Fe 007</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10129,14 +10129,14 @@
         <v>31</v>
       </c>
       <c r="V134" t="n">
-        <v>54.71245</v>
+        <v>52.9469</v>
       </c>
       <c r="W134" t="n">
-        <v>-66.66257</v>
+        <v>-66.95802999999999</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10146,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Houston 3</t>
+          <t>Timmins No 7</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>023J/10/Fe 010</t>
+          <t>023J/14/Fe 025</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10201,14 +10201,14 @@
         <v>31</v>
       </c>
       <c r="V135" t="n">
-        <v>54.69887</v>
+        <v>54.89246</v>
       </c>
       <c r="W135" t="n">
-        <v>-66.64483</v>
+        <v>-67.07259000000001</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
         </is>
       </c>
     </row>
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kivivic No 3</t>
+          <t>Mile 2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>023O/03/Fe 003</t>
+          <t>023B/15/Fe 011</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -10273,14 +10273,14 @@
         <v>31</v>
       </c>
       <c r="V136" t="n">
-        <v>55.05061</v>
+        <v>52.97907</v>
       </c>
       <c r="W136" t="n">
-        <v>-67.26130000000001</v>
+        <v>-66.88907</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Kivivic No 4</t>
+          <t>Wabush No. 8</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>023O/03/Fe 004</t>
+          <t>023B/15/Fe 005</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>31</v>
       </c>
       <c r="V137" t="n">
-        <v>55.04865</v>
+        <v>52.9791</v>
       </c>
       <c r="W137" t="n">
-        <v>-67.28158000000001</v>
+        <v>-66.90604999999999</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10362,24 +10362,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kivivic No 5</t>
+          <t>Wabush No. 4</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>023O/03/Fe 005</t>
+          <t>023B/15/Fe 004</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>31</v>
       </c>
       <c r="V138" t="n">
-        <v>55.06664</v>
+        <v>52.95373</v>
       </c>
       <c r="W138" t="n">
-        <v>-67.29537000000001</v>
+        <v>-66.94092000000001</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -10434,24 +10434,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Duley No. 1</t>
+          <t>Timmins No 8</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>023B/14/Fe 001</t>
+          <t>023J/14/Fe 026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>31</v>
       </c>
       <c r="V139" t="n">
-        <v>52.87237</v>
+        <v>54.89589</v>
       </c>
       <c r="W139" t="n">
-        <v>-67.05874</v>
+        <v>-67.07944000000001</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
         </is>
       </c>
     </row>
@@ -10506,24 +10506,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mills Lake</t>
+          <t>Timmins No 5</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>023B/14/Fe 002</t>
+          <t>023J/14/Fe 024</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>31</v>
       </c>
       <c r="V140" t="n">
-        <v>52.79808</v>
+        <v>54.86384</v>
       </c>
       <c r="W140" t="n">
-        <v>-67.00413</v>
+        <v>-67.09327</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
         </is>
       </c>
     </row>
@@ -10578,24 +10578,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Howells River West Zone A</t>
+          <t>Sheps Lake</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>023J/14/Fe 001</t>
+          <t>023J/11/Fe 001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10633,14 +10633,14 @@
         <v>31</v>
       </c>
       <c r="V141" t="n">
-        <v>54.90958</v>
+        <v>54.73475</v>
       </c>
       <c r="W141" t="n">
-        <v>-67.26052</v>
+        <v>-67.06362</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Houston 1</t>
+          <t>Neal 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>023J/10/Fe 008</t>
+          <t>023B/14/Fe 008</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10705,14 +10705,14 @@
         <v>31</v>
       </c>
       <c r="V142" t="n">
-        <v>54.70748</v>
+        <v>52.95013</v>
       </c>
       <c r="W142" t="n">
-        <v>-66.65615</v>
+        <v>-67.15191</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10722,24 +10722,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Redmond 5</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>023J/10/Fe 005</t>
+          <t>023B/14/Fe 028</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10777,14 +10777,14 @@
         <v>31</v>
       </c>
       <c r="V143" t="n">
-        <v>54.70854</v>
+        <v>52.94868</v>
       </c>
       <c r="W143" t="n">
-        <v>-66.79174999999999</v>
+        <v>-67.01146</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sawyer Lake</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>023I/05/Fe 001</t>
+          <t>023B/14/Fe 020</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>31</v>
       </c>
       <c r="V144" t="n">
-        <v>54.45206</v>
+        <v>52.83351</v>
       </c>
       <c r="W144" t="n">
-        <v>-65.98627</v>
+        <v>-67.0311</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
         </is>
       </c>
     </row>
@@ -10938,24 +10938,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Howells River West Zone A</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>023B/14/Fe 020</t>
+          <t>023J/14/Fe 001</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>31</v>
       </c>
       <c r="V146" t="n">
-        <v>52.83351</v>
+        <v>54.90958</v>
       </c>
       <c r="W146" t="n">
-        <v>-67.0311</v>
+        <v>-67.26052</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -11010,24 +11010,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Wabush No. 1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>023B/14/Fe 028</t>
+          <t>023B/15/Fe 002</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11065,14 +11065,14 @@
         <v>31</v>
       </c>
       <c r="V147" t="n">
-        <v>52.94868</v>
+        <v>52.9599</v>
       </c>
       <c r="W147" t="n">
-        <v>-67.01146</v>
+        <v>-66.9704</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sheps Lake</t>
+          <t>Redmond 5</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>023J/11/Fe 001</t>
+          <t>023J/10/Fe 005</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11137,14 +11137,14 @@
         <v>31</v>
       </c>
       <c r="V148" t="n">
-        <v>54.73475</v>
+        <v>54.70854</v>
       </c>
       <c r="W148" t="n">
-        <v>-67.06362</v>
+        <v>-66.79174999999999</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Neal 1</t>
+          <t>Mills Lake</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>023B/14/Fe 008</t>
+          <t>023B/14/Fe 002</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -11209,14 +11209,14 @@
         <v>31</v>
       </c>
       <c r="V149" t="n">
-        <v>52.95013</v>
+        <v>52.79808</v>
       </c>
       <c r="W149" t="n">
-        <v>-67.15191</v>
+        <v>-67.00413</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ruth Lake No 8</t>
+          <t>Houston 1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>023J/15/Fe 009</t>
+          <t>023J/10/Fe 008</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11281,14 +11281,14 @@
         <v>31</v>
       </c>
       <c r="V150" t="n">
-        <v>54.78104</v>
+        <v>54.70748</v>
       </c>
       <c r="W150" t="n">
-        <v>-66.86577</v>
+        <v>-66.65615</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ruth Lake No 2</t>
+          <t>Houston 3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>023J/15/Fe 011</t>
+          <t>023J/10/Fe 010</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11353,14 +11353,14 @@
         <v>31</v>
       </c>
       <c r="V151" t="n">
-        <v>54.79747</v>
+        <v>54.69887</v>
       </c>
       <c r="W151" t="n">
-        <v>-66.87487</v>
+        <v>-66.64483</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -11370,24 +11370,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Elizabeth No. 2</t>
+          <t>Houston 2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>023J/15/Fe 032</t>
+          <t>023J/10/Fe 009</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11425,14 +11425,14 @@
         <v>31</v>
       </c>
       <c r="V152" t="n">
-        <v>54.77182</v>
+        <v>54.71245</v>
       </c>
       <c r="W152" t="n">
-        <v>-66.88666000000001</v>
+        <v>-66.66257</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -11442,24 +11442,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Knob Lake 1</t>
+          <t>Kivivic No 4</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>023J/15/Fe 013</t>
+          <t>023O/03/Fe 004</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11497,14 +11497,14 @@
         <v>31</v>
       </c>
       <c r="V153" t="n">
-        <v>54.7766</v>
+        <v>55.04865</v>
       </c>
       <c r="W153" t="n">
-        <v>-66.80589000000001</v>
+        <v>-67.28158000000001</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11514,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Howse</t>
+          <t>Kivivic No 5</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>023J/14/Fe 028</t>
+          <t>023O/03/Fe 005</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11569,14 +11569,14 @@
         <v>31</v>
       </c>
       <c r="V154" t="n">
-        <v>54.9089</v>
+        <v>55.06664</v>
       </c>
       <c r="W154" t="n">
-        <v>-67.14075</v>
+        <v>-67.29537000000001</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mine Hill</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>001N/07/Pph004</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pyrophyllite</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11641,14 +11641,14 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>47.48</v>
+        <v>53.40462</v>
       </c>
       <c r="W155" t="n">
-        <v>-52.95479</v>
+        <v>-65.08734</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Iron Springs Mine</t>
+          <t>Parsons Pond No 3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>001L/14/Fl 008</t>
+          <t>012H/13/Btm003</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11785,14 +11785,14 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>46.88701</v>
+        <v>49.97912</v>
       </c>
       <c r="W157" t="n">
-        <v>-55.421</v>
+        <v>-57.64547</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Parsons Pond No 2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>012H/13/Btm002</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11857,14 +11857,14 @@
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>48.56074</v>
+        <v>49.97421</v>
       </c>
       <c r="W158" t="n">
-        <v>-58.8161</v>
+        <v>-57.60538</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hares Ears Vein</t>
+          <t>Parsons Pond No 4</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>001L/14/Fl 007</t>
+          <t>012H/13/Btm004</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11920,23 +11920,23 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T159" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U159" t="n">
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>46.88814</v>
+        <v>49.99787</v>
       </c>
       <c r="W159" t="n">
-        <v>-55.41178</v>
+        <v>-57.63818</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Collier Point</t>
+          <t>Middle Arm Brook</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>001N/12/Ba 001</t>
+          <t>012H/16/Vir001</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Barium</t>
+          <t>Virginite</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12001,14 +12001,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>47.59126</v>
+        <v>49.80048</v>
       </c>
       <c r="W160" t="n">
-        <v>-53.69011</v>
+        <v>-56.31995</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Lord &amp; Lady Gulch Mine</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>001L/14/Fl 005</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12073,14 +12073,14 @@
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>48.30663</v>
+        <v>46.87554</v>
       </c>
       <c r="W161" t="n">
-        <v>-58.68165</v>
+        <v>-55.4111</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Parsons Pond Cart Track</t>
+          <t>Baie Verte Mine</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>012I/04/Btm001</t>
+          <t>012H/16/Asb008</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Oil Shale</t>
+          <t>Magnesium, Asbestos</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12136,23 +12136,23 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T162" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U162" t="n">
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>50.00564</v>
+        <v>49.97974</v>
       </c>
       <c r="W162" t="n">
-        <v>-57.63187</v>
+        <v>-56.19399</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
         </is>
       </c>
     </row>
@@ -12162,12 +12162,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Baie Verte Mine</t>
+          <t>Black Duck Mine</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>012H/16/Asb008</t>
+          <t>001L/14/Fl 010</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Magnesium, Asbestos</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12217,14 +12217,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>49.97974</v>
+        <v>46.93201</v>
       </c>
       <c r="W163" t="n">
-        <v>-56.19399</v>
+        <v>-55.38881</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Borney Lake</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>002D/14/Stn001</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12289,14 +12289,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>48.9264</v>
+        <v>48.30663</v>
       </c>
       <c r="W164" t="n">
-        <v>-55.44535</v>
+        <v>-58.68165</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Doctors Pond Veins</t>
+          <t>Southern Cross Veins</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>001L/14/Fl 036</t>
+          <t>001L/14/Fl 020</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12361,14 +12361,14 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>46.92769</v>
+        <v>46.88974</v>
       </c>
       <c r="W165" t="n">
-        <v>-55.37593</v>
+        <v>-55.42958</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Parsons Pond No 3</t>
+          <t>Tarefare Mine</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>012H/13/Btm003</t>
+          <t>001L/14/Fl 006</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12433,14 +12433,14 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>49.97912</v>
+        <v>46.8912</v>
       </c>
       <c r="W166" t="n">
-        <v>-57.64547</v>
+        <v>-55.43112</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tarefare Mine</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>001L/14/Fl 006</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12505,14 +12505,14 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>46.8912</v>
+        <v>53.469</v>
       </c>
       <c r="W167" t="n">
-        <v>-55.43112</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -12522,12 +12522,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Blue Beach Mine</t>
+          <t>Mine Hill</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>001L/14/Fl 001</t>
+          <t>001N/07/Pph004</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Pyrophyllite</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12577,14 +12577,14 @@
         <v>30</v>
       </c>
       <c r="V168" t="n">
-        <v>46.91553</v>
+        <v>47.48</v>
       </c>
       <c r="W168" t="n">
-        <v>-55.40729</v>
+        <v>-52.95479</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
         </is>
       </c>
     </row>
@@ -12594,12 +12594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Black Duck Mine</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>001L/14/Fl 010</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12649,14 +12649,14 @@
         <v>30</v>
       </c>
       <c r="V169" t="n">
-        <v>46.93201</v>
+        <v>48.56074</v>
       </c>
       <c r="W169" t="n">
-        <v>-55.38881</v>
+        <v>-58.8161</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Southern Cross Veins</t>
+          <t>Collier Point</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>001L/14/Fl 020</t>
+          <t>001N/12/Ba 001</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Barium</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12721,14 +12721,14 @@
         <v>30</v>
       </c>
       <c r="V170" t="n">
-        <v>46.88974</v>
+        <v>47.59126</v>
       </c>
       <c r="W170" t="n">
-        <v>-55.42958</v>
+        <v>-53.69011</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
         </is>
       </c>
     </row>
@@ -12738,12 +12738,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Lord &amp; Lady Gulch Mine</t>
+          <t>Parsons Pond Cart Track</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>001L/14/Fl 005</t>
+          <t>012I/04/Btm001</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil Shale</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12784,23 +12784,23 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T171" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U171" t="n">
         <v>30</v>
       </c>
       <c r="V171" t="n">
-        <v>46.87554</v>
+        <v>50.00564</v>
       </c>
       <c r="W171" t="n">
-        <v>-55.4111</v>
+        <v>-57.63187</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Scrape Vein</t>
+          <t>Doctors Pond Veins</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>001L/14/Fl 035</t>
+          <t>001L/14/Fl 036</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -12865,14 +12865,14 @@
         <v>30</v>
       </c>
       <c r="V172" t="n">
-        <v>46.92547</v>
+        <v>46.92769</v>
       </c>
       <c r="W172" t="n">
-        <v>-55.37193</v>
+        <v>-55.37593</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Little Salt Cove</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>001L/14/Fl 016</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12937,14 +12937,14 @@
         <v>30</v>
       </c>
       <c r="V173" t="n">
-        <v>53.40462</v>
+        <v>46.87654</v>
       </c>
       <c r="W173" t="n">
-        <v>-65.08734</v>
+        <v>-55.43141</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12954,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Scrape Vein</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>001L/14/Fl 035</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13009,14 +13009,14 @@
         <v>30</v>
       </c>
       <c r="V174" t="n">
-        <v>48.50411</v>
+        <v>46.92547</v>
       </c>
       <c r="W174" t="n">
-        <v>-58.53451</v>
+        <v>-55.37193</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Bluff Head Mine</t>
+          <t>Director Mine</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>012B/15/Cr 001</t>
+          <t>001L/14/Fl 009</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Asbestos, Chromium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13081,14 +13081,14 @@
         <v>30</v>
       </c>
       <c r="V175" t="n">
-        <v>48.77717</v>
+        <v>46.90681</v>
       </c>
       <c r="W175" t="n">
-        <v>-58.59931</v>
+        <v>-55.42107</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
         </is>
       </c>
     </row>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Iron Springs Mine</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>001L/14/Fl 008</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13153,14 +13153,14 @@
         <v>30</v>
       </c>
       <c r="V176" t="n">
-        <v>53.469</v>
+        <v>46.88701</v>
       </c>
       <c r="W176" t="n">
-        <v>-64.91218000000001</v>
+        <v>-55.421</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Director Mine</t>
+          <t>Borney Lake</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>001L/14/Fl 009</t>
+          <t>002D/14/Stn001</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13225,14 +13225,14 @@
         <v>30</v>
       </c>
       <c r="V177" t="n">
-        <v>46.90681</v>
+        <v>48.9264</v>
       </c>
       <c r="W177" t="n">
-        <v>-55.42107</v>
+        <v>-55.44535</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Little Salt Cove</t>
+          <t>Bluff Head Mine</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>001L/14/Fl 016</t>
+          <t>012B/15/Cr 001</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Asbestos, Chromium</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13297,14 +13297,14 @@
         <v>30</v>
       </c>
       <c r="V178" t="n">
-        <v>46.87654</v>
+        <v>48.77717</v>
       </c>
       <c r="W178" t="n">
-        <v>-55.43141</v>
+        <v>-58.59931</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Middle Arm Brook</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>012H/16/Vir001</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Virginite</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13441,14 +13441,14 @@
         <v>30</v>
       </c>
       <c r="V180" t="n">
-        <v>49.80048</v>
+        <v>48.50411</v>
       </c>
       <c r="W180" t="n">
-        <v>-56.31995</v>
+        <v>-58.53451</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13458,12 +13458,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Parsons Pond No 2</t>
+          <t>Blue Beach Mine</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>012H/13/Btm002</t>
+          <t>001L/14/Fl 001</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13513,14 +13513,14 @@
         <v>30</v>
       </c>
       <c r="V181" t="n">
-        <v>49.97421</v>
+        <v>46.91553</v>
       </c>
       <c r="W181" t="n">
-        <v>-57.60538</v>
+        <v>-55.40729</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
         </is>
       </c>
     </row>
@@ -13530,12 +13530,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Parsons Pond No 1</t>
+          <t>Hares Ears Vein</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>012H/13/Btm001</t>
+          <t>001L/14/Fl 007</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13576,23 +13576,23 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T182" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U182" t="n">
         <v>30</v>
       </c>
       <c r="V182" t="n">
-        <v>49.99228</v>
+        <v>46.88814</v>
       </c>
       <c r="W182" t="n">
-        <v>-57.58928</v>
+        <v>-55.41178</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Parsons Pond No 4</t>
+          <t>Parsons Pond No 1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>012H/13/Btm004</t>
+          <t>012H/13/Btm001</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13648,23 +13648,23 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T183" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U183" t="n">
         <v>30</v>
       </c>
       <c r="V183" t="n">
-        <v>49.99787</v>
+        <v>49.99228</v>
       </c>
       <c r="W183" t="n">
-        <v>-57.63818</v>
+        <v>-57.58928</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Grey Copper Mine</t>
+          <t>Little Bay Mine</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>002E/11/Cu 001</t>
+          <t>002E/12/Cu 030</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Iron, Copper</t>
+          <t>Iron, Gold, Copper</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13729,14 +13729,14 @@
         <v>26</v>
       </c>
       <c r="V184" t="n">
-        <v>49.5173</v>
+        <v>49.5961</v>
       </c>
       <c r="W184" t="n">
-        <v>-55.2721</v>
+        <v>-55.94531</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Scotia Formation</t>
+          <t>Fleming No 3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>001N/10/Fe 002</t>
+          <t>023J/14/Fe 022</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13801,14 +13801,14 @@
         <v>26</v>
       </c>
       <c r="V185" t="n">
-        <v>47.64169</v>
+        <v>54.85836</v>
       </c>
       <c r="W185" t="n">
-        <v>-52.97639</v>
+        <v>-67.03167999999999</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Gull Island Formation</t>
+          <t>Timmins No 2</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>001N/10/Fe 003</t>
+          <t>023J/14/Fe 019</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -13873,14 +13873,14 @@
         <v>26</v>
       </c>
       <c r="V186" t="n">
-        <v>47.65193</v>
+        <v>54.89421</v>
       </c>
       <c r="W186" t="n">
-        <v>-52.95654</v>
+        <v>-67.08716</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Redmond No 2</t>
+          <t>Timmins No 4</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>023J/10/Fe 002</t>
+          <t>023J/14/Fe 023</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13945,14 +13945,14 @@
         <v>26</v>
       </c>
       <c r="V187" t="n">
-        <v>54.69738</v>
+        <v>54.89884</v>
       </c>
       <c r="W187" t="n">
-        <v>-66.77224</v>
+        <v>-67.10881000000001</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
         </is>
       </c>
     </row>
@@ -13962,24 +13962,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Little Bay Mine</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>002E/12/Cu 030</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Iron, Gold, Copper</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14017,14 +14017,14 @@
         <v>26</v>
       </c>
       <c r="V188" t="n">
-        <v>49.5961</v>
+        <v>47.53392</v>
       </c>
       <c r="W188" t="n">
-        <v>-55.94531</v>
+        <v>-53.18293</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -14034,24 +14034,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Dominion Formation</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>001N/10/Fe 001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14089,14 +14089,14 @@
         <v>26</v>
       </c>
       <c r="V189" t="n">
-        <v>49.50376</v>
+        <v>47.64164</v>
       </c>
       <c r="W189" t="n">
-        <v>-55.21553</v>
+        <v>-52.95309</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14106,24 +14106,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Redmond No 2</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>023J/10/Fe 002</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14161,14 +14161,14 @@
         <v>26</v>
       </c>
       <c r="V190" t="n">
-        <v>47.53392</v>
+        <v>54.69738</v>
       </c>
       <c r="W190" t="n">
-        <v>-53.18293</v>
+        <v>-66.77224</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dominion Formation</t>
+          <t>Gull Island Formation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>001N/10/Fe 001</t>
+          <t>001N/10/Fe 003</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -14233,14 +14233,14 @@
         <v>26</v>
       </c>
       <c r="V191" t="n">
-        <v>47.64164</v>
+        <v>47.65193</v>
       </c>
       <c r="W191" t="n">
-        <v>-52.95309</v>
+        <v>-52.95654</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -14250,12 +14250,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cliff Mine</t>
+          <t>Scotia Formation</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>012B/09/Fe 001</t>
+          <t>001N/10/Fe 002</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -14305,14 +14305,14 @@
         <v>26</v>
       </c>
       <c r="V192" t="n">
-        <v>48.54434</v>
+        <v>47.64169</v>
       </c>
       <c r="W192" t="n">
-        <v>-58.49915</v>
+        <v>-52.97639</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Skindles Mine</t>
+          <t>Timmins No 1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>012B/09/Fe 004</t>
+          <t>023J/14/Fe 018</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14377,14 +14377,14 @@
         <v>26</v>
       </c>
       <c r="V193" t="n">
-        <v>48.54069</v>
+        <v>54.88449</v>
       </c>
       <c r="W193" t="n">
-        <v>-58.48888</v>
+        <v>-67.08575</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
         </is>
       </c>
     </row>
@@ -14394,24 +14394,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Timmins No 6</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>023J/15/Fe 010</t>
+          <t>023J/14/Fe 021</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14449,14 +14449,14 @@
         <v>26</v>
       </c>
       <c r="V194" t="n">
-        <v>54.77437</v>
+        <v>54.90148</v>
       </c>
       <c r="W194" t="n">
-        <v>-66.82881</v>
+        <v>-67.09757999999999</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14466,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ruth Lake No 7</t>
+          <t>Skindles Mine</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>023J/15/Fe 006</t>
+          <t>012B/09/Fe 004</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
         <v>26</v>
       </c>
       <c r="V195" t="n">
-        <v>54.80557</v>
+        <v>48.54069</v>
       </c>
       <c r="W195" t="n">
-        <v>-66.90618000000001</v>
+        <v>-58.48888</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14538,24 +14538,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Ruth Lake No 5</t>
+          <t>Cliff Mine</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>023J/15/Fe 007</t>
+          <t>012B/09/Fe 001</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14593,14 +14593,14 @@
         <v>26</v>
       </c>
       <c r="V196" t="n">
-        <v>54.80503</v>
+        <v>48.54434</v>
       </c>
       <c r="W196" t="n">
-        <v>-66.88023</v>
+        <v>-58.49915</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14610,24 +14610,24 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ruth Lake No 6</t>
+          <t>Grey Copper Mine</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>023J/15/Fe 008</t>
+          <t>002E/11/Cu 001</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron, Copper</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14665,14 +14665,14 @@
         <v>26</v>
       </c>
       <c r="V197" t="n">
-        <v>54.80104</v>
+        <v>49.5173</v>
       </c>
       <c r="W197" t="n">
-        <v>-66.87327999999999</v>
+        <v>-55.2721</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -14682,24 +14682,24 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ruth Lake No 9</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>023J/15/Fe 005</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14737,14 +14737,14 @@
         <v>26</v>
       </c>
       <c r="V198" t="n">
-        <v>54.80033</v>
+        <v>49.50376</v>
       </c>
       <c r="W198" t="n">
-        <v>-66.89447</v>
+        <v>-55.21553</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14754,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ruth Lake No 1</t>
+          <t>Smallwood Mine</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>023J/15/Fe 002</t>
+          <t>023G/02/Fe 001</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14809,14 +14809,14 @@
         <v>26</v>
       </c>
       <c r="V199" t="n">
-        <v>54.79145</v>
+        <v>53.03718</v>
       </c>
       <c r="W199" t="n">
-        <v>-66.85449</v>
+        <v>-66.93694000000001</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14826,24 +14826,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Wishart No 1 (Wishart Mine)</t>
+          <t>Wishart No 2 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>023J/15/Fe 003</t>
+          <t>023J/15/Fe 004</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14881,14 +14881,14 @@
         <v>26</v>
       </c>
       <c r="V200" t="n">
-        <v>54.76166</v>
+        <v>54.7654</v>
       </c>
       <c r="W200" t="n">
-        <v>-66.88793</v>
+        <v>-66.9067</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Wishart No 2 (Wishart Mine)</t>
+          <t>Lorraine Mine</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>023J/15/Fe 004</t>
+          <t>023G/02/Fe 004</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14953,14 +14953,14 @@
         <v>26</v>
       </c>
       <c r="V201" t="n">
-        <v>54.7654</v>
+        <v>53.06833</v>
       </c>
       <c r="W201" t="n">
-        <v>-66.9067</v>
+        <v>-66.94949</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14970,12 +14970,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ruth Lake No 3</t>
+          <t>Ruth Lake No 1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>023J/15/Fe 001</t>
+          <t>023J/15/Fe 002</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
         <v>26</v>
       </c>
       <c r="V202" t="n">
-        <v>54.80404</v>
+        <v>54.79145</v>
       </c>
       <c r="W202" t="n">
-        <v>-66.87016</v>
+        <v>-66.85449</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -15042,12 +15042,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Smallwood Mine</t>
+          <t>Ruth Lake No 3</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>023G/02/Fe 001</t>
+          <t>023J/15/Fe 001</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -15097,14 +15097,14 @@
         <v>26</v>
       </c>
       <c r="V203" t="n">
-        <v>53.03718</v>
+        <v>54.80404</v>
       </c>
       <c r="W203" t="n">
-        <v>-66.93694000000001</v>
+        <v>-66.87016</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15114,24 +15114,24 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lorraine Mine</t>
+          <t>Wishart No 1 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>023G/02/Fe 004</t>
+          <t>023J/15/Fe 003</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -15169,14 +15169,14 @@
         <v>26</v>
       </c>
       <c r="V204" t="n">
-        <v>53.06833</v>
+        <v>54.76166</v>
       </c>
       <c r="W204" t="n">
-        <v>-66.94949</v>
+        <v>-66.88793</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Fleming No 3</t>
+          <t>Ruth Lake No 9</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>023J/14/Fe 022</t>
+          <t>023J/15/Fe 005</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -15241,14 +15241,14 @@
         <v>26</v>
       </c>
       <c r="V205" t="n">
-        <v>54.85836</v>
+        <v>54.80033</v>
       </c>
       <c r="W205" t="n">
-        <v>-67.03167999999999</v>
+        <v>-66.89447</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -15258,24 +15258,24 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Timmins No 1</t>
+          <t>Ruth Lake No 5</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>023J/14/Fe 018</t>
+          <t>023J/15/Fe 007</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -15313,14 +15313,14 @@
         <v>26</v>
       </c>
       <c r="V206" t="n">
-        <v>54.88449</v>
+        <v>54.80503</v>
       </c>
       <c r="W206" t="n">
-        <v>-67.08575</v>
+        <v>-66.88023</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15330,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timmins No 4</t>
+          <t>Ruth Lake No 7</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>023J/14/Fe 023</t>
+          <t>023J/15/Fe 006</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15385,14 +15385,14 @@
         <v>26</v>
       </c>
       <c r="V207" t="n">
-        <v>54.89884</v>
+        <v>54.80557</v>
       </c>
       <c r="W207" t="n">
-        <v>-67.10881000000001</v>
+        <v>-66.90618000000001</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -15402,24 +15402,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Timmins No 2</t>
+          <t>Ruth Lake No 6</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>023J/14/Fe 019</t>
+          <t>023J/15/Fe 008</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15457,14 +15457,14 @@
         <v>26</v>
       </c>
       <c r="V208" t="n">
-        <v>54.89421</v>
+        <v>54.80104</v>
       </c>
       <c r="W208" t="n">
-        <v>-67.08716</v>
+        <v>-66.87327999999999</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -15474,24 +15474,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Timmins No 6</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>023J/14/Fe 021</t>
+          <t>023J/15/Fe 010</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15529,14 +15529,14 @@
         <v>26</v>
       </c>
       <c r="V209" t="n">
-        <v>54.90148</v>
+        <v>54.77437</v>
       </c>
       <c r="W209" t="n">
-        <v>-67.09757999999999</v>
+        <v>-66.82881</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -15618,24 +15618,24 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Whalesback Mine</t>
+          <t>Ming Footwall Deposit</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>012H/09/Cu 001</t>
+          <t>012H/16/Cu 030</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Zinc, Titanium, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -15664,23 +15664,23 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T211" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U211" t="n">
         <v>19</v>
       </c>
       <c r="V211" t="n">
-        <v>49.59682</v>
+        <v>49.91174</v>
       </c>
       <c r="W211" t="n">
-        <v>-56.00604</v>
+        <v>-56.08642</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F09%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -15690,24 +15690,24 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ming Footwall Deposit</t>
+          <t>Ming Mine</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>012H/16/Cu 030</t>
+          <t>012H/16/Cu 010</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -15745,14 +15745,14 @@
         <v>19</v>
       </c>
       <c r="V212" t="n">
-        <v>49.91174</v>
+        <v>49.9128</v>
       </c>
       <c r="W212" t="n">
-        <v>-56.08642</v>
+        <v>-56.08313</v>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20010</t>
         </is>
       </c>
     </row>
@@ -15762,24 +15762,24 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Ming Mine</t>
+          <t>Whalesback Mine</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>012H/16/Cu 010</t>
+          <t>012H/09/Cu 001</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Zinc, Titanium, Copper</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -15808,23 +15808,23 @@
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T213" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U213" t="n">
         <v>19</v>
       </c>
       <c r="V213" t="n">
-        <v>49.9128</v>
+        <v>49.59682</v>
       </c>
       <c r="W213" t="n">
-        <v>-56.08313</v>
+        <v>-56.00604</v>
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F09%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -15900,78 +15900,6 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>214</v>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Workington</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>002C/03/Fe 001</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I215" t="b">
-        <v>0</v>
-      </c>
-      <c r="J215" t="b">
-        <v>0</v>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="n">
-        <v>0</v>
-      </c>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
-      <c r="R215" t="inlineStr"/>
-      <c r="S215" t="n">
-        <v>4</v>
-      </c>
-      <c r="T215" t="n">
-        <v>100</v>
-      </c>
-      <c r="U215" t="n">
-        <v>10</v>
-      </c>
-      <c r="V215" t="n">
-        <v>48.00096</v>
-      </c>
-      <c r="W215" t="n">
-        <v>-53.01864</v>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Copper Creek BV</t>
+          <t>Michelin Deposit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>012H/16/Cu 040</t>
+          <t>013J/12/U  001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>44</v>
       </c>
       <c r="V2" t="n">
-        <v>49.91887</v>
+        <v>54.58562</v>
       </c>
       <c r="W2" t="n">
-        <v>-56.20986</v>
+        <v>-59.98056</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Horseshoe Zone</t>
+          <t>Rainbow Deposit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>002E/02/Au 039</t>
+          <t>013J/12/U  008</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,23 +688,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>49.01341</v>
+        <v>54.56417</v>
       </c>
       <c r="W3" t="n">
-        <v>-54.81741</v>
+        <v>-59.99369</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viking Gold-Thor Trend</t>
+          <t>Jacques Lake</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012H/10/Au 011</t>
+          <t>013J/12/U  018</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -760,23 +760,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>49.69447</v>
+        <v>54.71754</v>
       </c>
       <c r="W4" t="n">
-        <v>-56.99193</v>
+        <v>-59.59268</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PW Zone</t>
+          <t>Road Zone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>011O/10/Au 011</t>
+          <t>012H/15/Au 011</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -841,14 +841,14 @@
         <v>44</v>
       </c>
       <c r="V5" t="n">
-        <v>47.74631</v>
+        <v>49.88465</v>
       </c>
       <c r="W5" t="n">
-        <v>-58.94364</v>
+        <v>-56.83885</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deep Fox</t>
+          <t>Apsy Zone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>003D/05/Ree007</t>
+          <t>012H/15/Au 014</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>44</v>
       </c>
       <c r="V6" t="n">
-        <v>52.3805</v>
+        <v>49.89471</v>
       </c>
       <c r="W6" t="n">
-        <v>-55.64987</v>
+        <v>-56.82917</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mart Lake Graphite</t>
+          <t>Deer Cove Main Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>023B/14/Gf 001</t>
+          <t>012I/01/Au 001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>44</v>
       </c>
       <c r="V7" t="n">
-        <v>52.8283</v>
+        <v>50.01619</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.01484000000001</v>
+        <v>-56.04389</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rainbow Deposit</t>
+          <t>Turners Ridge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>013J/12/U  008</t>
+          <t>012H/11/Pb 001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
         <v>44</v>
       </c>
       <c r="V8" t="n">
-        <v>54.56417</v>
+        <v>49.59029</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.99369</v>
+        <v>-57.00443</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michelin Deposit</t>
+          <t>Mann #1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>013J/12/U  001</t>
+          <t>013L/01/Be 001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Niobium, Uranium, Zinc, Beryllium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>44</v>
       </c>
       <c r="V9" t="n">
-        <v>54.58562</v>
+        <v>54.23929</v>
       </c>
       <c r="W9" t="n">
-        <v>-59.98056</v>
+        <v>-62.3924</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deer Cove Main Zone</t>
+          <t>Two Tom Lake</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>012I/01/Au 001</t>
+          <t>013L/01/REE001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>50.01619</v>
+        <v>54.21359</v>
       </c>
       <c r="W10" t="n">
-        <v>-56.04389</v>
+        <v>-62.14192</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apsy Zone</t>
+          <t>Nash Lake (Main Zone)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>012H/15/Au 014</t>
+          <t>013J/13/U  006</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1273,14 +1273,14 @@
         <v>44</v>
       </c>
       <c r="V11" t="n">
-        <v>49.89471</v>
+        <v>54.91032</v>
       </c>
       <c r="W11" t="n">
-        <v>-56.82917</v>
+        <v>-59.62004</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
         </is>
       </c>
     </row>
@@ -1290,24 +1290,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Road Zone</t>
+          <t>Inda Lake</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012H/15/Au 011</t>
+          <t>013J/13/U  009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Molybdenum, Copper, Uranium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>44</v>
       </c>
       <c r="V12" t="n">
-        <v>49.88465</v>
+        <v>54.92456</v>
       </c>
       <c r="W12" t="n">
-        <v>-56.83885</v>
+        <v>-59.5807</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jacques Lake</t>
+          <t>Gear Lake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>013J/12/U  018</t>
+          <t>013J/13/U  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1417,14 +1417,14 @@
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>54.71754</v>
+        <v>54.94329</v>
       </c>
       <c r="W13" t="n">
-        <v>-59.59268</v>
+        <v>-59.54386</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
         </is>
       </c>
     </row>
@@ -1434,24 +1434,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Turners Ridge</t>
+          <t>Kitts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>012H/11/Pb 001</t>
+          <t>013J/14/U  001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>44</v>
       </c>
       <c r="V14" t="n">
-        <v>49.59029</v>
+        <v>54.99779</v>
       </c>
       <c r="W14" t="n">
-        <v>-57.00443</v>
+        <v>-59.4872</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kitts</t>
+          <t>H Brook Showing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>013J/14/U  001</t>
+          <t>011O/15/Au 004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>44</v>
       </c>
       <c r="V16" t="n">
-        <v>54.99779</v>
+        <v>47.7624</v>
       </c>
       <c r="W16" t="n">
-        <v>-59.4872</v>
+        <v>-58.91357</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gear Lake</t>
+          <t>Cape Ray Gold Deposit #4 Zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>013J/13/U  010</t>
+          <t>011O/15/Au 001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>44</v>
       </c>
       <c r="V17" t="n">
-        <v>54.94329</v>
+        <v>47.76081</v>
       </c>
       <c r="W17" t="n">
-        <v>-59.54386</v>
+        <v>-58.91872</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -1722,24 +1722,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inda Lake</t>
+          <t>Cape Ray Gold Deposit 41 Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>013J/13/U  009</t>
+          <t>011O/15/Au 002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1777,14 +1777,14 @@
         <v>44</v>
       </c>
       <c r="V18" t="n">
-        <v>54.92456</v>
+        <v>47.75858</v>
       </c>
       <c r="W18" t="n">
-        <v>-59.5807</v>
+        <v>-58.92331</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nash Lake (Main Zone)</t>
+          <t>51 Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>013J/13/U  006</t>
+          <t>011O/15/Au 003</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>44</v>
       </c>
       <c r="V19" t="n">
-        <v>54.91032</v>
+        <v>47.75077</v>
       </c>
       <c r="W19" t="n">
-        <v>-59.62004</v>
+        <v>-58.93823</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H Brook Showing</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>011O/15/Au 004</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>44</v>
       </c>
       <c r="V20" t="n">
-        <v>47.7624</v>
+        <v>48.69485</v>
       </c>
       <c r="W20" t="n">
-        <v>-58.91357</v>
+        <v>-58.68177</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>51 Zone</t>
+          <t>Keats</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>011O/15/Au 003</t>
+          <t>002D/15/Au 010</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>44</v>
       </c>
       <c r="V21" t="n">
-        <v>47.75077</v>
+        <v>48.97891</v>
       </c>
       <c r="W21" t="n">
-        <v>-58.93823</v>
+        <v>-54.8402</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit 41 Zone</t>
+          <t>Point Leamington Deposit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>011O/15/Au 002</t>
+          <t>002E/05/Zn 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Silver, Copper, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>44</v>
       </c>
       <c r="V22" t="n">
-        <v>47.75858</v>
+        <v>49.27672</v>
       </c>
       <c r="W22" t="n">
-        <v>-58.92331</v>
+        <v>-55.63152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit #4 Zone</t>
+          <t>Bull Road Showing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>011O/15/Au 001</t>
+          <t>002E/12/Zn 007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Copper, Silver, Lead, Antimony, Zinc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>44</v>
       </c>
       <c r="V23" t="n">
-        <v>47.76081</v>
+        <v>49.51431</v>
       </c>
       <c r="W23" t="n">
-        <v>-58.91872</v>
+        <v>-55.7118</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -2154,24 +2154,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Two Tom Lake</t>
+          <t>Windowglass Hill - Main Zone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>013L/01/REE001</t>
+          <t>011O/10/Au 001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Copper, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>44</v>
       </c>
       <c r="V24" t="n">
-        <v>54.21359</v>
+        <v>47.74279</v>
       </c>
       <c r="W24" t="n">
-        <v>-62.14192</v>
+        <v>-58.95727</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mann #1</t>
+          <t>Voisey's Bay, Far Eastern Deeps</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>013L/01/Be 001</t>
+          <t>014D/08/Ni 013</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Niobium, Uranium, Zinc, Beryllium</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>44</v>
       </c>
       <c r="V25" t="n">
-        <v>54.23929</v>
+        <v>56.32109</v>
       </c>
       <c r="W25" t="n">
-        <v>-62.3924</v>
+        <v>-62.06064</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
         </is>
       </c>
     </row>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Ackley City</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>001M/11/Mo 002</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Zinc, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2353,14 +2353,14 @@
         <v>44</v>
       </c>
       <c r="V26" t="n">
-        <v>48.69485</v>
+        <v>47.69347</v>
       </c>
       <c r="W26" t="n">
-        <v>-58.68177</v>
+        <v>-55.20716</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
         </is>
       </c>
     </row>
@@ -2370,24 +2370,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Keats</t>
+          <t>Strickland - Copper Zone</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>002D/15/Au 010</t>
+          <t>011O/16/Cu 001</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>44</v>
       </c>
       <c r="V27" t="n">
-        <v>48.97891</v>
+        <v>47.80365</v>
       </c>
       <c r="W27" t="n">
-        <v>-54.8402</v>
+        <v>-58.30275</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -2442,24 +2442,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bull Road Showing</t>
+          <t>Two Time</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>002E/12/Zn 007</t>
+          <t>013K/11/U  005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Antimony, Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2497,14 +2497,14 @@
         <v>44</v>
       </c>
       <c r="V28" t="n">
-        <v>49.51431</v>
+        <v>54.56554</v>
       </c>
       <c r="W28" t="n">
-        <v>-55.7118</v>
+        <v>-61.17152</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2514,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Point Leamington Deposit</t>
+          <t>Voisey's Bay, South Eastern Deeps</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>002E/05/Zn 001</t>
+          <t>014D/08/Ni 017</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead, Zinc</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>44</v>
       </c>
       <c r="V29" t="n">
-        <v>49.27672</v>
+        <v>56.31756</v>
       </c>
       <c r="W29" t="n">
-        <v>-55.63152</v>
+        <v>-62.06953</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Windowglass Hill - Main Zone</t>
+          <t>Voisey's Bay, North Eastern Deeps</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>011O/10/Au 001</t>
+          <t>014D/08/Ni 011</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2641,14 +2641,14 @@
         <v>44</v>
       </c>
       <c r="V30" t="n">
-        <v>47.74279</v>
+        <v>56.32929</v>
       </c>
       <c r="W30" t="n">
-        <v>-58.95727</v>
+        <v>-62.07733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
         </is>
       </c>
     </row>
@@ -2730,24 +2730,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Voisey's Bay, North Eastern Deeps</t>
+          <t>Moran Lake C-Zone</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>014D/08/Ni 011</t>
+          <t>013K/07/U  002</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2785,14 +2785,14 @@
         <v>44</v>
       </c>
       <c r="V32" t="n">
-        <v>56.32929</v>
+        <v>54.47908</v>
       </c>
       <c r="W32" t="n">
-        <v>-62.07733</v>
+        <v>-60.9581</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Voisey's Bay, South Eastern Deeps</t>
+          <t>Area 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>014D/08/Ni 017</t>
+          <t>013K/07/U  007</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Vanadium, Uranium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2857,14 +2857,14 @@
         <v>44</v>
       </c>
       <c r="V33" t="n">
-        <v>56.31756</v>
+        <v>54.46751</v>
       </c>
       <c r="W33" t="n">
-        <v>-62.06953</v>
+        <v>-60.98105</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
         </is>
       </c>
     </row>
@@ -2874,24 +2874,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Two Time</t>
+          <t>Jaclyn Main - Golden Promise</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>013K/11/U  005</t>
+          <t>012A/16/Au 002</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2929,14 +2929,14 @@
         <v>44</v>
       </c>
       <c r="V34" t="n">
-        <v>54.56554</v>
+        <v>48.90572</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.17152</v>
+        <v>-56.15002</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Strickland - Main Zone</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>013K/07/U  007</t>
+          <t>011O/16/Zn 001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Vanadium, Uranium</t>
+          <t>Lead, Copper, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>44</v>
       </c>
       <c r="V35" t="n">
-        <v>54.46751</v>
+        <v>47.80818</v>
       </c>
       <c r="W35" t="n">
-        <v>-60.98105</v>
+        <v>-58.29993</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Moran Lake C-Zone</t>
+          <t>Strickland - Silver Hill Zone</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>013K/07/U  002</t>
+          <t>011O/16/Zn 002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>44</v>
       </c>
       <c r="V36" t="n">
-        <v>54.47908</v>
+        <v>47.81</v>
       </c>
       <c r="W36" t="n">
-        <v>-60.9581</v>
+        <v>-58.2985</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -3090,24 +3090,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grey River Tungsten</t>
+          <t>Moly Brook</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>011P/11/W  001</t>
+          <t>011P/11/Mo 001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,14 +3145,14 @@
         <v>44</v>
       </c>
       <c r="V37" t="n">
-        <v>47.59343</v>
+        <v>47.61683</v>
       </c>
       <c r="W37" t="n">
-        <v>-57.10342</v>
+        <v>-57.1034</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3162,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Moly Brook</t>
+          <t>Grey River Tungsten</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>011P/11/Mo 001</t>
+          <t>011P/11/W  001</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3217,14 +3217,14 @@
         <v>44</v>
       </c>
       <c r="V38" t="n">
-        <v>47.61683</v>
+        <v>47.59343</v>
       </c>
       <c r="W38" t="n">
-        <v>-57.1034</v>
+        <v>-57.10342</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Strickland - Silver Hill Zone</t>
+          <t>Springer's Hill-Main Showing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>011O/16/Zn 002</t>
+          <t>012B/16/Cr 002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>44</v>
       </c>
       <c r="V39" t="n">
-        <v>47.81</v>
+        <v>48.7927</v>
       </c>
       <c r="W39" t="n">
-        <v>-58.2985</v>
+        <v>-58.44526</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
         </is>
       </c>
     </row>
@@ -3306,24 +3306,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Strickland - Main Zone</t>
+          <t>Saddle Zone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>011O/16/Zn 001</t>
+          <t>002E/02/Au 038</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Gold, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U40" t="n">
         <v>44</v>
       </c>
       <c r="V40" t="n">
-        <v>47.80818</v>
+        <v>49.00899</v>
       </c>
       <c r="W40" t="n">
-        <v>-58.29993</v>
+        <v>-54.81554</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
         </is>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jaclyn Main - Golden Promise</t>
+          <t>Keats South</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>012A/16/Au 002</t>
+          <t>002D/15/Au 060</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>44</v>
       </c>
       <c r="V41" t="n">
-        <v>48.90572</v>
+        <v>48.97791</v>
       </c>
       <c r="W41" t="n">
-        <v>-56.15002</v>
+        <v>-54.84407</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Strickland - Copper Zone</t>
+          <t>Viking Gold-Thor Trend</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>011O/16/Cu 001</t>
+          <t>012H/10/Au 011</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3496,23 +3496,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U42" t="n">
         <v>44</v>
       </c>
       <c r="V42" t="n">
-        <v>47.80365</v>
+        <v>49.69447</v>
       </c>
       <c r="W42" t="n">
-        <v>-58.30275</v>
+        <v>-56.99193</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ackley City</t>
+          <t>Horseshoe Zone</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>001M/11/Mo 002</t>
+          <t>002E/02/Au 039</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>44</v>
       </c>
       <c r="V43" t="n">
-        <v>47.69347</v>
+        <v>49.01341</v>
       </c>
       <c r="W43" t="n">
-        <v>-55.20716</v>
+        <v>-54.81741</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
         </is>
       </c>
     </row>
@@ -3594,24 +3594,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Far Eastern Deeps</t>
+          <t>Copper Creek BV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>014D/08/Ni 013</t>
+          <t>012H/16/Cu 040</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>44</v>
       </c>
       <c r="V44" t="n">
-        <v>56.32109</v>
+        <v>49.91887</v>
       </c>
       <c r="W44" t="n">
-        <v>-62.06064</v>
+        <v>-56.20986</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Springer's Hill-Main Showing</t>
+          <t>Deep Fox</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>012B/16/Cr 002</t>
+          <t>003D/05/Ree007</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>44</v>
       </c>
       <c r="V45" t="n">
-        <v>48.7927</v>
+        <v>52.3805</v>
       </c>
       <c r="W45" t="n">
-        <v>-58.44526</v>
+        <v>-55.64987</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Keats South</t>
+          <t>PW Zone</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>002D/15/Au 060</t>
+          <t>011O/10/Au 011</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>44</v>
       </c>
       <c r="V46" t="n">
-        <v>48.97791</v>
+        <v>47.74631</v>
       </c>
       <c r="W46" t="n">
-        <v>-54.84407</v>
+        <v>-58.94364</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saddle Zone</t>
+          <t>Mart Lake Graphite</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>002E/02/Au 038</t>
+          <t>023B/14/Gf 001</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Graphite</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3856,23 +3856,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
         <v>44</v>
       </c>
       <c r="V47" t="n">
-        <v>49.00899</v>
+        <v>52.8283</v>
       </c>
       <c r="W47" t="n">
-        <v>-54.81554</v>
+        <v>-67.01484000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lewis Brook Mine</t>
+          <t>Foxtrot</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>012B/15/Asb001</t>
+          <t>003D/05/Ree001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>37</v>
       </c>
       <c r="V48" t="n">
-        <v>48.77071</v>
+        <v>52.40035</v>
       </c>
       <c r="W48" t="n">
-        <v>-58.56548</v>
+        <v>-55.82418</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Beaver Dam</t>
+          <t>Deer Cove Talc Zone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>012H/15/Au 018</t>
+          <t>012I/01/Tlc001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Arsenic, Gold</t>
+          <t>Magnesium, Talc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4009,14 +4009,14 @@
         <v>37</v>
       </c>
       <c r="V49" t="n">
-        <v>49.86141</v>
+        <v>50.01534</v>
       </c>
       <c r="W49" t="n">
-        <v>-56.85295</v>
+        <v>-56.04949</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Strange Lake</t>
+          <t>Beaver Dam</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>024A/08/Ree001</t>
+          <t>012H/15/Au 018</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
+          <t>Arsenic, Gold</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>56.31656</v>
+        <v>49.86141</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.12678</v>
+        <v>-56.85295</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Norsk South Block</t>
+          <t>Strange Lake</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>012B/10/Dol004</t>
+          <t>024A/08/Ree001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>48.52445</v>
+        <v>56.31656</v>
       </c>
       <c r="W51" t="n">
-        <v>-58.99684</v>
+        <v>-64.12678</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Norsk North Block</t>
+          <t>Sheep Brook</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>012B/10/Dol003</t>
+          <t>012B/08/Gyp001</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4225,14 +4225,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>48.53397</v>
+        <v>48.39536</v>
       </c>
       <c r="W52" t="n">
-        <v>-58.9773</v>
+        <v>-58.42046</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Round Pond Deposit</t>
+          <t>Porcupine Strand North Beach</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012P/08/Zn 015</t>
+          <t>013I/03/Ti 001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fluorine, Lead, Zinc</t>
+          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>51.25735</v>
+        <v>54.03818</v>
       </c>
       <c r="W53" t="n">
-        <v>-56.26701</v>
+        <v>-57.31912</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4386,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Porcupine Strand North Beach</t>
+          <t>Round Pond Deposit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>013I/03/Ti 001</t>
+          <t>012P/08/Zn 015</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
+          <t>Fluorine, Lead, Zinc</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4441,14 +4441,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>54.03818</v>
+        <v>51.25735</v>
       </c>
       <c r="W55" t="n">
-        <v>-57.31912</v>
+        <v>-56.26701</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deer Cove Talc Zone</t>
+          <t>Norsk South Block</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>012I/01/Tlc001</t>
+          <t>012B/10/Dol004</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Magnesium, Talc</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>50.01534</v>
+        <v>48.52445</v>
       </c>
       <c r="W56" t="n">
-        <v>-56.04949</v>
+        <v>-58.99684</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Foxtrot</t>
+          <t>Norsk North Block</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>003D/05/Ree001</t>
+          <t>012B/10/Dol003</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>52.40035</v>
+        <v>48.53397</v>
       </c>
       <c r="W57" t="n">
-        <v>-55.82418</v>
+        <v>-58.9773</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Lewis Brook Mine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>012B/15/Asb001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>48.39536</v>
+        <v>48.77071</v>
       </c>
       <c r="W60" t="n">
-        <v>-58.42046</v>
+        <v>-58.56548</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Ovoid</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>014D/08/Ni 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>56.33134</v>
+        <v>47.4063</v>
       </c>
       <c r="W61" t="n">
-        <v>-62.09706</v>
+        <v>-52.70699</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGS Vein</t>
+          <t>York Harbour Mine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>001L/14/Fl 013</t>
+          <t>012G/01/Cu 002</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Fluorine</t>
+          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>46.91489</v>
+        <v>49.05208</v>
       </c>
       <c r="W62" t="n">
-        <v>-55.48584</v>
+        <v>-58.30769</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -4962,24 +4962,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blow-Me-Down Chromite #1</t>
+          <t>Sleepy Hollow</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>012G/01/Cr 001</t>
+          <t>002E/12/Cu 031</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5008,23 +5008,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T63" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U63" t="n">
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>49.01096</v>
+        <v>49.59747</v>
       </c>
       <c r="W63" t="n">
-        <v>-58.24371</v>
+        <v>-55.94735</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
         </is>
       </c>
     </row>
@@ -5034,24 +5034,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Goose Cove</t>
+          <t>Miles Cove Mine</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>002M/05/Cu 001</t>
+          <t>002E/12/Cu 012</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zinc, Nickel, Iron, Copper</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>51.31009</v>
+        <v>49.53936</v>
       </c>
       <c r="W64" t="n">
-        <v>-55.62342</v>
+        <v>-55.79062</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>York Harbour Mine</t>
+          <t>Goose Cove</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>012G/01/Cu 002</t>
+          <t>002M/05/Cu 001</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
+          <t>Zinc, Nickel, Iron, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>49.05208</v>
+        <v>51.31009</v>
       </c>
       <c r="W65" t="n">
-        <v>-58.30769</v>
+        <v>-55.62342</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5178,24 +5178,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Blow-Me-Down Chromite #1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012G/01/Cr 001</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U66" t="n">
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>50.27283</v>
+        <v>49.01096</v>
       </c>
       <c r="W66" t="n">
-        <v>-57.46448</v>
+        <v>-58.24371</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Terra Nova Mine</t>
+          <t>Voisey's Bay, Ovoid</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>012H/16/Cu 004</t>
+          <t>014D/08/Ni 001</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>49.92133</v>
+        <v>56.33134</v>
       </c>
       <c r="W67" t="n">
-        <v>-56.22896</v>
+        <v>-62.09706</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-G Zone</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 007</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>50.31118</v>
+        <v>50.29448</v>
       </c>
       <c r="W68" t="n">
-        <v>-57.43009</v>
+        <v>-57.44714</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-Q Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>012I/06/Zn 016</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>50.29741</v>
+        <v>50.27283</v>
       </c>
       <c r="W69" t="n">
-        <v>-57.48016</v>
+        <v>-57.46448</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Browning Mine</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>012H/10/Au 001</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>49.71799</v>
+        <v>50.31118</v>
       </c>
       <c r="W70" t="n">
-        <v>-56.92565</v>
+        <v>-57.43009</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5538,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Goldenville</t>
+          <t>Daniel's Harbour Mine-H Zone</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>012H/16/Au 033</t>
+          <t>012I/06/Zn 008</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper, Iron, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5584,23 +5584,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>49.99193</v>
+        <v>50.29179</v>
       </c>
       <c r="W71" t="n">
-        <v>-56.05735</v>
+        <v>-57.44599</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stog'er Tight</t>
+          <t>Daniel's Harbour Mine-J Zone</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>012H/16/Au 041</t>
+          <t>012I/06/Zn 009</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5665,14 +5665,14 @@
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>49.9661</v>
+        <v>50.30247</v>
       </c>
       <c r="W72" t="n">
-        <v>-56.07765</v>
+        <v>-57.47459</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>Daniel's Harbour Mine-K Zone</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>012I/06/Zn 010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5737,14 +5737,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>49.19579</v>
+        <v>50.2935</v>
       </c>
       <c r="W73" t="n">
-        <v>-57.84974</v>
+        <v>-57.46875</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
         </is>
       </c>
     </row>
@@ -5754,24 +5754,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>Daniel's Harbour Mine-L Zone</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>012I/06/Zn 011</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Lead, Dolomite, Zinc</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5809,14 +5809,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>52.961</v>
+        <v>50.27686</v>
       </c>
       <c r="W74" t="n">
-        <v>-66.81446</v>
+        <v>-57.46788</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5826,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-J Zone</t>
+          <t>Daniel's Harbour Mine-M Zone</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>012I/06/Zn 009</t>
+          <t>012I/06/Zn 012</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>50.30247</v>
+        <v>50.29514</v>
       </c>
       <c r="W75" t="n">
-        <v>-57.47459</v>
+        <v>-57.44013</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-L Zone</t>
+          <t>Daniel's Harbour Mine-N Zone</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>012I/06/Zn 011</t>
+          <t>012I/06/Zn 013</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lead, Dolomite, Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>50.27686</v>
+        <v>50.29873</v>
       </c>
       <c r="W76" t="n">
-        <v>-57.46788</v>
+        <v>-57.48691</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
         </is>
       </c>
     </row>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-N Zone</t>
+          <t>Terra Nova Mine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>012I/06/Zn 013</t>
+          <t>012H/16/Cu 004</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>50.29873</v>
+        <v>49.92133</v>
       </c>
       <c r="W77" t="n">
-        <v>-57.48691</v>
+        <v>-56.22896</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6042,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-F Zone</t>
+          <t>Goldenville</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>012I/06/Zn 006</t>
+          <t>012H/16/Au 033</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper, Iron, Gold</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6088,23 +6088,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T78" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U78" t="n">
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>50.29437</v>
+        <v>49.99193</v>
       </c>
       <c r="W78" t="n">
-        <v>-57.45374</v>
+        <v>-56.05735</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
         </is>
       </c>
     </row>
@@ -6114,24 +6114,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-E Zone</t>
+          <t>Stog'er Tight</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>012I/06/Zn 005</t>
+          <t>012H/16/Au 041</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>50.31067</v>
+        <v>49.9661</v>
       </c>
       <c r="W79" t="n">
-        <v>-57.44799</v>
+        <v>-56.07765</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-C Zone</t>
+          <t>Daniel's Harbour Mine-B Zone</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>012I/06/Zn 003</t>
+          <t>012I/06/Zn 002</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6241,14 +6241,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>50.30435</v>
+        <v>50.2975</v>
       </c>
       <c r="W80" t="n">
-        <v>-57.45355</v>
+        <v>-57.45784</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-D Zone</t>
+          <t>Daniel's Harbour Mine-E Zone</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>012I/06/Zn 004</t>
+          <t>012I/06/Zn 005</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6313,14 +6313,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>50.30795</v>
+        <v>50.31067</v>
       </c>
       <c r="W81" t="n">
-        <v>-57.45218</v>
+        <v>-57.44799</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-B Zone</t>
+          <t>Daniel's Harbour Mine-C Zone</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>012I/06/Zn 002</t>
+          <t>012I/06/Zn 003</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6385,14 +6385,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>50.2975</v>
+        <v>50.30435</v>
       </c>
       <c r="W82" t="n">
-        <v>-57.45784</v>
+        <v>-57.45355</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
         </is>
       </c>
     </row>
@@ -6402,12 +6402,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-H Zone</t>
+          <t>Daniel's Harbour Mine-D Zone</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>012I/06/Zn 008</t>
+          <t>012I/06/Zn 004</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6457,14 +6457,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>50.29179</v>
+        <v>50.30795</v>
       </c>
       <c r="W83" t="n">
-        <v>-57.44599</v>
+        <v>-57.45218</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-G Zone</t>
+          <t>Pilley's Island Mine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>012I/06/Zn 007</t>
+          <t>002E/12/Cu 001</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6529,14 +6529,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>50.29448</v>
+        <v>49.50863</v>
       </c>
       <c r="W84" t="n">
-        <v>-57.44714</v>
+        <v>-55.71872</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-M Zone</t>
+          <t>AGS Vein</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>012I/06/Zn 012</t>
+          <t>001L/14/Fl 013</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc, Lead, Copper, Fluorine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6601,14 +6601,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>50.29514</v>
+        <v>46.91489</v>
       </c>
       <c r="W85" t="n">
-        <v>-57.44013</v>
+        <v>-55.48584</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
         </is>
       </c>
     </row>
@@ -6618,24 +6618,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Nugget Pond</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>002E/13/Au 001</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6673,14 +6673,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>49.45488</v>
+        <v>49.84502</v>
       </c>
       <c r="W86" t="n">
-        <v>-55.49811</v>
+        <v>-55.77536</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -6690,24 +6690,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stoneyhouse</t>
+          <t>Bishop North</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>001M/01/Cu 001</t>
+          <t>012B/08/Fe 001</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6745,14 +6745,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>47.0541</v>
+        <v>48.40317</v>
       </c>
       <c r="W87" t="n">
-        <v>-54.11056</v>
+        <v>-58.3315</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6762,24 +6762,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Indian Head Mine</t>
+          <t>Upper Drill Brook Mine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>012B/10/Fe 001</t>
+          <t>012B/09/Fe 002</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>48.52416</v>
+        <v>48.53533</v>
       </c>
       <c r="W88" t="n">
-        <v>-58.5148</v>
+        <v>-58.48601</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -6834,24 +6834,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tilt Cove/East Mine/Upper Dump</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>002E/13/Au 028</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Zinc, Gold</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>49.88512</v>
+        <v>48.5353</v>
       </c>
       <c r="W89" t="n">
-        <v>-55.62192</v>
+        <v>-58.48804</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -6906,12 +6906,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tilt Cove Mine</t>
+          <t>Betts Cove Mine</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>002E/13/Cu 001</t>
+          <t>002E/13/Cu 002</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Silver, Zinc, Copper</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>49.88214</v>
+        <v>49.81179</v>
       </c>
       <c r="W90" t="n">
-        <v>-55.62813</v>
+        <v>-55.80608</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Stewart Mine</t>
+          <t>Tilt Cove Mine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>002E/10/Au 001</t>
+          <t>002E/13/Cu 001</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Silver, Antimony, Copper, Zinc, Gold</t>
+          <t>Gold, Nickel, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>49.58065</v>
+        <v>49.88214</v>
       </c>
       <c r="W91" t="n">
-        <v>-54.85442</v>
+        <v>-55.62813</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7050,24 +7050,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Tilt Cove/East Mine/Upper Dump</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>002E/13/Au 028</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Silver, Nickel, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7105,14 +7105,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>48.5353</v>
+        <v>49.88512</v>
       </c>
       <c r="W92" t="n">
-        <v>-58.48804</v>
+        <v>-55.62192</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
         </is>
       </c>
     </row>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pine Cove</t>
+          <t>Cross Cove</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>012H/16/Au 023</t>
+          <t>002E/10/Sb 001</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>49.96066</v>
+        <v>49.57534</v>
       </c>
       <c r="W93" t="n">
-        <v>-56.13074</v>
+        <v>-54.86876</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
         </is>
       </c>
     </row>
@@ -7194,24 +7194,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bishop South</t>
+          <t>Stoneyhouse</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>012B/08/Fe 002</t>
+          <t>001M/01/Cu 001</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7249,14 +7249,14 @@
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>48.39996</v>
+        <v>47.0541</v>
       </c>
       <c r="W94" t="n">
-        <v>-58.33683</v>
+        <v>-54.11056</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7266,24 +7266,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bishop North</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>012B/08/Fe 001</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7321,14 +7321,14 @@
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>48.40317</v>
+        <v>49.45488</v>
       </c>
       <c r="W95" t="n">
-        <v>-58.3315</v>
+        <v>-55.49811</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -7338,24 +7338,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Upper Drill Brook Mine</t>
+          <t>Argyle</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>012B/09/Fe 002</t>
+          <t>012H/16/Au 083</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7393,14 +7393,14 @@
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>48.53533</v>
+        <v>49.97838</v>
       </c>
       <c r="W96" t="n">
-        <v>-58.48601</v>
+        <v>-56.05952</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
         </is>
       </c>
     </row>
@@ -7410,24 +7410,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Turk's Gut</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>001N/11/Cu 001</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7465,14 +7465,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>47.50226</v>
+        <v>47.4438</v>
       </c>
       <c r="W97" t="n">
-        <v>-53.20074</v>
+        <v>-54.4169</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cross Cove</t>
+          <t>Turk's Gut</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>002E/10/Sb 001</t>
+          <t>001N/11/Cu 001</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>49.57534</v>
+        <v>47.50226</v>
       </c>
       <c r="W98" t="n">
-        <v>-54.86876</v>
+        <v>-53.20074</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Daniel's Harbour Mine-A Zone</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>012I/06/Zn 001</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>47.4438</v>
+        <v>50.29576</v>
       </c>
       <c r="W99" t="n">
-        <v>-54.4169</v>
+        <v>-57.46512</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -7626,24 +7626,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>La Manche</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001N/12/Pb 001</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Silver, Barium, Lead</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>35</v>
       </c>
       <c r="V100" t="n">
-        <v>47.4063</v>
+        <v>47.6889</v>
       </c>
       <c r="W100" t="n">
-        <v>-52.70699</v>
+        <v>-53.93901</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -7770,24 +7770,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Miles Cove Mine</t>
+          <t>Hope Brook</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>002E/12/Cu 012</t>
+          <t>011O/09/Au 003</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7825,14 +7825,14 @@
         <v>35</v>
       </c>
       <c r="V102" t="n">
-        <v>49.53936</v>
+        <v>47.73806</v>
       </c>
       <c r="W102" t="n">
-        <v>-55.79062</v>
+        <v>-58.09531</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Pilley's Island Mine</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>002E/12/Cu 001</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>35</v>
       </c>
       <c r="V103" t="n">
-        <v>49.50863</v>
+        <v>52.961</v>
       </c>
       <c r="W103" t="n">
-        <v>-55.71872</v>
+        <v>-66.81446</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -7914,24 +7914,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hope Brook</t>
+          <t>Ming West</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>011O/09/Au 003</t>
+          <t>012H/16/Cu 029</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7960,23 +7960,23 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T104" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U104" t="n">
         <v>35</v>
       </c>
       <c r="V104" t="n">
-        <v>47.73806</v>
+        <v>49.9148</v>
       </c>
       <c r="W104" t="n">
-        <v>-58.09531</v>
+        <v>-56.08996</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
         </is>
       </c>
     </row>
@@ -7986,24 +7986,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>La Manche</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>001N/12/Pb 001</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Barium, Lead</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8041,14 +8041,14 @@
         <v>35</v>
       </c>
       <c r="V105" t="n">
-        <v>47.6889</v>
+        <v>49.19579</v>
       </c>
       <c r="W105" t="n">
-        <v>-53.93901</v>
+        <v>-57.84974</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -8058,24 +8058,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sleepy Hollow</t>
+          <t>Daniel's Harbour Mine-Q Zone</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>002E/12/Cu 031</t>
+          <t>012I/06/Zn 016</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8113,14 +8113,14 @@
         <v>35</v>
       </c>
       <c r="V106" t="n">
-        <v>49.59747</v>
+        <v>50.29741</v>
       </c>
       <c r="W106" t="n">
-        <v>-55.94735</v>
+        <v>-57.48016</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
         </is>
       </c>
     </row>
@@ -8130,24 +8130,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ming West</t>
+          <t>Browning Mine</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>012H/16/Cu 029</t>
+          <t>012H/10/Au 001</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8176,23 +8176,23 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T107" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U107" t="n">
         <v>35</v>
       </c>
       <c r="V107" t="n">
-        <v>49.9148</v>
+        <v>49.71799</v>
       </c>
       <c r="W107" t="n">
-        <v>-56.08996</v>
+        <v>-56.92565</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -8202,24 +8202,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-A Zone</t>
+          <t>Pine Cove</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>012I/06/Zn 001</t>
+          <t>012H/16/Au 023</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8257,14 +8257,14 @@
         <v>35</v>
       </c>
       <c r="V108" t="n">
-        <v>50.29576</v>
+        <v>49.96066</v>
       </c>
       <c r="W108" t="n">
-        <v>-57.46512</v>
+        <v>-56.13074</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Argyle</t>
+          <t>Bishop South</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>012H/16/Au 083</t>
+          <t>012B/08/Fe 002</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>35</v>
       </c>
       <c r="V109" t="n">
-        <v>49.97838</v>
+        <v>48.39996</v>
       </c>
       <c r="W109" t="n">
-        <v>-56.05952</v>
+        <v>-58.33683</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -8346,24 +8346,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-K Zone</t>
+          <t>Daniel's Harbour Mine-F Zone</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>012I/06/Zn 010</t>
+          <t>012I/06/Zn 006</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>35</v>
       </c>
       <c r="V110" t="n">
-        <v>50.2935</v>
+        <v>50.29437</v>
       </c>
       <c r="W110" t="n">
-        <v>-57.46875</v>
+        <v>-57.45374</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
         </is>
       </c>
     </row>
@@ -8418,24 +8418,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Betts Cove Mine</t>
+          <t>Stewart Mine</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>002E/13/Cu 002</t>
+          <t>002E/10/Au 001</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Silver, Antimony, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>35</v>
       </c>
       <c r="V111" t="n">
-        <v>49.81179</v>
+        <v>49.58065</v>
       </c>
       <c r="W111" t="n">
-        <v>-55.80608</v>
+        <v>-54.85442</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -8490,24 +8490,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nugget Pond</t>
+          <t>Indian Head Mine</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>002E/13/Au 001</t>
+          <t>012B/10/Fe 001</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>35</v>
       </c>
       <c r="V112" t="n">
-        <v>49.84502</v>
+        <v>48.52416</v>
       </c>
       <c r="W112" t="n">
-        <v>-55.77536</v>
+        <v>-58.5148</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8562,24 +8562,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timmins No 8</t>
+          <t>Goethite Bay North</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>023J/14/Fe 026</t>
+          <t>023G/02/Fe 041</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8617,14 +8617,14 @@
         <v>31</v>
       </c>
       <c r="V113" t="n">
-        <v>54.89589</v>
+        <v>53.18717</v>
       </c>
       <c r="W113" t="n">
-        <v>-67.07944000000001</v>
+        <v>-66.74445</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
         </is>
       </c>
     </row>
@@ -8634,24 +8634,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timmins No 5</t>
+          <t>Ruth Lake No 2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>023J/14/Fe 024</t>
+          <t>023J/15/Fe 011</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>31</v>
       </c>
       <c r="V114" t="n">
-        <v>54.86384</v>
+        <v>54.79747</v>
       </c>
       <c r="W114" t="n">
-        <v>-67.09327</v>
+        <v>-66.87487</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mile 2</t>
+          <t>Block 103 - Greenbush Zone</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>023B/15/Fe 011</t>
+          <t>023J/14/Fe 043</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -8761,14 +8761,14 @@
         <v>31</v>
       </c>
       <c r="V115" t="n">
-        <v>52.97907</v>
+        <v>54.97234</v>
       </c>
       <c r="W115" t="n">
-        <v>-66.88907</v>
+        <v>-67.25158</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wabush No. 1</t>
+          <t>Elizabeth No. 2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>023B/15/Fe 002</t>
+          <t>023J/15/Fe 032</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>31</v>
       </c>
       <c r="V116" t="n">
-        <v>52.9599</v>
+        <v>54.77182</v>
       </c>
       <c r="W116" t="n">
-        <v>-66.9704</v>
+        <v>-66.88666000000001</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Julienne Lake</t>
+          <t>Lorraine No. 4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>023G/02/Fe 009</t>
+          <t>023G/02/Fe 008</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8905,14 +8905,14 @@
         <v>31</v>
       </c>
       <c r="V117" t="n">
-        <v>53.13733</v>
+        <v>53.08316</v>
       </c>
       <c r="W117" t="n">
-        <v>-66.78360000000001</v>
+        <v>-66.87726000000001</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Joyce Lake</t>
+          <t>Elizabeth No. 1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>023J/15/Fe 030</t>
+          <t>023J/15/Fe 031</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -8977,14 +8977,14 @@
         <v>31</v>
       </c>
       <c r="V118" t="n">
-        <v>54.8993</v>
+        <v>54.78743</v>
       </c>
       <c r="W118" t="n">
-        <v>-66.53366</v>
+        <v>-66.90081000000001</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
         </is>
       </c>
     </row>
@@ -8994,24 +8994,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Attikamagen Deposit</t>
+          <t>Wabush No. 7</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>023J/16/Fe 001</t>
+          <t>023G/02/Fe 007</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9049,14 +9049,14 @@
         <v>31</v>
       </c>
       <c r="V119" t="n">
-        <v>54.80989</v>
+        <v>53.02512</v>
       </c>
       <c r="W119" t="n">
-        <v>-66.47658</v>
+        <v>-66.90531</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Goethite Bay North</t>
+          <t>Knob Lake 1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>023G/02/Fe 041</t>
+          <t>023J/15/Fe 013</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9121,14 +9121,14 @@
         <v>31</v>
       </c>
       <c r="V120" t="n">
-        <v>53.18717</v>
+        <v>54.7766</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.74445</v>
+        <v>-66.80589000000001</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
         </is>
       </c>
     </row>
@@ -9138,24 +9138,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Wabush No. 6</t>
+          <t>Howse</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>023G/02/Fe 006</t>
+          <t>023J/14/Fe 028</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9193,14 +9193,14 @@
         <v>31</v>
       </c>
       <c r="V121" t="n">
-        <v>53.01798</v>
+        <v>54.9089</v>
       </c>
       <c r="W121" t="n">
-        <v>-66.89297999999999</v>
+        <v>-67.14075</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -9210,24 +9210,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Canning</t>
+          <t>Ferriman No 7</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>023B/15/Fe 007</t>
+          <t>023J/15/Fe 014</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9265,14 +9265,14 @@
         <v>31</v>
       </c>
       <c r="V122" t="n">
-        <v>52.9469</v>
+        <v>54.81281</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.95802999999999</v>
+        <v>-66.94580999999999</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
         </is>
       </c>
     </row>
@@ -9282,24 +9282,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timmins No 7</t>
+          <t>Duley No. 1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>023J/14/Fe 025</t>
+          <t>023B/14/Fe 001</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9337,14 +9337,14 @@
         <v>31</v>
       </c>
       <c r="V123" t="n">
-        <v>54.89246</v>
+        <v>52.87237</v>
       </c>
       <c r="W123" t="n">
-        <v>-67.07259000000001</v>
+        <v>-67.05874</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ferriman No 7</t>
+          <t>Kivivic No 3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>023J/15/Fe 014</t>
+          <t>023O/03/Fe 003</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9409,14 +9409,14 @@
         <v>31</v>
       </c>
       <c r="V124" t="n">
-        <v>54.81281</v>
+        <v>55.05061</v>
       </c>
       <c r="W124" t="n">
-        <v>-66.94580999999999</v>
+        <v>-67.26130000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -9426,24 +9426,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Wabush No. 4</t>
+          <t>Sawyer Lake</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>023B/15/Fe 004</t>
+          <t>023I/05/Fe 001</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9481,14 +9481,14 @@
         <v>31</v>
       </c>
       <c r="V125" t="n">
-        <v>52.95373</v>
+        <v>54.45206</v>
       </c>
       <c r="W125" t="n">
-        <v>-66.94092000000001</v>
+        <v>-65.98627</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9498,24 +9498,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Block 103 - Greenbush Zone</t>
+          <t>Ruth Lake No 8</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>023J/14/Fe 043</t>
+          <t>023J/15/Fe 009</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9553,14 +9553,14 @@
         <v>31</v>
       </c>
       <c r="V126" t="n">
-        <v>54.97234</v>
+        <v>54.78104</v>
       </c>
       <c r="W126" t="n">
-        <v>-67.25158</v>
+        <v>-66.86577</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9570,12 +9570,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Howells River North</t>
+          <t>Attikamagen Deposit</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>023O/03/Fe 007</t>
+          <t>023J/16/Fe 001</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -9625,14 +9625,14 @@
         <v>31</v>
       </c>
       <c r="V127" t="n">
-        <v>55.01179</v>
+        <v>54.80989</v>
       </c>
       <c r="W127" t="n">
-        <v>-67.37214</v>
+        <v>-66.47658</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Duley No. 2</t>
+          <t>Joyce Lake</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>023B/15/Fe 008</t>
+          <t>023J/15/Fe 030</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>31</v>
       </c>
       <c r="V128" t="n">
-        <v>52.87214</v>
+        <v>54.8993</v>
       </c>
       <c r="W128" t="n">
-        <v>-66.99635000000001</v>
+        <v>-66.53366</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
         </is>
       </c>
     </row>
@@ -9714,12 +9714,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Elizabeth No. 1</t>
+          <t>Howells Lake</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>023J/15/Fe 031</t>
+          <t>023O/03/Fe 006</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -9769,14 +9769,14 @@
         <v>31</v>
       </c>
       <c r="V129" t="n">
-        <v>54.78743</v>
+        <v>55.06346</v>
       </c>
       <c r="W129" t="n">
-        <v>-66.90081000000001</v>
+        <v>-67.40528</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9786,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Howells Lake</t>
+          <t>Howells River North</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>023O/03/Fe 006</t>
+          <t>023O/03/Fe 007</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9841,14 +9841,14 @@
         <v>31</v>
       </c>
       <c r="V130" t="n">
-        <v>55.06346</v>
+        <v>55.01179</v>
       </c>
       <c r="W130" t="n">
-        <v>-67.40528</v>
+        <v>-67.37214</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Wabush No. 7</t>
+          <t>Wabush No. 6</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>023G/02/Fe 007</t>
+          <t>023G/02/Fe 006</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9913,14 +9913,14 @@
         <v>31</v>
       </c>
       <c r="V131" t="n">
-        <v>53.02512</v>
+        <v>53.01798</v>
       </c>
       <c r="W131" t="n">
-        <v>-66.90531</v>
+        <v>-66.89297999999999</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lorraine No. 4</t>
+          <t>Julienne Lake</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>023G/02/Fe 008</t>
+          <t>023G/02/Fe 009</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9985,14 +9985,14 @@
         <v>31</v>
       </c>
       <c r="V132" t="n">
-        <v>53.08316</v>
+        <v>53.13733</v>
       </c>
       <c r="W132" t="n">
-        <v>-66.87726000000001</v>
+        <v>-66.78360000000001</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wabush No. 8</t>
+          <t>Duley No. 2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>023B/15/Fe 005</t>
+          <t>023B/15/Fe 008</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -10057,14 +10057,14 @@
         <v>31</v>
       </c>
       <c r="V133" t="n">
-        <v>52.9791</v>
+        <v>52.87214</v>
       </c>
       <c r="W133" t="n">
-        <v>-66.90604999999999</v>
+        <v>-66.99635000000001</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Houston 2</t>
+          <t>Canning</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>023J/10/Fe 009</t>
+          <t>023B/15/Fe 007</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10129,14 +10129,14 @@
         <v>31</v>
       </c>
       <c r="V134" t="n">
-        <v>54.71245</v>
+        <v>52.9469</v>
       </c>
       <c r="W134" t="n">
-        <v>-66.66257</v>
+        <v>-66.95802999999999</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10146,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Houston 3</t>
+          <t>Timmins No 7</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>023J/10/Fe 010</t>
+          <t>023J/14/Fe 025</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10201,14 +10201,14 @@
         <v>31</v>
       </c>
       <c r="V135" t="n">
-        <v>54.69887</v>
+        <v>54.89246</v>
       </c>
       <c r="W135" t="n">
-        <v>-66.64483</v>
+        <v>-67.07259000000001</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
         </is>
       </c>
     </row>
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kivivic No 3</t>
+          <t>Mile 2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>023O/03/Fe 003</t>
+          <t>023B/15/Fe 011</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -10273,14 +10273,14 @@
         <v>31</v>
       </c>
       <c r="V136" t="n">
-        <v>55.05061</v>
+        <v>52.97907</v>
       </c>
       <c r="W136" t="n">
-        <v>-67.26130000000001</v>
+        <v>-66.88907</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Kivivic No 4</t>
+          <t>Wabush No. 8</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>023O/03/Fe 004</t>
+          <t>023B/15/Fe 005</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>31</v>
       </c>
       <c r="V137" t="n">
-        <v>55.04865</v>
+        <v>52.9791</v>
       </c>
       <c r="W137" t="n">
-        <v>-67.28158000000001</v>
+        <v>-66.90604999999999</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10362,24 +10362,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kivivic No 5</t>
+          <t>Wabush No. 4</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>023O/03/Fe 005</t>
+          <t>023B/15/Fe 004</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>31</v>
       </c>
       <c r="V138" t="n">
-        <v>55.06664</v>
+        <v>52.95373</v>
       </c>
       <c r="W138" t="n">
-        <v>-67.29537000000001</v>
+        <v>-66.94092000000001</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -10434,24 +10434,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Duley No. 1</t>
+          <t>Timmins No 8</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>023B/14/Fe 001</t>
+          <t>023J/14/Fe 026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>31</v>
       </c>
       <c r="V139" t="n">
-        <v>52.87237</v>
+        <v>54.89589</v>
       </c>
       <c r="W139" t="n">
-        <v>-67.05874</v>
+        <v>-67.07944000000001</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
         </is>
       </c>
     </row>
@@ -10506,24 +10506,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mills Lake</t>
+          <t>Timmins No 5</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>023B/14/Fe 002</t>
+          <t>023J/14/Fe 024</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>31</v>
       </c>
       <c r="V140" t="n">
-        <v>52.79808</v>
+        <v>54.86384</v>
       </c>
       <c r="W140" t="n">
-        <v>-67.00413</v>
+        <v>-67.09327</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
         </is>
       </c>
     </row>
@@ -10578,24 +10578,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Howells River West Zone A</t>
+          <t>Sheps Lake</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>023J/14/Fe 001</t>
+          <t>023J/11/Fe 001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10633,14 +10633,14 @@
         <v>31</v>
       </c>
       <c r="V141" t="n">
-        <v>54.90958</v>
+        <v>54.73475</v>
       </c>
       <c r="W141" t="n">
-        <v>-67.26052</v>
+        <v>-67.06362</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Houston 1</t>
+          <t>Neal 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>023J/10/Fe 008</t>
+          <t>023B/14/Fe 008</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10705,14 +10705,14 @@
         <v>31</v>
       </c>
       <c r="V142" t="n">
-        <v>54.70748</v>
+        <v>52.95013</v>
       </c>
       <c r="W142" t="n">
-        <v>-66.65615</v>
+        <v>-67.15191</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10722,24 +10722,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Redmond 5</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>023J/10/Fe 005</t>
+          <t>023B/14/Fe 028</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10777,14 +10777,14 @@
         <v>31</v>
       </c>
       <c r="V143" t="n">
-        <v>54.70854</v>
+        <v>52.94868</v>
       </c>
       <c r="W143" t="n">
-        <v>-66.79174999999999</v>
+        <v>-67.01146</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sawyer Lake</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>023I/05/Fe 001</t>
+          <t>023B/14/Fe 020</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>31</v>
       </c>
       <c r="V144" t="n">
-        <v>54.45206</v>
+        <v>52.83351</v>
       </c>
       <c r="W144" t="n">
-        <v>-65.98627</v>
+        <v>-67.0311</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
         </is>
       </c>
     </row>
@@ -10938,24 +10938,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Howells River West Zone A</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>023B/14/Fe 020</t>
+          <t>023J/14/Fe 001</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>31</v>
       </c>
       <c r="V146" t="n">
-        <v>52.83351</v>
+        <v>54.90958</v>
       </c>
       <c r="W146" t="n">
-        <v>-67.0311</v>
+        <v>-67.26052</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -11010,24 +11010,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Wabush No. 1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>023B/14/Fe 028</t>
+          <t>023B/15/Fe 002</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11065,14 +11065,14 @@
         <v>31</v>
       </c>
       <c r="V147" t="n">
-        <v>52.94868</v>
+        <v>52.9599</v>
       </c>
       <c r="W147" t="n">
-        <v>-67.01146</v>
+        <v>-66.9704</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sheps Lake</t>
+          <t>Redmond 5</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>023J/11/Fe 001</t>
+          <t>023J/10/Fe 005</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11137,14 +11137,14 @@
         <v>31</v>
       </c>
       <c r="V148" t="n">
-        <v>54.73475</v>
+        <v>54.70854</v>
       </c>
       <c r="W148" t="n">
-        <v>-67.06362</v>
+        <v>-66.79174999999999</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Neal 1</t>
+          <t>Mills Lake</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>023B/14/Fe 008</t>
+          <t>023B/14/Fe 002</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -11209,14 +11209,14 @@
         <v>31</v>
       </c>
       <c r="V149" t="n">
-        <v>52.95013</v>
+        <v>52.79808</v>
       </c>
       <c r="W149" t="n">
-        <v>-67.15191</v>
+        <v>-67.00413</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ruth Lake No 8</t>
+          <t>Houston 1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>023J/15/Fe 009</t>
+          <t>023J/10/Fe 008</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11281,14 +11281,14 @@
         <v>31</v>
       </c>
       <c r="V150" t="n">
-        <v>54.78104</v>
+        <v>54.70748</v>
       </c>
       <c r="W150" t="n">
-        <v>-66.86577</v>
+        <v>-66.65615</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ruth Lake No 2</t>
+          <t>Houston 3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>023J/15/Fe 011</t>
+          <t>023J/10/Fe 010</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11353,14 +11353,14 @@
         <v>31</v>
       </c>
       <c r="V151" t="n">
-        <v>54.79747</v>
+        <v>54.69887</v>
       </c>
       <c r="W151" t="n">
-        <v>-66.87487</v>
+        <v>-66.64483</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -11370,24 +11370,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Elizabeth No. 2</t>
+          <t>Houston 2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>023J/15/Fe 032</t>
+          <t>023J/10/Fe 009</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11425,14 +11425,14 @@
         <v>31</v>
       </c>
       <c r="V152" t="n">
-        <v>54.77182</v>
+        <v>54.71245</v>
       </c>
       <c r="W152" t="n">
-        <v>-66.88666000000001</v>
+        <v>-66.66257</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -11442,24 +11442,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Knob Lake 1</t>
+          <t>Kivivic No 4</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>023J/15/Fe 013</t>
+          <t>023O/03/Fe 004</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11497,14 +11497,14 @@
         <v>31</v>
       </c>
       <c r="V153" t="n">
-        <v>54.7766</v>
+        <v>55.04865</v>
       </c>
       <c r="W153" t="n">
-        <v>-66.80589000000001</v>
+        <v>-67.28158000000001</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11514,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Howse</t>
+          <t>Kivivic No 5</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>023J/14/Fe 028</t>
+          <t>023O/03/Fe 005</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11569,14 +11569,14 @@
         <v>31</v>
       </c>
       <c r="V154" t="n">
-        <v>54.9089</v>
+        <v>55.06664</v>
       </c>
       <c r="W154" t="n">
-        <v>-67.14075</v>
+        <v>-67.29537000000001</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mine Hill</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>001N/07/Pph004</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pyrophyllite</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11641,14 +11641,14 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>47.48</v>
+        <v>53.40462</v>
       </c>
       <c r="W155" t="n">
-        <v>-52.95479</v>
+        <v>-65.08734</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Iron Springs Mine</t>
+          <t>Parsons Pond No 3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>001L/14/Fl 008</t>
+          <t>012H/13/Btm003</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11785,14 +11785,14 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>46.88701</v>
+        <v>49.97912</v>
       </c>
       <c r="W157" t="n">
-        <v>-55.421</v>
+        <v>-57.64547</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Parsons Pond No 2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>012H/13/Btm002</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11857,14 +11857,14 @@
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>48.56074</v>
+        <v>49.97421</v>
       </c>
       <c r="W158" t="n">
-        <v>-58.8161</v>
+        <v>-57.60538</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hares Ears Vein</t>
+          <t>Parsons Pond No 4</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>001L/14/Fl 007</t>
+          <t>012H/13/Btm004</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11920,23 +11920,23 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T159" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U159" t="n">
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>46.88814</v>
+        <v>49.99787</v>
       </c>
       <c r="W159" t="n">
-        <v>-55.41178</v>
+        <v>-57.63818</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Collier Point</t>
+          <t>Middle Arm Brook</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>001N/12/Ba 001</t>
+          <t>012H/16/Vir001</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Barium</t>
+          <t>Virginite</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12001,14 +12001,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>47.59126</v>
+        <v>49.80048</v>
       </c>
       <c r="W160" t="n">
-        <v>-53.69011</v>
+        <v>-56.31995</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Lord &amp; Lady Gulch Mine</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>001L/14/Fl 005</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12073,14 +12073,14 @@
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>48.30663</v>
+        <v>46.87554</v>
       </c>
       <c r="W161" t="n">
-        <v>-58.68165</v>
+        <v>-55.4111</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Parsons Pond Cart Track</t>
+          <t>Baie Verte Mine</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>012I/04/Btm001</t>
+          <t>012H/16/Asb008</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Oil Shale</t>
+          <t>Magnesium, Asbestos</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12136,23 +12136,23 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T162" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U162" t="n">
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>50.00564</v>
+        <v>49.97974</v>
       </c>
       <c r="W162" t="n">
-        <v>-57.63187</v>
+        <v>-56.19399</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
         </is>
       </c>
     </row>
@@ -12162,12 +12162,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Baie Verte Mine</t>
+          <t>Black Duck Mine</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>012H/16/Asb008</t>
+          <t>001L/14/Fl 010</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Magnesium, Asbestos</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12217,14 +12217,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>49.97974</v>
+        <v>46.93201</v>
       </c>
       <c r="W163" t="n">
-        <v>-56.19399</v>
+        <v>-55.38881</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Borney Lake</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>002D/14/Stn001</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12289,14 +12289,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>48.9264</v>
+        <v>48.30663</v>
       </c>
       <c r="W164" t="n">
-        <v>-55.44535</v>
+        <v>-58.68165</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Doctors Pond Veins</t>
+          <t>Southern Cross Veins</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>001L/14/Fl 036</t>
+          <t>001L/14/Fl 020</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12361,14 +12361,14 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>46.92769</v>
+        <v>46.88974</v>
       </c>
       <c r="W165" t="n">
-        <v>-55.37593</v>
+        <v>-55.42958</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Parsons Pond No 3</t>
+          <t>Tarefare Mine</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>012H/13/Btm003</t>
+          <t>001L/14/Fl 006</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12433,14 +12433,14 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>49.97912</v>
+        <v>46.8912</v>
       </c>
       <c r="W166" t="n">
-        <v>-57.64547</v>
+        <v>-55.43112</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tarefare Mine</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>001L/14/Fl 006</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12505,14 +12505,14 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>46.8912</v>
+        <v>53.469</v>
       </c>
       <c r="W167" t="n">
-        <v>-55.43112</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -12522,12 +12522,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Blue Beach Mine</t>
+          <t>Mine Hill</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>001L/14/Fl 001</t>
+          <t>001N/07/Pph004</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Pyrophyllite</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12577,14 +12577,14 @@
         <v>30</v>
       </c>
       <c r="V168" t="n">
-        <v>46.91553</v>
+        <v>47.48</v>
       </c>
       <c r="W168" t="n">
-        <v>-55.40729</v>
+        <v>-52.95479</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
         </is>
       </c>
     </row>
@@ -12594,12 +12594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Black Duck Mine</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>001L/14/Fl 010</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12649,14 +12649,14 @@
         <v>30</v>
       </c>
       <c r="V169" t="n">
-        <v>46.93201</v>
+        <v>48.56074</v>
       </c>
       <c r="W169" t="n">
-        <v>-55.38881</v>
+        <v>-58.8161</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Southern Cross Veins</t>
+          <t>Collier Point</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>001L/14/Fl 020</t>
+          <t>001N/12/Ba 001</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Barium</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12721,14 +12721,14 @@
         <v>30</v>
       </c>
       <c r="V170" t="n">
-        <v>46.88974</v>
+        <v>47.59126</v>
       </c>
       <c r="W170" t="n">
-        <v>-55.42958</v>
+        <v>-53.69011</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
         </is>
       </c>
     </row>
@@ -12738,12 +12738,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Lord &amp; Lady Gulch Mine</t>
+          <t>Parsons Pond Cart Track</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>001L/14/Fl 005</t>
+          <t>012I/04/Btm001</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil Shale</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12784,23 +12784,23 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T171" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U171" t="n">
         <v>30</v>
       </c>
       <c r="V171" t="n">
-        <v>46.87554</v>
+        <v>50.00564</v>
       </c>
       <c r="W171" t="n">
-        <v>-55.4111</v>
+        <v>-57.63187</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Scrape Vein</t>
+          <t>Doctors Pond Veins</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>001L/14/Fl 035</t>
+          <t>001L/14/Fl 036</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -12865,14 +12865,14 @@
         <v>30</v>
       </c>
       <c r="V172" t="n">
-        <v>46.92547</v>
+        <v>46.92769</v>
       </c>
       <c r="W172" t="n">
-        <v>-55.37193</v>
+        <v>-55.37593</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Little Salt Cove</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>001L/14/Fl 016</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12937,14 +12937,14 @@
         <v>30</v>
       </c>
       <c r="V173" t="n">
-        <v>53.40462</v>
+        <v>46.87654</v>
       </c>
       <c r="W173" t="n">
-        <v>-65.08734</v>
+        <v>-55.43141</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12954,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Scrape Vein</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>001L/14/Fl 035</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13009,14 +13009,14 @@
         <v>30</v>
       </c>
       <c r="V174" t="n">
-        <v>48.50411</v>
+        <v>46.92547</v>
       </c>
       <c r="W174" t="n">
-        <v>-58.53451</v>
+        <v>-55.37193</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Bluff Head Mine</t>
+          <t>Director Mine</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>012B/15/Cr 001</t>
+          <t>001L/14/Fl 009</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Asbestos, Chromium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13081,14 +13081,14 @@
         <v>30</v>
       </c>
       <c r="V175" t="n">
-        <v>48.77717</v>
+        <v>46.90681</v>
       </c>
       <c r="W175" t="n">
-        <v>-58.59931</v>
+        <v>-55.42107</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
         </is>
       </c>
     </row>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Iron Springs Mine</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>001L/14/Fl 008</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13153,14 +13153,14 @@
         <v>30</v>
       </c>
       <c r="V176" t="n">
-        <v>53.469</v>
+        <v>46.88701</v>
       </c>
       <c r="W176" t="n">
-        <v>-64.91218000000001</v>
+        <v>-55.421</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Director Mine</t>
+          <t>Borney Lake</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>001L/14/Fl 009</t>
+          <t>002D/14/Stn001</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13225,14 +13225,14 @@
         <v>30</v>
       </c>
       <c r="V177" t="n">
-        <v>46.90681</v>
+        <v>48.9264</v>
       </c>
       <c r="W177" t="n">
-        <v>-55.42107</v>
+        <v>-55.44535</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Little Salt Cove</t>
+          <t>Bluff Head Mine</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>001L/14/Fl 016</t>
+          <t>012B/15/Cr 001</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Asbestos, Chromium</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13297,14 +13297,14 @@
         <v>30</v>
       </c>
       <c r="V178" t="n">
-        <v>46.87654</v>
+        <v>48.77717</v>
       </c>
       <c r="W178" t="n">
-        <v>-55.43141</v>
+        <v>-58.59931</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Middle Arm Brook</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>012H/16/Vir001</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Virginite</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13441,14 +13441,14 @@
         <v>30</v>
       </c>
       <c r="V180" t="n">
-        <v>49.80048</v>
+        <v>48.50411</v>
       </c>
       <c r="W180" t="n">
-        <v>-56.31995</v>
+        <v>-58.53451</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13458,12 +13458,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Parsons Pond No 2</t>
+          <t>Blue Beach Mine</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>012H/13/Btm002</t>
+          <t>001L/14/Fl 001</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13513,14 +13513,14 @@
         <v>30</v>
       </c>
       <c r="V181" t="n">
-        <v>49.97421</v>
+        <v>46.91553</v>
       </c>
       <c r="W181" t="n">
-        <v>-57.60538</v>
+        <v>-55.40729</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
         </is>
       </c>
     </row>
@@ -13530,12 +13530,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Parsons Pond No 1</t>
+          <t>Hares Ears Vein</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>012H/13/Btm001</t>
+          <t>001L/14/Fl 007</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13576,23 +13576,23 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T182" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U182" t="n">
         <v>30</v>
       </c>
       <c r="V182" t="n">
-        <v>49.99228</v>
+        <v>46.88814</v>
       </c>
       <c r="W182" t="n">
-        <v>-57.58928</v>
+        <v>-55.41178</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Parsons Pond No 4</t>
+          <t>Parsons Pond No 1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>012H/13/Btm004</t>
+          <t>012H/13/Btm001</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13648,23 +13648,23 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T183" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U183" t="n">
         <v>30</v>
       </c>
       <c r="V183" t="n">
-        <v>49.99787</v>
+        <v>49.99228</v>
       </c>
       <c r="W183" t="n">
-        <v>-57.63818</v>
+        <v>-57.58928</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Grey Copper Mine</t>
+          <t>Little Bay Mine</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>002E/11/Cu 001</t>
+          <t>002E/12/Cu 030</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Iron, Copper</t>
+          <t>Iron, Gold, Copper</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13729,14 +13729,14 @@
         <v>26</v>
       </c>
       <c r="V184" t="n">
-        <v>49.5173</v>
+        <v>49.5961</v>
       </c>
       <c r="W184" t="n">
-        <v>-55.2721</v>
+        <v>-55.94531</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Scotia Formation</t>
+          <t>Fleming No 3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>001N/10/Fe 002</t>
+          <t>023J/14/Fe 022</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13801,14 +13801,14 @@
         <v>26</v>
       </c>
       <c r="V185" t="n">
-        <v>47.64169</v>
+        <v>54.85836</v>
       </c>
       <c r="W185" t="n">
-        <v>-52.97639</v>
+        <v>-67.03167999999999</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Gull Island Formation</t>
+          <t>Timmins No 2</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>001N/10/Fe 003</t>
+          <t>023J/14/Fe 019</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -13873,14 +13873,14 @@
         <v>26</v>
       </c>
       <c r="V186" t="n">
-        <v>47.65193</v>
+        <v>54.89421</v>
       </c>
       <c r="W186" t="n">
-        <v>-52.95654</v>
+        <v>-67.08716</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Redmond No 2</t>
+          <t>Timmins No 4</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>023J/10/Fe 002</t>
+          <t>023J/14/Fe 023</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13945,14 +13945,14 @@
         <v>26</v>
       </c>
       <c r="V187" t="n">
-        <v>54.69738</v>
+        <v>54.89884</v>
       </c>
       <c r="W187" t="n">
-        <v>-66.77224</v>
+        <v>-67.10881000000001</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
         </is>
       </c>
     </row>
@@ -13962,24 +13962,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Little Bay Mine</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>002E/12/Cu 030</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Iron, Gold, Copper</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14017,14 +14017,14 @@
         <v>26</v>
       </c>
       <c r="V188" t="n">
-        <v>49.5961</v>
+        <v>47.53392</v>
       </c>
       <c r="W188" t="n">
-        <v>-55.94531</v>
+        <v>-53.18293</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -14034,24 +14034,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Dominion Formation</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>001N/10/Fe 001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14089,14 +14089,14 @@
         <v>26</v>
       </c>
       <c r="V189" t="n">
-        <v>49.50376</v>
+        <v>47.64164</v>
       </c>
       <c r="W189" t="n">
-        <v>-55.21553</v>
+        <v>-52.95309</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14106,24 +14106,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Redmond No 2</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>023J/10/Fe 002</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14161,14 +14161,14 @@
         <v>26</v>
       </c>
       <c r="V190" t="n">
-        <v>47.53392</v>
+        <v>54.69738</v>
       </c>
       <c r="W190" t="n">
-        <v>-53.18293</v>
+        <v>-66.77224</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dominion Formation</t>
+          <t>Gull Island Formation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>001N/10/Fe 001</t>
+          <t>001N/10/Fe 003</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -14233,14 +14233,14 @@
         <v>26</v>
       </c>
       <c r="V191" t="n">
-        <v>47.64164</v>
+        <v>47.65193</v>
       </c>
       <c r="W191" t="n">
-        <v>-52.95309</v>
+        <v>-52.95654</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -14250,12 +14250,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cliff Mine</t>
+          <t>Scotia Formation</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>012B/09/Fe 001</t>
+          <t>001N/10/Fe 002</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -14305,14 +14305,14 @@
         <v>26</v>
       </c>
       <c r="V192" t="n">
-        <v>48.54434</v>
+        <v>47.64169</v>
       </c>
       <c r="W192" t="n">
-        <v>-58.49915</v>
+        <v>-52.97639</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Skindles Mine</t>
+          <t>Timmins No 1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>012B/09/Fe 004</t>
+          <t>023J/14/Fe 018</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14377,14 +14377,14 @@
         <v>26</v>
       </c>
       <c r="V193" t="n">
-        <v>48.54069</v>
+        <v>54.88449</v>
       </c>
       <c r="W193" t="n">
-        <v>-58.48888</v>
+        <v>-67.08575</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
         </is>
       </c>
     </row>
@@ -14394,24 +14394,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Timmins No 6</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>023J/15/Fe 010</t>
+          <t>023J/14/Fe 021</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14449,14 +14449,14 @@
         <v>26</v>
       </c>
       <c r="V194" t="n">
-        <v>54.77437</v>
+        <v>54.90148</v>
       </c>
       <c r="W194" t="n">
-        <v>-66.82881</v>
+        <v>-67.09757999999999</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14466,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ruth Lake No 7</t>
+          <t>Skindles Mine</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>023J/15/Fe 006</t>
+          <t>012B/09/Fe 004</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
         <v>26</v>
       </c>
       <c r="V195" t="n">
-        <v>54.80557</v>
+        <v>48.54069</v>
       </c>
       <c r="W195" t="n">
-        <v>-66.90618000000001</v>
+        <v>-58.48888</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14538,24 +14538,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Ruth Lake No 5</t>
+          <t>Cliff Mine</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>023J/15/Fe 007</t>
+          <t>012B/09/Fe 001</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14593,14 +14593,14 @@
         <v>26</v>
       </c>
       <c r="V196" t="n">
-        <v>54.80503</v>
+        <v>48.54434</v>
       </c>
       <c r="W196" t="n">
-        <v>-66.88023</v>
+        <v>-58.49915</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14610,24 +14610,24 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ruth Lake No 6</t>
+          <t>Grey Copper Mine</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>023J/15/Fe 008</t>
+          <t>002E/11/Cu 001</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron, Copper</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14665,14 +14665,14 @@
         <v>26</v>
       </c>
       <c r="V197" t="n">
-        <v>54.80104</v>
+        <v>49.5173</v>
       </c>
       <c r="W197" t="n">
-        <v>-66.87327999999999</v>
+        <v>-55.2721</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -14682,24 +14682,24 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ruth Lake No 9</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>023J/15/Fe 005</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14737,14 +14737,14 @@
         <v>26</v>
       </c>
       <c r="V198" t="n">
-        <v>54.80033</v>
+        <v>49.50376</v>
       </c>
       <c r="W198" t="n">
-        <v>-66.89447</v>
+        <v>-55.21553</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14754,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ruth Lake No 1</t>
+          <t>Smallwood Mine</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>023J/15/Fe 002</t>
+          <t>023G/02/Fe 001</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14809,14 +14809,14 @@
         <v>26</v>
       </c>
       <c r="V199" t="n">
-        <v>54.79145</v>
+        <v>53.03718</v>
       </c>
       <c r="W199" t="n">
-        <v>-66.85449</v>
+        <v>-66.93694000000001</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14826,24 +14826,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Wishart No 1 (Wishart Mine)</t>
+          <t>Wishart No 2 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>023J/15/Fe 003</t>
+          <t>023J/15/Fe 004</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14881,14 +14881,14 @@
         <v>26</v>
       </c>
       <c r="V200" t="n">
-        <v>54.76166</v>
+        <v>54.7654</v>
       </c>
       <c r="W200" t="n">
-        <v>-66.88793</v>
+        <v>-66.9067</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Wishart No 2 (Wishart Mine)</t>
+          <t>Lorraine Mine</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>023J/15/Fe 004</t>
+          <t>023G/02/Fe 004</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14953,14 +14953,14 @@
         <v>26</v>
       </c>
       <c r="V201" t="n">
-        <v>54.7654</v>
+        <v>53.06833</v>
       </c>
       <c r="W201" t="n">
-        <v>-66.9067</v>
+        <v>-66.94949</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14970,12 +14970,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ruth Lake No 3</t>
+          <t>Ruth Lake No 1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>023J/15/Fe 001</t>
+          <t>023J/15/Fe 002</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
         <v>26</v>
       </c>
       <c r="V202" t="n">
-        <v>54.80404</v>
+        <v>54.79145</v>
       </c>
       <c r="W202" t="n">
-        <v>-66.87016</v>
+        <v>-66.85449</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -15042,12 +15042,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Smallwood Mine</t>
+          <t>Ruth Lake No 3</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>023G/02/Fe 001</t>
+          <t>023J/15/Fe 001</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -15097,14 +15097,14 @@
         <v>26</v>
       </c>
       <c r="V203" t="n">
-        <v>53.03718</v>
+        <v>54.80404</v>
       </c>
       <c r="W203" t="n">
-        <v>-66.93694000000001</v>
+        <v>-66.87016</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15114,24 +15114,24 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lorraine Mine</t>
+          <t>Wishart No 1 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>023G/02/Fe 004</t>
+          <t>023J/15/Fe 003</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -15169,14 +15169,14 @@
         <v>26</v>
       </c>
       <c r="V204" t="n">
-        <v>53.06833</v>
+        <v>54.76166</v>
       </c>
       <c r="W204" t="n">
-        <v>-66.94949</v>
+        <v>-66.88793</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Fleming No 3</t>
+          <t>Ruth Lake No 9</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>023J/14/Fe 022</t>
+          <t>023J/15/Fe 005</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -15241,14 +15241,14 @@
         <v>26</v>
       </c>
       <c r="V205" t="n">
-        <v>54.85836</v>
+        <v>54.80033</v>
       </c>
       <c r="W205" t="n">
-        <v>-67.03167999999999</v>
+        <v>-66.89447</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -15258,24 +15258,24 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Timmins No 1</t>
+          <t>Ruth Lake No 5</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>023J/14/Fe 018</t>
+          <t>023J/15/Fe 007</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -15313,14 +15313,14 @@
         <v>26</v>
       </c>
       <c r="V206" t="n">
-        <v>54.88449</v>
+        <v>54.80503</v>
       </c>
       <c r="W206" t="n">
-        <v>-67.08575</v>
+        <v>-66.88023</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15330,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timmins No 4</t>
+          <t>Ruth Lake No 7</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>023J/14/Fe 023</t>
+          <t>023J/15/Fe 006</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15385,14 +15385,14 @@
         <v>26</v>
       </c>
       <c r="V207" t="n">
-        <v>54.89884</v>
+        <v>54.80557</v>
       </c>
       <c r="W207" t="n">
-        <v>-67.10881000000001</v>
+        <v>-66.90618000000001</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -15402,24 +15402,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Timmins No 2</t>
+          <t>Ruth Lake No 6</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>023J/14/Fe 019</t>
+          <t>023J/15/Fe 008</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15457,14 +15457,14 @@
         <v>26</v>
       </c>
       <c r="V208" t="n">
-        <v>54.89421</v>
+        <v>54.80104</v>
       </c>
       <c r="W208" t="n">
-        <v>-67.08716</v>
+        <v>-66.87327999999999</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -15474,24 +15474,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Timmins No 6</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>023J/14/Fe 021</t>
+          <t>023J/15/Fe 010</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15529,14 +15529,14 @@
         <v>26</v>
       </c>
       <c r="V209" t="n">
-        <v>54.90148</v>
+        <v>54.77437</v>
       </c>
       <c r="W209" t="n">
-        <v>-67.09757999999999</v>
+        <v>-66.82881</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -15618,24 +15618,24 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Whalesback Mine</t>
+          <t>Ming Footwall Deposit</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>012H/09/Cu 001</t>
+          <t>012H/16/Cu 030</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Zinc, Titanium, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -15664,23 +15664,23 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T211" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U211" t="n">
         <v>19</v>
       </c>
       <c r="V211" t="n">
-        <v>49.59682</v>
+        <v>49.91174</v>
       </c>
       <c r="W211" t="n">
-        <v>-56.00604</v>
+        <v>-56.08642</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F09%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -15690,24 +15690,24 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ming Footwall Deposit</t>
+          <t>Ming Mine</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>012H/16/Cu 030</t>
+          <t>012H/16/Cu 010</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -15745,14 +15745,14 @@
         <v>19</v>
       </c>
       <c r="V212" t="n">
-        <v>49.91174</v>
+        <v>49.9128</v>
       </c>
       <c r="W212" t="n">
-        <v>-56.08642</v>
+        <v>-56.08313</v>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20010</t>
         </is>
       </c>
     </row>
@@ -15762,24 +15762,24 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Ming Mine</t>
+          <t>Whalesback Mine</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>012H/16/Cu 010</t>
+          <t>012H/09/Cu 001</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Zinc, Titanium, Copper</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -15808,23 +15808,23 @@
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T213" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U213" t="n">
         <v>19</v>
       </c>
       <c r="V213" t="n">
-        <v>49.9128</v>
+        <v>49.59682</v>
       </c>
       <c r="W213" t="n">
-        <v>-56.08313</v>
+        <v>-56.00604</v>
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F09%2FCu%20001</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X214"/>
+  <dimension ref="A1:X209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15540,366 +15540,6 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>1807 Zone</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>012H/16/Cu 033</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I210" t="b">
-        <v>0</v>
-      </c>
-      <c r="J210" t="b">
-        <v>0</v>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="n">
-        <v>3</v>
-      </c>
-      <c r="T210" t="n">
-        <v>75</v>
-      </c>
-      <c r="U210" t="n">
-        <v>19</v>
-      </c>
-      <c r="V210" t="n">
-        <v>49.92292</v>
-      </c>
-      <c r="W210" t="n">
-        <v>-56.07708</v>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20033</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Whalesback Mine</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>012H/09/Cu 001</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Zinc, Titanium, Copper</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I211" t="b">
-        <v>0</v>
-      </c>
-      <c r="J211" t="b">
-        <v>0</v>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="n">
-        <v>0</v>
-      </c>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="n">
-        <v>1</v>
-      </c>
-      <c r="T211" t="n">
-        <v>25</v>
-      </c>
-      <c r="U211" t="n">
-        <v>19</v>
-      </c>
-      <c r="V211" t="n">
-        <v>49.59682</v>
-      </c>
-      <c r="W211" t="n">
-        <v>-56.00604</v>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F09%2FCu%20001</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>211</v>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Ming Footwall Deposit</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>012H/16/Cu 030</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Lead, Zinc, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I212" t="b">
-        <v>0</v>
-      </c>
-      <c r="J212" t="b">
-        <v>0</v>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr"/>
-      <c r="S212" t="n">
-        <v>2</v>
-      </c>
-      <c r="T212" t="n">
-        <v>50</v>
-      </c>
-      <c r="U212" t="n">
-        <v>19</v>
-      </c>
-      <c r="V212" t="n">
-        <v>49.91174</v>
-      </c>
-      <c r="W212" t="n">
-        <v>-56.08642</v>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20030</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>212</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Ming Mine</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>012H/16/Cu 010</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I213" t="b">
-        <v>0</v>
-      </c>
-      <c r="J213" t="b">
-        <v>0</v>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr"/>
-      <c r="S213" t="n">
-        <v>2</v>
-      </c>
-      <c r="T213" t="n">
-        <v>50</v>
-      </c>
-      <c r="U213" t="n">
-        <v>19</v>
-      </c>
-      <c r="V213" t="n">
-        <v>49.9128</v>
-      </c>
-      <c r="W213" t="n">
-        <v>-56.08313</v>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20010</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>213</v>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>1806 Zone</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>012H/16/Au 078</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Gold</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I214" t="b">
-        <v>0</v>
-      </c>
-      <c r="J214" t="b">
-        <v>0</v>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="n">
-        <v>0</v>
-      </c>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr"/>
-      <c r="S214" t="n">
-        <v>1</v>
-      </c>
-      <c r="T214" t="n">
-        <v>25</v>
-      </c>
-      <c r="U214" t="n">
-        <v>19</v>
-      </c>
-      <c r="V214" t="n">
-        <v>49.9162</v>
-      </c>
-      <c r="W214" t="n">
-        <v>-56.0807</v>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20078</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Copper Creek BV</t>
+          <t>Michelin Deposit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>012H/16/Cu 040</t>
+          <t>013J/12/U  001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>44</v>
       </c>
       <c r="V2" t="n">
-        <v>49.91887</v>
+        <v>54.58562</v>
       </c>
       <c r="W2" t="n">
-        <v>-56.20986</v>
+        <v>-59.98056</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Horseshoe Zone</t>
+          <t>Rainbow Deposit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>002E/02/Au 039</t>
+          <t>013J/12/U  008</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,23 +688,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>49.01341</v>
+        <v>54.56417</v>
       </c>
       <c r="W3" t="n">
-        <v>-54.81741</v>
+        <v>-59.99369</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viking Gold-Thor Trend</t>
+          <t>Jacques Lake</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012H/10/Au 011</t>
+          <t>013J/12/U  018</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -760,23 +760,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>49.69447</v>
+        <v>54.71754</v>
       </c>
       <c r="W4" t="n">
-        <v>-56.99193</v>
+        <v>-59.59268</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PW Zone</t>
+          <t>Road Zone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>011O/10/Au 011</t>
+          <t>012H/15/Au 011</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -841,14 +841,14 @@
         <v>44</v>
       </c>
       <c r="V5" t="n">
-        <v>47.74631</v>
+        <v>49.88465</v>
       </c>
       <c r="W5" t="n">
-        <v>-58.94364</v>
+        <v>-56.83885</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deep Fox</t>
+          <t>Apsy Zone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>003D/05/Ree007</t>
+          <t>012H/15/Au 014</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>44</v>
       </c>
       <c r="V6" t="n">
-        <v>52.3805</v>
+        <v>49.89471</v>
       </c>
       <c r="W6" t="n">
-        <v>-55.64987</v>
+        <v>-56.82917</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mart Lake Graphite</t>
+          <t>Deer Cove Main Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>023B/14/Gf 001</t>
+          <t>012I/01/Au 001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>44</v>
       </c>
       <c r="V7" t="n">
-        <v>52.8283</v>
+        <v>50.01619</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.01484000000001</v>
+        <v>-56.04389</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rainbow Deposit</t>
+          <t>Turners Ridge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>013J/12/U  008</t>
+          <t>012H/11/Pb 001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
         <v>44</v>
       </c>
       <c r="V8" t="n">
-        <v>54.56417</v>
+        <v>49.59029</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.99369</v>
+        <v>-57.00443</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michelin Deposit</t>
+          <t>Mann #1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>013J/12/U  001</t>
+          <t>013L/01/Be 001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Niobium, Uranium, Zinc, Beryllium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>44</v>
       </c>
       <c r="V9" t="n">
-        <v>54.58562</v>
+        <v>54.23929</v>
       </c>
       <c r="W9" t="n">
-        <v>-59.98056</v>
+        <v>-62.3924</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deer Cove Main Zone</t>
+          <t>Two Tom Lake</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>012I/01/Au 001</t>
+          <t>013L/01/REE001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>50.01619</v>
+        <v>54.21359</v>
       </c>
       <c r="W10" t="n">
-        <v>-56.04389</v>
+        <v>-62.14192</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apsy Zone</t>
+          <t>Nash Lake (Main Zone)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>012H/15/Au 014</t>
+          <t>013J/13/U  006</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1273,14 +1273,14 @@
         <v>44</v>
       </c>
       <c r="V11" t="n">
-        <v>49.89471</v>
+        <v>54.91032</v>
       </c>
       <c r="W11" t="n">
-        <v>-56.82917</v>
+        <v>-59.62004</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
         </is>
       </c>
     </row>
@@ -1290,24 +1290,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Road Zone</t>
+          <t>Inda Lake</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012H/15/Au 011</t>
+          <t>013J/13/U  009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Molybdenum, Copper, Uranium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>44</v>
       </c>
       <c r="V12" t="n">
-        <v>49.88465</v>
+        <v>54.92456</v>
       </c>
       <c r="W12" t="n">
-        <v>-56.83885</v>
+        <v>-59.5807</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jacques Lake</t>
+          <t>Gear Lake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>013J/12/U  018</t>
+          <t>013J/13/U  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1417,14 +1417,14 @@
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>54.71754</v>
+        <v>54.94329</v>
       </c>
       <c r="W13" t="n">
-        <v>-59.59268</v>
+        <v>-59.54386</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
         </is>
       </c>
     </row>
@@ -1434,24 +1434,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Turners Ridge</t>
+          <t>Kitts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>012H/11/Pb 001</t>
+          <t>013J/14/U  001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>44</v>
       </c>
       <c r="V14" t="n">
-        <v>49.59029</v>
+        <v>54.99779</v>
       </c>
       <c r="W14" t="n">
-        <v>-57.00443</v>
+        <v>-59.4872</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kitts</t>
+          <t>H Brook Showing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>013J/14/U  001</t>
+          <t>011O/15/Au 004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>44</v>
       </c>
       <c r="V16" t="n">
-        <v>54.99779</v>
+        <v>47.7624</v>
       </c>
       <c r="W16" t="n">
-        <v>-59.4872</v>
+        <v>-58.91357</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gear Lake</t>
+          <t>Cape Ray Gold Deposit #4 Zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>013J/13/U  010</t>
+          <t>011O/15/Au 001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>44</v>
       </c>
       <c r="V17" t="n">
-        <v>54.94329</v>
+        <v>47.76081</v>
       </c>
       <c r="W17" t="n">
-        <v>-59.54386</v>
+        <v>-58.91872</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -1722,24 +1722,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inda Lake</t>
+          <t>Cape Ray Gold Deposit 41 Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>013J/13/U  009</t>
+          <t>011O/15/Au 002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1777,14 +1777,14 @@
         <v>44</v>
       </c>
       <c r="V18" t="n">
-        <v>54.92456</v>
+        <v>47.75858</v>
       </c>
       <c r="W18" t="n">
-        <v>-59.5807</v>
+        <v>-58.92331</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nash Lake (Main Zone)</t>
+          <t>51 Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>013J/13/U  006</t>
+          <t>011O/15/Au 003</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>44</v>
       </c>
       <c r="V19" t="n">
-        <v>54.91032</v>
+        <v>47.75077</v>
       </c>
       <c r="W19" t="n">
-        <v>-59.62004</v>
+        <v>-58.93823</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H Brook Showing</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>011O/15/Au 004</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>44</v>
       </c>
       <c r="V20" t="n">
-        <v>47.7624</v>
+        <v>48.69485</v>
       </c>
       <c r="W20" t="n">
-        <v>-58.91357</v>
+        <v>-58.68177</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>51 Zone</t>
+          <t>Keats</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>011O/15/Au 003</t>
+          <t>002D/15/Au 010</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>44</v>
       </c>
       <c r="V21" t="n">
-        <v>47.75077</v>
+        <v>48.97891</v>
       </c>
       <c r="W21" t="n">
-        <v>-58.93823</v>
+        <v>-54.8402</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit 41 Zone</t>
+          <t>Point Leamington Deposit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>011O/15/Au 002</t>
+          <t>002E/05/Zn 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Silver, Copper, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>44</v>
       </c>
       <c r="V22" t="n">
-        <v>47.75858</v>
+        <v>49.27672</v>
       </c>
       <c r="W22" t="n">
-        <v>-58.92331</v>
+        <v>-55.63152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit #4 Zone</t>
+          <t>Bull Road Showing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>011O/15/Au 001</t>
+          <t>002E/12/Zn 007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Copper, Silver, Lead, Antimony, Zinc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>44</v>
       </c>
       <c r="V23" t="n">
-        <v>47.76081</v>
+        <v>49.51431</v>
       </c>
       <c r="W23" t="n">
-        <v>-58.91872</v>
+        <v>-55.7118</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -2154,24 +2154,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Two Tom Lake</t>
+          <t>Windowglass Hill - Main Zone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>013L/01/REE001</t>
+          <t>011O/10/Au 001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Copper, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>44</v>
       </c>
       <c r="V24" t="n">
-        <v>54.21359</v>
+        <v>47.74279</v>
       </c>
       <c r="W24" t="n">
-        <v>-62.14192</v>
+        <v>-58.95727</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mann #1</t>
+          <t>Voisey's Bay, Far Eastern Deeps</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>013L/01/Be 001</t>
+          <t>014D/08/Ni 013</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Niobium, Uranium, Zinc, Beryllium</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>44</v>
       </c>
       <c r="V25" t="n">
-        <v>54.23929</v>
+        <v>56.32109</v>
       </c>
       <c r="W25" t="n">
-        <v>-62.3924</v>
+        <v>-62.06064</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
         </is>
       </c>
     </row>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Ackley City</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>001M/11/Mo 002</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Zinc, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2353,14 +2353,14 @@
         <v>44</v>
       </c>
       <c r="V26" t="n">
-        <v>48.69485</v>
+        <v>47.69347</v>
       </c>
       <c r="W26" t="n">
-        <v>-58.68177</v>
+        <v>-55.20716</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
         </is>
       </c>
     </row>
@@ -2370,24 +2370,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Keats</t>
+          <t>Strickland - Copper Zone</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>002D/15/Au 010</t>
+          <t>011O/16/Cu 001</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>44</v>
       </c>
       <c r="V27" t="n">
-        <v>48.97891</v>
+        <v>47.80365</v>
       </c>
       <c r="W27" t="n">
-        <v>-54.8402</v>
+        <v>-58.30275</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -2442,24 +2442,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bull Road Showing</t>
+          <t>Two Time</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>002E/12/Zn 007</t>
+          <t>013K/11/U  005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Antimony, Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2497,14 +2497,14 @@
         <v>44</v>
       </c>
       <c r="V28" t="n">
-        <v>49.51431</v>
+        <v>54.56554</v>
       </c>
       <c r="W28" t="n">
-        <v>-55.7118</v>
+        <v>-61.17152</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2514,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Point Leamington Deposit</t>
+          <t>Voisey's Bay, South Eastern Deeps</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>002E/05/Zn 001</t>
+          <t>014D/08/Ni 017</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead, Zinc</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>44</v>
       </c>
       <c r="V29" t="n">
-        <v>49.27672</v>
+        <v>56.31756</v>
       </c>
       <c r="W29" t="n">
-        <v>-55.63152</v>
+        <v>-62.06953</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Windowglass Hill - Main Zone</t>
+          <t>Voisey's Bay, North Eastern Deeps</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>011O/10/Au 001</t>
+          <t>014D/08/Ni 011</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2641,14 +2641,14 @@
         <v>44</v>
       </c>
       <c r="V30" t="n">
-        <v>47.74279</v>
+        <v>56.32929</v>
       </c>
       <c r="W30" t="n">
-        <v>-58.95727</v>
+        <v>-62.07733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
         </is>
       </c>
     </row>
@@ -2730,24 +2730,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Voisey's Bay, North Eastern Deeps</t>
+          <t>Moran Lake C-Zone</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>014D/08/Ni 011</t>
+          <t>013K/07/U  002</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2785,14 +2785,14 @@
         <v>44</v>
       </c>
       <c r="V32" t="n">
-        <v>56.32929</v>
+        <v>54.47908</v>
       </c>
       <c r="W32" t="n">
-        <v>-62.07733</v>
+        <v>-60.9581</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Voisey's Bay, South Eastern Deeps</t>
+          <t>Area 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>014D/08/Ni 017</t>
+          <t>013K/07/U  007</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Vanadium, Uranium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2857,14 +2857,14 @@
         <v>44</v>
       </c>
       <c r="V33" t="n">
-        <v>56.31756</v>
+        <v>54.46751</v>
       </c>
       <c r="W33" t="n">
-        <v>-62.06953</v>
+        <v>-60.98105</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
         </is>
       </c>
     </row>
@@ -2874,24 +2874,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Two Time</t>
+          <t>Jaclyn Main - Golden Promise</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>013K/11/U  005</t>
+          <t>012A/16/Au 002</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2929,14 +2929,14 @@
         <v>44</v>
       </c>
       <c r="V34" t="n">
-        <v>54.56554</v>
+        <v>48.90572</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.17152</v>
+        <v>-56.15002</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Strickland - Main Zone</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>013K/07/U  007</t>
+          <t>011O/16/Zn 001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Vanadium, Uranium</t>
+          <t>Lead, Copper, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>44</v>
       </c>
       <c r="V35" t="n">
-        <v>54.46751</v>
+        <v>47.80818</v>
       </c>
       <c r="W35" t="n">
-        <v>-60.98105</v>
+        <v>-58.29993</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Moran Lake C-Zone</t>
+          <t>Strickland - Silver Hill Zone</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>013K/07/U  002</t>
+          <t>011O/16/Zn 002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>44</v>
       </c>
       <c r="V36" t="n">
-        <v>54.47908</v>
+        <v>47.81</v>
       </c>
       <c r="W36" t="n">
-        <v>-60.9581</v>
+        <v>-58.2985</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -3090,24 +3090,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grey River Tungsten</t>
+          <t>Moly Brook</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>011P/11/W  001</t>
+          <t>011P/11/Mo 001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,14 +3145,14 @@
         <v>44</v>
       </c>
       <c r="V37" t="n">
-        <v>47.59343</v>
+        <v>47.61683</v>
       </c>
       <c r="W37" t="n">
-        <v>-57.10342</v>
+        <v>-57.1034</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3162,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Moly Brook</t>
+          <t>Grey River Tungsten</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>011P/11/Mo 001</t>
+          <t>011P/11/W  001</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3217,14 +3217,14 @@
         <v>44</v>
       </c>
       <c r="V38" t="n">
-        <v>47.61683</v>
+        <v>47.59343</v>
       </c>
       <c r="W38" t="n">
-        <v>-57.1034</v>
+        <v>-57.10342</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Strickland - Silver Hill Zone</t>
+          <t>Springer's Hill-Main Showing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>011O/16/Zn 002</t>
+          <t>012B/16/Cr 002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>44</v>
       </c>
       <c r="V39" t="n">
-        <v>47.81</v>
+        <v>48.7927</v>
       </c>
       <c r="W39" t="n">
-        <v>-58.2985</v>
+        <v>-58.44526</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
         </is>
       </c>
     </row>
@@ -3306,24 +3306,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Strickland - Main Zone</t>
+          <t>Saddle Zone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>011O/16/Zn 001</t>
+          <t>002E/02/Au 038</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Gold, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U40" t="n">
         <v>44</v>
       </c>
       <c r="V40" t="n">
-        <v>47.80818</v>
+        <v>49.00899</v>
       </c>
       <c r="W40" t="n">
-        <v>-58.29993</v>
+        <v>-54.81554</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
         </is>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jaclyn Main - Golden Promise</t>
+          <t>Keats South</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>012A/16/Au 002</t>
+          <t>002D/15/Au 060</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>44</v>
       </c>
       <c r="V41" t="n">
-        <v>48.90572</v>
+        <v>48.97791</v>
       </c>
       <c r="W41" t="n">
-        <v>-56.15002</v>
+        <v>-54.84407</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Strickland - Copper Zone</t>
+          <t>Viking Gold-Thor Trend</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>011O/16/Cu 001</t>
+          <t>012H/10/Au 011</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3496,23 +3496,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U42" t="n">
         <v>44</v>
       </c>
       <c r="V42" t="n">
-        <v>47.80365</v>
+        <v>49.69447</v>
       </c>
       <c r="W42" t="n">
-        <v>-58.30275</v>
+        <v>-56.99193</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ackley City</t>
+          <t>Horseshoe Zone</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>001M/11/Mo 002</t>
+          <t>002E/02/Au 039</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>44</v>
       </c>
       <c r="V43" t="n">
-        <v>47.69347</v>
+        <v>49.01341</v>
       </c>
       <c r="W43" t="n">
-        <v>-55.20716</v>
+        <v>-54.81741</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
         </is>
       </c>
     </row>
@@ -3594,24 +3594,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Far Eastern Deeps</t>
+          <t>Copper Creek BV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>014D/08/Ni 013</t>
+          <t>012H/16/Cu 040</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>44</v>
       </c>
       <c r="V44" t="n">
-        <v>56.32109</v>
+        <v>49.91887</v>
       </c>
       <c r="W44" t="n">
-        <v>-62.06064</v>
+        <v>-56.20986</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Springer's Hill-Main Showing</t>
+          <t>Deep Fox</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>012B/16/Cr 002</t>
+          <t>003D/05/Ree007</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>44</v>
       </c>
       <c r="V45" t="n">
-        <v>48.7927</v>
+        <v>52.3805</v>
       </c>
       <c r="W45" t="n">
-        <v>-58.44526</v>
+        <v>-55.64987</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Keats South</t>
+          <t>PW Zone</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>002D/15/Au 060</t>
+          <t>011O/10/Au 011</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>44</v>
       </c>
       <c r="V46" t="n">
-        <v>48.97791</v>
+        <v>47.74631</v>
       </c>
       <c r="W46" t="n">
-        <v>-54.84407</v>
+        <v>-58.94364</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saddle Zone</t>
+          <t>Mart Lake Graphite</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>002E/02/Au 038</t>
+          <t>023B/14/Gf 001</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Graphite</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3856,23 +3856,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
         <v>44</v>
       </c>
       <c r="V47" t="n">
-        <v>49.00899</v>
+        <v>52.8283</v>
       </c>
       <c r="W47" t="n">
-        <v>-54.81554</v>
+        <v>-67.01484000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lewis Brook Mine</t>
+          <t>Foxtrot</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>012B/15/Asb001</t>
+          <t>003D/05/Ree001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>37</v>
       </c>
       <c r="V48" t="n">
-        <v>48.77071</v>
+        <v>52.40035</v>
       </c>
       <c r="W48" t="n">
-        <v>-58.56548</v>
+        <v>-55.82418</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Beaver Dam</t>
+          <t>Deer Cove Talc Zone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>012H/15/Au 018</t>
+          <t>012I/01/Tlc001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Arsenic, Gold</t>
+          <t>Magnesium, Talc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4009,14 +4009,14 @@
         <v>37</v>
       </c>
       <c r="V49" t="n">
-        <v>49.86141</v>
+        <v>50.01534</v>
       </c>
       <c r="W49" t="n">
-        <v>-56.85295</v>
+        <v>-56.04949</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Strange Lake</t>
+          <t>Beaver Dam</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>024A/08/Ree001</t>
+          <t>012H/15/Au 018</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
+          <t>Arsenic, Gold</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>56.31656</v>
+        <v>49.86141</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.12678</v>
+        <v>-56.85295</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Norsk South Block</t>
+          <t>Strange Lake</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>012B/10/Dol004</t>
+          <t>024A/08/Ree001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>48.52445</v>
+        <v>56.31656</v>
       </c>
       <c r="W51" t="n">
-        <v>-58.99684</v>
+        <v>-64.12678</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Norsk North Block</t>
+          <t>Sheep Brook</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>012B/10/Dol003</t>
+          <t>012B/08/Gyp001</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4225,14 +4225,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>48.53397</v>
+        <v>48.39536</v>
       </c>
       <c r="W52" t="n">
-        <v>-58.9773</v>
+        <v>-58.42046</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Round Pond Deposit</t>
+          <t>Porcupine Strand North Beach</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012P/08/Zn 015</t>
+          <t>013I/03/Ti 001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fluorine, Lead, Zinc</t>
+          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>51.25735</v>
+        <v>54.03818</v>
       </c>
       <c r="W53" t="n">
-        <v>-56.26701</v>
+        <v>-57.31912</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4386,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Porcupine Strand North Beach</t>
+          <t>Round Pond Deposit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>013I/03/Ti 001</t>
+          <t>012P/08/Zn 015</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
+          <t>Fluorine, Lead, Zinc</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4441,14 +4441,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>54.03818</v>
+        <v>51.25735</v>
       </c>
       <c r="W55" t="n">
-        <v>-57.31912</v>
+        <v>-56.26701</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deer Cove Talc Zone</t>
+          <t>Norsk South Block</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>012I/01/Tlc001</t>
+          <t>012B/10/Dol004</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Magnesium, Talc</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>50.01534</v>
+        <v>48.52445</v>
       </c>
       <c r="W56" t="n">
-        <v>-56.04949</v>
+        <v>-58.99684</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Foxtrot</t>
+          <t>Norsk North Block</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>003D/05/Ree001</t>
+          <t>012B/10/Dol003</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>52.40035</v>
+        <v>48.53397</v>
       </c>
       <c r="W57" t="n">
-        <v>-55.82418</v>
+        <v>-58.9773</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Lewis Brook Mine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>012B/15/Asb001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>48.39536</v>
+        <v>48.77071</v>
       </c>
       <c r="W60" t="n">
-        <v>-58.42046</v>
+        <v>-58.56548</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Ovoid</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>014D/08/Ni 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>56.33134</v>
+        <v>47.4063</v>
       </c>
       <c r="W61" t="n">
-        <v>-62.09706</v>
+        <v>-52.70699</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGS Vein</t>
+          <t>York Harbour Mine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>001L/14/Fl 013</t>
+          <t>012G/01/Cu 002</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Fluorine</t>
+          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>46.91489</v>
+        <v>49.05208</v>
       </c>
       <c r="W62" t="n">
-        <v>-55.48584</v>
+        <v>-58.30769</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -4962,24 +4962,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blow-Me-Down Chromite #1</t>
+          <t>Sleepy Hollow</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>012G/01/Cr 001</t>
+          <t>002E/12/Cu 031</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5008,23 +5008,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T63" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U63" t="n">
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>49.01096</v>
+        <v>49.59747</v>
       </c>
       <c r="W63" t="n">
-        <v>-58.24371</v>
+        <v>-55.94735</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
         </is>
       </c>
     </row>
@@ -5034,24 +5034,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Goose Cove</t>
+          <t>Miles Cove Mine</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>002M/05/Cu 001</t>
+          <t>002E/12/Cu 012</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zinc, Nickel, Iron, Copper</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>51.31009</v>
+        <v>49.53936</v>
       </c>
       <c r="W64" t="n">
-        <v>-55.62342</v>
+        <v>-55.79062</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>York Harbour Mine</t>
+          <t>Goose Cove</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>012G/01/Cu 002</t>
+          <t>002M/05/Cu 001</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
+          <t>Zinc, Nickel, Iron, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>49.05208</v>
+        <v>51.31009</v>
       </c>
       <c r="W65" t="n">
-        <v>-58.30769</v>
+        <v>-55.62342</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5178,24 +5178,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Blow-Me-Down Chromite #1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012G/01/Cr 001</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U66" t="n">
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>50.27283</v>
+        <v>49.01096</v>
       </c>
       <c r="W66" t="n">
-        <v>-57.46448</v>
+        <v>-58.24371</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Terra Nova Mine</t>
+          <t>Voisey's Bay, Ovoid</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>012H/16/Cu 004</t>
+          <t>014D/08/Ni 001</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>49.92133</v>
+        <v>56.33134</v>
       </c>
       <c r="W67" t="n">
-        <v>-56.22896</v>
+        <v>-62.09706</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-G Zone</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 007</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>50.31118</v>
+        <v>50.29448</v>
       </c>
       <c r="W68" t="n">
-        <v>-57.43009</v>
+        <v>-57.44714</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-Q Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>012I/06/Zn 016</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>50.29741</v>
+        <v>50.27283</v>
       </c>
       <c r="W69" t="n">
-        <v>-57.48016</v>
+        <v>-57.46448</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Browning Mine</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>012H/10/Au 001</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>49.71799</v>
+        <v>50.31118</v>
       </c>
       <c r="W70" t="n">
-        <v>-56.92565</v>
+        <v>-57.43009</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5538,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Goldenville</t>
+          <t>Daniel's Harbour Mine-H Zone</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>012H/16/Au 033</t>
+          <t>012I/06/Zn 008</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper, Iron, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5584,23 +5584,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>49.99193</v>
+        <v>50.29179</v>
       </c>
       <c r="W71" t="n">
-        <v>-56.05735</v>
+        <v>-57.44599</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stog'er Tight</t>
+          <t>Daniel's Harbour Mine-J Zone</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>012H/16/Au 041</t>
+          <t>012I/06/Zn 009</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5665,14 +5665,14 @@
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>49.9661</v>
+        <v>50.30247</v>
       </c>
       <c r="W72" t="n">
-        <v>-56.07765</v>
+        <v>-57.47459</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>Daniel's Harbour Mine-K Zone</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>012I/06/Zn 010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5737,14 +5737,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>49.19579</v>
+        <v>50.2935</v>
       </c>
       <c r="W73" t="n">
-        <v>-57.84974</v>
+        <v>-57.46875</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
         </is>
       </c>
     </row>
@@ -5754,24 +5754,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>Daniel's Harbour Mine-L Zone</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>012I/06/Zn 011</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Lead, Dolomite, Zinc</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5809,14 +5809,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>52.961</v>
+        <v>50.27686</v>
       </c>
       <c r="W74" t="n">
-        <v>-66.81446</v>
+        <v>-57.46788</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5826,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-J Zone</t>
+          <t>Daniel's Harbour Mine-M Zone</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>012I/06/Zn 009</t>
+          <t>012I/06/Zn 012</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>50.30247</v>
+        <v>50.29514</v>
       </c>
       <c r="W75" t="n">
-        <v>-57.47459</v>
+        <v>-57.44013</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-L Zone</t>
+          <t>Daniel's Harbour Mine-N Zone</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>012I/06/Zn 011</t>
+          <t>012I/06/Zn 013</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lead, Dolomite, Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>50.27686</v>
+        <v>50.29873</v>
       </c>
       <c r="W76" t="n">
-        <v>-57.46788</v>
+        <v>-57.48691</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
         </is>
       </c>
     </row>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-N Zone</t>
+          <t>Terra Nova Mine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>012I/06/Zn 013</t>
+          <t>012H/16/Cu 004</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>50.29873</v>
+        <v>49.92133</v>
       </c>
       <c r="W77" t="n">
-        <v>-57.48691</v>
+        <v>-56.22896</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6042,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-F Zone</t>
+          <t>Goldenville</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>012I/06/Zn 006</t>
+          <t>012H/16/Au 033</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper, Iron, Gold</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6088,23 +6088,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T78" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U78" t="n">
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>50.29437</v>
+        <v>49.99193</v>
       </c>
       <c r="W78" t="n">
-        <v>-57.45374</v>
+        <v>-56.05735</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
         </is>
       </c>
     </row>
@@ -6114,24 +6114,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-E Zone</t>
+          <t>Stog'er Tight</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>012I/06/Zn 005</t>
+          <t>012H/16/Au 041</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>50.31067</v>
+        <v>49.9661</v>
       </c>
       <c r="W79" t="n">
-        <v>-57.44799</v>
+        <v>-56.07765</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-C Zone</t>
+          <t>Daniel's Harbour Mine-B Zone</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>012I/06/Zn 003</t>
+          <t>012I/06/Zn 002</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6241,14 +6241,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>50.30435</v>
+        <v>50.2975</v>
       </c>
       <c r="W80" t="n">
-        <v>-57.45355</v>
+        <v>-57.45784</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-D Zone</t>
+          <t>Daniel's Harbour Mine-E Zone</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>012I/06/Zn 004</t>
+          <t>012I/06/Zn 005</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6313,14 +6313,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>50.30795</v>
+        <v>50.31067</v>
       </c>
       <c r="W81" t="n">
-        <v>-57.45218</v>
+        <v>-57.44799</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-B Zone</t>
+          <t>Daniel's Harbour Mine-C Zone</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>012I/06/Zn 002</t>
+          <t>012I/06/Zn 003</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6385,14 +6385,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>50.2975</v>
+        <v>50.30435</v>
       </c>
       <c r="W82" t="n">
-        <v>-57.45784</v>
+        <v>-57.45355</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
         </is>
       </c>
     </row>
@@ -6402,12 +6402,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-H Zone</t>
+          <t>Daniel's Harbour Mine-D Zone</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>012I/06/Zn 008</t>
+          <t>012I/06/Zn 004</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6457,14 +6457,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>50.29179</v>
+        <v>50.30795</v>
       </c>
       <c r="W83" t="n">
-        <v>-57.44599</v>
+        <v>-57.45218</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-G Zone</t>
+          <t>Pilley's Island Mine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>012I/06/Zn 007</t>
+          <t>002E/12/Cu 001</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6529,14 +6529,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>50.29448</v>
+        <v>49.50863</v>
       </c>
       <c r="W84" t="n">
-        <v>-57.44714</v>
+        <v>-55.71872</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-M Zone</t>
+          <t>AGS Vein</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>012I/06/Zn 012</t>
+          <t>001L/14/Fl 013</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc, Lead, Copper, Fluorine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6601,14 +6601,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>50.29514</v>
+        <v>46.91489</v>
       </c>
       <c r="W85" t="n">
-        <v>-57.44013</v>
+        <v>-55.48584</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
         </is>
       </c>
     </row>
@@ -6618,24 +6618,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Nugget Pond</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>002E/13/Au 001</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6673,14 +6673,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>49.45488</v>
+        <v>49.84502</v>
       </c>
       <c r="W86" t="n">
-        <v>-55.49811</v>
+        <v>-55.77536</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -6690,24 +6690,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stoneyhouse</t>
+          <t>Bishop North</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>001M/01/Cu 001</t>
+          <t>012B/08/Fe 001</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6745,14 +6745,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>47.0541</v>
+        <v>48.40317</v>
       </c>
       <c r="W87" t="n">
-        <v>-54.11056</v>
+        <v>-58.3315</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6762,24 +6762,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Indian Head Mine</t>
+          <t>Upper Drill Brook Mine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>012B/10/Fe 001</t>
+          <t>012B/09/Fe 002</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>48.52416</v>
+        <v>48.53533</v>
       </c>
       <c r="W88" t="n">
-        <v>-58.5148</v>
+        <v>-58.48601</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -6834,24 +6834,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tilt Cove/East Mine/Upper Dump</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>002E/13/Au 028</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Zinc, Gold</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>49.88512</v>
+        <v>48.5353</v>
       </c>
       <c r="W89" t="n">
-        <v>-55.62192</v>
+        <v>-58.48804</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -6906,12 +6906,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tilt Cove Mine</t>
+          <t>Betts Cove Mine</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>002E/13/Cu 001</t>
+          <t>002E/13/Cu 002</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Silver, Zinc, Copper</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>49.88214</v>
+        <v>49.81179</v>
       </c>
       <c r="W90" t="n">
-        <v>-55.62813</v>
+        <v>-55.80608</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Stewart Mine</t>
+          <t>Tilt Cove Mine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>002E/10/Au 001</t>
+          <t>002E/13/Cu 001</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Silver, Antimony, Copper, Zinc, Gold</t>
+          <t>Gold, Nickel, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>49.58065</v>
+        <v>49.88214</v>
       </c>
       <c r="W91" t="n">
-        <v>-54.85442</v>
+        <v>-55.62813</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7050,24 +7050,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Tilt Cove/East Mine/Upper Dump</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>002E/13/Au 028</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Silver, Nickel, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7105,14 +7105,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>48.5353</v>
+        <v>49.88512</v>
       </c>
       <c r="W92" t="n">
-        <v>-58.48804</v>
+        <v>-55.62192</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
         </is>
       </c>
     </row>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pine Cove</t>
+          <t>Cross Cove</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>012H/16/Au 023</t>
+          <t>002E/10/Sb 001</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>49.96066</v>
+        <v>49.57534</v>
       </c>
       <c r="W93" t="n">
-        <v>-56.13074</v>
+        <v>-54.86876</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
         </is>
       </c>
     </row>
@@ -7194,24 +7194,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bishop South</t>
+          <t>Stoneyhouse</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>012B/08/Fe 002</t>
+          <t>001M/01/Cu 001</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7249,14 +7249,14 @@
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>48.39996</v>
+        <v>47.0541</v>
       </c>
       <c r="W94" t="n">
-        <v>-58.33683</v>
+        <v>-54.11056</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7266,24 +7266,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bishop North</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>012B/08/Fe 001</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7321,14 +7321,14 @@
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>48.40317</v>
+        <v>49.45488</v>
       </c>
       <c r="W95" t="n">
-        <v>-58.3315</v>
+        <v>-55.49811</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -7338,24 +7338,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Upper Drill Brook Mine</t>
+          <t>Argyle</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>012B/09/Fe 002</t>
+          <t>012H/16/Au 083</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7393,14 +7393,14 @@
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>48.53533</v>
+        <v>49.97838</v>
       </c>
       <c r="W96" t="n">
-        <v>-58.48601</v>
+        <v>-56.05952</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
         </is>
       </c>
     </row>
@@ -7410,24 +7410,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Turk's Gut</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>001N/11/Cu 001</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7465,14 +7465,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>47.50226</v>
+        <v>47.4438</v>
       </c>
       <c r="W97" t="n">
-        <v>-53.20074</v>
+        <v>-54.4169</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cross Cove</t>
+          <t>Turk's Gut</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>002E/10/Sb 001</t>
+          <t>001N/11/Cu 001</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>49.57534</v>
+        <v>47.50226</v>
       </c>
       <c r="W98" t="n">
-        <v>-54.86876</v>
+        <v>-53.20074</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Daniel's Harbour Mine-A Zone</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>012I/06/Zn 001</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>47.4438</v>
+        <v>50.29576</v>
       </c>
       <c r="W99" t="n">
-        <v>-54.4169</v>
+        <v>-57.46512</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -7626,24 +7626,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>La Manche</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001N/12/Pb 001</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Silver, Barium, Lead</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>35</v>
       </c>
       <c r="V100" t="n">
-        <v>47.4063</v>
+        <v>47.6889</v>
       </c>
       <c r="W100" t="n">
-        <v>-52.70699</v>
+        <v>-53.93901</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -7770,24 +7770,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Miles Cove Mine</t>
+          <t>Hope Brook</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>002E/12/Cu 012</t>
+          <t>011O/09/Au 003</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7825,14 +7825,14 @@
         <v>35</v>
       </c>
       <c r="V102" t="n">
-        <v>49.53936</v>
+        <v>47.73806</v>
       </c>
       <c r="W102" t="n">
-        <v>-55.79062</v>
+        <v>-58.09531</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Pilley's Island Mine</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>002E/12/Cu 001</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>35</v>
       </c>
       <c r="V103" t="n">
-        <v>49.50863</v>
+        <v>52.961</v>
       </c>
       <c r="W103" t="n">
-        <v>-55.71872</v>
+        <v>-66.81446</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -7914,24 +7914,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hope Brook</t>
+          <t>Ming West</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>011O/09/Au 003</t>
+          <t>012H/16/Cu 029</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7960,23 +7960,23 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T104" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U104" t="n">
         <v>35</v>
       </c>
       <c r="V104" t="n">
-        <v>47.73806</v>
+        <v>49.9148</v>
       </c>
       <c r="W104" t="n">
-        <v>-58.09531</v>
+        <v>-56.08996</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
         </is>
       </c>
     </row>
@@ -7986,24 +7986,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>La Manche</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>001N/12/Pb 001</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Barium, Lead</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8041,14 +8041,14 @@
         <v>35</v>
       </c>
       <c r="V105" t="n">
-        <v>47.6889</v>
+        <v>49.19579</v>
       </c>
       <c r="W105" t="n">
-        <v>-53.93901</v>
+        <v>-57.84974</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -8058,24 +8058,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sleepy Hollow</t>
+          <t>Daniel's Harbour Mine-Q Zone</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>002E/12/Cu 031</t>
+          <t>012I/06/Zn 016</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8113,14 +8113,14 @@
         <v>35</v>
       </c>
       <c r="V106" t="n">
-        <v>49.59747</v>
+        <v>50.29741</v>
       </c>
       <c r="W106" t="n">
-        <v>-55.94735</v>
+        <v>-57.48016</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
         </is>
       </c>
     </row>
@@ -8130,24 +8130,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ming West</t>
+          <t>Browning Mine</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>012H/16/Cu 029</t>
+          <t>012H/10/Au 001</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8176,23 +8176,23 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T107" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U107" t="n">
         <v>35</v>
       </c>
       <c r="V107" t="n">
-        <v>49.9148</v>
+        <v>49.71799</v>
       </c>
       <c r="W107" t="n">
-        <v>-56.08996</v>
+        <v>-56.92565</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -8202,24 +8202,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-A Zone</t>
+          <t>Pine Cove</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>012I/06/Zn 001</t>
+          <t>012H/16/Au 023</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8257,14 +8257,14 @@
         <v>35</v>
       </c>
       <c r="V108" t="n">
-        <v>50.29576</v>
+        <v>49.96066</v>
       </c>
       <c r="W108" t="n">
-        <v>-57.46512</v>
+        <v>-56.13074</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Argyle</t>
+          <t>Bishop South</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>012H/16/Au 083</t>
+          <t>012B/08/Fe 002</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>35</v>
       </c>
       <c r="V109" t="n">
-        <v>49.97838</v>
+        <v>48.39996</v>
       </c>
       <c r="W109" t="n">
-        <v>-56.05952</v>
+        <v>-58.33683</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -8346,24 +8346,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-K Zone</t>
+          <t>Daniel's Harbour Mine-F Zone</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>012I/06/Zn 010</t>
+          <t>012I/06/Zn 006</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>35</v>
       </c>
       <c r="V110" t="n">
-        <v>50.2935</v>
+        <v>50.29437</v>
       </c>
       <c r="W110" t="n">
-        <v>-57.46875</v>
+        <v>-57.45374</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
         </is>
       </c>
     </row>
@@ -8418,24 +8418,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Betts Cove Mine</t>
+          <t>Stewart Mine</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>002E/13/Cu 002</t>
+          <t>002E/10/Au 001</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Silver, Antimony, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>35</v>
       </c>
       <c r="V111" t="n">
-        <v>49.81179</v>
+        <v>49.58065</v>
       </c>
       <c r="W111" t="n">
-        <v>-55.80608</v>
+        <v>-54.85442</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -8490,24 +8490,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nugget Pond</t>
+          <t>Indian Head Mine</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>002E/13/Au 001</t>
+          <t>012B/10/Fe 001</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>35</v>
       </c>
       <c r="V112" t="n">
-        <v>49.84502</v>
+        <v>48.52416</v>
       </c>
       <c r="W112" t="n">
-        <v>-55.77536</v>
+        <v>-58.5148</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8562,24 +8562,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timmins No 8</t>
+          <t>Goethite Bay North</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>023J/14/Fe 026</t>
+          <t>023G/02/Fe 041</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8617,14 +8617,14 @@
         <v>31</v>
       </c>
       <c r="V113" t="n">
-        <v>54.89589</v>
+        <v>53.18717</v>
       </c>
       <c r="W113" t="n">
-        <v>-67.07944000000001</v>
+        <v>-66.74445</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
         </is>
       </c>
     </row>
@@ -8634,24 +8634,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timmins No 5</t>
+          <t>Ruth Lake No 2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>023J/14/Fe 024</t>
+          <t>023J/15/Fe 011</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>31</v>
       </c>
       <c r="V114" t="n">
-        <v>54.86384</v>
+        <v>54.79747</v>
       </c>
       <c r="W114" t="n">
-        <v>-67.09327</v>
+        <v>-66.87487</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mile 2</t>
+          <t>Block 103 - Greenbush Zone</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>023B/15/Fe 011</t>
+          <t>023J/14/Fe 043</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -8761,14 +8761,14 @@
         <v>31</v>
       </c>
       <c r="V115" t="n">
-        <v>52.97907</v>
+        <v>54.97234</v>
       </c>
       <c r="W115" t="n">
-        <v>-66.88907</v>
+        <v>-67.25158</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wabush No. 1</t>
+          <t>Elizabeth No. 2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>023B/15/Fe 002</t>
+          <t>023J/15/Fe 032</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>31</v>
       </c>
       <c r="V116" t="n">
-        <v>52.9599</v>
+        <v>54.77182</v>
       </c>
       <c r="W116" t="n">
-        <v>-66.9704</v>
+        <v>-66.88666000000001</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Julienne Lake</t>
+          <t>Lorraine No. 4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>023G/02/Fe 009</t>
+          <t>023G/02/Fe 008</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8905,14 +8905,14 @@
         <v>31</v>
       </c>
       <c r="V117" t="n">
-        <v>53.13733</v>
+        <v>53.08316</v>
       </c>
       <c r="W117" t="n">
-        <v>-66.78360000000001</v>
+        <v>-66.87726000000001</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Joyce Lake</t>
+          <t>Elizabeth No. 1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>023J/15/Fe 030</t>
+          <t>023J/15/Fe 031</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -8977,14 +8977,14 @@
         <v>31</v>
       </c>
       <c r="V118" t="n">
-        <v>54.8993</v>
+        <v>54.78743</v>
       </c>
       <c r="W118" t="n">
-        <v>-66.53366</v>
+        <v>-66.90081000000001</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
         </is>
       </c>
     </row>
@@ -8994,24 +8994,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Attikamagen Deposit</t>
+          <t>Wabush No. 7</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>023J/16/Fe 001</t>
+          <t>023G/02/Fe 007</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9049,14 +9049,14 @@
         <v>31</v>
       </c>
       <c r="V119" t="n">
-        <v>54.80989</v>
+        <v>53.02512</v>
       </c>
       <c r="W119" t="n">
-        <v>-66.47658</v>
+        <v>-66.90531</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Goethite Bay North</t>
+          <t>Knob Lake 1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>023G/02/Fe 041</t>
+          <t>023J/15/Fe 013</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9121,14 +9121,14 @@
         <v>31</v>
       </c>
       <c r="V120" t="n">
-        <v>53.18717</v>
+        <v>54.7766</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.74445</v>
+        <v>-66.80589000000001</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
         </is>
       </c>
     </row>
@@ -9138,24 +9138,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Wabush No. 6</t>
+          <t>Howse</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>023G/02/Fe 006</t>
+          <t>023J/14/Fe 028</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9193,14 +9193,14 @@
         <v>31</v>
       </c>
       <c r="V121" t="n">
-        <v>53.01798</v>
+        <v>54.9089</v>
       </c>
       <c r="W121" t="n">
-        <v>-66.89297999999999</v>
+        <v>-67.14075</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -9210,24 +9210,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Canning</t>
+          <t>Ferriman No 7</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>023B/15/Fe 007</t>
+          <t>023J/15/Fe 014</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9265,14 +9265,14 @@
         <v>31</v>
       </c>
       <c r="V122" t="n">
-        <v>52.9469</v>
+        <v>54.81281</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.95802999999999</v>
+        <v>-66.94580999999999</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
         </is>
       </c>
     </row>
@@ -9282,24 +9282,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timmins No 7</t>
+          <t>Duley No. 1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>023J/14/Fe 025</t>
+          <t>023B/14/Fe 001</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9337,14 +9337,14 @@
         <v>31</v>
       </c>
       <c r="V123" t="n">
-        <v>54.89246</v>
+        <v>52.87237</v>
       </c>
       <c r="W123" t="n">
-        <v>-67.07259000000001</v>
+        <v>-67.05874</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ferriman No 7</t>
+          <t>Kivivic No 3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>023J/15/Fe 014</t>
+          <t>023O/03/Fe 003</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9409,14 +9409,14 @@
         <v>31</v>
       </c>
       <c r="V124" t="n">
-        <v>54.81281</v>
+        <v>55.05061</v>
       </c>
       <c r="W124" t="n">
-        <v>-66.94580999999999</v>
+        <v>-67.26130000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -9426,24 +9426,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Wabush No. 4</t>
+          <t>Sawyer Lake</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>023B/15/Fe 004</t>
+          <t>023I/05/Fe 001</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9481,14 +9481,14 @@
         <v>31</v>
       </c>
       <c r="V125" t="n">
-        <v>52.95373</v>
+        <v>54.45206</v>
       </c>
       <c r="W125" t="n">
-        <v>-66.94092000000001</v>
+        <v>-65.98627</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9498,24 +9498,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Block 103 - Greenbush Zone</t>
+          <t>Ruth Lake No 8</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>023J/14/Fe 043</t>
+          <t>023J/15/Fe 009</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9553,14 +9553,14 @@
         <v>31</v>
       </c>
       <c r="V126" t="n">
-        <v>54.97234</v>
+        <v>54.78104</v>
       </c>
       <c r="W126" t="n">
-        <v>-67.25158</v>
+        <v>-66.86577</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9570,12 +9570,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Howells River North</t>
+          <t>Attikamagen Deposit</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>023O/03/Fe 007</t>
+          <t>023J/16/Fe 001</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -9625,14 +9625,14 @@
         <v>31</v>
       </c>
       <c r="V127" t="n">
-        <v>55.01179</v>
+        <v>54.80989</v>
       </c>
       <c r="W127" t="n">
-        <v>-67.37214</v>
+        <v>-66.47658</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Duley No. 2</t>
+          <t>Joyce Lake</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>023B/15/Fe 008</t>
+          <t>023J/15/Fe 030</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>31</v>
       </c>
       <c r="V128" t="n">
-        <v>52.87214</v>
+        <v>54.8993</v>
       </c>
       <c r="W128" t="n">
-        <v>-66.99635000000001</v>
+        <v>-66.53366</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
         </is>
       </c>
     </row>
@@ -9714,12 +9714,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Elizabeth No. 1</t>
+          <t>Howells Lake</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>023J/15/Fe 031</t>
+          <t>023O/03/Fe 006</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -9769,14 +9769,14 @@
         <v>31</v>
       </c>
       <c r="V129" t="n">
-        <v>54.78743</v>
+        <v>55.06346</v>
       </c>
       <c r="W129" t="n">
-        <v>-66.90081000000001</v>
+        <v>-67.40528</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9786,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Howells Lake</t>
+          <t>Howells River North</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>023O/03/Fe 006</t>
+          <t>023O/03/Fe 007</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9841,14 +9841,14 @@
         <v>31</v>
       </c>
       <c r="V130" t="n">
-        <v>55.06346</v>
+        <v>55.01179</v>
       </c>
       <c r="W130" t="n">
-        <v>-67.40528</v>
+        <v>-67.37214</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Wabush No. 7</t>
+          <t>Wabush No. 6</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>023G/02/Fe 007</t>
+          <t>023G/02/Fe 006</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9913,14 +9913,14 @@
         <v>31</v>
       </c>
       <c r="V131" t="n">
-        <v>53.02512</v>
+        <v>53.01798</v>
       </c>
       <c r="W131" t="n">
-        <v>-66.90531</v>
+        <v>-66.89297999999999</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lorraine No. 4</t>
+          <t>Julienne Lake</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>023G/02/Fe 008</t>
+          <t>023G/02/Fe 009</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9985,14 +9985,14 @@
         <v>31</v>
       </c>
       <c r="V132" t="n">
-        <v>53.08316</v>
+        <v>53.13733</v>
       </c>
       <c r="W132" t="n">
-        <v>-66.87726000000001</v>
+        <v>-66.78360000000001</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wabush No. 8</t>
+          <t>Duley No. 2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>023B/15/Fe 005</t>
+          <t>023B/15/Fe 008</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -10057,14 +10057,14 @@
         <v>31</v>
       </c>
       <c r="V133" t="n">
-        <v>52.9791</v>
+        <v>52.87214</v>
       </c>
       <c r="W133" t="n">
-        <v>-66.90604999999999</v>
+        <v>-66.99635000000001</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Houston 2</t>
+          <t>Canning</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>023J/10/Fe 009</t>
+          <t>023B/15/Fe 007</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10129,14 +10129,14 @@
         <v>31</v>
       </c>
       <c r="V134" t="n">
-        <v>54.71245</v>
+        <v>52.9469</v>
       </c>
       <c r="W134" t="n">
-        <v>-66.66257</v>
+        <v>-66.95802999999999</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10146,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Houston 3</t>
+          <t>Timmins No 7</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>023J/10/Fe 010</t>
+          <t>023J/14/Fe 025</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10201,14 +10201,14 @@
         <v>31</v>
       </c>
       <c r="V135" t="n">
-        <v>54.69887</v>
+        <v>54.89246</v>
       </c>
       <c r="W135" t="n">
-        <v>-66.64483</v>
+        <v>-67.07259000000001</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
         </is>
       </c>
     </row>
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kivivic No 3</t>
+          <t>Mile 2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>023O/03/Fe 003</t>
+          <t>023B/15/Fe 011</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -10273,14 +10273,14 @@
         <v>31</v>
       </c>
       <c r="V136" t="n">
-        <v>55.05061</v>
+        <v>52.97907</v>
       </c>
       <c r="W136" t="n">
-        <v>-67.26130000000001</v>
+        <v>-66.88907</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Kivivic No 4</t>
+          <t>Wabush No. 8</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>023O/03/Fe 004</t>
+          <t>023B/15/Fe 005</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>31</v>
       </c>
       <c r="V137" t="n">
-        <v>55.04865</v>
+        <v>52.9791</v>
       </c>
       <c r="W137" t="n">
-        <v>-67.28158000000001</v>
+        <v>-66.90604999999999</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10362,24 +10362,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kivivic No 5</t>
+          <t>Wabush No. 4</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>023O/03/Fe 005</t>
+          <t>023B/15/Fe 004</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>31</v>
       </c>
       <c r="V138" t="n">
-        <v>55.06664</v>
+        <v>52.95373</v>
       </c>
       <c r="W138" t="n">
-        <v>-67.29537000000001</v>
+        <v>-66.94092000000001</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -10434,24 +10434,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Duley No. 1</t>
+          <t>Timmins No 8</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>023B/14/Fe 001</t>
+          <t>023J/14/Fe 026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>31</v>
       </c>
       <c r="V139" t="n">
-        <v>52.87237</v>
+        <v>54.89589</v>
       </c>
       <c r="W139" t="n">
-        <v>-67.05874</v>
+        <v>-67.07944000000001</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
         </is>
       </c>
     </row>
@@ -10506,24 +10506,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mills Lake</t>
+          <t>Timmins No 5</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>023B/14/Fe 002</t>
+          <t>023J/14/Fe 024</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>31</v>
       </c>
       <c r="V140" t="n">
-        <v>52.79808</v>
+        <v>54.86384</v>
       </c>
       <c r="W140" t="n">
-        <v>-67.00413</v>
+        <v>-67.09327</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
         </is>
       </c>
     </row>
@@ -10578,24 +10578,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Howells River West Zone A</t>
+          <t>Sheps Lake</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>023J/14/Fe 001</t>
+          <t>023J/11/Fe 001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10633,14 +10633,14 @@
         <v>31</v>
       </c>
       <c r="V141" t="n">
-        <v>54.90958</v>
+        <v>54.73475</v>
       </c>
       <c r="W141" t="n">
-        <v>-67.26052</v>
+        <v>-67.06362</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Houston 1</t>
+          <t>Neal 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>023J/10/Fe 008</t>
+          <t>023B/14/Fe 008</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10705,14 +10705,14 @@
         <v>31</v>
       </c>
       <c r="V142" t="n">
-        <v>54.70748</v>
+        <v>52.95013</v>
       </c>
       <c r="W142" t="n">
-        <v>-66.65615</v>
+        <v>-67.15191</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10722,24 +10722,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Redmond 5</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>023J/10/Fe 005</t>
+          <t>023B/14/Fe 028</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10777,14 +10777,14 @@
         <v>31</v>
       </c>
       <c r="V143" t="n">
-        <v>54.70854</v>
+        <v>52.94868</v>
       </c>
       <c r="W143" t="n">
-        <v>-66.79174999999999</v>
+        <v>-67.01146</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sawyer Lake</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>023I/05/Fe 001</t>
+          <t>023B/14/Fe 020</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>31</v>
       </c>
       <c r="V144" t="n">
-        <v>54.45206</v>
+        <v>52.83351</v>
       </c>
       <c r="W144" t="n">
-        <v>-65.98627</v>
+        <v>-67.0311</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
         </is>
       </c>
     </row>
@@ -10938,24 +10938,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Howells River West Zone A</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>023B/14/Fe 020</t>
+          <t>023J/14/Fe 001</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>31</v>
       </c>
       <c r="V146" t="n">
-        <v>52.83351</v>
+        <v>54.90958</v>
       </c>
       <c r="W146" t="n">
-        <v>-67.0311</v>
+        <v>-67.26052</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -11010,24 +11010,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Wabush No. 1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>023B/14/Fe 028</t>
+          <t>023B/15/Fe 002</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11065,14 +11065,14 @@
         <v>31</v>
       </c>
       <c r="V147" t="n">
-        <v>52.94868</v>
+        <v>52.9599</v>
       </c>
       <c r="W147" t="n">
-        <v>-67.01146</v>
+        <v>-66.9704</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sheps Lake</t>
+          <t>Redmond 5</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>023J/11/Fe 001</t>
+          <t>023J/10/Fe 005</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11137,14 +11137,14 @@
         <v>31</v>
       </c>
       <c r="V148" t="n">
-        <v>54.73475</v>
+        <v>54.70854</v>
       </c>
       <c r="W148" t="n">
-        <v>-67.06362</v>
+        <v>-66.79174999999999</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Neal 1</t>
+          <t>Mills Lake</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>023B/14/Fe 008</t>
+          <t>023B/14/Fe 002</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -11209,14 +11209,14 @@
         <v>31</v>
       </c>
       <c r="V149" t="n">
-        <v>52.95013</v>
+        <v>52.79808</v>
       </c>
       <c r="W149" t="n">
-        <v>-67.15191</v>
+        <v>-67.00413</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ruth Lake No 8</t>
+          <t>Houston 1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>023J/15/Fe 009</t>
+          <t>023J/10/Fe 008</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11281,14 +11281,14 @@
         <v>31</v>
       </c>
       <c r="V150" t="n">
-        <v>54.78104</v>
+        <v>54.70748</v>
       </c>
       <c r="W150" t="n">
-        <v>-66.86577</v>
+        <v>-66.65615</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ruth Lake No 2</t>
+          <t>Houston 3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>023J/15/Fe 011</t>
+          <t>023J/10/Fe 010</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11353,14 +11353,14 @@
         <v>31</v>
       </c>
       <c r="V151" t="n">
-        <v>54.79747</v>
+        <v>54.69887</v>
       </c>
       <c r="W151" t="n">
-        <v>-66.87487</v>
+        <v>-66.64483</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -11370,24 +11370,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Elizabeth No. 2</t>
+          <t>Houston 2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>023J/15/Fe 032</t>
+          <t>023J/10/Fe 009</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11425,14 +11425,14 @@
         <v>31</v>
       </c>
       <c r="V152" t="n">
-        <v>54.77182</v>
+        <v>54.71245</v>
       </c>
       <c r="W152" t="n">
-        <v>-66.88666000000001</v>
+        <v>-66.66257</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -11442,24 +11442,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Knob Lake 1</t>
+          <t>Kivivic No 4</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>023J/15/Fe 013</t>
+          <t>023O/03/Fe 004</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11497,14 +11497,14 @@
         <v>31</v>
       </c>
       <c r="V153" t="n">
-        <v>54.7766</v>
+        <v>55.04865</v>
       </c>
       <c r="W153" t="n">
-        <v>-66.80589000000001</v>
+        <v>-67.28158000000001</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11514,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Howse</t>
+          <t>Kivivic No 5</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>023J/14/Fe 028</t>
+          <t>023O/03/Fe 005</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11569,14 +11569,14 @@
         <v>31</v>
       </c>
       <c r="V154" t="n">
-        <v>54.9089</v>
+        <v>55.06664</v>
       </c>
       <c r="W154" t="n">
-        <v>-67.14075</v>
+        <v>-67.29537000000001</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mine Hill</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>001N/07/Pph004</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pyrophyllite</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11641,14 +11641,14 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>47.48</v>
+        <v>53.40462</v>
       </c>
       <c r="W155" t="n">
-        <v>-52.95479</v>
+        <v>-65.08734</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Iron Springs Mine</t>
+          <t>Parsons Pond No 3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>001L/14/Fl 008</t>
+          <t>012H/13/Btm003</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11785,14 +11785,14 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>46.88701</v>
+        <v>49.97912</v>
       </c>
       <c r="W157" t="n">
-        <v>-55.421</v>
+        <v>-57.64547</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Parsons Pond No 2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>012H/13/Btm002</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11857,14 +11857,14 @@
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>48.56074</v>
+        <v>49.97421</v>
       </c>
       <c r="W158" t="n">
-        <v>-58.8161</v>
+        <v>-57.60538</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hares Ears Vein</t>
+          <t>Parsons Pond No 4</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>001L/14/Fl 007</t>
+          <t>012H/13/Btm004</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11920,23 +11920,23 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T159" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U159" t="n">
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>46.88814</v>
+        <v>49.99787</v>
       </c>
       <c r="W159" t="n">
-        <v>-55.41178</v>
+        <v>-57.63818</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Collier Point</t>
+          <t>Middle Arm Brook</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>001N/12/Ba 001</t>
+          <t>012H/16/Vir001</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Barium</t>
+          <t>Virginite</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12001,14 +12001,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>47.59126</v>
+        <v>49.80048</v>
       </c>
       <c r="W160" t="n">
-        <v>-53.69011</v>
+        <v>-56.31995</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Lord &amp; Lady Gulch Mine</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>001L/14/Fl 005</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12073,14 +12073,14 @@
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>48.30663</v>
+        <v>46.87554</v>
       </c>
       <c r="W161" t="n">
-        <v>-58.68165</v>
+        <v>-55.4111</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Parsons Pond Cart Track</t>
+          <t>Baie Verte Mine</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>012I/04/Btm001</t>
+          <t>012H/16/Asb008</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Oil Shale</t>
+          <t>Magnesium, Asbestos</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12136,23 +12136,23 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T162" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U162" t="n">
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>50.00564</v>
+        <v>49.97974</v>
       </c>
       <c r="W162" t="n">
-        <v>-57.63187</v>
+        <v>-56.19399</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
         </is>
       </c>
     </row>
@@ -12162,12 +12162,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Baie Verte Mine</t>
+          <t>Black Duck Mine</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>012H/16/Asb008</t>
+          <t>001L/14/Fl 010</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Magnesium, Asbestos</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12217,14 +12217,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>49.97974</v>
+        <v>46.93201</v>
       </c>
       <c r="W163" t="n">
-        <v>-56.19399</v>
+        <v>-55.38881</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Borney Lake</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>002D/14/Stn001</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12289,14 +12289,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>48.9264</v>
+        <v>48.30663</v>
       </c>
       <c r="W164" t="n">
-        <v>-55.44535</v>
+        <v>-58.68165</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Doctors Pond Veins</t>
+          <t>Southern Cross Veins</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>001L/14/Fl 036</t>
+          <t>001L/14/Fl 020</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12361,14 +12361,14 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>46.92769</v>
+        <v>46.88974</v>
       </c>
       <c r="W165" t="n">
-        <v>-55.37593</v>
+        <v>-55.42958</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Parsons Pond No 3</t>
+          <t>Tarefare Mine</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>012H/13/Btm003</t>
+          <t>001L/14/Fl 006</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12433,14 +12433,14 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>49.97912</v>
+        <v>46.8912</v>
       </c>
       <c r="W166" t="n">
-        <v>-57.64547</v>
+        <v>-55.43112</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tarefare Mine</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>001L/14/Fl 006</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12505,14 +12505,14 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>46.8912</v>
+        <v>53.469</v>
       </c>
       <c r="W167" t="n">
-        <v>-55.43112</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -12522,12 +12522,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Blue Beach Mine</t>
+          <t>Mine Hill</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>001L/14/Fl 001</t>
+          <t>001N/07/Pph004</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Pyrophyllite</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12577,14 +12577,14 @@
         <v>30</v>
       </c>
       <c r="V168" t="n">
-        <v>46.91553</v>
+        <v>47.48</v>
       </c>
       <c r="W168" t="n">
-        <v>-55.40729</v>
+        <v>-52.95479</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
         </is>
       </c>
     </row>
@@ -12594,12 +12594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Black Duck Mine</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>001L/14/Fl 010</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12649,14 +12649,14 @@
         <v>30</v>
       </c>
       <c r="V169" t="n">
-        <v>46.93201</v>
+        <v>48.56074</v>
       </c>
       <c r="W169" t="n">
-        <v>-55.38881</v>
+        <v>-58.8161</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Southern Cross Veins</t>
+          <t>Collier Point</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>001L/14/Fl 020</t>
+          <t>001N/12/Ba 001</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Barium</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12721,14 +12721,14 @@
         <v>30</v>
       </c>
       <c r="V170" t="n">
-        <v>46.88974</v>
+        <v>47.59126</v>
       </c>
       <c r="W170" t="n">
-        <v>-55.42958</v>
+        <v>-53.69011</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
         </is>
       </c>
     </row>
@@ -12738,12 +12738,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Lord &amp; Lady Gulch Mine</t>
+          <t>Parsons Pond Cart Track</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>001L/14/Fl 005</t>
+          <t>012I/04/Btm001</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil Shale</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12784,23 +12784,23 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T171" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U171" t="n">
         <v>30</v>
       </c>
       <c r="V171" t="n">
-        <v>46.87554</v>
+        <v>50.00564</v>
       </c>
       <c r="W171" t="n">
-        <v>-55.4111</v>
+        <v>-57.63187</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Scrape Vein</t>
+          <t>Doctors Pond Veins</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>001L/14/Fl 035</t>
+          <t>001L/14/Fl 036</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -12865,14 +12865,14 @@
         <v>30</v>
       </c>
       <c r="V172" t="n">
-        <v>46.92547</v>
+        <v>46.92769</v>
       </c>
       <c r="W172" t="n">
-        <v>-55.37193</v>
+        <v>-55.37593</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Little Salt Cove</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>001L/14/Fl 016</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12937,14 +12937,14 @@
         <v>30</v>
       </c>
       <c r="V173" t="n">
-        <v>53.40462</v>
+        <v>46.87654</v>
       </c>
       <c r="W173" t="n">
-        <v>-65.08734</v>
+        <v>-55.43141</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12954,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Scrape Vein</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>001L/14/Fl 035</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13009,14 +13009,14 @@
         <v>30</v>
       </c>
       <c r="V174" t="n">
-        <v>48.50411</v>
+        <v>46.92547</v>
       </c>
       <c r="W174" t="n">
-        <v>-58.53451</v>
+        <v>-55.37193</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Bluff Head Mine</t>
+          <t>Director Mine</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>012B/15/Cr 001</t>
+          <t>001L/14/Fl 009</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Asbestos, Chromium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13081,14 +13081,14 @@
         <v>30</v>
       </c>
       <c r="V175" t="n">
-        <v>48.77717</v>
+        <v>46.90681</v>
       </c>
       <c r="W175" t="n">
-        <v>-58.59931</v>
+        <v>-55.42107</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
         </is>
       </c>
     </row>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Iron Springs Mine</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>001L/14/Fl 008</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13153,14 +13153,14 @@
         <v>30</v>
       </c>
       <c r="V176" t="n">
-        <v>53.469</v>
+        <v>46.88701</v>
       </c>
       <c r="W176" t="n">
-        <v>-64.91218000000001</v>
+        <v>-55.421</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Director Mine</t>
+          <t>Borney Lake</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>001L/14/Fl 009</t>
+          <t>002D/14/Stn001</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13225,14 +13225,14 @@
         <v>30</v>
       </c>
       <c r="V177" t="n">
-        <v>46.90681</v>
+        <v>48.9264</v>
       </c>
       <c r="W177" t="n">
-        <v>-55.42107</v>
+        <v>-55.44535</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Little Salt Cove</t>
+          <t>Bluff Head Mine</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>001L/14/Fl 016</t>
+          <t>012B/15/Cr 001</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Asbestos, Chromium</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13297,14 +13297,14 @@
         <v>30</v>
       </c>
       <c r="V178" t="n">
-        <v>46.87654</v>
+        <v>48.77717</v>
       </c>
       <c r="W178" t="n">
-        <v>-55.43141</v>
+        <v>-58.59931</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Middle Arm Brook</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>012H/16/Vir001</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Virginite</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13441,14 +13441,14 @@
         <v>30</v>
       </c>
       <c r="V180" t="n">
-        <v>49.80048</v>
+        <v>48.50411</v>
       </c>
       <c r="W180" t="n">
-        <v>-56.31995</v>
+        <v>-58.53451</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13458,12 +13458,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Parsons Pond No 2</t>
+          <t>Blue Beach Mine</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>012H/13/Btm002</t>
+          <t>001L/14/Fl 001</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13513,14 +13513,14 @@
         <v>30</v>
       </c>
       <c r="V181" t="n">
-        <v>49.97421</v>
+        <v>46.91553</v>
       </c>
       <c r="W181" t="n">
-        <v>-57.60538</v>
+        <v>-55.40729</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
         </is>
       </c>
     </row>
@@ -13530,12 +13530,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Parsons Pond No 1</t>
+          <t>Hares Ears Vein</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>012H/13/Btm001</t>
+          <t>001L/14/Fl 007</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13576,23 +13576,23 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T182" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U182" t="n">
         <v>30</v>
       </c>
       <c r="V182" t="n">
-        <v>49.99228</v>
+        <v>46.88814</v>
       </c>
       <c r="W182" t="n">
-        <v>-57.58928</v>
+        <v>-55.41178</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Parsons Pond No 4</t>
+          <t>Parsons Pond No 1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>012H/13/Btm004</t>
+          <t>012H/13/Btm001</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13648,23 +13648,23 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T183" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U183" t="n">
         <v>30</v>
       </c>
       <c r="V183" t="n">
-        <v>49.99787</v>
+        <v>49.99228</v>
       </c>
       <c r="W183" t="n">
-        <v>-57.63818</v>
+        <v>-57.58928</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Grey Copper Mine</t>
+          <t>Little Bay Mine</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>002E/11/Cu 001</t>
+          <t>002E/12/Cu 030</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Iron, Copper</t>
+          <t>Iron, Gold, Copper</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13729,14 +13729,14 @@
         <v>26</v>
       </c>
       <c r="V184" t="n">
-        <v>49.5173</v>
+        <v>49.5961</v>
       </c>
       <c r="W184" t="n">
-        <v>-55.2721</v>
+        <v>-55.94531</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Scotia Formation</t>
+          <t>Fleming No 3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>001N/10/Fe 002</t>
+          <t>023J/14/Fe 022</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13801,14 +13801,14 @@
         <v>26</v>
       </c>
       <c r="V185" t="n">
-        <v>47.64169</v>
+        <v>54.85836</v>
       </c>
       <c r="W185" t="n">
-        <v>-52.97639</v>
+        <v>-67.03167999999999</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Gull Island Formation</t>
+          <t>Timmins No 2</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>001N/10/Fe 003</t>
+          <t>023J/14/Fe 019</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -13873,14 +13873,14 @@
         <v>26</v>
       </c>
       <c r="V186" t="n">
-        <v>47.65193</v>
+        <v>54.89421</v>
       </c>
       <c r="W186" t="n">
-        <v>-52.95654</v>
+        <v>-67.08716</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Redmond No 2</t>
+          <t>Timmins No 4</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>023J/10/Fe 002</t>
+          <t>023J/14/Fe 023</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13945,14 +13945,14 @@
         <v>26</v>
       </c>
       <c r="V187" t="n">
-        <v>54.69738</v>
+        <v>54.89884</v>
       </c>
       <c r="W187" t="n">
-        <v>-66.77224</v>
+        <v>-67.10881000000001</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
         </is>
       </c>
     </row>
@@ -13962,24 +13962,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Little Bay Mine</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>002E/12/Cu 030</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Iron, Gold, Copper</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14017,14 +14017,14 @@
         <v>26</v>
       </c>
       <c r="V188" t="n">
-        <v>49.5961</v>
+        <v>47.53392</v>
       </c>
       <c r="W188" t="n">
-        <v>-55.94531</v>
+        <v>-53.18293</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -14034,24 +14034,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Dominion Formation</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>001N/10/Fe 001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14089,14 +14089,14 @@
         <v>26</v>
       </c>
       <c r="V189" t="n">
-        <v>49.50376</v>
+        <v>47.64164</v>
       </c>
       <c r="W189" t="n">
-        <v>-55.21553</v>
+        <v>-52.95309</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14106,24 +14106,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Redmond No 2</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>023J/10/Fe 002</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14161,14 +14161,14 @@
         <v>26</v>
       </c>
       <c r="V190" t="n">
-        <v>47.53392</v>
+        <v>54.69738</v>
       </c>
       <c r="W190" t="n">
-        <v>-53.18293</v>
+        <v>-66.77224</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dominion Formation</t>
+          <t>Gull Island Formation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>001N/10/Fe 001</t>
+          <t>001N/10/Fe 003</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -14233,14 +14233,14 @@
         <v>26</v>
       </c>
       <c r="V191" t="n">
-        <v>47.64164</v>
+        <v>47.65193</v>
       </c>
       <c r="W191" t="n">
-        <v>-52.95309</v>
+        <v>-52.95654</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -14250,12 +14250,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cliff Mine</t>
+          <t>Scotia Formation</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>012B/09/Fe 001</t>
+          <t>001N/10/Fe 002</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -14305,14 +14305,14 @@
         <v>26</v>
       </c>
       <c r="V192" t="n">
-        <v>48.54434</v>
+        <v>47.64169</v>
       </c>
       <c r="W192" t="n">
-        <v>-58.49915</v>
+        <v>-52.97639</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Skindles Mine</t>
+          <t>Timmins No 1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>012B/09/Fe 004</t>
+          <t>023J/14/Fe 018</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14377,14 +14377,14 @@
         <v>26</v>
       </c>
       <c r="V193" t="n">
-        <v>48.54069</v>
+        <v>54.88449</v>
       </c>
       <c r="W193" t="n">
-        <v>-58.48888</v>
+        <v>-67.08575</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
         </is>
       </c>
     </row>
@@ -14394,24 +14394,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Timmins No 6</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>023J/15/Fe 010</t>
+          <t>023J/14/Fe 021</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14449,14 +14449,14 @@
         <v>26</v>
       </c>
       <c r="V194" t="n">
-        <v>54.77437</v>
+        <v>54.90148</v>
       </c>
       <c r="W194" t="n">
-        <v>-66.82881</v>
+        <v>-67.09757999999999</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14466,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ruth Lake No 7</t>
+          <t>Skindles Mine</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>023J/15/Fe 006</t>
+          <t>012B/09/Fe 004</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
         <v>26</v>
       </c>
       <c r="V195" t="n">
-        <v>54.80557</v>
+        <v>48.54069</v>
       </c>
       <c r="W195" t="n">
-        <v>-66.90618000000001</v>
+        <v>-58.48888</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14538,24 +14538,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Ruth Lake No 5</t>
+          <t>Cliff Mine</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>023J/15/Fe 007</t>
+          <t>012B/09/Fe 001</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14593,14 +14593,14 @@
         <v>26</v>
       </c>
       <c r="V196" t="n">
-        <v>54.80503</v>
+        <v>48.54434</v>
       </c>
       <c r="W196" t="n">
-        <v>-66.88023</v>
+        <v>-58.49915</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14610,24 +14610,24 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ruth Lake No 6</t>
+          <t>Grey Copper Mine</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>023J/15/Fe 008</t>
+          <t>002E/11/Cu 001</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron, Copper</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14665,14 +14665,14 @@
         <v>26</v>
       </c>
       <c r="V197" t="n">
-        <v>54.80104</v>
+        <v>49.5173</v>
       </c>
       <c r="W197" t="n">
-        <v>-66.87327999999999</v>
+        <v>-55.2721</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -14682,24 +14682,24 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ruth Lake No 9</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>023J/15/Fe 005</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14737,14 +14737,14 @@
         <v>26</v>
       </c>
       <c r="V198" t="n">
-        <v>54.80033</v>
+        <v>49.50376</v>
       </c>
       <c r="W198" t="n">
-        <v>-66.89447</v>
+        <v>-55.21553</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14754,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ruth Lake No 1</t>
+          <t>Smallwood Mine</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>023J/15/Fe 002</t>
+          <t>023G/02/Fe 001</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14809,14 +14809,14 @@
         <v>26</v>
       </c>
       <c r="V199" t="n">
-        <v>54.79145</v>
+        <v>53.03718</v>
       </c>
       <c r="W199" t="n">
-        <v>-66.85449</v>
+        <v>-66.93694000000001</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14826,24 +14826,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Wishart No 1 (Wishart Mine)</t>
+          <t>Wishart No 2 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>023J/15/Fe 003</t>
+          <t>023J/15/Fe 004</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14881,14 +14881,14 @@
         <v>26</v>
       </c>
       <c r="V200" t="n">
-        <v>54.76166</v>
+        <v>54.7654</v>
       </c>
       <c r="W200" t="n">
-        <v>-66.88793</v>
+        <v>-66.9067</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Wishart No 2 (Wishart Mine)</t>
+          <t>Lorraine Mine</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>023J/15/Fe 004</t>
+          <t>023G/02/Fe 004</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14953,14 +14953,14 @@
         <v>26</v>
       </c>
       <c r="V201" t="n">
-        <v>54.7654</v>
+        <v>53.06833</v>
       </c>
       <c r="W201" t="n">
-        <v>-66.9067</v>
+        <v>-66.94949</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14970,12 +14970,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ruth Lake No 3</t>
+          <t>Ruth Lake No 1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>023J/15/Fe 001</t>
+          <t>023J/15/Fe 002</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
         <v>26</v>
       </c>
       <c r="V202" t="n">
-        <v>54.80404</v>
+        <v>54.79145</v>
       </c>
       <c r="W202" t="n">
-        <v>-66.87016</v>
+        <v>-66.85449</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -15042,12 +15042,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Smallwood Mine</t>
+          <t>Ruth Lake No 3</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>023G/02/Fe 001</t>
+          <t>023J/15/Fe 001</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -15097,14 +15097,14 @@
         <v>26</v>
       </c>
       <c r="V203" t="n">
-        <v>53.03718</v>
+        <v>54.80404</v>
       </c>
       <c r="W203" t="n">
-        <v>-66.93694000000001</v>
+        <v>-66.87016</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15114,24 +15114,24 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lorraine Mine</t>
+          <t>Wishart No 1 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>023G/02/Fe 004</t>
+          <t>023J/15/Fe 003</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -15169,14 +15169,14 @@
         <v>26</v>
       </c>
       <c r="V204" t="n">
-        <v>53.06833</v>
+        <v>54.76166</v>
       </c>
       <c r="W204" t="n">
-        <v>-66.94949</v>
+        <v>-66.88793</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Fleming No 3</t>
+          <t>Ruth Lake No 9</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>023J/14/Fe 022</t>
+          <t>023J/15/Fe 005</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -15241,14 +15241,14 @@
         <v>26</v>
       </c>
       <c r="V205" t="n">
-        <v>54.85836</v>
+        <v>54.80033</v>
       </c>
       <c r="W205" t="n">
-        <v>-67.03167999999999</v>
+        <v>-66.89447</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -15258,24 +15258,24 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Timmins No 1</t>
+          <t>Ruth Lake No 5</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>023J/14/Fe 018</t>
+          <t>023J/15/Fe 007</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -15313,14 +15313,14 @@
         <v>26</v>
       </c>
       <c r="V206" t="n">
-        <v>54.88449</v>
+        <v>54.80503</v>
       </c>
       <c r="W206" t="n">
-        <v>-67.08575</v>
+        <v>-66.88023</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15330,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timmins No 4</t>
+          <t>Ruth Lake No 7</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>023J/14/Fe 023</t>
+          <t>023J/15/Fe 006</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15385,14 +15385,14 @@
         <v>26</v>
       </c>
       <c r="V207" t="n">
-        <v>54.89884</v>
+        <v>54.80557</v>
       </c>
       <c r="W207" t="n">
-        <v>-67.10881000000001</v>
+        <v>-66.90618000000001</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -15402,24 +15402,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Timmins No 2</t>
+          <t>Ruth Lake No 6</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>023J/14/Fe 019</t>
+          <t>023J/15/Fe 008</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15457,14 +15457,14 @@
         <v>26</v>
       </c>
       <c r="V208" t="n">
-        <v>54.89421</v>
+        <v>54.80104</v>
       </c>
       <c r="W208" t="n">
-        <v>-67.08716</v>
+        <v>-66.87327999999999</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -15474,24 +15474,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Timmins No 6</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>023J/14/Fe 021</t>
+          <t>023J/15/Fe 010</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15529,14 +15529,14 @@
         <v>26</v>
       </c>
       <c r="V209" t="n">
-        <v>54.90148</v>
+        <v>54.77437</v>
       </c>
       <c r="W209" t="n">
-        <v>-67.09757999999999</v>
+        <v>-66.82881</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Michelin Deposit</t>
+          <t>Copper Creek BV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>013J/12/U  001</t>
+          <t>012H/16/Cu 040</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>44</v>
       </c>
       <c r="V2" t="n">
-        <v>54.58562</v>
+        <v>49.91887</v>
       </c>
       <c r="W2" t="n">
-        <v>-59.98056</v>
+        <v>-56.20986</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rainbow Deposit</t>
+          <t>Horseshoe Zone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>013J/12/U  008</t>
+          <t>002E/02/Au 039</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,23 +688,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>54.56417</v>
+        <v>49.01341</v>
       </c>
       <c r="W3" t="n">
-        <v>-59.99369</v>
+        <v>-54.81741</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jacques Lake</t>
+          <t>Viking Gold-Thor Trend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>013J/12/U  018</t>
+          <t>012H/10/Au 011</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -760,23 +760,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U4" t="n">
         <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>54.71754</v>
+        <v>49.69447</v>
       </c>
       <c r="W4" t="n">
-        <v>-59.59268</v>
+        <v>-56.99193</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Road Zone</t>
+          <t>PW Zone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>012H/15/Au 011</t>
+          <t>011O/10/Au 011</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -841,14 +841,14 @@
         <v>44</v>
       </c>
       <c r="V5" t="n">
-        <v>49.88465</v>
+        <v>47.74631</v>
       </c>
       <c r="W5" t="n">
-        <v>-56.83885</v>
+        <v>-58.94364</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apsy Zone</t>
+          <t>Deep Fox</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>012H/15/Au 014</t>
+          <t>003D/05/Ree007</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>44</v>
       </c>
       <c r="V6" t="n">
-        <v>49.89471</v>
+        <v>52.3805</v>
       </c>
       <c r="W6" t="n">
-        <v>-56.82917</v>
+        <v>-55.64987</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deer Cove Main Zone</t>
+          <t>Mart Lake Graphite</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>012I/01/Au 001</t>
+          <t>023B/14/Gf 001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>44</v>
       </c>
       <c r="V7" t="n">
-        <v>50.01619</v>
+        <v>52.8283</v>
       </c>
       <c r="W7" t="n">
-        <v>-56.04389</v>
+        <v>-67.01484000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Turners Ridge</t>
+          <t>Rainbow Deposit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>012H/11/Pb 001</t>
+          <t>013J/12/U  008</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U8" t="n">
         <v>44</v>
       </c>
       <c r="V8" t="n">
-        <v>49.59029</v>
+        <v>54.56417</v>
       </c>
       <c r="W8" t="n">
-        <v>-57.00443</v>
+        <v>-59.99369</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mann #1</t>
+          <t>Michelin Deposit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>013L/01/Be 001</t>
+          <t>013J/12/U  001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Niobium, Uranium, Zinc, Beryllium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>44</v>
       </c>
       <c r="V9" t="n">
-        <v>54.23929</v>
+        <v>54.58562</v>
       </c>
       <c r="W9" t="n">
-        <v>-62.3924</v>
+        <v>-59.98056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Two Tom Lake</t>
+          <t>Deer Cove Main Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>013L/01/REE001</t>
+          <t>012I/01/Au 001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>54.21359</v>
+        <v>50.01619</v>
       </c>
       <c r="W10" t="n">
-        <v>-62.14192</v>
+        <v>-56.04389</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nash Lake (Main Zone)</t>
+          <t>Apsy Zone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>013J/13/U  006</t>
+          <t>012H/15/Au 014</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1273,14 +1273,14 @@
         <v>44</v>
       </c>
       <c r="V11" t="n">
-        <v>54.91032</v>
+        <v>49.89471</v>
       </c>
       <c r="W11" t="n">
-        <v>-59.62004</v>
+        <v>-56.82917</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
         </is>
       </c>
     </row>
@@ -1290,24 +1290,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inda Lake</t>
+          <t>Road Zone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>013J/13/U  009</t>
+          <t>012H/15/Au 011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Uranium</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>44</v>
       </c>
       <c r="V12" t="n">
-        <v>54.92456</v>
+        <v>49.88465</v>
       </c>
       <c r="W12" t="n">
-        <v>-59.5807</v>
+        <v>-56.83885</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gear Lake</t>
+          <t>Jacques Lake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>013J/13/U  010</t>
+          <t>013J/12/U  018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1417,14 +1417,14 @@
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>54.94329</v>
+        <v>54.71754</v>
       </c>
       <c r="W13" t="n">
-        <v>-59.54386</v>
+        <v>-59.59268</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
         </is>
       </c>
     </row>
@@ -1434,24 +1434,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kitts</t>
+          <t>Turners Ridge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>013J/14/U  001</t>
+          <t>012H/11/Pb 001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>44</v>
       </c>
       <c r="V14" t="n">
-        <v>54.99779</v>
+        <v>49.59029</v>
       </c>
       <c r="W14" t="n">
-        <v>-59.4872</v>
+        <v>-57.00443</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H Brook Showing</t>
+          <t>Kitts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>011O/15/Au 004</t>
+          <t>013J/14/U  001</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U16" t="n">
         <v>44</v>
       </c>
       <c r="V16" t="n">
-        <v>47.7624</v>
+        <v>54.99779</v>
       </c>
       <c r="W16" t="n">
-        <v>-58.91357</v>
+        <v>-59.4872</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit #4 Zone</t>
+          <t>Gear Lake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>011O/15/Au 001</t>
+          <t>013J/13/U  010</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>44</v>
       </c>
       <c r="V17" t="n">
-        <v>47.76081</v>
+        <v>54.94329</v>
       </c>
       <c r="W17" t="n">
-        <v>-58.91872</v>
+        <v>-59.54386</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
         </is>
       </c>
     </row>
@@ -1722,24 +1722,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit 41 Zone</t>
+          <t>Inda Lake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>011O/15/Au 002</t>
+          <t>013J/13/U  009</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Molybdenum, Copper, Uranium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1777,14 +1777,14 @@
         <v>44</v>
       </c>
       <c r="V18" t="n">
-        <v>47.75858</v>
+        <v>54.92456</v>
       </c>
       <c r="W18" t="n">
-        <v>-58.92331</v>
+        <v>-59.5807</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>51 Zone</t>
+          <t>Nash Lake (Main Zone)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>011O/15/Au 003</t>
+          <t>013J/13/U  006</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>44</v>
       </c>
       <c r="V19" t="n">
-        <v>47.75077</v>
+        <v>54.91032</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.93823</v>
+        <v>-59.62004</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>H Brook Showing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>011O/15/Au 004</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>44</v>
       </c>
       <c r="V20" t="n">
-        <v>48.69485</v>
+        <v>47.7624</v>
       </c>
       <c r="W20" t="n">
-        <v>-58.68177</v>
+        <v>-58.91357</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Keats</t>
+          <t>51 Zone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>002D/15/Au 010</t>
+          <t>011O/15/Au 003</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>44</v>
       </c>
       <c r="V21" t="n">
-        <v>48.97891</v>
+        <v>47.75077</v>
       </c>
       <c r="W21" t="n">
-        <v>-54.8402</v>
+        <v>-58.93823</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Point Leamington Deposit</t>
+          <t>Cape Ray Gold Deposit 41 Zone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>002E/05/Zn 001</t>
+          <t>011O/15/Au 002</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead, Zinc</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>44</v>
       </c>
       <c r="V22" t="n">
-        <v>49.27672</v>
+        <v>47.75858</v>
       </c>
       <c r="W22" t="n">
-        <v>-55.63152</v>
+        <v>-58.92331</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bull Road Showing</t>
+          <t>Cape Ray Gold Deposit #4 Zone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>002E/12/Zn 007</t>
+          <t>011O/15/Au 001</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Antimony, Zinc</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>44</v>
       </c>
       <c r="V23" t="n">
-        <v>49.51431</v>
+        <v>47.76081</v>
       </c>
       <c r="W23" t="n">
-        <v>-55.7118</v>
+        <v>-58.91872</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2154,24 +2154,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Windowglass Hill - Main Zone</t>
+          <t>Two Tom Lake</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>011O/10/Au 001</t>
+          <t>013L/01/REE001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>44</v>
       </c>
       <c r="V24" t="n">
-        <v>47.74279</v>
+        <v>54.21359</v>
       </c>
       <c r="W24" t="n">
-        <v>-58.95727</v>
+        <v>-62.14192</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Far Eastern Deeps</t>
+          <t>Mann #1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>014D/08/Ni 013</t>
+          <t>013L/01/Be 001</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Niobium, Uranium, Zinc, Beryllium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>44</v>
       </c>
       <c r="V25" t="n">
-        <v>56.32109</v>
+        <v>54.23929</v>
       </c>
       <c r="W25" t="n">
-        <v>-62.06064</v>
+        <v>-62.3924</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
         </is>
       </c>
     </row>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ackley City</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>001M/11/Mo 002</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Molybdenum</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2353,14 +2353,14 @@
         <v>44</v>
       </c>
       <c r="V26" t="n">
-        <v>47.69347</v>
+        <v>48.69485</v>
       </c>
       <c r="W26" t="n">
-        <v>-55.20716</v>
+        <v>-58.68177</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -2370,24 +2370,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Strickland - Copper Zone</t>
+          <t>Keats</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>011O/16/Cu 001</t>
+          <t>002D/15/Au 010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>44</v>
       </c>
       <c r="V27" t="n">
-        <v>47.80365</v>
+        <v>48.97891</v>
       </c>
       <c r="W27" t="n">
-        <v>-58.30275</v>
+        <v>-54.8402</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
         </is>
       </c>
     </row>
@@ -2442,24 +2442,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Two Time</t>
+          <t>Bull Road Showing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>013K/11/U  005</t>
+          <t>002E/12/Zn 007</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper, Silver, Lead, Antimony, Zinc</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2497,14 +2497,14 @@
         <v>44</v>
       </c>
       <c r="V28" t="n">
-        <v>54.56554</v>
+        <v>49.51431</v>
       </c>
       <c r="W28" t="n">
-        <v>-61.17152</v>
+        <v>-55.7118</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2514,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Voisey's Bay, South Eastern Deeps</t>
+          <t>Point Leamington Deposit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>014D/08/Ni 017</t>
+          <t>002E/05/Zn 001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Silver, Copper, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>44</v>
       </c>
       <c r="V29" t="n">
-        <v>56.31756</v>
+        <v>49.27672</v>
       </c>
       <c r="W29" t="n">
-        <v>-62.06953</v>
+        <v>-55.63152</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Voisey's Bay, North Eastern Deeps</t>
+          <t>Windowglass Hill - Main Zone</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>014D/08/Ni 011</t>
+          <t>011O/10/Au 001</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2641,14 +2641,14 @@
         <v>44</v>
       </c>
       <c r="V30" t="n">
-        <v>56.32929</v>
+        <v>47.74279</v>
       </c>
       <c r="W30" t="n">
-        <v>-62.07733</v>
+        <v>-58.95727</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2730,24 +2730,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moran Lake C-Zone</t>
+          <t>Voisey's Bay, North Eastern Deeps</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>013K/07/U  002</t>
+          <t>014D/08/Ni 011</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2785,14 +2785,14 @@
         <v>44</v>
       </c>
       <c r="V32" t="n">
-        <v>54.47908</v>
+        <v>56.32929</v>
       </c>
       <c r="W32" t="n">
-        <v>-60.9581</v>
+        <v>-62.07733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Voisey's Bay, South Eastern Deeps</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>013K/07/U  007</t>
+          <t>014D/08/Ni 017</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Vanadium, Uranium</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2857,14 +2857,14 @@
         <v>44</v>
       </c>
       <c r="V33" t="n">
-        <v>54.46751</v>
+        <v>56.31756</v>
       </c>
       <c r="W33" t="n">
-        <v>-60.98105</v>
+        <v>-62.06953</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
         </is>
       </c>
     </row>
@@ -2874,24 +2874,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jaclyn Main - Golden Promise</t>
+          <t>Two Time</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>012A/16/Au 002</t>
+          <t>013K/11/U  005</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2929,14 +2929,14 @@
         <v>44</v>
       </c>
       <c r="V34" t="n">
-        <v>48.90572</v>
+        <v>54.56554</v>
       </c>
       <c r="W34" t="n">
-        <v>-56.15002</v>
+        <v>-61.17152</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Strickland - Main Zone</t>
+          <t>Area 1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>011O/16/Zn 001</t>
+          <t>013K/07/U  007</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Gold, Zinc</t>
+          <t>Copper, Vanadium, Uranium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>44</v>
       </c>
       <c r="V35" t="n">
-        <v>47.80818</v>
+        <v>54.46751</v>
       </c>
       <c r="W35" t="n">
-        <v>-58.29993</v>
+        <v>-60.98105</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Strickland - Silver Hill Zone</t>
+          <t>Moran Lake C-Zone</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>011O/16/Zn 002</t>
+          <t>013K/07/U  002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>44</v>
       </c>
       <c r="V36" t="n">
-        <v>47.81</v>
+        <v>54.47908</v>
       </c>
       <c r="W36" t="n">
-        <v>-58.2985</v>
+        <v>-60.9581</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
         </is>
       </c>
     </row>
@@ -3090,24 +3090,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Moly Brook</t>
+          <t>Grey River Tungsten</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>011P/11/Mo 001</t>
+          <t>011P/11/W  001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,14 +3145,14 @@
         <v>44</v>
       </c>
       <c r="V37" t="n">
-        <v>47.61683</v>
+        <v>47.59343</v>
       </c>
       <c r="W37" t="n">
-        <v>-57.1034</v>
+        <v>-57.10342</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3162,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Grey River Tungsten</t>
+          <t>Moly Brook</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>011P/11/W  001</t>
+          <t>011P/11/Mo 001</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3217,14 +3217,14 @@
         <v>44</v>
       </c>
       <c r="V38" t="n">
-        <v>47.59343</v>
+        <v>47.61683</v>
       </c>
       <c r="W38" t="n">
-        <v>-57.10342</v>
+        <v>-57.1034</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Springer's Hill-Main Showing</t>
+          <t>Strickland - Silver Hill Zone</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>012B/16/Cr 002</t>
+          <t>011O/16/Zn 002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>44</v>
       </c>
       <c r="V39" t="n">
-        <v>48.7927</v>
+        <v>47.81</v>
       </c>
       <c r="W39" t="n">
-        <v>-58.44526</v>
+        <v>-58.2985</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -3306,24 +3306,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Saddle Zone</t>
+          <t>Strickland - Main Zone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>002E/02/Au 038</t>
+          <t>011O/16/Zn 001</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Copper, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U40" t="n">
         <v>44</v>
       </c>
       <c r="V40" t="n">
-        <v>49.00899</v>
+        <v>47.80818</v>
       </c>
       <c r="W40" t="n">
-        <v>-54.81554</v>
+        <v>-58.29993</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Keats South</t>
+          <t>Jaclyn Main - Golden Promise</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>002D/15/Au 060</t>
+          <t>012A/16/Au 002</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>44</v>
       </c>
       <c r="V41" t="n">
-        <v>48.97791</v>
+        <v>48.90572</v>
       </c>
       <c r="W41" t="n">
-        <v>-54.84407</v>
+        <v>-56.15002</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viking Gold-Thor Trend</t>
+          <t>Strickland - Copper Zone</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>012H/10/Au 011</t>
+          <t>011O/16/Cu 001</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3496,23 +3496,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
         <v>44</v>
       </c>
       <c r="V42" t="n">
-        <v>49.69447</v>
+        <v>47.80365</v>
       </c>
       <c r="W42" t="n">
-        <v>-56.99193</v>
+        <v>-58.30275</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Horseshoe Zone</t>
+          <t>Ackley City</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>002E/02/Au 039</t>
+          <t>001M/11/Mo 002</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>44</v>
       </c>
       <c r="V43" t="n">
-        <v>49.01341</v>
+        <v>47.69347</v>
       </c>
       <c r="W43" t="n">
-        <v>-54.81741</v>
+        <v>-55.20716</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
         </is>
       </c>
     </row>
@@ -3594,24 +3594,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Copper Creek BV</t>
+          <t>Voisey's Bay, Far Eastern Deeps</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>012H/16/Cu 040</t>
+          <t>014D/08/Ni 013</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>44</v>
       </c>
       <c r="V44" t="n">
-        <v>49.91887</v>
+        <v>56.32109</v>
       </c>
       <c r="W44" t="n">
-        <v>-56.20986</v>
+        <v>-62.06064</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deep Fox</t>
+          <t>Springer's Hill-Main Showing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>003D/05/Ree007</t>
+          <t>012B/16/Cr 002</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>44</v>
       </c>
       <c r="V45" t="n">
-        <v>52.3805</v>
+        <v>48.7927</v>
       </c>
       <c r="W45" t="n">
-        <v>-55.64987</v>
+        <v>-58.44526</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PW Zone</t>
+          <t>Keats South</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>011O/10/Au 011</t>
+          <t>002D/15/Au 060</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>44</v>
       </c>
       <c r="V46" t="n">
-        <v>47.74631</v>
+        <v>48.97791</v>
       </c>
       <c r="W46" t="n">
-        <v>-58.94364</v>
+        <v>-54.84407</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mart Lake Graphite</t>
+          <t>Saddle Zone</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>023B/14/Gf 001</t>
+          <t>002E/02/Au 038</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3856,23 +3856,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U47" t="n">
         <v>44</v>
       </c>
       <c r="V47" t="n">
-        <v>52.8283</v>
+        <v>49.00899</v>
       </c>
       <c r="W47" t="n">
-        <v>-67.01484000000001</v>
+        <v>-54.81554</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Foxtrot</t>
+          <t>Lewis Brook Mine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>003D/05/Ree001</t>
+          <t>012B/15/Asb001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>37</v>
       </c>
       <c r="V48" t="n">
-        <v>52.40035</v>
+        <v>48.77071</v>
       </c>
       <c r="W48" t="n">
-        <v>-55.82418</v>
+        <v>-58.56548</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deer Cove Talc Zone</t>
+          <t>Beaver Dam</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>012I/01/Tlc001</t>
+          <t>012H/15/Au 018</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Magnesium, Talc</t>
+          <t>Arsenic, Gold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4009,14 +4009,14 @@
         <v>37</v>
       </c>
       <c r="V49" t="n">
-        <v>50.01534</v>
+        <v>49.86141</v>
       </c>
       <c r="W49" t="n">
-        <v>-56.04949</v>
+        <v>-56.85295</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Beaver Dam</t>
+          <t>Strange Lake</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>012H/15/Au 018</t>
+          <t>024A/08/Ree001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Arsenic, Gold</t>
+          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>49.86141</v>
+        <v>56.31656</v>
       </c>
       <c r="W50" t="n">
-        <v>-56.85295</v>
+        <v>-64.12678</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Strange Lake</t>
+          <t>Norsk South Block</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>024A/08/Ree001</t>
+          <t>012B/10/Dol004</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>56.31656</v>
+        <v>48.52445</v>
       </c>
       <c r="W51" t="n">
-        <v>-64.12678</v>
+        <v>-58.99684</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Norsk North Block</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>012B/10/Dol003</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4225,14 +4225,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>48.39536</v>
+        <v>48.53397</v>
       </c>
       <c r="W52" t="n">
-        <v>-58.42046</v>
+        <v>-58.9773</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Porcupine Strand North Beach</t>
+          <t>Round Pond Deposit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>013I/03/Ti 001</t>
+          <t>012P/08/Zn 015</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
+          <t>Fluorine, Lead, Zinc</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>54.03818</v>
+        <v>51.25735</v>
       </c>
       <c r="W53" t="n">
-        <v>-57.31912</v>
+        <v>-56.26701</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4386,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Round Pond Deposit</t>
+          <t>Porcupine Strand North Beach</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>012P/08/Zn 015</t>
+          <t>013I/03/Ti 001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fluorine, Lead, Zinc</t>
+          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4441,14 +4441,14 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>51.25735</v>
+        <v>54.03818</v>
       </c>
       <c r="W55" t="n">
-        <v>-56.26701</v>
+        <v>-57.31912</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Norsk South Block</t>
+          <t>Deer Cove Talc Zone</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>012B/10/Dol004</t>
+          <t>012I/01/Tlc001</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Magnesium, Talc</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>48.52445</v>
+        <v>50.01534</v>
       </c>
       <c r="W56" t="n">
-        <v>-58.99684</v>
+        <v>-56.04949</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Norsk North Block</t>
+          <t>Foxtrot</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>012B/10/Dol003</t>
+          <t>003D/05/Ree001</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>48.53397</v>
+        <v>52.40035</v>
       </c>
       <c r="W57" t="n">
-        <v>-58.9773</v>
+        <v>-55.82418</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lewis Brook Mine</t>
+          <t>Sheep Brook</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>012B/15/Asb001</t>
+          <t>012B/08/Gyp001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>37</v>
       </c>
       <c r="V60" t="n">
-        <v>48.77071</v>
+        <v>48.39536</v>
       </c>
       <c r="W60" t="n">
-        <v>-58.56548</v>
+        <v>-58.42046</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Voisey's Bay, Ovoid</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>014D/08/Ni 001</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>47.4063</v>
+        <v>56.33134</v>
       </c>
       <c r="W61" t="n">
-        <v>-52.70699</v>
+        <v>-62.09706</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>York Harbour Mine</t>
+          <t>AGS Vein</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>012G/01/Cu 002</t>
+          <t>001L/14/Fl 013</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
+          <t>Zinc, Lead, Copper, Fluorine</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>49.05208</v>
+        <v>46.91489</v>
       </c>
       <c r="W62" t="n">
-        <v>-58.30769</v>
+        <v>-55.48584</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
         </is>
       </c>
     </row>
@@ -4962,24 +4962,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sleepy Hollow</t>
+          <t>Blow-Me-Down Chromite #1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>002E/12/Cu 031</t>
+          <t>012G/01/Cr 001</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5008,23 +5008,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T63" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U63" t="n">
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>49.59747</v>
+        <v>49.01096</v>
       </c>
       <c r="W63" t="n">
-        <v>-55.94735</v>
+        <v>-58.24371</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -5034,24 +5034,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Miles Cove Mine</t>
+          <t>Goose Cove</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>002E/12/Cu 012</t>
+          <t>002M/05/Cu 001</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Zinc, Nickel, Iron, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>49.53936</v>
+        <v>51.31009</v>
       </c>
       <c r="W64" t="n">
-        <v>-55.79062</v>
+        <v>-55.62342</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Goose Cove</t>
+          <t>York Harbour Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>002M/05/Cu 001</t>
+          <t>012G/01/Cu 002</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zinc, Nickel, Iron, Copper</t>
+          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>51.31009</v>
+        <v>49.05208</v>
       </c>
       <c r="W65" t="n">
-        <v>-55.62342</v>
+        <v>-58.30769</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -5178,24 +5178,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blow-Me-Down Chromite #1</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>012G/01/Cr 001</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>49.01096</v>
+        <v>50.27283</v>
       </c>
       <c r="W66" t="n">
-        <v>-58.24371</v>
+        <v>-57.46448</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Ovoid</t>
+          <t>Terra Nova Mine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>014D/08/Ni 001</t>
+          <t>012H/16/Cu 004</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>56.33134</v>
+        <v>49.92133</v>
       </c>
       <c r="W67" t="n">
-        <v>-62.09706</v>
+        <v>-56.22896</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-G Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>012I/06/Zn 007</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>50.29448</v>
+        <v>50.31118</v>
       </c>
       <c r="W68" t="n">
-        <v>-57.44714</v>
+        <v>-57.43009</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-Q Zone</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 016</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>50.27283</v>
+        <v>50.29741</v>
       </c>
       <c r="W69" t="n">
-        <v>-57.46448</v>
+        <v>-57.48016</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Browning Mine</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012H/10/Au 001</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>50.31118</v>
+        <v>49.71799</v>
       </c>
       <c r="W70" t="n">
-        <v>-57.43009</v>
+        <v>-56.92565</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5538,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-H Zone</t>
+          <t>Goldenville</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>012I/06/Zn 008</t>
+          <t>012H/16/Au 033</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper, Iron, Gold</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5584,23 +5584,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T71" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U71" t="n">
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>50.29179</v>
+        <v>49.99193</v>
       </c>
       <c r="W71" t="n">
-        <v>-57.44599</v>
+        <v>-56.05735</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-J Zone</t>
+          <t>Stog'er Tight</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>012I/06/Zn 009</t>
+          <t>012H/16/Au 041</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5665,14 +5665,14 @@
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>50.30247</v>
+        <v>49.9661</v>
       </c>
       <c r="W72" t="n">
-        <v>-57.47459</v>
+        <v>-56.07765</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-K Zone</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>012I/06/Zn 010</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5737,14 +5737,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>50.2935</v>
+        <v>49.19579</v>
       </c>
       <c r="W73" t="n">
-        <v>-57.46875</v>
+        <v>-57.84974</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -5754,24 +5754,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-L Zone</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>012I/06/Zn 011</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lead, Dolomite, Zinc</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5809,14 +5809,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>50.27686</v>
+        <v>52.961</v>
       </c>
       <c r="W74" t="n">
-        <v>-57.46788</v>
+        <v>-66.81446</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5826,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-M Zone</t>
+          <t>Daniel's Harbour Mine-J Zone</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>012I/06/Zn 012</t>
+          <t>012I/06/Zn 009</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>50.29514</v>
+        <v>50.30247</v>
       </c>
       <c r="W75" t="n">
-        <v>-57.44013</v>
+        <v>-57.47459</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-N Zone</t>
+          <t>Daniel's Harbour Mine-L Zone</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>012I/06/Zn 013</t>
+          <t>012I/06/Zn 011</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Lead, Dolomite, Zinc</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>50.29873</v>
+        <v>50.27686</v>
       </c>
       <c r="W76" t="n">
-        <v>-57.48691</v>
+        <v>-57.46788</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
         </is>
       </c>
     </row>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Terra Nova Mine</t>
+          <t>Daniel's Harbour Mine-N Zone</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>012H/16/Cu 004</t>
+          <t>012I/06/Zn 013</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>49.92133</v>
+        <v>50.29873</v>
       </c>
       <c r="W77" t="n">
-        <v>-56.22896</v>
+        <v>-57.48691</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6042,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Goldenville</t>
+          <t>Daniel's Harbour Mine-F Zone</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>012H/16/Au 033</t>
+          <t>012I/06/Zn 006</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Copper, Iron, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6088,23 +6088,23 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U78" t="n">
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>49.99193</v>
+        <v>50.29437</v>
       </c>
       <c r="W78" t="n">
-        <v>-56.05735</v>
+        <v>-57.45374</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
         </is>
       </c>
     </row>
@@ -6114,24 +6114,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Stog'er Tight</t>
+          <t>Daniel's Harbour Mine-E Zone</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>012H/16/Au 041</t>
+          <t>012I/06/Zn 005</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>49.9661</v>
+        <v>50.31067</v>
       </c>
       <c r="W79" t="n">
-        <v>-56.07765</v>
+        <v>-57.44799</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-B Zone</t>
+          <t>Daniel's Harbour Mine-C Zone</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>012I/06/Zn 002</t>
+          <t>012I/06/Zn 003</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6241,14 +6241,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>50.2975</v>
+        <v>50.30435</v>
       </c>
       <c r="W80" t="n">
-        <v>-57.45784</v>
+        <v>-57.45355</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
         </is>
       </c>
     </row>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-E Zone</t>
+          <t>Daniel's Harbour Mine-D Zone</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>012I/06/Zn 005</t>
+          <t>012I/06/Zn 004</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6313,14 +6313,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>50.31067</v>
+        <v>50.30795</v>
       </c>
       <c r="W81" t="n">
-        <v>-57.44799</v>
+        <v>-57.45218</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-C Zone</t>
+          <t>Daniel's Harbour Mine-B Zone</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>012I/06/Zn 003</t>
+          <t>012I/06/Zn 002</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6385,14 +6385,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>50.30435</v>
+        <v>50.2975</v>
       </c>
       <c r="W82" t="n">
-        <v>-57.45355</v>
+        <v>-57.45784</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -6402,12 +6402,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-D Zone</t>
+          <t>Daniel's Harbour Mine-H Zone</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>012I/06/Zn 004</t>
+          <t>012I/06/Zn 008</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6457,14 +6457,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>50.30795</v>
+        <v>50.29179</v>
       </c>
       <c r="W83" t="n">
-        <v>-57.45218</v>
+        <v>-57.44599</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pilley's Island Mine</t>
+          <t>Daniel's Harbour Mine-G Zone</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>002E/12/Cu 001</t>
+          <t>012I/06/Zn 007</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6529,14 +6529,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>49.50863</v>
+        <v>50.29448</v>
       </c>
       <c r="W84" t="n">
-        <v>-55.71872</v>
+        <v>-57.44714</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AGS Vein</t>
+          <t>Daniel's Harbour Mine-M Zone</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>001L/14/Fl 013</t>
+          <t>012I/06/Zn 012</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6601,14 +6601,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>46.91489</v>
+        <v>50.29514</v>
       </c>
       <c r="W85" t="n">
-        <v>-55.48584</v>
+        <v>-57.44013</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
         </is>
       </c>
     </row>
@@ -6618,24 +6618,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nugget Pond</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>002E/13/Au 001</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6673,14 +6673,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>49.84502</v>
+        <v>49.45488</v>
       </c>
       <c r="W86" t="n">
-        <v>-55.77536</v>
+        <v>-55.49811</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -6690,24 +6690,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bishop North</t>
+          <t>Stoneyhouse</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>012B/08/Fe 001</t>
+          <t>001M/01/Cu 001</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6745,14 +6745,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>48.40317</v>
+        <v>47.0541</v>
       </c>
       <c r="W87" t="n">
-        <v>-58.3315</v>
+        <v>-54.11056</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -6762,24 +6762,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Upper Drill Brook Mine</t>
+          <t>Indian Head Mine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>012B/09/Fe 002</t>
+          <t>012B/10/Fe 001</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>48.53533</v>
+        <v>48.52416</v>
       </c>
       <c r="W88" t="n">
-        <v>-58.48601</v>
+        <v>-58.5148</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6834,24 +6834,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Tilt Cove/East Mine/Upper Dump</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>002E/13/Au 028</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Silver, Nickel, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>48.5353</v>
+        <v>49.88512</v>
       </c>
       <c r="W89" t="n">
-        <v>-58.48804</v>
+        <v>-55.62192</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
         </is>
       </c>
     </row>
@@ -6906,12 +6906,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Betts Cove Mine</t>
+          <t>Tilt Cove Mine</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>002E/13/Cu 002</t>
+          <t>002E/13/Cu 001</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Gold, Nickel, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>49.81179</v>
+        <v>49.88214</v>
       </c>
       <c r="W90" t="n">
-        <v>-55.80608</v>
+        <v>-55.62813</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tilt Cove Mine</t>
+          <t>Stewart Mine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>002E/13/Cu 001</t>
+          <t>002E/10/Au 001</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Silver, Zinc, Copper</t>
+          <t>Silver, Antimony, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>49.88214</v>
+        <v>49.58065</v>
       </c>
       <c r="W91" t="n">
-        <v>-55.62813</v>
+        <v>-54.85442</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -7050,24 +7050,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tilt Cove/East Mine/Upper Dump</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>002E/13/Au 028</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Zinc, Gold</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7105,14 +7105,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>49.88512</v>
+        <v>48.5353</v>
       </c>
       <c r="W92" t="n">
-        <v>-55.62192</v>
+        <v>-58.48804</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cross Cove</t>
+          <t>Pine Cove</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>002E/10/Sb 001</t>
+          <t>012H/16/Au 023</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>49.57534</v>
+        <v>49.96066</v>
       </c>
       <c r="W93" t="n">
-        <v>-54.86876</v>
+        <v>-56.13074</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
         </is>
       </c>
     </row>
@@ -7194,24 +7194,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Stoneyhouse</t>
+          <t>Bishop South</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>001M/01/Cu 001</t>
+          <t>012B/08/Fe 002</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7249,14 +7249,14 @@
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>47.0541</v>
+        <v>48.39996</v>
       </c>
       <c r="W94" t="n">
-        <v>-54.11056</v>
+        <v>-58.33683</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7266,24 +7266,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Bishop North</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>012B/08/Fe 001</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7321,14 +7321,14 @@
         <v>35</v>
       </c>
       <c r="V95" t="n">
-        <v>49.45488</v>
+        <v>48.40317</v>
       </c>
       <c r="W95" t="n">
-        <v>-55.49811</v>
+        <v>-58.3315</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -7338,24 +7338,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Argyle</t>
+          <t>Upper Drill Brook Mine</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>012H/16/Au 083</t>
+          <t>012B/09/Fe 002</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7393,14 +7393,14 @@
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>49.97838</v>
+        <v>48.53533</v>
       </c>
       <c r="W96" t="n">
-        <v>-56.05952</v>
+        <v>-58.48601</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7410,24 +7410,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Turk's Gut</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/11/Cu 001</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7465,14 +7465,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>47.4438</v>
+        <v>47.50226</v>
       </c>
       <c r="W97" t="n">
-        <v>-54.4169</v>
+        <v>-53.20074</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Turk's Gut</t>
+          <t>Cross Cove</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>001N/11/Cu 001</t>
+          <t>002E/10/Sb 001</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>47.50226</v>
+        <v>49.57534</v>
       </c>
       <c r="W98" t="n">
-        <v>-53.20074</v>
+        <v>-54.86876</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-A Zone</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>012I/06/Zn 001</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>50.29576</v>
+        <v>47.4438</v>
       </c>
       <c r="W99" t="n">
-        <v>-57.46512</v>
+        <v>-54.4169</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7626,24 +7626,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>La Manche</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>001N/12/Pb 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Barium, Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>35</v>
       </c>
       <c r="V100" t="n">
-        <v>47.6889</v>
+        <v>47.4063</v>
       </c>
       <c r="W100" t="n">
-        <v>-53.93901</v>
+        <v>-52.70699</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -7770,24 +7770,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hope Brook</t>
+          <t>Miles Cove Mine</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>011O/09/Au 003</t>
+          <t>002E/12/Cu 012</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7825,14 +7825,14 @@
         <v>35</v>
       </c>
       <c r="V102" t="n">
-        <v>47.73806</v>
+        <v>49.53936</v>
       </c>
       <c r="W102" t="n">
-        <v>-58.09531</v>
+        <v>-55.79062</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>Pilley's Island Mine</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>002E/12/Cu 001</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>35</v>
       </c>
       <c r="V103" t="n">
-        <v>52.961</v>
+        <v>49.50863</v>
       </c>
       <c r="W103" t="n">
-        <v>-66.81446</v>
+        <v>-55.71872</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -7914,24 +7914,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ming West</t>
+          <t>Hope Brook</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>012H/16/Cu 029</t>
+          <t>011O/09/Au 003</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7960,23 +7960,23 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U104" t="n">
         <v>35</v>
       </c>
       <c r="V104" t="n">
-        <v>49.9148</v>
+        <v>47.73806</v>
       </c>
       <c r="W104" t="n">
-        <v>-56.08996</v>
+        <v>-58.09531</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -7986,24 +7986,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>La Manche</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>001N/12/Pb 001</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Zinc, Silver, Barium, Lead</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8041,14 +8041,14 @@
         <v>35</v>
       </c>
       <c r="V105" t="n">
-        <v>49.19579</v>
+        <v>47.6889</v>
       </c>
       <c r="W105" t="n">
-        <v>-57.84974</v>
+        <v>-53.93901</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -8058,24 +8058,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-Q Zone</t>
+          <t>Sleepy Hollow</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>012I/06/Zn 016</t>
+          <t>002E/12/Cu 031</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8113,14 +8113,14 @@
         <v>35</v>
       </c>
       <c r="V106" t="n">
-        <v>50.29741</v>
+        <v>49.59747</v>
       </c>
       <c r="W106" t="n">
-        <v>-57.48016</v>
+        <v>-55.94735</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
         </is>
       </c>
     </row>
@@ -8130,24 +8130,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Browning Mine</t>
+          <t>Ming West</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>012H/10/Au 001</t>
+          <t>012H/16/Cu 029</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8176,23 +8176,23 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T107" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U107" t="n">
         <v>35</v>
       </c>
       <c r="V107" t="n">
-        <v>49.71799</v>
+        <v>49.9148</v>
       </c>
       <c r="W107" t="n">
-        <v>-56.92565</v>
+        <v>-56.08996</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
         </is>
       </c>
     </row>
@@ -8202,24 +8202,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Pine Cove</t>
+          <t>Daniel's Harbour Mine-A Zone</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>012H/16/Au 023</t>
+          <t>012I/06/Zn 001</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8257,14 +8257,14 @@
         <v>35</v>
       </c>
       <c r="V108" t="n">
-        <v>49.96066</v>
+        <v>50.29576</v>
       </c>
       <c r="W108" t="n">
-        <v>-56.13074</v>
+        <v>-57.46512</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bishop South</t>
+          <t>Argyle</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>012B/08/Fe 002</t>
+          <t>012H/16/Au 083</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>35</v>
       </c>
       <c r="V109" t="n">
-        <v>48.39996</v>
+        <v>49.97838</v>
       </c>
       <c r="W109" t="n">
-        <v>-58.33683</v>
+        <v>-56.05952</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
         </is>
       </c>
     </row>
@@ -8346,24 +8346,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-F Zone</t>
+          <t>Daniel's Harbour Mine-K Zone</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>012I/06/Zn 006</t>
+          <t>012I/06/Zn 010</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>35</v>
       </c>
       <c r="V110" t="n">
-        <v>50.29437</v>
+        <v>50.2935</v>
       </c>
       <c r="W110" t="n">
-        <v>-57.45374</v>
+        <v>-57.46875</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
         </is>
       </c>
     </row>
@@ -8418,24 +8418,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Stewart Mine</t>
+          <t>Betts Cove Mine</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>002E/10/Au 001</t>
+          <t>002E/13/Cu 002</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Silver, Antimony, Copper, Zinc, Gold</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>35</v>
       </c>
       <c r="V111" t="n">
-        <v>49.58065</v>
+        <v>49.81179</v>
       </c>
       <c r="W111" t="n">
-        <v>-54.85442</v>
+        <v>-55.80608</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -8490,24 +8490,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Indian Head Mine</t>
+          <t>Nugget Pond</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>012B/10/Fe 001</t>
+          <t>002E/13/Au 001</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>35</v>
       </c>
       <c r="V112" t="n">
-        <v>48.52416</v>
+        <v>49.84502</v>
       </c>
       <c r="W112" t="n">
-        <v>-58.5148</v>
+        <v>-55.77536</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -8562,24 +8562,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Goethite Bay North</t>
+          <t>Timmins No 8</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>023G/02/Fe 041</t>
+          <t>023J/14/Fe 026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8617,14 +8617,14 @@
         <v>31</v>
       </c>
       <c r="V113" t="n">
-        <v>53.18717</v>
+        <v>54.89589</v>
       </c>
       <c r="W113" t="n">
-        <v>-66.74445</v>
+        <v>-67.07944000000001</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
         </is>
       </c>
     </row>
@@ -8634,24 +8634,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ruth Lake No 2</t>
+          <t>Timmins No 5</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>023J/15/Fe 011</t>
+          <t>023J/14/Fe 024</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>31</v>
       </c>
       <c r="V114" t="n">
-        <v>54.79747</v>
+        <v>54.86384</v>
       </c>
       <c r="W114" t="n">
-        <v>-66.87487</v>
+        <v>-67.09327</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Block 103 - Greenbush Zone</t>
+          <t>Mile 2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>023J/14/Fe 043</t>
+          <t>023B/15/Fe 011</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -8761,14 +8761,14 @@
         <v>31</v>
       </c>
       <c r="V115" t="n">
-        <v>54.97234</v>
+        <v>52.97907</v>
       </c>
       <c r="W115" t="n">
-        <v>-67.25158</v>
+        <v>-66.88907</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Elizabeth No. 2</t>
+          <t>Wabush No. 1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>023J/15/Fe 032</t>
+          <t>023B/15/Fe 002</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>31</v>
       </c>
       <c r="V116" t="n">
-        <v>54.77182</v>
+        <v>52.9599</v>
       </c>
       <c r="W116" t="n">
-        <v>-66.88666000000001</v>
+        <v>-66.9704</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lorraine No. 4</t>
+          <t>Julienne Lake</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>023G/02/Fe 008</t>
+          <t>023G/02/Fe 009</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8905,14 +8905,14 @@
         <v>31</v>
       </c>
       <c r="V117" t="n">
-        <v>53.08316</v>
+        <v>53.13733</v>
       </c>
       <c r="W117" t="n">
-        <v>-66.87726000000001</v>
+        <v>-66.78360000000001</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Elizabeth No. 1</t>
+          <t>Joyce Lake</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>023J/15/Fe 031</t>
+          <t>023J/15/Fe 030</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -8977,14 +8977,14 @@
         <v>31</v>
       </c>
       <c r="V118" t="n">
-        <v>54.78743</v>
+        <v>54.8993</v>
       </c>
       <c r="W118" t="n">
-        <v>-66.90081000000001</v>
+        <v>-66.53366</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
         </is>
       </c>
     </row>
@@ -8994,24 +8994,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wabush No. 7</t>
+          <t>Attikamagen Deposit</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>023G/02/Fe 007</t>
+          <t>023J/16/Fe 001</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9049,14 +9049,14 @@
         <v>31</v>
       </c>
       <c r="V119" t="n">
-        <v>53.02512</v>
+        <v>54.80989</v>
       </c>
       <c r="W119" t="n">
-        <v>-66.90531</v>
+        <v>-66.47658</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Knob Lake 1</t>
+          <t>Goethite Bay North</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>023J/15/Fe 013</t>
+          <t>023G/02/Fe 041</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9121,14 +9121,14 @@
         <v>31</v>
       </c>
       <c r="V120" t="n">
-        <v>54.7766</v>
+        <v>53.18717</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.80589000000001</v>
+        <v>-66.74445</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
         </is>
       </c>
     </row>
@@ -9138,24 +9138,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Howse</t>
+          <t>Wabush No. 6</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>023J/14/Fe 028</t>
+          <t>023G/02/Fe 006</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9193,14 +9193,14 @@
         <v>31</v>
       </c>
       <c r="V121" t="n">
-        <v>54.9089</v>
+        <v>53.01798</v>
       </c>
       <c r="W121" t="n">
-        <v>-67.14075</v>
+        <v>-66.89297999999999</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9210,24 +9210,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ferriman No 7</t>
+          <t>Canning</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>023J/15/Fe 014</t>
+          <t>023B/15/Fe 007</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9265,14 +9265,14 @@
         <v>31</v>
       </c>
       <c r="V122" t="n">
-        <v>54.81281</v>
+        <v>52.9469</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.94580999999999</v>
+        <v>-66.95802999999999</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9282,24 +9282,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Duley No. 1</t>
+          <t>Timmins No 7</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>023B/14/Fe 001</t>
+          <t>023J/14/Fe 025</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9337,14 +9337,14 @@
         <v>31</v>
       </c>
       <c r="V123" t="n">
-        <v>52.87237</v>
+        <v>54.89246</v>
       </c>
       <c r="W123" t="n">
-        <v>-67.05874</v>
+        <v>-67.07259000000001</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Kivivic No 3</t>
+          <t>Ferriman No 7</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>023O/03/Fe 003</t>
+          <t>023J/15/Fe 014</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9409,14 +9409,14 @@
         <v>31</v>
       </c>
       <c r="V124" t="n">
-        <v>55.05061</v>
+        <v>54.81281</v>
       </c>
       <c r="W124" t="n">
-        <v>-67.26130000000001</v>
+        <v>-66.94580999999999</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
         </is>
       </c>
     </row>
@@ -9426,24 +9426,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sawyer Lake</t>
+          <t>Wabush No. 4</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>023I/05/Fe 001</t>
+          <t>023B/15/Fe 004</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9481,14 +9481,14 @@
         <v>31</v>
       </c>
       <c r="V125" t="n">
-        <v>54.45206</v>
+        <v>52.95373</v>
       </c>
       <c r="W125" t="n">
-        <v>-65.98627</v>
+        <v>-66.94092000000001</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -9498,24 +9498,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ruth Lake No 8</t>
+          <t>Block 103 - Greenbush Zone</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>023J/15/Fe 009</t>
+          <t>023J/14/Fe 043</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9553,14 +9553,14 @@
         <v>31</v>
       </c>
       <c r="V126" t="n">
-        <v>54.78104</v>
+        <v>54.97234</v>
       </c>
       <c r="W126" t="n">
-        <v>-66.86577</v>
+        <v>-67.25158</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
         </is>
       </c>
     </row>
@@ -9570,12 +9570,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Attikamagen Deposit</t>
+          <t>Howells River North</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>023J/16/Fe 001</t>
+          <t>023O/03/Fe 007</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -9625,14 +9625,14 @@
         <v>31</v>
       </c>
       <c r="V127" t="n">
-        <v>54.80989</v>
+        <v>55.01179</v>
       </c>
       <c r="W127" t="n">
-        <v>-66.47658</v>
+        <v>-67.37214</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Joyce Lake</t>
+          <t>Duley No. 2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>023J/15/Fe 030</t>
+          <t>023B/15/Fe 008</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>31</v>
       </c>
       <c r="V128" t="n">
-        <v>54.8993</v>
+        <v>52.87214</v>
       </c>
       <c r="W128" t="n">
-        <v>-66.53366</v>
+        <v>-66.99635000000001</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -9714,12 +9714,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Howells Lake</t>
+          <t>Elizabeth No. 1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>023O/03/Fe 006</t>
+          <t>023J/15/Fe 031</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -9769,14 +9769,14 @@
         <v>31</v>
       </c>
       <c r="V129" t="n">
-        <v>55.06346</v>
+        <v>54.78743</v>
       </c>
       <c r="W129" t="n">
-        <v>-67.40528</v>
+        <v>-66.90081000000001</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
         </is>
       </c>
     </row>
@@ -9786,12 +9786,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Howells River North</t>
+          <t>Howells Lake</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>023O/03/Fe 007</t>
+          <t>023O/03/Fe 006</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9841,14 +9841,14 @@
         <v>31</v>
       </c>
       <c r="V130" t="n">
-        <v>55.01179</v>
+        <v>55.06346</v>
       </c>
       <c r="W130" t="n">
-        <v>-67.37214</v>
+        <v>-67.40528</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Wabush No. 6</t>
+          <t>Wabush No. 7</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>023G/02/Fe 006</t>
+          <t>023G/02/Fe 007</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9913,14 +9913,14 @@
         <v>31</v>
       </c>
       <c r="V131" t="n">
-        <v>53.01798</v>
+        <v>53.02512</v>
       </c>
       <c r="W131" t="n">
-        <v>-66.89297999999999</v>
+        <v>-66.90531</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Julienne Lake</t>
+          <t>Lorraine No. 4</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>023G/02/Fe 009</t>
+          <t>023G/02/Fe 008</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9985,14 +9985,14 @@
         <v>31</v>
       </c>
       <c r="V132" t="n">
-        <v>53.13733</v>
+        <v>53.08316</v>
       </c>
       <c r="W132" t="n">
-        <v>-66.78360000000001</v>
+        <v>-66.87726000000001</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Duley No. 2</t>
+          <t>Wabush No. 8</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>023B/15/Fe 008</t>
+          <t>023B/15/Fe 005</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -10057,14 +10057,14 @@
         <v>31</v>
       </c>
       <c r="V133" t="n">
-        <v>52.87214</v>
+        <v>52.9791</v>
       </c>
       <c r="W133" t="n">
-        <v>-66.99635000000001</v>
+        <v>-66.90604999999999</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Canning</t>
+          <t>Houston 2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>023B/15/Fe 007</t>
+          <t>023J/10/Fe 009</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10129,14 +10129,14 @@
         <v>31</v>
       </c>
       <c r="V134" t="n">
-        <v>52.9469</v>
+        <v>54.71245</v>
       </c>
       <c r="W134" t="n">
-        <v>-66.95802999999999</v>
+        <v>-66.66257</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10146,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Timmins No 7</t>
+          <t>Houston 3</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>023J/14/Fe 025</t>
+          <t>023J/10/Fe 010</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10201,14 +10201,14 @@
         <v>31</v>
       </c>
       <c r="V135" t="n">
-        <v>54.89246</v>
+        <v>54.69887</v>
       </c>
       <c r="W135" t="n">
-        <v>-67.07259000000001</v>
+        <v>-66.64483</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mile 2</t>
+          <t>Kivivic No 3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>023B/15/Fe 011</t>
+          <t>023O/03/Fe 003</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -10273,14 +10273,14 @@
         <v>31</v>
       </c>
       <c r="V136" t="n">
-        <v>52.97907</v>
+        <v>55.05061</v>
       </c>
       <c r="W136" t="n">
-        <v>-66.88907</v>
+        <v>-67.26130000000001</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Wabush No. 8</t>
+          <t>Kivivic No 4</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>023B/15/Fe 005</t>
+          <t>023O/03/Fe 004</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>31</v>
       </c>
       <c r="V137" t="n">
-        <v>52.9791</v>
+        <v>55.04865</v>
       </c>
       <c r="W137" t="n">
-        <v>-66.90604999999999</v>
+        <v>-67.28158000000001</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -10362,24 +10362,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Wabush No. 4</t>
+          <t>Kivivic No 5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>023B/15/Fe 004</t>
+          <t>023O/03/Fe 005</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>31</v>
       </c>
       <c r="V138" t="n">
-        <v>52.95373</v>
+        <v>55.06664</v>
       </c>
       <c r="W138" t="n">
-        <v>-66.94092000000001</v>
+        <v>-67.29537000000001</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10434,24 +10434,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Timmins No 8</t>
+          <t>Duley No. 1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>023J/14/Fe 026</t>
+          <t>023B/14/Fe 001</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>31</v>
       </c>
       <c r="V139" t="n">
-        <v>54.89589</v>
+        <v>52.87237</v>
       </c>
       <c r="W139" t="n">
-        <v>-67.07944000000001</v>
+        <v>-67.05874</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10506,24 +10506,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Timmins No 5</t>
+          <t>Mills Lake</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>023J/14/Fe 024</t>
+          <t>023B/14/Fe 002</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>31</v>
       </c>
       <c r="V140" t="n">
-        <v>54.86384</v>
+        <v>52.79808</v>
       </c>
       <c r="W140" t="n">
-        <v>-67.09327</v>
+        <v>-67.00413</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -10578,24 +10578,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sheps Lake</t>
+          <t>Howells River West Zone A</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>023J/11/Fe 001</t>
+          <t>023J/14/Fe 001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10633,14 +10633,14 @@
         <v>31</v>
       </c>
       <c r="V141" t="n">
-        <v>54.73475</v>
+        <v>54.90958</v>
       </c>
       <c r="W141" t="n">
-        <v>-67.06362</v>
+        <v>-67.26052</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Neal 1</t>
+          <t>Houston 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>023B/14/Fe 008</t>
+          <t>023J/10/Fe 008</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10705,14 +10705,14 @@
         <v>31</v>
       </c>
       <c r="V142" t="n">
-        <v>52.95013</v>
+        <v>54.70748</v>
       </c>
       <c r="W142" t="n">
-        <v>-67.15191</v>
+        <v>-66.65615</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -10722,24 +10722,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Redmond 5</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>023B/14/Fe 028</t>
+          <t>023J/10/Fe 005</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10777,14 +10777,14 @@
         <v>31</v>
       </c>
       <c r="V143" t="n">
-        <v>52.94868</v>
+        <v>54.70854</v>
       </c>
       <c r="W143" t="n">
-        <v>-67.01146</v>
+        <v>-66.79174999999999</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sawyer Lake</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>023B/14/Fe 020</t>
+          <t>023I/05/Fe 001</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>31</v>
       </c>
       <c r="V144" t="n">
-        <v>52.83351</v>
+        <v>54.45206</v>
       </c>
       <c r="W144" t="n">
-        <v>-67.0311</v>
+        <v>-65.98627</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -10938,24 +10938,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Howells River West Zone A</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>023J/14/Fe 001</t>
+          <t>023B/14/Fe 020</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>31</v>
       </c>
       <c r="V146" t="n">
-        <v>54.90958</v>
+        <v>52.83351</v>
       </c>
       <c r="W146" t="n">
-        <v>-67.26052</v>
+        <v>-67.0311</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
         </is>
       </c>
     </row>
@@ -11010,24 +11010,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Wabush No. 1</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>023B/15/Fe 002</t>
+          <t>023B/14/Fe 028</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11065,14 +11065,14 @@
         <v>31</v>
       </c>
       <c r="V147" t="n">
-        <v>52.9599</v>
+        <v>52.94868</v>
       </c>
       <c r="W147" t="n">
-        <v>-66.9704</v>
+        <v>-67.01146</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Redmond 5</t>
+          <t>Sheps Lake</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>023J/10/Fe 005</t>
+          <t>023J/11/Fe 001</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11137,14 +11137,14 @@
         <v>31</v>
       </c>
       <c r="V148" t="n">
-        <v>54.70854</v>
+        <v>54.73475</v>
       </c>
       <c r="W148" t="n">
-        <v>-66.79174999999999</v>
+        <v>-67.06362</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Mills Lake</t>
+          <t>Neal 1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>023B/14/Fe 002</t>
+          <t>023B/14/Fe 008</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -11209,14 +11209,14 @@
         <v>31</v>
       </c>
       <c r="V149" t="n">
-        <v>52.79808</v>
+        <v>52.95013</v>
       </c>
       <c r="W149" t="n">
-        <v>-67.00413</v>
+        <v>-67.15191</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Houston 1</t>
+          <t>Ruth Lake No 8</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>023J/10/Fe 008</t>
+          <t>023J/15/Fe 009</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11281,14 +11281,14 @@
         <v>31</v>
       </c>
       <c r="V150" t="n">
-        <v>54.70748</v>
+        <v>54.78104</v>
       </c>
       <c r="W150" t="n">
-        <v>-66.65615</v>
+        <v>-66.86577</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Houston 3</t>
+          <t>Ruth Lake No 2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>023J/10/Fe 010</t>
+          <t>023J/15/Fe 011</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11353,14 +11353,14 @@
         <v>31</v>
       </c>
       <c r="V151" t="n">
-        <v>54.69887</v>
+        <v>54.79747</v>
       </c>
       <c r="W151" t="n">
-        <v>-66.64483</v>
+        <v>-66.87487</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -11370,24 +11370,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Houston 2</t>
+          <t>Elizabeth No. 2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>023J/10/Fe 009</t>
+          <t>023J/15/Fe 032</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11425,14 +11425,14 @@
         <v>31</v>
       </c>
       <c r="V152" t="n">
-        <v>54.71245</v>
+        <v>54.77182</v>
       </c>
       <c r="W152" t="n">
-        <v>-66.66257</v>
+        <v>-66.88666000000001</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
         </is>
       </c>
     </row>
@@ -11442,24 +11442,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Kivivic No 4</t>
+          <t>Knob Lake 1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>023O/03/Fe 004</t>
+          <t>023J/15/Fe 013</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11497,14 +11497,14 @@
         <v>31</v>
       </c>
       <c r="V153" t="n">
-        <v>55.04865</v>
+        <v>54.7766</v>
       </c>
       <c r="W153" t="n">
-        <v>-67.28158000000001</v>
+        <v>-66.80589000000001</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11514,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Kivivic No 5</t>
+          <t>Howse</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>023O/03/Fe 005</t>
+          <t>023J/14/Fe 028</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11569,14 +11569,14 @@
         <v>31</v>
       </c>
       <c r="V154" t="n">
-        <v>55.06664</v>
+        <v>54.9089</v>
       </c>
       <c r="W154" t="n">
-        <v>-67.29537000000001</v>
+        <v>-67.14075</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Mine Hill</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>001N/07/Pph004</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Pyrophyllite</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11641,14 +11641,14 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>53.40462</v>
+        <v>47.48</v>
       </c>
       <c r="W155" t="n">
-        <v>-65.08734</v>
+        <v>-52.95479</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Parsons Pond No 3</t>
+          <t>Iron Springs Mine</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>012H/13/Btm003</t>
+          <t>001L/14/Fl 008</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11785,14 +11785,14 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>49.97912</v>
+        <v>46.88701</v>
       </c>
       <c r="W157" t="n">
-        <v>-57.64547</v>
+        <v>-55.421</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Parsons Pond No 2</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>012H/13/Btm002</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11857,14 +11857,14 @@
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>49.97421</v>
+        <v>48.56074</v>
       </c>
       <c r="W158" t="n">
-        <v>-57.60538</v>
+        <v>-58.8161</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Parsons Pond No 4</t>
+          <t>Hares Ears Vein</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>012H/13/Btm004</t>
+          <t>001L/14/Fl 007</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11920,23 +11920,23 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T159" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U159" t="n">
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>49.99787</v>
+        <v>46.88814</v>
       </c>
       <c r="W159" t="n">
-        <v>-57.63818</v>
+        <v>-55.41178</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Middle Arm Brook</t>
+          <t>Collier Point</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>012H/16/Vir001</t>
+          <t>001N/12/Ba 001</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Virginite</t>
+          <t>Barium</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12001,14 +12001,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>49.80048</v>
+        <v>47.59126</v>
       </c>
       <c r="W160" t="n">
-        <v>-56.31995</v>
+        <v>-53.69011</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lord &amp; Lady Gulch Mine</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>001L/14/Fl 005</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12073,14 +12073,14 @@
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>46.87554</v>
+        <v>48.30663</v>
       </c>
       <c r="W161" t="n">
-        <v>-55.4111</v>
+        <v>-58.68165</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Baie Verte Mine</t>
+          <t>Parsons Pond Cart Track</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>012H/16/Asb008</t>
+          <t>012I/04/Btm001</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Magnesium, Asbestos</t>
+          <t>Oil Shale</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12136,23 +12136,23 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T162" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U162" t="n">
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>49.97974</v>
+        <v>50.00564</v>
       </c>
       <c r="W162" t="n">
-        <v>-56.19399</v>
+        <v>-57.63187</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -12162,12 +12162,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Black Duck Mine</t>
+          <t>Baie Verte Mine</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>001L/14/Fl 010</t>
+          <t>012H/16/Asb008</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Magnesium, Asbestos</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12217,14 +12217,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>46.93201</v>
+        <v>49.97974</v>
       </c>
       <c r="W163" t="n">
-        <v>-55.38881</v>
+        <v>-56.19399</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Borney Lake</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>002D/14/Stn001</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12289,14 +12289,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>48.30663</v>
+        <v>48.9264</v>
       </c>
       <c r="W164" t="n">
-        <v>-58.68165</v>
+        <v>-55.44535</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Southern Cross Veins</t>
+          <t>Doctors Pond Veins</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>001L/14/Fl 020</t>
+          <t>001L/14/Fl 036</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12361,14 +12361,14 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>46.88974</v>
+        <v>46.92769</v>
       </c>
       <c r="W165" t="n">
-        <v>-55.42958</v>
+        <v>-55.37593</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tarefare Mine</t>
+          <t>Parsons Pond No 3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>001L/14/Fl 006</t>
+          <t>012H/13/Btm003</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12433,14 +12433,14 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>46.8912</v>
+        <v>49.97912</v>
       </c>
       <c r="W166" t="n">
-        <v>-55.43112</v>
+        <v>-57.64547</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Tarefare Mine</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>001L/14/Fl 006</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12505,14 +12505,14 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>53.469</v>
+        <v>46.8912</v>
       </c>
       <c r="W167" t="n">
-        <v>-64.91218000000001</v>
+        <v>-55.43112</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
         </is>
       </c>
     </row>
@@ -12522,12 +12522,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mine Hill</t>
+          <t>Blue Beach Mine</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>001N/07/Pph004</t>
+          <t>001L/14/Fl 001</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pyrophyllite</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12577,14 +12577,14 @@
         <v>30</v>
       </c>
       <c r="V168" t="n">
-        <v>47.48</v>
+        <v>46.91553</v>
       </c>
       <c r="W168" t="n">
-        <v>-52.95479</v>
+        <v>-55.40729</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
         </is>
       </c>
     </row>
@@ -12594,12 +12594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Black Duck Mine</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>001L/14/Fl 010</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12649,14 +12649,14 @@
         <v>30</v>
       </c>
       <c r="V169" t="n">
-        <v>48.56074</v>
+        <v>46.93201</v>
       </c>
       <c r="W169" t="n">
-        <v>-58.8161</v>
+        <v>-55.38881</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Collier Point</t>
+          <t>Southern Cross Veins</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>001N/12/Ba 001</t>
+          <t>001L/14/Fl 020</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Barium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12721,14 +12721,14 @@
         <v>30</v>
       </c>
       <c r="V170" t="n">
-        <v>47.59126</v>
+        <v>46.88974</v>
       </c>
       <c r="W170" t="n">
-        <v>-53.69011</v>
+        <v>-55.42958</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
         </is>
       </c>
     </row>
@@ -12738,12 +12738,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Parsons Pond Cart Track</t>
+          <t>Lord &amp; Lady Gulch Mine</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>012I/04/Btm001</t>
+          <t>001L/14/Fl 005</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Oil Shale</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12784,23 +12784,23 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T171" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U171" t="n">
         <v>30</v>
       </c>
       <c r="V171" t="n">
-        <v>50.00564</v>
+        <v>46.87554</v>
       </c>
       <c r="W171" t="n">
-        <v>-57.63187</v>
+        <v>-55.4111</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Doctors Pond Veins</t>
+          <t>Scrape Vein</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>001L/14/Fl 036</t>
+          <t>001L/14/Fl 035</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -12865,14 +12865,14 @@
         <v>30</v>
       </c>
       <c r="V172" t="n">
-        <v>46.92769</v>
+        <v>46.92547</v>
       </c>
       <c r="W172" t="n">
-        <v>-55.37593</v>
+        <v>-55.37193</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Little Salt Cove</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>001L/14/Fl 016</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12937,14 +12937,14 @@
         <v>30</v>
       </c>
       <c r="V173" t="n">
-        <v>46.87654</v>
+        <v>53.40462</v>
       </c>
       <c r="W173" t="n">
-        <v>-55.43141</v>
+        <v>-65.08734</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12954,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Scrape Vein</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>001L/14/Fl 035</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13009,14 +13009,14 @@
         <v>30</v>
       </c>
       <c r="V174" t="n">
-        <v>46.92547</v>
+        <v>48.50411</v>
       </c>
       <c r="W174" t="n">
-        <v>-55.37193</v>
+        <v>-58.53451</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Director Mine</t>
+          <t>Bluff Head Mine</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>001L/14/Fl 009</t>
+          <t>012B/15/Cr 001</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Asbestos, Chromium</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13081,14 +13081,14 @@
         <v>30</v>
       </c>
       <c r="V175" t="n">
-        <v>46.90681</v>
+        <v>48.77717</v>
       </c>
       <c r="W175" t="n">
-        <v>-55.42107</v>
+        <v>-58.59931</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Iron Springs Mine</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>001L/14/Fl 008</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13153,14 +13153,14 @@
         <v>30</v>
       </c>
       <c r="V176" t="n">
-        <v>46.88701</v>
+        <v>53.469</v>
       </c>
       <c r="W176" t="n">
-        <v>-55.421</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Borney Lake</t>
+          <t>Director Mine</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>002D/14/Stn001</t>
+          <t>001L/14/Fl 009</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13225,14 +13225,14 @@
         <v>30</v>
       </c>
       <c r="V177" t="n">
-        <v>48.9264</v>
+        <v>46.90681</v>
       </c>
       <c r="W177" t="n">
-        <v>-55.44535</v>
+        <v>-55.42107</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Bluff Head Mine</t>
+          <t>Little Salt Cove</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>012B/15/Cr 001</t>
+          <t>001L/14/Fl 016</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Asbestos, Chromium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13297,14 +13297,14 @@
         <v>30</v>
       </c>
       <c r="V178" t="n">
-        <v>48.77717</v>
+        <v>46.87654</v>
       </c>
       <c r="W178" t="n">
-        <v>-58.59931</v>
+        <v>-55.43141</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
         </is>
       </c>
     </row>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Middle Arm Brook</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>012H/16/Vir001</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Virginite</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13441,14 +13441,14 @@
         <v>30</v>
       </c>
       <c r="V180" t="n">
-        <v>48.50411</v>
+        <v>49.80048</v>
       </c>
       <c r="W180" t="n">
-        <v>-58.53451</v>
+        <v>-56.31995</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
         </is>
       </c>
     </row>
@@ -13458,12 +13458,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Blue Beach Mine</t>
+          <t>Parsons Pond No 2</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>001L/14/Fl 001</t>
+          <t>012H/13/Btm002</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13513,14 +13513,14 @@
         <v>30</v>
       </c>
       <c r="V181" t="n">
-        <v>46.91553</v>
+        <v>49.97421</v>
       </c>
       <c r="W181" t="n">
-        <v>-55.40729</v>
+        <v>-57.60538</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
         </is>
       </c>
     </row>
@@ -13530,12 +13530,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hares Ears Vein</t>
+          <t>Parsons Pond No 1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>001L/14/Fl 007</t>
+          <t>012H/13/Btm001</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13576,23 +13576,23 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T182" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U182" t="n">
         <v>30</v>
       </c>
       <c r="V182" t="n">
-        <v>46.88814</v>
+        <v>49.99228</v>
       </c>
       <c r="W182" t="n">
-        <v>-55.41178</v>
+        <v>-57.58928</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Parsons Pond No 1</t>
+          <t>Parsons Pond No 4</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>012H/13/Btm001</t>
+          <t>012H/13/Btm004</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13648,23 +13648,23 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T183" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U183" t="n">
         <v>30</v>
       </c>
       <c r="V183" t="n">
-        <v>49.99228</v>
+        <v>49.99787</v>
       </c>
       <c r="W183" t="n">
-        <v>-57.58928</v>
+        <v>-57.63818</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
         </is>
       </c>
     </row>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Little Bay Mine</t>
+          <t>Grey Copper Mine</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>002E/12/Cu 030</t>
+          <t>002E/11/Cu 001</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Iron, Gold, Copper</t>
+          <t>Iron, Copper</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13729,14 +13729,14 @@
         <v>26</v>
       </c>
       <c r="V184" t="n">
-        <v>49.5961</v>
+        <v>49.5173</v>
       </c>
       <c r="W184" t="n">
-        <v>-55.94531</v>
+        <v>-55.2721</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Fleming No 3</t>
+          <t>Scotia Formation</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>023J/14/Fe 022</t>
+          <t>001N/10/Fe 002</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13801,14 +13801,14 @@
         <v>26</v>
       </c>
       <c r="V185" t="n">
-        <v>54.85836</v>
+        <v>47.64169</v>
       </c>
       <c r="W185" t="n">
-        <v>-67.03167999999999</v>
+        <v>-52.97639</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Timmins No 2</t>
+          <t>Gull Island Formation</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>023J/14/Fe 019</t>
+          <t>001N/10/Fe 003</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -13873,14 +13873,14 @@
         <v>26</v>
       </c>
       <c r="V186" t="n">
-        <v>54.89421</v>
+        <v>47.65193</v>
       </c>
       <c r="W186" t="n">
-        <v>-67.08716</v>
+        <v>-52.95654</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Timmins No 4</t>
+          <t>Redmond No 2</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>023J/14/Fe 023</t>
+          <t>023J/10/Fe 002</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13945,14 +13945,14 @@
         <v>26</v>
       </c>
       <c r="V187" t="n">
-        <v>54.89884</v>
+        <v>54.69738</v>
       </c>
       <c r="W187" t="n">
-        <v>-67.10881000000001</v>
+        <v>-66.77224</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -13962,24 +13962,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Little Bay Mine</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>002E/12/Cu 030</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron, Gold, Copper</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14017,14 +14017,14 @@
         <v>26</v>
       </c>
       <c r="V188" t="n">
-        <v>47.53392</v>
+        <v>49.5961</v>
       </c>
       <c r="W188" t="n">
-        <v>-53.18293</v>
+        <v>-55.94531</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -14034,24 +14034,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dominion Formation</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>001N/10/Fe 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14089,14 +14089,14 @@
         <v>26</v>
       </c>
       <c r="V189" t="n">
-        <v>47.64164</v>
+        <v>49.50376</v>
       </c>
       <c r="W189" t="n">
-        <v>-52.95309</v>
+        <v>-55.21553</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14106,24 +14106,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Redmond No 2</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>023J/10/Fe 002</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14161,14 +14161,14 @@
         <v>26</v>
       </c>
       <c r="V190" t="n">
-        <v>54.69738</v>
+        <v>47.53392</v>
       </c>
       <c r="W190" t="n">
-        <v>-66.77224</v>
+        <v>-53.18293</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Gull Island Formation</t>
+          <t>Dominion Formation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>001N/10/Fe 003</t>
+          <t>001N/10/Fe 001</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -14233,14 +14233,14 @@
         <v>26</v>
       </c>
       <c r="V191" t="n">
-        <v>47.65193</v>
+        <v>47.64164</v>
       </c>
       <c r="W191" t="n">
-        <v>-52.95654</v>
+        <v>-52.95309</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14250,12 +14250,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Scotia Formation</t>
+          <t>Cliff Mine</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>001N/10/Fe 002</t>
+          <t>012B/09/Fe 001</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -14305,14 +14305,14 @@
         <v>26</v>
       </c>
       <c r="V192" t="n">
-        <v>47.64169</v>
+        <v>48.54434</v>
       </c>
       <c r="W192" t="n">
-        <v>-52.97639</v>
+        <v>-58.49915</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Timmins No 1</t>
+          <t>Skindles Mine</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>023J/14/Fe 018</t>
+          <t>012B/09/Fe 004</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14377,14 +14377,14 @@
         <v>26</v>
       </c>
       <c r="V193" t="n">
-        <v>54.88449</v>
+        <v>48.54069</v>
       </c>
       <c r="W193" t="n">
-        <v>-67.08575</v>
+        <v>-58.48888</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14394,24 +14394,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Timmins No 6</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>023J/14/Fe 021</t>
+          <t>023J/15/Fe 010</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14449,14 +14449,14 @@
         <v>26</v>
       </c>
       <c r="V194" t="n">
-        <v>54.90148</v>
+        <v>54.77437</v>
       </c>
       <c r="W194" t="n">
-        <v>-67.09757999999999</v>
+        <v>-66.82881</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14466,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Skindles Mine</t>
+          <t>Ruth Lake No 7</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>012B/09/Fe 004</t>
+          <t>023J/15/Fe 006</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
         <v>26</v>
       </c>
       <c r="V195" t="n">
-        <v>48.54069</v>
+        <v>54.80557</v>
       </c>
       <c r="W195" t="n">
-        <v>-58.48888</v>
+        <v>-66.90618000000001</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -14538,24 +14538,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Cliff Mine</t>
+          <t>Ruth Lake No 5</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>012B/09/Fe 001</t>
+          <t>023J/15/Fe 007</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14593,14 +14593,14 @@
         <v>26</v>
       </c>
       <c r="V196" t="n">
-        <v>48.54434</v>
+        <v>54.80503</v>
       </c>
       <c r="W196" t="n">
-        <v>-58.49915</v>
+        <v>-66.88023</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -14610,24 +14610,24 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Grey Copper Mine</t>
+          <t>Ruth Lake No 6</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>002E/11/Cu 001</t>
+          <t>023J/15/Fe 008</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Iron, Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14665,14 +14665,14 @@
         <v>26</v>
       </c>
       <c r="V197" t="n">
-        <v>49.5173</v>
+        <v>54.80104</v>
       </c>
       <c r="W197" t="n">
-        <v>-55.2721</v>
+        <v>-66.87327999999999</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -14682,24 +14682,24 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Ruth Lake No 9</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>023J/15/Fe 005</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14737,14 +14737,14 @@
         <v>26</v>
       </c>
       <c r="V198" t="n">
-        <v>49.50376</v>
+        <v>54.80033</v>
       </c>
       <c r="W198" t="n">
-        <v>-55.21553</v>
+        <v>-66.89447</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14754,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Smallwood Mine</t>
+          <t>Ruth Lake No 1</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>023G/02/Fe 001</t>
+          <t>023J/15/Fe 002</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14809,14 +14809,14 @@
         <v>26</v>
       </c>
       <c r="V199" t="n">
-        <v>53.03718</v>
+        <v>54.79145</v>
       </c>
       <c r="W199" t="n">
-        <v>-66.93694000000001</v>
+        <v>-66.85449</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14826,24 +14826,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Wishart No 2 (Wishart Mine)</t>
+          <t>Wishart No 1 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>023J/15/Fe 004</t>
+          <t>023J/15/Fe 003</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14881,14 +14881,14 @@
         <v>26</v>
       </c>
       <c r="V200" t="n">
-        <v>54.7654</v>
+        <v>54.76166</v>
       </c>
       <c r="W200" t="n">
-        <v>-66.9067</v>
+        <v>-66.88793</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lorraine Mine</t>
+          <t>Wishart No 2 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>023G/02/Fe 004</t>
+          <t>023J/15/Fe 004</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14953,14 +14953,14 @@
         <v>26</v>
       </c>
       <c r="V201" t="n">
-        <v>53.06833</v>
+        <v>54.7654</v>
       </c>
       <c r="W201" t="n">
-        <v>-66.94949</v>
+        <v>-66.9067</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14970,12 +14970,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ruth Lake No 1</t>
+          <t>Ruth Lake No 3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>023J/15/Fe 002</t>
+          <t>023J/15/Fe 001</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
         <v>26</v>
       </c>
       <c r="V202" t="n">
-        <v>54.79145</v>
+        <v>54.80404</v>
       </c>
       <c r="W202" t="n">
-        <v>-66.85449</v>
+        <v>-66.87016</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15042,12 +15042,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Ruth Lake No 3</t>
+          <t>Smallwood Mine</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>023J/15/Fe 001</t>
+          <t>023G/02/Fe 001</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -15097,14 +15097,14 @@
         <v>26</v>
       </c>
       <c r="V203" t="n">
-        <v>54.80404</v>
+        <v>53.03718</v>
       </c>
       <c r="W203" t="n">
-        <v>-66.87016</v>
+        <v>-66.93694000000001</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15114,24 +15114,24 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Wishart No 1 (Wishart Mine)</t>
+          <t>Lorraine Mine</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>023J/15/Fe 003</t>
+          <t>023G/02/Fe 004</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -15169,14 +15169,14 @@
         <v>26</v>
       </c>
       <c r="V204" t="n">
-        <v>54.76166</v>
+        <v>53.06833</v>
       </c>
       <c r="W204" t="n">
-        <v>-66.88793</v>
+        <v>-66.94949</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ruth Lake No 9</t>
+          <t>Fleming No 3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>023J/15/Fe 005</t>
+          <t>023J/14/Fe 022</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -15241,14 +15241,14 @@
         <v>26</v>
       </c>
       <c r="V205" t="n">
-        <v>54.80033</v>
+        <v>54.85836</v>
       </c>
       <c r="W205" t="n">
-        <v>-66.89447</v>
+        <v>-67.03167999999999</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
         </is>
       </c>
     </row>
@@ -15258,24 +15258,24 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ruth Lake No 5</t>
+          <t>Timmins No 1</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>023J/15/Fe 007</t>
+          <t>023J/14/Fe 018</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -15313,14 +15313,14 @@
         <v>26</v>
       </c>
       <c r="V206" t="n">
-        <v>54.80503</v>
+        <v>54.88449</v>
       </c>
       <c r="W206" t="n">
-        <v>-66.88023</v>
+        <v>-67.08575</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15330,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Ruth Lake No 7</t>
+          <t>Timmins No 4</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>023J/15/Fe 006</t>
+          <t>023J/14/Fe 023</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15385,14 +15385,14 @@
         <v>26</v>
       </c>
       <c r="V207" t="n">
-        <v>54.80557</v>
+        <v>54.89884</v>
       </c>
       <c r="W207" t="n">
-        <v>-66.90618000000001</v>
+        <v>-67.10881000000001</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
         </is>
       </c>
     </row>
@@ -15402,24 +15402,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ruth Lake No 6</t>
+          <t>Timmins No 2</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>023J/15/Fe 008</t>
+          <t>023J/14/Fe 019</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15457,14 +15457,14 @@
         <v>26</v>
       </c>
       <c r="V208" t="n">
-        <v>54.80104</v>
+        <v>54.89421</v>
       </c>
       <c r="W208" t="n">
-        <v>-66.87327999999999</v>
+        <v>-67.08716</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
         </is>
       </c>
     </row>
@@ -15474,24 +15474,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Timmins No 6</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>023J/15/Fe 010</t>
+          <t>023J/14/Fe 021</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15529,14 +15529,14 @@
         <v>26</v>
       </c>
       <c r="V209" t="n">
-        <v>54.77437</v>
+        <v>54.90148</v>
       </c>
       <c r="W209" t="n">
-        <v>-66.82881</v>
+        <v>-67.09757999999999</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Copper Creek BV</t>
+          <t>Horseshoe Zone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>012H/16/Cu 040</t>
+          <t>002E/02/Au 039</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>44</v>
       </c>
       <c r="V2" t="n">
-        <v>49.91887</v>
+        <v>49.01341</v>
       </c>
       <c r="W2" t="n">
-        <v>-56.20986</v>
+        <v>-54.81741</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Horseshoe Zone</t>
+          <t>Deep Fox</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>002E/02/Au 039</t>
+          <t>003D/05/Ree007</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>49.01341</v>
+        <v>52.3805</v>
       </c>
       <c r="W3" t="n">
-        <v>-54.81741</v>
+        <v>-55.64987</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viking Gold-Thor Trend</t>
+          <t>Mart Lake Graphite</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012H/10/Au 011</t>
+          <t>023B/14/Gf 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Copper, Zinc, Silver, Graphite</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -760,23 +760,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>49.69447</v>
+        <v>52.8283</v>
       </c>
       <c r="W4" t="n">
-        <v>-56.99193</v>
+        <v>-67.01484000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PW Zone</t>
+          <t>Deer Cove Main Zone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>011O/10/Au 011</t>
+          <t>012I/01/Au 001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,14 +841,14 @@
         <v>44</v>
       </c>
       <c r="V5" t="n">
-        <v>47.74631</v>
+        <v>50.01619</v>
       </c>
       <c r="W5" t="n">
-        <v>-58.94364</v>
+        <v>-56.04389</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deep Fox</t>
+          <t>Windowglass Hill - Main Zone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>003D/05/Ree007</t>
+          <t>011O/10/Au 001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Copper, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>44</v>
       </c>
       <c r="V6" t="n">
-        <v>52.3805</v>
+        <v>47.74279</v>
       </c>
       <c r="W6" t="n">
-        <v>-55.64987</v>
+        <v>-58.95727</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mart Lake Graphite</t>
+          <t>Bull Road Showing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>023B/14/Gf 001</t>
+          <t>002E/12/Zn 007</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Graphite</t>
+          <t>Copper, Silver, Lead, Antimony, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>44</v>
       </c>
       <c r="V7" t="n">
-        <v>52.8283</v>
+        <v>49.51431</v>
       </c>
       <c r="W7" t="n">
-        <v>-67.01484000000001</v>
+        <v>-55.7118</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rainbow Deposit</t>
+          <t>Keats</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>013J/12/U  008</t>
+          <t>002D/15/Au 010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>44</v>
       </c>
       <c r="V8" t="n">
-        <v>54.56417</v>
+        <v>48.97891</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.99369</v>
+        <v>-54.8402</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michelin Deposit</t>
+          <t>Keats South</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>013J/12/U  001</t>
+          <t>002D/15/Au 060</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>44</v>
       </c>
       <c r="V9" t="n">
-        <v>54.58562</v>
+        <v>48.97791</v>
       </c>
       <c r="W9" t="n">
-        <v>-59.98056</v>
+        <v>-54.84407</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deer Cove Main Zone</t>
+          <t>Voisey's Bay, South Eastern Deeps</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>012I/01/Au 001</t>
+          <t>014D/08/Ni 017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>50.01619</v>
+        <v>56.31756</v>
       </c>
       <c r="W10" t="n">
-        <v>-56.04389</v>
+        <v>-62.06953</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apsy Zone</t>
+          <t>Area 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>012H/15/Au 014</t>
+          <t>013K/07/U  007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Copper, Vanadium, Uranium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1273,14 +1273,14 @@
         <v>44</v>
       </c>
       <c r="V11" t="n">
-        <v>49.89471</v>
+        <v>54.46751</v>
       </c>
       <c r="W11" t="n">
-        <v>-56.82917</v>
+        <v>-60.98105</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
         </is>
       </c>
     </row>
@@ -1290,24 +1290,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Road Zone</t>
+          <t>Moly Brook</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012H/15/Au 011</t>
+          <t>011P/11/Mo 001</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>44</v>
       </c>
       <c r="V12" t="n">
-        <v>49.88465</v>
+        <v>47.61683</v>
       </c>
       <c r="W12" t="n">
-        <v>-56.83885</v>
+        <v>-57.1034</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
         </is>
       </c>
     </row>
@@ -1362,24 +1362,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jacques Lake</t>
+          <t>Voisey's Bay, Far Eastern Deeps</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>013J/12/U  018</t>
+          <t>014D/08/Ni 013</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1417,14 +1417,14 @@
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>54.71754</v>
+        <v>56.32109</v>
       </c>
       <c r="W13" t="n">
-        <v>-59.59268</v>
+        <v>-62.06064</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
         </is>
       </c>
     </row>
@@ -1434,24 +1434,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Turners Ridge</t>
+          <t>Voisey's Bay, North Eastern Deeps</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>012H/11/Pb 001</t>
+          <t>014D/08/Ni 011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>44</v>
       </c>
       <c r="V14" t="n">
-        <v>49.59029</v>
+        <v>56.32929</v>
       </c>
       <c r="W14" t="n">
-        <v>-57.00443</v>
+        <v>-62.07733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
         </is>
       </c>
     </row>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aillik Prospect</t>
+          <t>Voisey's Bay, Southeast Extension</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>013O/03/Mo 003</t>
+          <t>014D/08/Ni 012</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Uranium, Fluorine, Copper, Molybdenum</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1561,14 +1561,14 @@
         <v>44</v>
       </c>
       <c r="V15" t="n">
-        <v>55.21102</v>
+        <v>56.32489</v>
       </c>
       <c r="W15" t="n">
-        <v>-59.16645</v>
+        <v>-62.08804</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013O%2F03%2FMo%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20012</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kitts</t>
+          <t>Saddle Zone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>013J/14/U  001</t>
+          <t>002E/02/Au 038</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>44</v>
       </c>
       <c r="V16" t="n">
-        <v>54.99779</v>
+        <v>49.00899</v>
       </c>
       <c r="W16" t="n">
-        <v>-59.4872</v>
+        <v>-54.81554</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gear Lake</t>
+          <t>Two Tom Lake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>013J/13/U  010</t>
+          <t>013L/01/REE001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>44</v>
       </c>
       <c r="V17" t="n">
-        <v>54.94329</v>
+        <v>54.21359</v>
       </c>
       <c r="W17" t="n">
-        <v>-59.54386</v>
+        <v>-62.14192</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
         </is>
       </c>
     </row>
@@ -1722,24 +1722,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inda Lake</t>
+          <t>Road Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>013J/13/U  009</t>
+          <t>012H/15/Au 011</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Uranium</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1774,17 +1774,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>54.92456</v>
+        <v>49.88465</v>
       </c>
       <c r="W18" t="n">
-        <v>-59.5807</v>
+        <v>-56.83885</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nash Lake (Main Zone)</t>
+          <t>Apsy Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>013J/13/U  006</t>
+          <t>012H/15/Au 014</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1846,17 +1846,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V19" t="n">
-        <v>54.91032</v>
+        <v>49.89471</v>
       </c>
       <c r="W19" t="n">
-        <v>-59.62004</v>
+        <v>-56.82917</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H Brook Showing</t>
+          <t>Viking Gold-Thor Trend</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>011O/15/Au 004</t>
+          <t>012H/10/Au 011</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1912,23 +1912,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V20" t="n">
-        <v>47.7624</v>
+        <v>49.69447</v>
       </c>
       <c r="W20" t="n">
-        <v>-58.91357</v>
+        <v>-56.99193</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>51 Zone</t>
+          <t>PW Zone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>011O/15/Au 003</t>
+          <t>011O/10/Au 011</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1990,17 +1990,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V21" t="n">
-        <v>47.75077</v>
+        <v>47.74631</v>
       </c>
       <c r="W21" t="n">
-        <v>-58.93823</v>
+        <v>-58.94364</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit 41 Zone</t>
+          <t>Cape Ray Gold Deposit #4 Zone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>011O/15/Au 002</t>
+          <t>011O/15/Au 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2062,17 +2062,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V22" t="n">
-        <v>47.75858</v>
+        <v>47.76081</v>
       </c>
       <c r="W22" t="n">
-        <v>-58.92331</v>
+        <v>-58.91872</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit #4 Zone</t>
+          <t>Cape Ray Gold Deposit 41 Zone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>011O/15/Au 001</t>
+          <t>011O/15/Au 002</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2134,17 +2134,17 @@
         <v>325</v>
       </c>
       <c r="U23" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V23" t="n">
-        <v>47.76081</v>
+        <v>47.75858</v>
       </c>
       <c r="W23" t="n">
-        <v>-58.91872</v>
+        <v>-58.92331</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -2154,24 +2154,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Two Tom Lake</t>
+          <t>Point Leamington Deposit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>013L/01/REE001</t>
+          <t>002E/05/Zn 001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Silver, Copper, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2206,17 +2206,17 @@
         <v>325</v>
       </c>
       <c r="U24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V24" t="n">
-        <v>54.21359</v>
+        <v>49.27672</v>
       </c>
       <c r="W24" t="n">
-        <v>-62.14192</v>
+        <v>-55.63152</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mann #1</t>
+          <t>Strickland - Silver Hill Zone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>013L/01/Be 001</t>
+          <t>011O/16/Zn 002</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Niobium, Uranium, Zinc, Beryllium</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2278,17 +2278,17 @@
         <v>325</v>
       </c>
       <c r="U25" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>54.23929</v>
+        <v>47.81</v>
       </c>
       <c r="W25" t="n">
-        <v>-62.3924</v>
+        <v>-58.2985</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>51 Zone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>011O/15/Au 003</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2350,17 +2350,17 @@
         <v>325</v>
       </c>
       <c r="U26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>48.69485</v>
+        <v>47.75077</v>
       </c>
       <c r="W26" t="n">
-        <v>-58.68177</v>
+        <v>-58.93823</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -2370,24 +2370,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Keats</t>
+          <t>Gear Lake</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>002D/15/Au 010</t>
+          <t>013J/13/U  010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2422,17 +2422,17 @@
         <v>325</v>
       </c>
       <c r="U27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V27" t="n">
-        <v>48.97891</v>
+        <v>54.94329</v>
       </c>
       <c r="W27" t="n">
-        <v>-54.8402</v>
+        <v>-59.54386</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
         </is>
       </c>
     </row>
@@ -2442,24 +2442,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bull Road Showing</t>
+          <t>Nash Lake (Main Zone)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>002E/12/Zn 007</t>
+          <t>013J/13/U  006</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Antimony, Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2494,17 +2494,17 @@
         <v>325</v>
       </c>
       <c r="U28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V28" t="n">
-        <v>49.51431</v>
+        <v>54.91032</v>
       </c>
       <c r="W28" t="n">
-        <v>-55.7118</v>
+        <v>-59.62004</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2514,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Point Leamington Deposit</t>
+          <t>Aillik Prospect</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>002E/05/Zn 001</t>
+          <t>013O/03/Mo 003</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead, Zinc</t>
+          <t>Uranium, Fluorine, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2566,17 +2566,17 @@
         <v>325</v>
       </c>
       <c r="U29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V29" t="n">
-        <v>49.27672</v>
+        <v>55.21102</v>
       </c>
       <c r="W29" t="n">
-        <v>-55.63152</v>
+        <v>-59.16645</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013O%2F03%2FMo%20003</t>
         </is>
       </c>
     </row>
@@ -2586,24 +2586,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Windowglass Hill - Main Zone</t>
+          <t>Kitts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>011O/10/Au 001</t>
+          <t>013J/14/U  001</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2632,23 +2632,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V30" t="n">
-        <v>47.74279</v>
+        <v>54.99779</v>
       </c>
       <c r="W30" t="n">
-        <v>-58.95727</v>
+        <v>-59.4872</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -2658,24 +2658,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Southeast Extension</t>
+          <t>Jacques Lake</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>014D/08/Ni 012</t>
+          <t>013J/12/U  018</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2710,17 +2710,17 @@
         <v>325</v>
       </c>
       <c r="U31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V31" t="n">
-        <v>56.32489</v>
+        <v>54.71754</v>
       </c>
       <c r="W31" t="n">
-        <v>-62.08804</v>
+        <v>-59.59268</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
         </is>
       </c>
     </row>
@@ -2730,24 +2730,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Voisey's Bay, North Eastern Deeps</t>
+          <t>Michelin Deposit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>014D/08/Ni 011</t>
+          <t>013J/12/U  001</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2782,17 +2782,17 @@
         <v>325</v>
       </c>
       <c r="U32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V32" t="n">
-        <v>56.32929</v>
+        <v>54.58562</v>
       </c>
       <c r="W32" t="n">
-        <v>-62.07733</v>
+        <v>-59.98056</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -2802,24 +2802,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Voisey's Bay, South Eastern Deeps</t>
+          <t>Rainbow Deposit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>014D/08/Ni 017</t>
+          <t>013J/12/U  008</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2848,23 +2848,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V33" t="n">
-        <v>56.31756</v>
+        <v>54.56417</v>
       </c>
       <c r="W33" t="n">
-        <v>-62.06953</v>
+        <v>-59.99369</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
         <v>325</v>
       </c>
       <c r="U34" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V34" t="n">
         <v>54.56554</v>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Springer's Hill-Main Showing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>013K/07/U  007</t>
+          <t>012B/16/Cr 002</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Vanadium, Uranium</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2998,17 +2998,17 @@
         <v>325</v>
       </c>
       <c r="U35" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V35" t="n">
-        <v>54.46751</v>
+        <v>48.7927</v>
       </c>
       <c r="W35" t="n">
-        <v>-60.98105</v>
+        <v>-58.44526</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Moran Lake C-Zone</t>
+          <t>Mann #1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>013K/07/U  002</t>
+          <t>013L/01/Be 001</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
+          <t>Niobium, Uranium, Zinc, Beryllium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3070,17 +3070,17 @@
         <v>325</v>
       </c>
       <c r="U36" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V36" t="n">
-        <v>54.47908</v>
+        <v>54.23929</v>
       </c>
       <c r="W36" t="n">
-        <v>-60.9581</v>
+        <v>-62.3924</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
         </is>
       </c>
     </row>
@@ -3090,24 +3090,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grey River Tungsten</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>011P/11/W  001</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3142,17 +3142,17 @@
         <v>325</v>
       </c>
       <c r="U37" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V37" t="n">
-        <v>47.59343</v>
+        <v>48.69485</v>
       </c>
       <c r="W37" t="n">
-        <v>-57.10342</v>
+        <v>-58.68177</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3162,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Moly Brook</t>
+          <t>Moran Lake C-Zone</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>011P/11/Mo 001</t>
+          <t>013K/07/U  002</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Vanadium, Copper, Iron, Silver, Uranium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3214,17 +3214,17 @@
         <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="V38" t="n">
-        <v>47.61683</v>
+        <v>54.47908</v>
       </c>
       <c r="W38" t="n">
-        <v>-57.1034</v>
+        <v>-60.9581</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20002</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Strickland - Silver Hill Zone</t>
+          <t>Lewis Brook Mine</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>011O/16/Zn 002</t>
+          <t>012B/15/Asb001</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3286,17 +3286,17 @@
         <v>325</v>
       </c>
       <c r="U39" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V39" t="n">
-        <v>47.81</v>
+        <v>48.77071</v>
       </c>
       <c r="W39" t="n">
-        <v>-58.2985</v>
+        <v>-58.56548</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
         </is>
       </c>
     </row>
@@ -3306,24 +3306,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Strickland - Main Zone</t>
+          <t>Beaver Dam</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>011O/16/Zn 001</t>
+          <t>012H/15/Au 018</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Gold, Zinc</t>
+          <t>Arsenic, Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3358,17 +3358,17 @@
         <v>325</v>
       </c>
       <c r="U40" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V40" t="n">
-        <v>47.80818</v>
+        <v>49.86141</v>
       </c>
       <c r="W40" t="n">
-        <v>-58.29993</v>
+        <v>-56.85295</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
         </is>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jaclyn Main - Golden Promise</t>
+          <t>Strange Lake</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>012A/16/Au 002</t>
+          <t>024A/08/Ree001</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3430,17 +3430,17 @@
         <v>325</v>
       </c>
       <c r="U41" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V41" t="n">
-        <v>48.90572</v>
+        <v>56.31656</v>
       </c>
       <c r="W41" t="n">
-        <v>-56.15002</v>
+        <v>-64.12678</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Strickland - Copper Zone</t>
+          <t>Grey River Tungsten</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>011O/16/Cu 001</t>
+          <t>011P/11/W  001</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper</t>
+          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3502,17 +3502,17 @@
         <v>325</v>
       </c>
       <c r="U42" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V42" t="n">
-        <v>47.80365</v>
+        <v>47.59343</v>
       </c>
       <c r="W42" t="n">
-        <v>-58.30275</v>
+        <v>-57.10342</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ackley City</t>
+          <t>Inda Lake</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>001M/11/Mo 002</t>
+          <t>013J/13/U  009</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Molybdenum</t>
+          <t>Molybdenum, Copper, Uranium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3574,17 +3574,17 @@
         <v>325</v>
       </c>
       <c r="U43" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V43" t="n">
-        <v>47.69347</v>
+        <v>54.92456</v>
       </c>
       <c r="W43" t="n">
-        <v>-55.20716</v>
+        <v>-59.5807</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
         </is>
       </c>
     </row>
@@ -3594,24 +3594,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Far Eastern Deeps</t>
+          <t>Burnt Lake North (Main Zone)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>014D/08/Ni 013</t>
+          <t>013J/12/U  012</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Fluorine, Zinc, Lead, Molybdenum, Gold, Silver, Uranium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3646,17 +3646,17 @@
         <v>325</v>
       </c>
       <c r="U44" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V44" t="n">
-        <v>56.32109</v>
+        <v>54.63965</v>
       </c>
       <c r="W44" t="n">
-        <v>-62.06064</v>
+        <v>-59.70939</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20012</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Springer's Hill-Main Showing</t>
+          <t>Round Pond Deposit</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>012B/16/Cr 002</t>
+          <t>012P/08/Zn 015</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Fluorine, Lead, Zinc</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3718,17 +3718,17 @@
         <v>325</v>
       </c>
       <c r="U45" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V45" t="n">
-        <v>48.7927</v>
+        <v>51.25735</v>
       </c>
       <c r="W45" t="n">
-        <v>-58.44526</v>
+        <v>-56.26701</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Keats South</t>
+          <t>Norsk North Block</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>002D/15/Au 060</t>
+          <t>012B/10/Dol003</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3790,17 +3790,17 @@
         <v>325</v>
       </c>
       <c r="U46" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V46" t="n">
-        <v>48.97791</v>
+        <v>48.53397</v>
       </c>
       <c r="W46" t="n">
-        <v>-54.84407</v>
+        <v>-58.9773</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saddle Zone</t>
+          <t>Norsk South Block</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>002E/02/Au 038</t>
+          <t>012B/10/Dol004</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3856,23 +3856,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V47" t="n">
-        <v>49.00899</v>
+        <v>48.52445</v>
       </c>
       <c r="W47" t="n">
-        <v>-54.81554</v>
+        <v>-58.99684</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lewis Brook Mine</t>
+          <t>Porcupine Strand North Beach</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>012B/15/Asb001</t>
+          <t>013I/03/Ti 001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>37</v>
       </c>
       <c r="V48" t="n">
-        <v>48.77071</v>
+        <v>54.03818</v>
       </c>
       <c r="W48" t="n">
-        <v>-58.56548</v>
+        <v>-57.31912</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Beaver Dam</t>
+          <t>Deer Cove Talc Zone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>012H/15/Au 018</t>
+          <t>012I/01/Tlc001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Arsenic, Gold</t>
+          <t>Magnesium, Talc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4009,14 +4009,14 @@
         <v>37</v>
       </c>
       <c r="V49" t="n">
-        <v>49.86141</v>
+        <v>50.01534</v>
       </c>
       <c r="W49" t="n">
-        <v>-56.85295</v>
+        <v>-56.04949</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Strange Lake</t>
+          <t>Sheep Brook</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>024A/08/Ree001</t>
+          <t>012B/08/Gyp001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>56.31656</v>
+        <v>48.39536</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.12678</v>
+        <v>-58.42046</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Norsk South Block</t>
+          <t>Romaines Brook</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>012B/10/Dol004</t>
+          <t>012B/10/Gyp001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Magnesium, Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>48.52445</v>
+        <v>48.55534</v>
       </c>
       <c r="W51" t="n">
-        <v>-58.99684</v>
+        <v>-58.66751</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Norsk North Block</t>
+          <t>Foxtrot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>012B/10/Dol003</t>
+          <t>003D/05/Ree001</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4225,14 +4225,14 @@
         <v>37</v>
       </c>
       <c r="V52" t="n">
-        <v>48.53397</v>
+        <v>52.40035</v>
       </c>
       <c r="W52" t="n">
-        <v>-58.9773</v>
+        <v>-55.82418</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Round Pond Deposit</t>
+          <t>Mount Margaret Pond Vein</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012P/08/Zn 015</t>
+          <t>001L/14/Fl 039</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fluorine, Lead, Zinc</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>51.25735</v>
+        <v>46.95861</v>
       </c>
       <c r="W53" t="n">
-        <v>-56.26701</v>
+        <v>-55.38707</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20039</t>
         </is>
       </c>
     </row>
@@ -4314,24 +4314,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Burnt Lake North (Main Zone)</t>
+          <t>Ackley City</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>013J/12/U  012</t>
+          <t>001M/11/Mo 002</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fluorine, Zinc, Lead, Molybdenum, Gold, Silver, Uranium</t>
+          <t>Zinc, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4366,17 +4366,17 @@
         <v>325</v>
       </c>
       <c r="U54" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V54" t="n">
-        <v>54.63965</v>
+        <v>47.69347</v>
       </c>
       <c r="W54" t="n">
-        <v>-59.70939</v>
+        <v>-55.20716</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
         </is>
       </c>
     </row>
@@ -4386,24 +4386,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Porcupine Strand North Beach</t>
+          <t>Turners Ridge</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>013I/03/Ti 001</t>
+          <t>012H/11/Pb 001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4432,23 +4432,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U55" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V55" t="n">
-        <v>54.03818</v>
+        <v>49.59029</v>
       </c>
       <c r="W55" t="n">
-        <v>-57.31912</v>
+        <v>-57.00443</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F11%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -4458,24 +4458,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deer Cove Talc Zone</t>
+          <t>Copper Creek BV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>012I/01/Tlc001</t>
+          <t>012H/16/Cu 040</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Magnesium, Talc</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4510,17 +4510,17 @@
         <v>325</v>
       </c>
       <c r="U56" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V56" t="n">
-        <v>50.01534</v>
+        <v>49.91887</v>
       </c>
       <c r="W56" t="n">
-        <v>-56.04949</v>
+        <v>-56.20986</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
         </is>
       </c>
     </row>
@@ -4530,24 +4530,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Foxtrot</t>
+          <t>Jaclyn Main - Golden Promise</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>003D/05/Ree001</t>
+          <t>012A/16/Au 002</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Zirconium, Yttrium, Niobium, Rare Earth Elements</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4582,17 +4582,17 @@
         <v>325</v>
       </c>
       <c r="U57" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V57" t="n">
-        <v>52.40035</v>
+        <v>48.90572</v>
       </c>
       <c r="W57" t="n">
-        <v>-55.82418</v>
+        <v>-56.15002</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -4602,29 +4602,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mount Margaret Pond Vein</t>
+          <t>Hope Brook</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>001L/14/Fl 039</t>
+          <t>011O/09/Au 003</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I58" t="b">
@@ -4654,17 +4654,17 @@
         <v>325</v>
       </c>
       <c r="U58" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V58" t="n">
-        <v>46.95861</v>
+        <v>47.73806</v>
       </c>
       <c r="W58" t="n">
-        <v>-55.38707</v>
+        <v>-58.09531</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -4674,24 +4674,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Romaines Brook</t>
+          <t>Strickland - Main Zone</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>012B/10/Gyp001</t>
+          <t>011O/16/Zn 001</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Magnesium, Anhydrite, Gypsum</t>
+          <t>Lead, Copper, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4726,17 +4726,17 @@
         <v>325</v>
       </c>
       <c r="U59" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V59" t="n">
-        <v>48.55534</v>
+        <v>47.80818</v>
       </c>
       <c r="W59" t="n">
-        <v>-58.66751</v>
+        <v>-58.29993</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -4746,29 +4746,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Voisey's Bay, Ovoid</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>014D/08/Ni 001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I60" t="b">
@@ -4798,17 +4798,17 @@
         <v>325</v>
       </c>
       <c r="U60" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V60" t="n">
-        <v>48.39536</v>
+        <v>56.33134</v>
       </c>
       <c r="W60" t="n">
-        <v>-58.42046</v>
+        <v>-62.09706</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Ovoid</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>014D/08/Ni 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>56.33134</v>
+        <v>47.4063</v>
       </c>
       <c r="W61" t="n">
-        <v>-62.09706</v>
+        <v>-52.70699</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -4890,29 +4890,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGS Vein</t>
+          <t>Strickland - Copper Zone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>001L/14/Fl 013</t>
+          <t>011O/16/Cu 001</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Fluorine</t>
+          <t>Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I62" t="b">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>46.91489</v>
+        <v>47.80365</v>
       </c>
       <c r="W62" t="n">
-        <v>-55.48584</v>
+        <v>-58.30275</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -4962,24 +4962,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blow-Me-Down Chromite #1</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>012G/01/Cr 001</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5008,23 +5008,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T63" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U63" t="n">
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>49.01096</v>
+        <v>47.4438</v>
       </c>
       <c r="W63" t="n">
-        <v>-58.24371</v>
+        <v>-54.4169</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5034,29 +5034,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Goose Cove</t>
+          <t>H Brook Showing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>002M/05/Cu 001</t>
+          <t>011O/15/Au 004</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zinc, Nickel, Iron, Copper</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>51.31009</v>
+        <v>47.7624</v>
       </c>
       <c r="W64" t="n">
-        <v>-55.62342</v>
+        <v>-58.91357</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
         </is>
       </c>
     </row>
@@ -5106,24 +5106,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>York Harbour Mine</t>
+          <t>Betts Cove Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>012G/01/Cu 002</t>
+          <t>002E/13/Cu 002</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>49.05208</v>
+        <v>49.81179</v>
       </c>
       <c r="W65" t="n">
-        <v>-58.30769</v>
+        <v>-55.80608</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -5178,24 +5178,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Tilt Cove Mine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>002E/13/Cu 001</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold, Nickel, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5233,14 +5233,14 @@
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>50.27283</v>
+        <v>49.88214</v>
       </c>
       <c r="W66" t="n">
-        <v>-57.46448</v>
+        <v>-55.62813</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Terra Nova Mine</t>
+          <t>Nugget Pond</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>012H/16/Cu 004</t>
+          <t>002E/13/Au 001</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>49.92133</v>
+        <v>49.84502</v>
       </c>
       <c r="W67" t="n">
-        <v>-56.22896</v>
+        <v>-55.77536</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -5322,24 +5322,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>50.31118</v>
+        <v>48.5353</v>
       </c>
       <c r="W68" t="n">
-        <v>-57.43009</v>
+        <v>-58.48804</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -5394,24 +5394,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-Q Zone</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>012I/06/Zn 016</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>50.29741</v>
+        <v>49.19579</v>
       </c>
       <c r="W69" t="n">
-        <v>-57.48016</v>
+        <v>-57.84974</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -5466,24 +5466,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Browning Mine</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>012H/10/Au 001</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Gold</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>49.71799</v>
+        <v>52.961</v>
       </c>
       <c r="W70" t="n">
-        <v>-56.92565</v>
+        <v>-66.81446</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5538,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Goldenville</t>
+          <t>Argyle</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>012H/16/Au 033</t>
+          <t>012H/16/Au 083</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper, Iron, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5584,23 +5584,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>49.99193</v>
+        <v>49.97838</v>
       </c>
       <c r="W71" t="n">
-        <v>-56.05735</v>
+        <v>-56.05952</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stog'er Tight</t>
+          <t>Ming West</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>012H/16/Au 041</t>
+          <t>012H/16/Cu 029</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5656,23 +5656,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U72" t="n">
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>49.9661</v>
+        <v>49.9148</v>
       </c>
       <c r="W72" t="n">
-        <v>-56.07765</v>
+        <v>-56.08996</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>Terra Nova Mine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>012H/16/Cu 004</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5737,14 +5737,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>49.19579</v>
+        <v>49.92133</v>
       </c>
       <c r="W73" t="n">
-        <v>-57.84974</v>
+        <v>-56.22896</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>Goldenville</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>012H/16/Au 033</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Copper, Iron, Gold</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5800,23 +5800,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U74" t="n">
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>52.961</v>
+        <v>49.99193</v>
       </c>
       <c r="W74" t="n">
-        <v>-66.81446</v>
+        <v>-56.05735</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
         </is>
       </c>
     </row>
@@ -5826,24 +5826,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-J Zone</t>
+          <t>Turk's Gut</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>012I/06/Zn 009</t>
+          <t>001N/11/Cu 001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>50.30247</v>
+        <v>47.50226</v>
       </c>
       <c r="W75" t="n">
-        <v>-57.47459</v>
+        <v>-53.20074</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5898,24 +5898,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-L Zone</t>
+          <t>Sleepy Hollow</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>012I/06/Zn 011</t>
+          <t>002E/12/Cu 031</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lead, Dolomite, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>50.27686</v>
+        <v>49.59747</v>
       </c>
       <c r="W76" t="n">
-        <v>-57.46788</v>
+        <v>-55.94735</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
         </is>
       </c>
     </row>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-N Zone</t>
+          <t>Pine Cove</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>012I/06/Zn 013</t>
+          <t>012H/16/Au 023</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>50.29873</v>
+        <v>49.96066</v>
       </c>
       <c r="W77" t="n">
-        <v>-57.48691</v>
+        <v>-56.13074</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6042,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-F Zone</t>
+          <t>Miles Cove Mine</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>012I/06/Zn 006</t>
+          <t>002E/12/Cu 012</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6094,17 +6094,17 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V78" t="n">
-        <v>50.29437</v>
+        <v>49.53936</v>
       </c>
       <c r="W78" t="n">
-        <v>-57.45374</v>
+        <v>-55.79062</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
         </is>
       </c>
     </row>
@@ -6114,24 +6114,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-E Zone</t>
+          <t>Stog'er Tight</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>012I/06/Zn 005</t>
+          <t>012H/16/Au 041</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6166,17 +6166,17 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V79" t="n">
-        <v>50.31067</v>
+        <v>49.9661</v>
       </c>
       <c r="W79" t="n">
-        <v>-57.44799</v>
+        <v>-56.07765</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
         </is>
       </c>
     </row>
@@ -6186,24 +6186,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-C Zone</t>
+          <t>Stewart Mine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>012I/06/Zn 003</t>
+          <t>002E/10/Au 001</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Antimony, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6238,17 +6238,17 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V80" t="n">
-        <v>50.30435</v>
+        <v>49.58065</v>
       </c>
       <c r="W80" t="n">
-        <v>-57.45355</v>
+        <v>-54.85442</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -6258,24 +6258,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-D Zone</t>
+          <t>Crescent Lake Mine</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>012I/06/Zn 004</t>
+          <t>002E/05/Cu 013</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6310,17 +6310,17 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V81" t="n">
-        <v>50.30795</v>
+        <v>49.48531</v>
       </c>
       <c r="W81" t="n">
-        <v>-57.45218</v>
+        <v>-55.84455</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FCu%20013</t>
         </is>
       </c>
     </row>
@@ -6330,24 +6330,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-B Zone</t>
+          <t>Tilt Cove/East Mine/Upper Dump</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>012I/06/Zn 002</t>
+          <t>002E/13/Au 028</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Nickel, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6382,17 +6382,17 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V82" t="n">
-        <v>50.2975</v>
+        <v>49.88512</v>
       </c>
       <c r="W82" t="n">
-        <v>-57.45784</v>
+        <v>-55.62192</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
         </is>
       </c>
     </row>
@@ -6402,24 +6402,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-H Zone</t>
+          <t>Stoneyhouse</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>012I/06/Zn 008</t>
+          <t>001M/01/Cu 001</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6454,17 +6454,17 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V83" t="n">
-        <v>50.29179</v>
+        <v>47.0541</v>
       </c>
       <c r="W83" t="n">
-        <v>-57.44599</v>
+        <v>-54.11056</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-G Zone</t>
+          <t>Upper Drill Brook Mine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>012I/06/Zn 007</t>
+          <t>012B/09/Fe 002</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6526,17 +6526,17 @@
         <v>325</v>
       </c>
       <c r="U84" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V84" t="n">
-        <v>50.29448</v>
+        <v>48.53533</v>
       </c>
       <c r="W84" t="n">
-        <v>-57.44714</v>
+        <v>-58.48601</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-M Zone</t>
+          <t>Blow-Me-Down Chromite #1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>012I/06/Zn 012</t>
+          <t>012G/01/Cr 001</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6592,23 +6592,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T85" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U85" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V85" t="n">
-        <v>50.29514</v>
+        <v>49.01096</v>
       </c>
       <c r="W85" t="n">
-        <v>-57.44013</v>
+        <v>-58.24371</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -6618,29 +6618,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Wabush No. 6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>023G/02/Fe 006</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6670,17 +6670,17 @@
         <v>325</v>
       </c>
       <c r="U86" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V86" t="n">
-        <v>49.45488</v>
+        <v>53.01798</v>
       </c>
       <c r="W86" t="n">
-        <v>-55.49811</v>
+        <v>-66.89297999999999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -6690,29 +6690,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stoneyhouse</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>001M/01/Cu 001</t>
+          <t>023B/14/Fe 028</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6742,17 +6742,17 @@
         <v>325</v>
       </c>
       <c r="U87" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V87" t="n">
-        <v>47.0541</v>
+        <v>52.94868</v>
       </c>
       <c r="W87" t="n">
-        <v>-54.11056</v>
+        <v>-67.01146</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F01%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -6762,29 +6762,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Indian Head Mine</t>
+          <t>Sawyer Lake</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>012B/10/Fe 001</t>
+          <t>023I/05/Fe 001</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6814,17 +6814,17 @@
         <v>325</v>
       </c>
       <c r="U88" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V88" t="n">
-        <v>48.52416</v>
+        <v>54.45206</v>
       </c>
       <c r="W88" t="n">
-        <v>-58.5148</v>
+        <v>-65.98627</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tilt Cove/East Mine/Upper Dump</t>
+          <t>Howells River West Zone A</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>002E/13/Au 028</t>
+          <t>023J/14/Fe 001</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Zinc, Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -6886,17 +6886,17 @@
         <v>325</v>
       </c>
       <c r="U89" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V89" t="n">
-        <v>49.88512</v>
+        <v>54.90958</v>
       </c>
       <c r="W89" t="n">
-        <v>-55.62192</v>
+        <v>-67.26052</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6906,29 +6906,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tilt Cove Mine</t>
+          <t>Sheps Lake</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>002E/13/Cu 001</t>
+          <t>023J/11/Fe 001</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Silver, Zinc, Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -6958,17 +6958,17 @@
         <v>325</v>
       </c>
       <c r="U90" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V90" t="n">
-        <v>49.88214</v>
+        <v>54.73475</v>
       </c>
       <c r="W90" t="n">
-        <v>-55.62813</v>
+        <v>-67.06362</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6978,29 +6978,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Stewart Mine</t>
+          <t>Block 103 - Greenbush Zone</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>002E/10/Au 001</t>
+          <t>023J/14/Fe 043</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Silver, Antimony, Copper, Zinc, Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7030,17 +7030,17 @@
         <v>325</v>
       </c>
       <c r="U91" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V91" t="n">
-        <v>49.58065</v>
+        <v>54.97234</v>
       </c>
       <c r="W91" t="n">
-        <v>-54.85442</v>
+        <v>-67.25158</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
         </is>
       </c>
     </row>
@@ -7050,29 +7050,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Elizabeth No. 2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>023J/15/Fe 032</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -7102,17 +7102,17 @@
         <v>325</v>
       </c>
       <c r="U92" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V92" t="n">
-        <v>48.5353</v>
+        <v>54.77182</v>
       </c>
       <c r="W92" t="n">
-        <v>-58.48804</v>
+        <v>-66.88666000000001</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
         </is>
       </c>
     </row>
@@ -7122,29 +7122,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pine Cove</t>
+          <t>Howells River North</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>012H/16/Au 023</t>
+          <t>023O/03/Fe 007</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7174,17 +7174,17 @@
         <v>325</v>
       </c>
       <c r="U93" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V93" t="n">
-        <v>49.96066</v>
+        <v>55.01179</v>
       </c>
       <c r="W93" t="n">
-        <v>-56.13074</v>
+        <v>-67.37214</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -7194,29 +7194,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bishop South</t>
+          <t>Lorraine No. 4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>012B/08/Fe 002</t>
+          <t>023G/02/Fe 008</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7246,17 +7246,17 @@
         <v>325</v>
       </c>
       <c r="U94" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V94" t="n">
-        <v>48.39996</v>
+        <v>53.08316</v>
       </c>
       <c r="W94" t="n">
-        <v>-58.33683</v>
+        <v>-66.87726000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -7266,29 +7266,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bishop North</t>
+          <t>Kivivic No 4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>012B/08/Fe 001</t>
+          <t>023O/03/Fe 004</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7318,17 +7318,17 @@
         <v>325</v>
       </c>
       <c r="U95" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V95" t="n">
-        <v>48.40317</v>
+        <v>55.04865</v>
       </c>
       <c r="W95" t="n">
-        <v>-58.3315</v>
+        <v>-67.28158000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -7338,29 +7338,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Upper Drill Brook Mine</t>
+          <t>Kivivic No 3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>012B/09/Fe 002</t>
+          <t>023O/03/Fe 003</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7390,17 +7390,17 @@
         <v>325</v>
       </c>
       <c r="U96" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V96" t="n">
-        <v>48.53533</v>
+        <v>55.05061</v>
       </c>
       <c r="W96" t="n">
-        <v>-58.48601</v>
+        <v>-67.26130000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -7410,29 +7410,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Turk's Gut</t>
+          <t>Houston 3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>001N/11/Cu 001</t>
+          <t>023J/10/Fe 010</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7462,17 +7462,17 @@
         <v>325</v>
       </c>
       <c r="U97" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V97" t="n">
-        <v>47.50226</v>
+        <v>54.69887</v>
       </c>
       <c r="W97" t="n">
-        <v>-53.20074</v>
+        <v>-66.64483</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -7482,29 +7482,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cross Cove</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>002E/10/Sb 001</t>
+          <t>023B/14/Fe 020</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7534,17 +7534,17 @@
         <v>325</v>
       </c>
       <c r="U98" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V98" t="n">
-        <v>49.57534</v>
+        <v>52.83351</v>
       </c>
       <c r="W98" t="n">
-        <v>-54.86876</v>
+        <v>-67.0311</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
         </is>
       </c>
     </row>
@@ -7554,29 +7554,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Howells River West Zone B</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>023J/14/Fe 002</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I99" t="b">
@@ -7606,17 +7606,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V99" t="n">
-        <v>47.4438</v>
+        <v>54.87235</v>
       </c>
       <c r="W99" t="n">
-        <v>-54.4169</v>
+        <v>-67.21584</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7626,29 +7626,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Neal 1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>023B/14/Fe 008</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -7678,17 +7678,17 @@
         <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V100" t="n">
-        <v>47.4063</v>
+        <v>52.95013</v>
       </c>
       <c r="W100" t="n">
-        <v>-52.70699</v>
+        <v>-67.15191</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -7698,29 +7698,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Crescent Lake Mine</t>
+          <t>Duley No. 1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>002E/05/Cu 013</t>
+          <t>023B/14/Fe 001</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I101" t="b">
@@ -7750,17 +7750,17 @@
         <v>325</v>
       </c>
       <c r="U101" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V101" t="n">
-        <v>49.48531</v>
+        <v>52.87237</v>
       </c>
       <c r="W101" t="n">
-        <v>-55.84455</v>
+        <v>-67.05874</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FCu%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -7770,29 +7770,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Miles Cove Mine</t>
+          <t>Mills Lake</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>002E/12/Cu 012</t>
+          <t>023B/14/Fe 002</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I102" t="b">
@@ -7822,17 +7822,17 @@
         <v>325</v>
       </c>
       <c r="U102" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V102" t="n">
-        <v>49.53936</v>
+        <v>52.79808</v>
       </c>
       <c r="W102" t="n">
-        <v>-55.79062</v>
+        <v>-67.00413</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7842,29 +7842,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Pilley's Island Mine</t>
+          <t>Kivivic No 5</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>002E/12/Cu 001</t>
+          <t>023O/03/Fe 005</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I103" t="b">
@@ -7894,17 +7894,17 @@
         <v>325</v>
       </c>
       <c r="U103" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V103" t="n">
-        <v>49.50863</v>
+        <v>55.06664</v>
       </c>
       <c r="W103" t="n">
-        <v>-55.71872</v>
+        <v>-67.29537000000001</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -7914,29 +7914,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hope Brook</t>
+          <t>Redmond 5</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>011O/09/Au 003</t>
+          <t>023J/10/Fe 005</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I104" t="b">
@@ -7966,17 +7966,17 @@
         <v>325</v>
       </c>
       <c r="U104" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V104" t="n">
-        <v>47.73806</v>
+        <v>54.70854</v>
       </c>
       <c r="W104" t="n">
-        <v>-58.09531</v>
+        <v>-66.79174999999999</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -7986,29 +7986,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>La Manche</t>
+          <t>Houston 1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>001N/12/Pb 001</t>
+          <t>023J/10/Fe 008</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Barium, Lead</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I105" t="b">
@@ -8038,17 +8038,17 @@
         <v>325</v>
       </c>
       <c r="U105" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V105" t="n">
-        <v>47.6889</v>
+        <v>54.70748</v>
       </c>
       <c r="W105" t="n">
-        <v>-53.93901</v>
+        <v>-66.65615</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -8058,29 +8058,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sleepy Hollow</t>
+          <t>Houston 2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>002E/12/Cu 031</t>
+          <t>023J/10/Fe 009</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I106" t="b">
@@ -8110,17 +8110,17 @@
         <v>325</v>
       </c>
       <c r="U106" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V106" t="n">
-        <v>49.59747</v>
+        <v>54.71245</v>
       </c>
       <c r="W106" t="n">
-        <v>-55.94735</v>
+        <v>-66.66257</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -8130,29 +8130,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ming West</t>
+          <t>Timmins No 7</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>012H/16/Cu 029</t>
+          <t>023J/14/Fe 025</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8176,23 +8176,23 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T107" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U107" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V107" t="n">
-        <v>49.9148</v>
+        <v>54.89246</v>
       </c>
       <c r="W107" t="n">
-        <v>-56.08996</v>
+        <v>-67.07259000000001</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
         </is>
       </c>
     </row>
@@ -8202,29 +8202,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-A Zone</t>
+          <t>Timmins No 5</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>012I/06/Zn 001</t>
+          <t>023J/14/Fe 024</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I108" t="b">
@@ -8254,17 +8254,17 @@
         <v>325</v>
       </c>
       <c r="U108" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V108" t="n">
-        <v>50.29576</v>
+        <v>54.86384</v>
       </c>
       <c r="W108" t="n">
-        <v>-57.46512</v>
+        <v>-67.09327</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
         </is>
       </c>
     </row>
@@ -8274,29 +8274,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Argyle</t>
+          <t>Duley No. 2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>012H/16/Au 083</t>
+          <t>023B/15/Fe 008</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8326,17 +8326,17 @@
         <v>325</v>
       </c>
       <c r="U109" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V109" t="n">
-        <v>49.97838</v>
+        <v>52.87214</v>
       </c>
       <c r="W109" t="n">
-        <v>-56.05952</v>
+        <v>-66.99635000000001</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -8346,29 +8346,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-K Zone</t>
+          <t>Mile 2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>012I/06/Zn 010</t>
+          <t>023B/15/Fe 011</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I110" t="b">
@@ -8398,17 +8398,17 @@
         <v>325</v>
       </c>
       <c r="U110" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V110" t="n">
-        <v>50.2935</v>
+        <v>52.97907</v>
       </c>
       <c r="W110" t="n">
-        <v>-57.46875</v>
+        <v>-66.88907</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8418,29 +8418,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Betts Cove Mine</t>
+          <t>Wabush No. 8</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>002E/13/Cu 002</t>
+          <t>023B/15/Fe 005</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I111" t="b">
@@ -8470,17 +8470,17 @@
         <v>325</v>
       </c>
       <c r="U111" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V111" t="n">
-        <v>49.81179</v>
+        <v>52.9791</v>
       </c>
       <c r="W111" t="n">
-        <v>-55.80608</v>
+        <v>-66.90604999999999</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -8490,29 +8490,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nugget Pond</t>
+          <t>Wabush No. 4</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>002E/13/Au 001</t>
+          <t>023B/15/Fe 004</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I112" t="b">
@@ -8542,17 +8542,17 @@
         <v>325</v>
       </c>
       <c r="U112" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="V112" t="n">
-        <v>49.84502</v>
+        <v>52.95373</v>
       </c>
       <c r="W112" t="n">
-        <v>-55.77536</v>
+        <v>-66.94092000000001</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timmins No 5</t>
+          <t>Ferriman No 7</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>023J/14/Fe 024</t>
+          <t>023J/15/Fe 014</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8689,14 +8689,14 @@
         <v>31</v>
       </c>
       <c r="V114" t="n">
-        <v>54.86384</v>
+        <v>54.81281</v>
       </c>
       <c r="W114" t="n">
-        <v>-67.09327</v>
+        <v>-66.94580999999999</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
         </is>
       </c>
     </row>
@@ -8706,24 +8706,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mile 2</t>
+          <t>Ruth Lake No 2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>023B/15/Fe 011</t>
+          <t>023J/15/Fe 011</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8761,14 +8761,14 @@
         <v>31</v>
       </c>
       <c r="V115" t="n">
-        <v>52.97907</v>
+        <v>54.79747</v>
       </c>
       <c r="W115" t="n">
-        <v>-66.88907</v>
+        <v>-66.87487</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8850,29 +8850,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Julienne Lake</t>
+          <t>Bishop North</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>023G/02/Fe 009</t>
+          <t>012B/08/Fe 001</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I117" t="b">
@@ -8905,14 +8905,14 @@
         <v>31</v>
       </c>
       <c r="V117" t="n">
-        <v>53.13733</v>
+        <v>48.40317</v>
       </c>
       <c r="W117" t="n">
-        <v>-66.78360000000001</v>
+        <v>-58.3315</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8922,29 +8922,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Joyce Lake</t>
+          <t>Indian Head Mine</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>023J/15/Fe 030</t>
+          <t>012B/10/Fe 001</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I118" t="b">
@@ -8977,14 +8977,14 @@
         <v>31</v>
       </c>
       <c r="V118" t="n">
-        <v>54.8993</v>
+        <v>48.52416</v>
       </c>
       <c r="W118" t="n">
-        <v>-66.53366</v>
+        <v>-58.5148</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8994,12 +8994,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Attikamagen Deposit</t>
+          <t>Howse</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>023J/16/Fe 001</t>
+          <t>023J/14/Fe 028</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9049,14 +9049,14 @@
         <v>31</v>
       </c>
       <c r="V119" t="n">
-        <v>54.80989</v>
+        <v>54.9089</v>
       </c>
       <c r="W119" t="n">
-        <v>-66.47658</v>
+        <v>-67.14075</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Goethite Bay North</t>
+          <t>Ruth Lake No 8</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>023G/02/Fe 041</t>
+          <t>023J/15/Fe 009</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9121,14 +9121,14 @@
         <v>31</v>
       </c>
       <c r="V120" t="n">
-        <v>53.18717</v>
+        <v>54.78104</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.74445</v>
+        <v>-66.86577</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Wabush No. 6</t>
+          <t>Knob Lake 1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>023G/02/Fe 006</t>
+          <t>023J/15/Fe 013</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9193,14 +9193,14 @@
         <v>31</v>
       </c>
       <c r="V121" t="n">
-        <v>53.01798</v>
+        <v>54.7766</v>
       </c>
       <c r="W121" t="n">
-        <v>-66.89297999999999</v>
+        <v>-66.80589000000001</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
         </is>
       </c>
     </row>
@@ -9210,29 +9210,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Canning</t>
+          <t>Bishop South</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>023B/15/Fe 007</t>
+          <t>012B/08/Fe 002</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I122" t="b">
@@ -9265,14 +9265,14 @@
         <v>31</v>
       </c>
       <c r="V122" t="n">
-        <v>52.9469</v>
+        <v>48.39996</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.95802999999999</v>
+        <v>-58.33683</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -9282,24 +9282,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timmins No 7</t>
+          <t>Goethite Bay North</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>023J/14/Fe 025</t>
+          <t>023G/02/Fe 041</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9337,14 +9337,14 @@
         <v>31</v>
       </c>
       <c r="V123" t="n">
-        <v>54.89246</v>
+        <v>53.18717</v>
       </c>
       <c r="W123" t="n">
-        <v>-67.07259000000001</v>
+        <v>-66.74445</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ferriman No 7</t>
+          <t>Elizabeth No. 1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>023J/15/Fe 014</t>
+          <t>023J/15/Fe 031</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9409,14 +9409,14 @@
         <v>31</v>
       </c>
       <c r="V124" t="n">
-        <v>54.81281</v>
+        <v>54.78743</v>
       </c>
       <c r="W124" t="n">
-        <v>-66.94580999999999</v>
+        <v>-66.90081000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
         </is>
       </c>
     </row>
@@ -9426,24 +9426,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Wabush No. 4</t>
+          <t>Howells Lake</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>023B/15/Fe 004</t>
+          <t>023O/03/Fe 006</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9481,14 +9481,14 @@
         <v>31</v>
       </c>
       <c r="V125" t="n">
-        <v>52.95373</v>
+        <v>55.06346</v>
       </c>
       <c r="W125" t="n">
-        <v>-66.94092000000001</v>
+        <v>-67.40528</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Block 103 - Greenbush Zone</t>
+          <t>Attikamagen Deposit</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>023J/14/Fe 043</t>
+          <t>023J/16/Fe 001</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9553,14 +9553,14 @@
         <v>31</v>
       </c>
       <c r="V126" t="n">
-        <v>54.97234</v>
+        <v>54.80989</v>
       </c>
       <c r="W126" t="n">
-        <v>-67.25158</v>
+        <v>-66.47658</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9570,24 +9570,24 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Howells River North</t>
+          <t>Wabush No. 7</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>023O/03/Fe 007</t>
+          <t>023G/02/Fe 007</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9625,14 +9625,14 @@
         <v>31</v>
       </c>
       <c r="V127" t="n">
-        <v>55.01179</v>
+        <v>53.02512</v>
       </c>
       <c r="W127" t="n">
-        <v>-67.37214</v>
+        <v>-66.90531</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Duley No. 2</t>
+          <t>Joyce Lake</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>023B/15/Fe 008</t>
+          <t>023J/15/Fe 030</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>31</v>
       </c>
       <c r="V128" t="n">
-        <v>52.87214</v>
+        <v>54.8993</v>
       </c>
       <c r="W128" t="n">
-        <v>-66.99635000000001</v>
+        <v>-66.53366</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
         </is>
       </c>
     </row>
@@ -9714,24 +9714,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Elizabeth No. 1</t>
+          <t>Julienne Lake</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>023J/15/Fe 031</t>
+          <t>023G/02/Fe 009</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9769,14 +9769,14 @@
         <v>31</v>
       </c>
       <c r="V129" t="n">
-        <v>54.78743</v>
+        <v>53.13733</v>
       </c>
       <c r="W129" t="n">
-        <v>-66.90081000000001</v>
+        <v>-66.78360000000001</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9786,24 +9786,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Howells Lake</t>
+          <t>Canning</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>023O/03/Fe 006</t>
+          <t>023B/15/Fe 007</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9841,14 +9841,14 @@
         <v>31</v>
       </c>
       <c r="V130" t="n">
-        <v>55.06346</v>
+        <v>52.9469</v>
       </c>
       <c r="W130" t="n">
-        <v>-67.40528</v>
+        <v>-66.95802999999999</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9858,29 +9858,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Wabush No. 7</t>
+          <t>Parsons Pond Cart Track</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>023G/02/Fe 007</t>
+          <t>012I/04/Btm001</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Oil Shale</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I131" t="b">
@@ -9904,23 +9904,23 @@
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T131" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U131" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V131" t="n">
-        <v>53.02512</v>
+        <v>50.00564</v>
       </c>
       <c r="W131" t="n">
-        <v>-66.90531</v>
+        <v>-57.63187</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -9930,29 +9930,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lorraine No. 4</t>
+          <t>Blue Beach Mine</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>023G/02/Fe 008</t>
+          <t>001L/14/Fl 001</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I132" t="b">
@@ -9982,17 +9982,17 @@
         <v>325</v>
       </c>
       <c r="U132" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V132" t="n">
-        <v>53.08316</v>
+        <v>46.91553</v>
       </c>
       <c r="W132" t="n">
-        <v>-66.87726000000001</v>
+        <v>-55.40729</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
         </is>
       </c>
     </row>
@@ -10002,29 +10002,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wabush No. 8</t>
+          <t>Iron Springs Mine</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>023B/15/Fe 005</t>
+          <t>001L/14/Fl 008</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I133" t="b">
@@ -10054,17 +10054,17 @@
         <v>325</v>
       </c>
       <c r="U133" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V133" t="n">
-        <v>52.9791</v>
+        <v>46.88701</v>
       </c>
       <c r="W133" t="n">
-        <v>-66.90604999999999</v>
+        <v>-55.421</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
         </is>
       </c>
     </row>
@@ -10074,29 +10074,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Houston 2</t>
+          <t>Salt Cove Valley Vein</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>023J/10/Fe 009</t>
+          <t>001L/14/Fl 015</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I134" t="b">
@@ -10126,17 +10126,17 @@
         <v>325</v>
       </c>
       <c r="U134" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V134" t="n">
-        <v>54.71245</v>
+        <v>46.87774</v>
       </c>
       <c r="W134" t="n">
-        <v>-66.66257</v>
+        <v>-55.43387</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20015</t>
         </is>
       </c>
     </row>
@@ -10146,29 +10146,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Houston 3</t>
+          <t>Black Duck Mine</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>023J/10/Fe 010</t>
+          <t>001L/14/Fl 010</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I135" t="b">
@@ -10198,17 +10198,17 @@
         <v>325</v>
       </c>
       <c r="U135" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V135" t="n">
-        <v>54.69887</v>
+        <v>46.93201</v>
       </c>
       <c r="W135" t="n">
-        <v>-66.64483</v>
+        <v>-55.38881</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
         </is>
       </c>
     </row>
@@ -10218,29 +10218,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kivivic No 3</t>
+          <t>AGS Vein</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>023O/03/Fe 003</t>
+          <t>001L/14/Fl 013</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Copper, Fluorine</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I136" t="b">
@@ -10270,17 +10270,17 @@
         <v>325</v>
       </c>
       <c r="U136" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V136" t="n">
-        <v>55.05061</v>
+        <v>46.91489</v>
       </c>
       <c r="W136" t="n">
-        <v>-67.26130000000001</v>
+        <v>-55.48584</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
         </is>
       </c>
     </row>
@@ -10290,29 +10290,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Kivivic No 4</t>
+          <t>La Manche</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>023O/03/Fe 004</t>
+          <t>001N/12/Pb 001</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Silver, Barium, Lead</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I137" t="b">
@@ -10342,17 +10342,17 @@
         <v>325</v>
       </c>
       <c r="U137" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V137" t="n">
-        <v>55.04865</v>
+        <v>47.6889</v>
       </c>
       <c r="W137" t="n">
-        <v>-67.28158000000001</v>
+        <v>-53.93901</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -10362,29 +10362,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kivivic No 5</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>023O/03/Fe 005</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I138" t="b">
@@ -10414,17 +10414,17 @@
         <v>325</v>
       </c>
       <c r="U138" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V138" t="n">
-        <v>55.06664</v>
+        <v>53.469</v>
       </c>
       <c r="W138" t="n">
-        <v>-67.29537000000001</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -10434,29 +10434,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Duley No. 1</t>
+          <t>Mine Hill</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>023B/14/Fe 001</t>
+          <t>001N/07/Pph004</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Pyrophyllite</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I139" t="b">
@@ -10486,17 +10486,17 @@
         <v>325</v>
       </c>
       <c r="U139" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V139" t="n">
-        <v>52.87237</v>
+        <v>47.48</v>
       </c>
       <c r="W139" t="n">
-        <v>-67.05874</v>
+        <v>-52.95479</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
         </is>
       </c>
     </row>
@@ -10506,29 +10506,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mills Lake</t>
+          <t>Silver Cliff</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>023B/14/Fe 002</t>
+          <t>001N/05/Pb 003</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Barium, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I140" t="b">
@@ -10558,17 +10558,17 @@
         <v>325</v>
       </c>
       <c r="U140" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V140" t="n">
-        <v>52.79808</v>
+        <v>47.30144</v>
       </c>
       <c r="W140" t="n">
-        <v>-67.00413</v>
+        <v>-53.94444</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F05%2FPb%20003</t>
         </is>
       </c>
     </row>
@@ -10578,29 +10578,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Howells River West Zone A</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>023J/14/Fe 001</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I141" t="b">
@@ -10630,17 +10630,17 @@
         <v>325</v>
       </c>
       <c r="U141" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V141" t="n">
-        <v>54.90958</v>
+        <v>53.40462</v>
       </c>
       <c r="W141" t="n">
-        <v>-67.26052</v>
+        <v>-65.08734</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -10650,29 +10650,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Houston 1</t>
+          <t>Collier Point</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>023J/10/Fe 008</t>
+          <t>001N/12/Ba 001</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Barium</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I142" t="b">
@@ -10702,17 +10702,17 @@
         <v>325</v>
       </c>
       <c r="U142" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V142" t="n">
-        <v>54.70748</v>
+        <v>47.59126</v>
       </c>
       <c r="W142" t="n">
-        <v>-66.65615</v>
+        <v>-53.69011</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
         </is>
       </c>
     </row>
@@ -10722,29 +10722,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Redmond 5</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>023J/10/Fe 005</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I143" t="b">
@@ -10774,17 +10774,17 @@
         <v>325</v>
       </c>
       <c r="U143" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V143" t="n">
-        <v>54.70854</v>
+        <v>48.56074</v>
       </c>
       <c r="W143" t="n">
-        <v>-66.79174999999999</v>
+        <v>-58.8161</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -10794,29 +10794,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sawyer Lake</t>
+          <t>Pilley's Island Mine</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>023I/05/Fe 001</t>
+          <t>002E/12/Cu 001</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I144" t="b">
@@ -10846,17 +10846,17 @@
         <v>325</v>
       </c>
       <c r="U144" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V144" t="n">
-        <v>54.45206</v>
+        <v>49.50863</v>
       </c>
       <c r="W144" t="n">
-        <v>-65.98627</v>
+        <v>-55.71872</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -10866,29 +10866,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Howells River West Zone B</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>023J/14/Fe 002</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I145" t="b">
@@ -10918,17 +10918,17 @@
         <v>325</v>
       </c>
       <c r="U145" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V145" t="n">
-        <v>54.87235</v>
+        <v>48.50411</v>
       </c>
       <c r="W145" t="n">
-        <v>-67.21584</v>
+        <v>-58.53451</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -10938,29 +10938,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Bluff Head Mine</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>023B/14/Fe 020</t>
+          <t>012B/15/Cr 001</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Asbestos, Chromium</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I146" t="b">
@@ -10990,17 +10990,17 @@
         <v>325</v>
       </c>
       <c r="U146" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V146" t="n">
-        <v>52.83351</v>
+        <v>48.77717</v>
       </c>
       <c r="W146" t="n">
-        <v>-67.0311</v>
+        <v>-58.59931</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -11010,29 +11010,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Cross Cove</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>023B/14/Fe 028</t>
+          <t>002E/10/Sb 001</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I147" t="b">
@@ -11062,17 +11062,17 @@
         <v>325</v>
       </c>
       <c r="U147" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V147" t="n">
-        <v>52.94868</v>
+        <v>49.57534</v>
       </c>
       <c r="W147" t="n">
-        <v>-67.01146</v>
+        <v>-54.86876</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
         </is>
       </c>
     </row>
@@ -11082,29 +11082,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sheps Lake</t>
+          <t>York Harbour Mine</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>023J/11/Fe 001</t>
+          <t>012G/01/Cu 002</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I148" t="b">
@@ -11134,17 +11134,17 @@
         <v>325</v>
       </c>
       <c r="U148" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V148" t="n">
-        <v>54.73475</v>
+        <v>49.05208</v>
       </c>
       <c r="W148" t="n">
-        <v>-67.06362</v>
+        <v>-58.30769</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -11154,29 +11154,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Neal 1</t>
+          <t>Lord &amp; Lady Gulch Mine</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>023B/14/Fe 008</t>
+          <t>001L/14/Fl 005</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I149" t="b">
@@ -11206,17 +11206,17 @@
         <v>325</v>
       </c>
       <c r="U149" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V149" t="n">
-        <v>52.95013</v>
+        <v>46.87554</v>
       </c>
       <c r="W149" t="n">
-        <v>-67.15191</v>
+        <v>-55.4111</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
         </is>
       </c>
     </row>
@@ -11226,29 +11226,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ruth Lake No 8</t>
+          <t>Goose Cove</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>023J/15/Fe 009</t>
+          <t>002M/05/Cu 001</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Zinc, Nickel, Iron, Copper</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I150" t="b">
@@ -11278,17 +11278,17 @@
         <v>325</v>
       </c>
       <c r="U150" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V150" t="n">
-        <v>54.78104</v>
+        <v>51.31009</v>
       </c>
       <c r="W150" t="n">
-        <v>-66.86577</v>
+        <v>-55.62342</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -11298,29 +11298,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ruth Lake No 2</t>
+          <t>Hares Ears Vein</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>023J/15/Fe 011</t>
+          <t>001L/14/Fl 007</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I151" t="b">
@@ -11350,17 +11350,17 @@
         <v>325</v>
       </c>
       <c r="U151" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V151" t="n">
-        <v>54.79747</v>
+        <v>46.88814</v>
       </c>
       <c r="W151" t="n">
-        <v>-66.87487</v>
+        <v>-55.41178</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
         </is>
       </c>
     </row>
@@ -11370,29 +11370,29 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Elizabeth No. 2</t>
+          <t>Tarefare Mine</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>023J/15/Fe 032</t>
+          <t>001L/14/Fl 006</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I152" t="b">
@@ -11422,17 +11422,17 @@
         <v>325</v>
       </c>
       <c r="U152" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V152" t="n">
-        <v>54.77182</v>
+        <v>46.8912</v>
       </c>
       <c r="W152" t="n">
-        <v>-66.88666000000001</v>
+        <v>-55.43112</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
         </is>
       </c>
     </row>
@@ -11442,29 +11442,29 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Knob Lake 1</t>
+          <t>Director Mine</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>023J/15/Fe 013</t>
+          <t>001L/14/Fl 009</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I153" t="b">
@@ -11494,17 +11494,17 @@
         <v>325</v>
       </c>
       <c r="U153" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V153" t="n">
-        <v>54.7766</v>
+        <v>46.90681</v>
       </c>
       <c r="W153" t="n">
-        <v>-66.80589000000001</v>
+        <v>-55.42107</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
         </is>
       </c>
     </row>
@@ -11514,29 +11514,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Howse</t>
+          <t>Doctors Pond Veins</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>023J/14/Fe 028</t>
+          <t>001L/14/Fl 036</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I154" t="b">
@@ -11566,17 +11566,17 @@
         <v>325</v>
       </c>
       <c r="U154" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V154" t="n">
-        <v>54.9089</v>
+        <v>46.92769</v>
       </c>
       <c r="W154" t="n">
-        <v>-67.14075</v>
+        <v>-55.37593</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mine Hill</t>
+          <t>Borney Lake</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>001N/07/Pph004</t>
+          <t>002D/14/Stn001</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pyrophyllite</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11641,14 +11641,14 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>47.48</v>
+        <v>48.9264</v>
       </c>
       <c r="W155" t="n">
-        <v>-52.95479</v>
+        <v>-55.44535</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
         </is>
       </c>
     </row>
@@ -11658,12 +11658,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Silver Cliff</t>
+          <t>Baie Verte Mine</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>001N/05/Pb 003</t>
+          <t>012H/16/Asb008</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Barium, Copper, Zinc, Lead</t>
+          <t>Magnesium, Asbestos</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11713,14 +11713,14 @@
         <v>30</v>
       </c>
       <c r="V156" t="n">
-        <v>47.30144</v>
+        <v>49.97974</v>
       </c>
       <c r="W156" t="n">
-        <v>-53.94444</v>
+        <v>-56.19399</v>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F05%2FPb%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Iron Springs Mine</t>
+          <t>Little Salt Cove</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>001L/14/Fl 008</t>
+          <t>001L/14/Fl 016</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -11785,14 +11785,14 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>46.88701</v>
+        <v>46.87654</v>
       </c>
       <c r="W157" t="n">
-        <v>-55.421</v>
+        <v>-55.43141</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Southern Cross Veins</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>001L/14/Fl 020</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11857,14 +11857,14 @@
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>48.56074</v>
+        <v>46.88974</v>
       </c>
       <c r="W158" t="n">
-        <v>-58.8161</v>
+        <v>-55.42958</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hares Ears Vein</t>
+          <t>Scrape Vein</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>001L/14/Fl 007</t>
+          <t>001L/14/Fl 035</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -11929,14 +11929,14 @@
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>46.88814</v>
+        <v>46.92547</v>
       </c>
       <c r="W159" t="n">
-        <v>-55.41178</v>
+        <v>-55.37193</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Collier Point</t>
+          <t>Parsons Pond No 2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>001N/12/Ba 001</t>
+          <t>012H/13/Btm002</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Barium</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12001,14 +12001,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>47.59126</v>
+        <v>49.97421</v>
       </c>
       <c r="W160" t="n">
-        <v>-53.69011</v>
+        <v>-57.60538</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Parsons Pond No 4</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>012H/13/Btm004</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12064,23 +12064,23 @@
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T161" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U161" t="n">
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>48.30663</v>
+        <v>49.99787</v>
       </c>
       <c r="W161" t="n">
-        <v>-58.68165</v>
+        <v>-57.63818</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Parsons Pond Cart Track</t>
+          <t>Parsons Pond No 1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>012I/04/Btm001</t>
+          <t>012H/13/Btm001</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Oil Shale</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12136,23 +12136,23 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T162" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U162" t="n">
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>50.00564</v>
+        <v>49.99228</v>
       </c>
       <c r="W162" t="n">
-        <v>-57.63187</v>
+        <v>-57.58928</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -12162,24 +12162,24 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Baie Verte Mine</t>
+          <t>Daniel's Harbour Mine-K Zone</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>012H/16/Asb008</t>
+          <t>012I/06/Zn 010</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Magnesium, Asbestos</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12217,14 +12217,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>49.97974</v>
+        <v>50.2935</v>
       </c>
       <c r="W163" t="n">
-        <v>-56.19399</v>
+        <v>-57.46875</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Borney Lake</t>
+          <t>Parsons Pond No 3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>002D/14/Stn001</t>
+          <t>012H/13/Btm003</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12289,14 +12289,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>48.9264</v>
+        <v>49.97912</v>
       </c>
       <c r="W164" t="n">
-        <v>-55.44535</v>
+        <v>-57.64547</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Doctors Pond Veins</t>
+          <t>Middle Arm Brook</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>001L/14/Fl 036</t>
+          <t>012H/16/Vir001</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Virginite</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -12361,14 +12361,14 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>46.92769</v>
+        <v>49.80048</v>
       </c>
       <c r="W165" t="n">
-        <v>-55.37593</v>
+        <v>-56.31995</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
         </is>
       </c>
     </row>
@@ -12378,24 +12378,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Parsons Pond No 3</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>012H/13/Btm003</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12433,14 +12433,14 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>49.97912</v>
+        <v>49.45488</v>
       </c>
       <c r="W166" t="n">
-        <v>-57.64547</v>
+        <v>-55.49811</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tarefare Mine</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>001L/14/Fl 006</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12505,14 +12505,14 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>46.8912</v>
+        <v>48.30663</v>
       </c>
       <c r="W167" t="n">
-        <v>-55.43112</v>
+        <v>-58.68165</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -12522,24 +12522,24 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Blue Beach Mine</t>
+          <t>Daniel's Harbour Mine-Q Zone</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>001L/14/Fl 001</t>
+          <t>012I/06/Zn 016</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12574,17 +12574,17 @@
         <v>325</v>
       </c>
       <c r="U168" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V168" t="n">
-        <v>46.91553</v>
+        <v>50.29741</v>
       </c>
       <c r="W168" t="n">
-        <v>-55.40729</v>
+        <v>-57.48016</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20016</t>
         </is>
       </c>
     </row>
@@ -12594,24 +12594,24 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Black Duck Mine</t>
+          <t>Daniel's Harbour Mine-J Zone</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>001L/14/Fl 010</t>
+          <t>012I/06/Zn 009</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12646,17 +12646,17 @@
         <v>325</v>
       </c>
       <c r="U169" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V169" t="n">
-        <v>46.93201</v>
+        <v>50.30247</v>
       </c>
       <c r="W169" t="n">
-        <v>-55.38881</v>
+        <v>-57.47459</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
         </is>
       </c>
     </row>
@@ -12666,24 +12666,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Southern Cross Veins</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>001L/14/Fl 020</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12718,17 +12718,17 @@
         <v>325</v>
       </c>
       <c r="U170" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V170" t="n">
-        <v>46.88974</v>
+        <v>50.27283</v>
       </c>
       <c r="W170" t="n">
-        <v>-55.42958</v>
+        <v>-57.46448</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -12738,24 +12738,24 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Lord &amp; Lady Gulch Mine</t>
+          <t>Browning Mine</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>001L/14/Fl 005</t>
+          <t>012H/10/Au 001</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12790,17 +12790,17 @@
         <v>325</v>
       </c>
       <c r="U171" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V171" t="n">
-        <v>46.87554</v>
+        <v>49.71799</v>
       </c>
       <c r="W171" t="n">
-        <v>-55.4111</v>
+        <v>-56.92565</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -12810,24 +12810,24 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Scrape Vein</t>
+          <t>Daniel's Harbour Mine-N Zone</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>001L/14/Fl 035</t>
+          <t>012I/06/Zn 013</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12862,17 +12862,17 @@
         <v>325</v>
       </c>
       <c r="U172" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V172" t="n">
-        <v>46.92547</v>
+        <v>50.29873</v>
       </c>
       <c r="W172" t="n">
-        <v>-55.37193</v>
+        <v>-57.48691</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20013</t>
         </is>
       </c>
     </row>
@@ -12882,24 +12882,24 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Daniel's Harbour Mine-M Zone</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012I/06/Zn 012</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12934,17 +12934,17 @@
         <v>325</v>
       </c>
       <c r="U173" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V173" t="n">
-        <v>53.40462</v>
+        <v>50.29514</v>
       </c>
       <c r="W173" t="n">
-        <v>-65.08734</v>
+        <v>-57.44013</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
         </is>
       </c>
     </row>
@@ -12954,24 +12954,24 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Daniel's Harbour Mine-A Zone</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>012I/06/Zn 001</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13006,17 +13006,17 @@
         <v>325</v>
       </c>
       <c r="U174" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V174" t="n">
-        <v>48.50411</v>
+        <v>50.29576</v>
       </c>
       <c r="W174" t="n">
-        <v>-58.53451</v>
+        <v>-57.46512</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -13026,24 +13026,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Bluff Head Mine</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>012B/15/Cr 001</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Asbestos, Chromium</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13078,17 +13078,17 @@
         <v>325</v>
       </c>
       <c r="U175" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V175" t="n">
-        <v>48.77717</v>
+        <v>50.31118</v>
       </c>
       <c r="W175" t="n">
-        <v>-58.59931</v>
+        <v>-57.43009</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -13098,24 +13098,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Daniel's Harbour Mine-D Zone</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>012I/06/Zn 004</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13150,17 +13150,17 @@
         <v>325</v>
       </c>
       <c r="U176" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V176" t="n">
-        <v>53.469</v>
+        <v>50.30795</v>
       </c>
       <c r="W176" t="n">
-        <v>-64.91218000000001</v>
+        <v>-57.45218</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
         </is>
       </c>
     </row>
@@ -13170,24 +13170,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Director Mine</t>
+          <t>Daniel's Harbour Mine-C Zone</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>001L/14/Fl 009</t>
+          <t>012I/06/Zn 003</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13222,17 +13222,17 @@
         <v>325</v>
       </c>
       <c r="U177" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V177" t="n">
-        <v>46.90681</v>
+        <v>50.30435</v>
       </c>
       <c r="W177" t="n">
-        <v>-55.42107</v>
+        <v>-57.45355</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
         </is>
       </c>
     </row>
@@ -13242,24 +13242,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Little Salt Cove</t>
+          <t>Daniel's Harbour Mine-E Zone</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>001L/14/Fl 016</t>
+          <t>012I/06/Zn 005</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13294,17 +13294,17 @@
         <v>325</v>
       </c>
       <c r="U178" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V178" t="n">
-        <v>46.87654</v>
+        <v>50.31067</v>
       </c>
       <c r="W178" t="n">
-        <v>-55.43141</v>
+        <v>-57.44799</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
         </is>
       </c>
     </row>
@@ -13314,24 +13314,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Salt Cove Valley Vein</t>
+          <t>Daniel's Harbour Mine-G Zone</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>001L/14/Fl 015</t>
+          <t>012I/06/Zn 007</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -13366,17 +13366,17 @@
         <v>325</v>
       </c>
       <c r="U179" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V179" t="n">
-        <v>46.87774</v>
+        <v>50.29448</v>
       </c>
       <c r="W179" t="n">
-        <v>-55.43387</v>
+        <v>-57.44714</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -13386,24 +13386,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Middle Arm Brook</t>
+          <t>Daniel's Harbour Mine-B Zone</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>012H/16/Vir001</t>
+          <t>012I/06/Zn 002</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Virginite</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13438,17 +13438,17 @@
         <v>325</v>
       </c>
       <c r="U180" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V180" t="n">
-        <v>49.80048</v>
+        <v>50.2975</v>
       </c>
       <c r="W180" t="n">
-        <v>-56.31995</v>
+        <v>-57.45784</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -13458,24 +13458,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Parsons Pond No 2</t>
+          <t>Daniel's Harbour Mine-H Zone</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>012H/13/Btm002</t>
+          <t>012I/06/Zn 008</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13510,17 +13510,17 @@
         <v>325</v>
       </c>
       <c r="U181" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V181" t="n">
-        <v>49.97421</v>
+        <v>50.29179</v>
       </c>
       <c r="W181" t="n">
-        <v>-57.60538</v>
+        <v>-57.44599</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
         </is>
       </c>
     </row>
@@ -13530,24 +13530,24 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Parsons Pond No 1</t>
+          <t>Daniel's Harbour Mine-F Zone</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>012H/13/Btm001</t>
+          <t>012I/06/Zn 006</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13576,23 +13576,23 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T182" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U182" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V182" t="n">
-        <v>49.99228</v>
+        <v>50.29437</v>
       </c>
       <c r="W182" t="n">
-        <v>-57.58928</v>
+        <v>-57.45374</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
         </is>
       </c>
     </row>
@@ -13602,24 +13602,24 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Parsons Pond No 4</t>
+          <t>Daniel's Harbour Mine-L Zone</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>012H/13/Btm004</t>
+          <t>012I/06/Zn 011</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Lead, Dolomite, Zinc</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13648,23 +13648,23 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T183" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U183" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V183" t="n">
-        <v>49.99787</v>
+        <v>50.27686</v>
       </c>
       <c r="W183" t="n">
-        <v>-57.63818</v>
+        <v>-57.46788</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
         </is>
       </c>
     </row>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Grey Copper Mine</t>
+          <t>Little Bay Mine</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>002E/11/Cu 001</t>
+          <t>002E/12/Cu 030</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Iron, Copper</t>
+          <t>Iron, Gold, Copper</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13729,14 +13729,14 @@
         <v>26</v>
       </c>
       <c r="V184" t="n">
-        <v>49.5173</v>
+        <v>49.5961</v>
       </c>
       <c r="W184" t="n">
-        <v>-55.2721</v>
+        <v>-55.94531</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Scotia Formation</t>
+          <t>Gull Island Formation</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>001N/10/Fe 002</t>
+          <t>001N/10/Fe 003</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13801,14 +13801,14 @@
         <v>26</v>
       </c>
       <c r="V185" t="n">
-        <v>47.64169</v>
+        <v>47.65193</v>
       </c>
       <c r="W185" t="n">
-        <v>-52.97639</v>
+        <v>-52.95654</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Gull Island Formation</t>
+          <t>Dominion Formation</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>001N/10/Fe 003</t>
+          <t>001N/10/Fe 001</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -13873,14 +13873,14 @@
         <v>26</v>
       </c>
       <c r="V186" t="n">
-        <v>47.65193</v>
+        <v>47.64164</v>
       </c>
       <c r="W186" t="n">
-        <v>-52.95654</v>
+        <v>-52.95309</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Redmond No 2</t>
+          <t>Scotia Formation</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>023J/10/Fe 002</t>
+          <t>001N/10/Fe 002</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13945,14 +13945,14 @@
         <v>26</v>
       </c>
       <c r="V187" t="n">
-        <v>54.69738</v>
+        <v>47.64169</v>
       </c>
       <c r="W187" t="n">
-        <v>-66.77224</v>
+        <v>-52.97639</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Little Bay Mine</t>
+          <t>Redmond No 2</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>002E/12/Cu 030</t>
+          <t>023J/10/Fe 002</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Iron, Gold, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14017,14 +14017,14 @@
         <v>26</v>
       </c>
       <c r="V188" t="n">
-        <v>49.5961</v>
+        <v>54.69738</v>
       </c>
       <c r="W188" t="n">
-        <v>-55.94531</v>
+        <v>-66.77224</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14034,24 +14034,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Grey Copper Mine</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>002E/11/Cu 001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron, Copper</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14089,14 +14089,14 @@
         <v>26</v>
       </c>
       <c r="V189" t="n">
-        <v>49.50376</v>
+        <v>49.5173</v>
       </c>
       <c r="W189" t="n">
-        <v>-55.21553</v>
+        <v>-55.2721</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -14106,12 +14106,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -14123,7 +14123,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14161,14 +14161,14 @@
         <v>26</v>
       </c>
       <c r="V190" t="n">
-        <v>47.53392</v>
+        <v>49.50376</v>
       </c>
       <c r="W190" t="n">
-        <v>-53.18293</v>
+        <v>-55.21553</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14178,24 +14178,24 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dominion Formation</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>001N/10/Fe 001</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -14233,14 +14233,14 @@
         <v>26</v>
       </c>
       <c r="V191" t="n">
-        <v>47.64164</v>
+        <v>47.53392</v>
       </c>
       <c r="W191" t="n">
-        <v>-52.95309</v>
+        <v>-53.18293</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -15042,12 +15042,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Smallwood Mine</t>
+          <t>Lorraine Mine</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>023G/02/Fe 001</t>
+          <t>023G/02/Fe 004</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -15097,14 +15097,14 @@
         <v>26</v>
       </c>
       <c r="V203" t="n">
-        <v>53.03718</v>
+        <v>53.06833</v>
       </c>
       <c r="W203" t="n">
-        <v>-66.93694000000001</v>
+        <v>-66.94949</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -15114,12 +15114,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lorraine Mine</t>
+          <t>Smallwood Mine</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>023G/02/Fe 004</t>
+          <t>023G/02/Fe 001</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -15169,14 +15169,14 @@
         <v>26</v>
       </c>
       <c r="V204" t="n">
-        <v>53.06833</v>
+        <v>53.03718</v>
       </c>
       <c r="W204" t="n">
-        <v>-66.94949</v>
+        <v>-66.93694000000001</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Fleming No 3</t>
+          <t>Timmins No 1</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>023J/14/Fe 022</t>
+          <t>023J/14/Fe 018</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -15241,14 +15241,14 @@
         <v>26</v>
       </c>
       <c r="V205" t="n">
-        <v>54.85836</v>
+        <v>54.88449</v>
       </c>
       <c r="W205" t="n">
-        <v>-67.03167999999999</v>
+        <v>-67.08575</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Timmins No 1</t>
+          <t>Timmins No 2</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>023J/14/Fe 018</t>
+          <t>023J/14/Fe 019</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -15313,14 +15313,14 @@
         <v>26</v>
       </c>
       <c r="V206" t="n">
-        <v>54.88449</v>
+        <v>54.89421</v>
       </c>
       <c r="W206" t="n">
-        <v>-67.08575</v>
+        <v>-67.08716</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15330,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timmins No 4</t>
+          <t>Timmins No 6</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>023J/14/Fe 023</t>
+          <t>023J/14/Fe 021</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15385,14 +15385,14 @@
         <v>26</v>
       </c>
       <c r="V207" t="n">
-        <v>54.89884</v>
+        <v>54.90148</v>
       </c>
       <c r="W207" t="n">
-        <v>-67.10881000000001</v>
+        <v>-67.09757999999999</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
         </is>
       </c>
     </row>
@@ -15402,12 +15402,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Timmins No 2</t>
+          <t>Fleming No 3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>023J/14/Fe 019</t>
+          <t>023J/14/Fe 022</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -15457,14 +15457,14 @@
         <v>26</v>
       </c>
       <c r="V208" t="n">
-        <v>54.89421</v>
+        <v>54.85836</v>
       </c>
       <c r="W208" t="n">
-        <v>-67.08716</v>
+        <v>-67.03167999999999</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
         </is>
       </c>
     </row>
@@ -15474,12 +15474,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Timmins No 6</t>
+          <t>Timmins No 4</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>023J/14/Fe 021</t>
+          <t>023J/14/Fe 023</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -15529,14 +15529,14 @@
         <v>26</v>
       </c>
       <c r="V209" t="n">
-        <v>54.90148</v>
+        <v>54.89884</v>
       </c>
       <c r="W209" t="n">
-        <v>-67.09757999999999</v>
+        <v>-67.10881000000001</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Horseshoe Zone</t>
+          <t>Two Tom Lake</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>002E/02/Au 039</t>
+          <t>013L/01/REE001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>44</v>
       </c>
       <c r="V2" t="n">
-        <v>49.01341</v>
+        <v>54.21359</v>
       </c>
       <c r="W2" t="n">
-        <v>-54.81741</v>
+        <v>-62.14192</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deep Fox</t>
+          <t>Deer Cove Main Zone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>003D/05/Ree007</t>
+          <t>012I/01/Au 001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>52.3805</v>
+        <v>50.01619</v>
       </c>
       <c r="W3" t="n">
-        <v>-55.64987</v>
+        <v>-56.04389</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mart Lake Graphite</t>
+          <t>Voisey's Bay, Far Eastern Deeps</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>023B/14/Gf 001</t>
+          <t>014D/08/Ni 013</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Graphite</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>52.8283</v>
+        <v>56.32109</v>
       </c>
       <c r="W4" t="n">
-        <v>-67.01484000000001</v>
+        <v>-62.06064</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deer Cove Main Zone</t>
+          <t>Windowglass Hill - Main Zone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>012I/01/Au 001</t>
+          <t>011O/10/Au 001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,14 +841,14 @@
         <v>44</v>
       </c>
       <c r="V5" t="n">
-        <v>50.01619</v>
+        <v>47.74279</v>
       </c>
       <c r="W5" t="n">
-        <v>-56.04389</v>
+        <v>-58.95727</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Windowglass Hill - Main Zone</t>
+          <t>Keats</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>011O/10/Au 001</t>
+          <t>002D/15/Au 010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>44</v>
       </c>
       <c r="V6" t="n">
-        <v>47.74279</v>
+        <v>48.97891</v>
       </c>
       <c r="W6" t="n">
-        <v>-58.95727</v>
+        <v>-54.8402</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bull Road Showing</t>
+          <t>Keats South</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>002E/12/Zn 007</t>
+          <t>002D/15/Au 060</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Antimony, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>44</v>
       </c>
       <c r="V7" t="n">
-        <v>49.51431</v>
+        <v>48.97791</v>
       </c>
       <c r="W7" t="n">
-        <v>-55.7118</v>
+        <v>-54.84407</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Keats</t>
+          <t>Saddle Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>002D/15/Au 010</t>
+          <t>002E/02/Au 038</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U8" t="n">
         <v>44</v>
       </c>
       <c r="V8" t="n">
-        <v>48.97891</v>
+        <v>49.00899</v>
       </c>
       <c r="W8" t="n">
-        <v>-54.8402</v>
+        <v>-54.81554</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Keats South</t>
+          <t>Deep Fox</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>002D/15/Au 060</t>
+          <t>003D/05/Ree007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>44</v>
       </c>
       <c r="V9" t="n">
-        <v>48.97791</v>
+        <v>52.3805</v>
       </c>
       <c r="W9" t="n">
-        <v>-54.84407</v>
+        <v>-55.64987</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Voisey's Bay, South Eastern Deeps</t>
+          <t>Horseshoe Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>014D/08/Ni 017</t>
+          <t>002E/02/Au 039</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>56.31756</v>
+        <v>49.01341</v>
       </c>
       <c r="W10" t="n">
-        <v>-62.06953</v>
+        <v>-54.81741</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Moly Brook</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>013K/07/U  007</t>
+          <t>011P/11/Mo 001</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Vanadium, Uranium</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1273,14 +1273,14 @@
         <v>44</v>
       </c>
       <c r="V11" t="n">
-        <v>54.46751</v>
+        <v>47.61683</v>
       </c>
       <c r="W11" t="n">
-        <v>-60.98105</v>
+        <v>-57.1034</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Moly Brook</t>
+          <t>Bull Road Showing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>011P/11/Mo 001</t>
+          <t>002E/12/Zn 007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Copper, Silver, Lead, Antimony, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>44</v>
       </c>
       <c r="V12" t="n">
-        <v>47.61683</v>
+        <v>49.51431</v>
       </c>
       <c r="W12" t="n">
-        <v>-57.1034</v>
+        <v>-55.7118</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Far Eastern Deeps</t>
+          <t>Voisey's Bay, North Eastern Deeps</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>014D/08/Ni 013</t>
+          <t>014D/08/Ni 011</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1417,14 +1417,14 @@
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>56.32109</v>
+        <v>56.32929</v>
       </c>
       <c r="W13" t="n">
-        <v>-62.06064</v>
+        <v>-62.07733</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Voisey's Bay, North Eastern Deeps</t>
+          <t>Mart Lake Graphite</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>014D/08/Ni 011</t>
+          <t>023B/14/Gf 001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper, Zinc, Silver, Graphite</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>44</v>
       </c>
       <c r="V14" t="n">
-        <v>56.32929</v>
+        <v>52.8283</v>
       </c>
       <c r="W14" t="n">
-        <v>-62.07733</v>
+        <v>-67.01484000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Southeast Extension</t>
+          <t>Area 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>014D/08/Ni 012</t>
+          <t>013K/07/U  007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper, Vanadium, Uranium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1561,14 +1561,14 @@
         <v>44</v>
       </c>
       <c r="V15" t="n">
-        <v>56.32489</v>
+        <v>54.46751</v>
       </c>
       <c r="W15" t="n">
-        <v>-62.08804</v>
+        <v>-60.98105</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Saddle Zone</t>
+          <t>Voisey's Bay, Southeast Extension</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>002E/02/Au 038</t>
+          <t>014D/08/Ni 012</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>44</v>
       </c>
       <c r="V16" t="n">
-        <v>49.00899</v>
+        <v>56.32489</v>
       </c>
       <c r="W16" t="n">
-        <v>-54.81554</v>
+        <v>-62.08804</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20012</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Two Tom Lake</t>
+          <t>Voisey's Bay, South Eastern Deeps</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>013L/01/REE001</t>
+          <t>014D/08/Ni 017</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>44</v>
       </c>
       <c r="V17" t="n">
-        <v>54.21359</v>
+        <v>56.31756</v>
       </c>
       <c r="W17" t="n">
-        <v>-62.14192</v>
+        <v>-62.06953</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Road Zone</t>
+          <t>Strickland - Silver Hill Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012H/15/Au 011</t>
+          <t>011O/16/Zn 002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1777,14 +1777,14 @@
         <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>49.88465</v>
+        <v>47.81</v>
       </c>
       <c r="W18" t="n">
-        <v>-56.83885</v>
+        <v>-58.2985</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apsy Zone</t>
+          <t>Cape Ray Gold Deposit 41 Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>012H/15/Au 014</t>
+          <t>011O/15/Au 002</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>43</v>
       </c>
       <c r="V19" t="n">
-        <v>49.89471</v>
+        <v>47.75858</v>
       </c>
       <c r="W19" t="n">
-        <v>-56.82917</v>
+        <v>-58.92331</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit #4 Zone</t>
+          <t>Point Leamington Deposit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>011O/15/Au 001</t>
+          <t>002E/05/Zn 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Silver, Copper, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>43</v>
       </c>
       <c r="V22" t="n">
-        <v>47.76081</v>
+        <v>49.27672</v>
       </c>
       <c r="W22" t="n">
-        <v>-58.91872</v>
+        <v>-55.63152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit 41 Zone</t>
+          <t>Apsy Zone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>011O/15/Au 002</t>
+          <t>012H/15/Au 014</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>43</v>
       </c>
       <c r="V23" t="n">
-        <v>47.75858</v>
+        <v>49.89471</v>
       </c>
       <c r="W23" t="n">
-        <v>-58.92331</v>
+        <v>-56.82917</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Point Leamington Deposit</t>
+          <t>Road Zone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>002E/05/Zn 001</t>
+          <t>012H/15/Au 011</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead, Zinc</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>43</v>
       </c>
       <c r="V24" t="n">
-        <v>49.27672</v>
+        <v>49.88465</v>
       </c>
       <c r="W24" t="n">
-        <v>-55.63152</v>
+        <v>-56.83885</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Strickland - Silver Hill Zone</t>
+          <t>51 Zone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>011O/16/Zn 002</t>
+          <t>011O/15/Au 003</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>47.81</v>
+        <v>47.75077</v>
       </c>
       <c r="W25" t="n">
-        <v>-58.2985</v>
+        <v>-58.93823</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>51 Zone</t>
+          <t>Cape Ray Gold Deposit #4 Zone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>011O/15/Au 003</t>
+          <t>011O/15/Au 001</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2353,14 +2353,14 @@
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>47.75077</v>
+        <v>47.76081</v>
       </c>
       <c r="W26" t="n">
-        <v>-58.93823</v>
+        <v>-58.91872</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gear Lake</t>
+          <t>Rainbow Deposit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>013J/13/U  010</t>
+          <t>013J/12/U  008</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2416,23 +2416,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U27" t="n">
         <v>42</v>
       </c>
       <c r="V27" t="n">
-        <v>54.94329</v>
+        <v>54.56417</v>
       </c>
       <c r="W27" t="n">
-        <v>-59.54386</v>
+        <v>-59.99369</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nash Lake (Main Zone)</t>
+          <t>Michelin Deposit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>013J/13/U  006</t>
+          <t>013J/12/U  001</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2497,14 +2497,14 @@
         <v>42</v>
       </c>
       <c r="V28" t="n">
-        <v>54.91032</v>
+        <v>54.58562</v>
       </c>
       <c r="W28" t="n">
-        <v>-59.62004</v>
+        <v>-59.98056</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aillik Prospect</t>
+          <t>Gear Lake</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>013O/03/Mo 003</t>
+          <t>013J/13/U  010</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Uranium, Fluorine, Copper, Molybdenum</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>42</v>
       </c>
       <c r="V29" t="n">
-        <v>55.21102</v>
+        <v>54.94329</v>
       </c>
       <c r="W29" t="n">
-        <v>-59.16645</v>
+        <v>-59.54386</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013O%2F03%2FMo%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kitts</t>
+          <t>Aillik Prospect</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>013J/14/U  001</t>
+          <t>013O/03/Mo 003</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Uranium, Fluorine, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2632,23 +2632,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>42</v>
       </c>
       <c r="V30" t="n">
-        <v>54.99779</v>
+        <v>55.21102</v>
       </c>
       <c r="W30" t="n">
-        <v>-59.4872</v>
+        <v>-59.16645</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013O%2F03%2FMo%20003</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jacques Lake</t>
+          <t>Kitts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>013J/12/U  018</t>
+          <t>013J/14/U  001</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2704,23 +2704,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T31" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U31" t="n">
         <v>42</v>
       </c>
       <c r="V31" t="n">
-        <v>54.71754</v>
+        <v>54.99779</v>
       </c>
       <c r="W31" t="n">
-        <v>-59.59268</v>
+        <v>-59.4872</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Michelin Deposit</t>
+          <t>Two Time</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>013J/12/U  001</t>
+          <t>013K/11/U  005</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2785,14 +2785,14 @@
         <v>42</v>
       </c>
       <c r="V32" t="n">
-        <v>54.58562</v>
+        <v>54.56554</v>
       </c>
       <c r="W32" t="n">
-        <v>-59.98056</v>
+        <v>-61.17152</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rainbow Deposit</t>
+          <t>Nash Lake (Main Zone)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>013J/12/U  008</t>
+          <t>013J/13/U  006</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2848,23 +2848,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
         <v>42</v>
       </c>
       <c r="V33" t="n">
-        <v>54.56417</v>
+        <v>54.91032</v>
       </c>
       <c r="W33" t="n">
-        <v>-59.99369</v>
+        <v>-59.62004</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2874,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Two Time</t>
+          <t>Jacques Lake</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>013K/11/U  005</t>
+          <t>013J/12/U  018</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2929,14 +2929,14 @@
         <v>42</v>
       </c>
       <c r="V34" t="n">
-        <v>54.56554</v>
+        <v>54.71754</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.17152</v>
+        <v>-59.59268</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Springer's Hill-Main Showing</t>
+          <t>Mann #1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>012B/16/Cr 002</t>
+          <t>013L/01/Be 001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Niobium, Uranium, Zinc, Beryllium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>41</v>
       </c>
       <c r="V35" t="n">
-        <v>48.7927</v>
+        <v>54.23929</v>
       </c>
       <c r="W35" t="n">
-        <v>-58.44526</v>
+        <v>-62.3924</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mann #1</t>
+          <t>Springer's Hill-Main Showing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>013L/01/Be 001</t>
+          <t>012B/16/Cr 002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Niobium, Uranium, Zinc, Beryllium</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>41</v>
       </c>
       <c r="V36" t="n">
-        <v>54.23929</v>
+        <v>48.7927</v>
       </c>
       <c r="W36" t="n">
-        <v>-62.3924</v>
+        <v>-58.44526</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lewis Brook Mine</t>
+          <t>Norsk South Block</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>012B/15/Asb001</t>
+          <t>012B/10/Dol004</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>37</v>
       </c>
       <c r="V39" t="n">
-        <v>48.77071</v>
+        <v>48.52445</v>
       </c>
       <c r="W39" t="n">
-        <v>-58.56548</v>
+        <v>-58.99684</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Beaver Dam</t>
+          <t>Burnt Lake North (Main Zone)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>012H/15/Au 018</t>
+          <t>013J/12/U  012</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Arsenic, Gold</t>
+          <t>Fluorine, Zinc, Lead, Molybdenum, Gold, Silver, Uranium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>37</v>
       </c>
       <c r="V40" t="n">
-        <v>49.86141</v>
+        <v>54.63965</v>
       </c>
       <c r="W40" t="n">
-        <v>-56.85295</v>
+        <v>-59.70939</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20012</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Strange Lake</t>
+          <t>Round Pond Deposit</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>024A/08/Ree001</t>
+          <t>012P/08/Zn 015</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
+          <t>Fluorine, Lead, Zinc</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>37</v>
       </c>
       <c r="V41" t="n">
-        <v>56.31656</v>
+        <v>51.25735</v>
       </c>
       <c r="W41" t="n">
-        <v>-64.12678</v>
+        <v>-56.26701</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Grey River Tungsten</t>
+          <t>Norsk North Block</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>011P/11/W  001</t>
+          <t>012B/10/Dol003</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>37</v>
       </c>
       <c r="V42" t="n">
-        <v>47.59343</v>
+        <v>48.53397</v>
       </c>
       <c r="W42" t="n">
-        <v>-57.10342</v>
+        <v>-58.9773</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Inda Lake</t>
+          <t>Porcupine Strand North Beach</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>013J/13/U  009</t>
+          <t>013I/03/Ti 001</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Uranium</t>
+          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>37</v>
       </c>
       <c r="V43" t="n">
-        <v>54.92456</v>
+        <v>54.03818</v>
       </c>
       <c r="W43" t="n">
-        <v>-59.5807</v>
+        <v>-57.31912</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Burnt Lake North (Main Zone)</t>
+          <t>Mount Margaret Pond Vein</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>013J/12/U  012</t>
+          <t>001L/14/Fl 039</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fluorine, Zinc, Lead, Molybdenum, Gold, Silver, Uranium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>37</v>
       </c>
       <c r="V44" t="n">
-        <v>54.63965</v>
+        <v>46.95861</v>
       </c>
       <c r="W44" t="n">
-        <v>-59.70939</v>
+        <v>-55.38707</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20039</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Round Pond Deposit</t>
+          <t>Inda Lake</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>012P/08/Zn 015</t>
+          <t>013J/13/U  009</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fluorine, Lead, Zinc</t>
+          <t>Molybdenum, Copper, Uranium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>37</v>
       </c>
       <c r="V45" t="n">
-        <v>51.25735</v>
+        <v>54.92456</v>
       </c>
       <c r="W45" t="n">
-        <v>-56.26701</v>
+        <v>-59.5807</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Norsk North Block</t>
+          <t>Romaines Brook</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>012B/10/Dol003</t>
+          <t>012B/10/Gyp001</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Magnesium, Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>37</v>
       </c>
       <c r="V46" t="n">
-        <v>48.53397</v>
+        <v>48.55534</v>
       </c>
       <c r="W46" t="n">
-        <v>-58.9773</v>
+        <v>-58.66751</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Norsk South Block</t>
+          <t>Sheep Brook</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>012B/10/Dol004</t>
+          <t>012B/08/Gyp001</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3865,14 +3865,14 @@
         <v>37</v>
       </c>
       <c r="V47" t="n">
-        <v>48.52445</v>
+        <v>48.39536</v>
       </c>
       <c r="W47" t="n">
-        <v>-58.99684</v>
+        <v>-58.42046</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Porcupine Strand North Beach</t>
+          <t>Lewis Brook Mine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>013I/03/Ti 001</t>
+          <t>012B/15/Asb001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>37</v>
       </c>
       <c r="V48" t="n">
-        <v>54.03818</v>
+        <v>48.77071</v>
       </c>
       <c r="W48" t="n">
-        <v>-57.31912</v>
+        <v>-58.56548</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
         </is>
       </c>
     </row>
@@ -3954,24 +3954,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deer Cove Talc Zone</t>
+          <t>Grey River Tungsten</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>012I/01/Tlc001</t>
+          <t>011P/11/W  001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Magnesium, Talc</t>
+          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4009,14 +4009,14 @@
         <v>37</v>
       </c>
       <c r="V49" t="n">
-        <v>50.01534</v>
+        <v>47.59343</v>
       </c>
       <c r="W49" t="n">
-        <v>-56.04949</v>
+        <v>-57.10342</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Strange Lake</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>024A/08/Ree001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>48.39536</v>
+        <v>56.31656</v>
       </c>
       <c r="W50" t="n">
-        <v>-58.42046</v>
+        <v>-64.12678</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Romaines Brook</t>
+          <t>Beaver Dam</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>012B/10/Gyp001</t>
+          <t>012H/15/Au 018</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Magnesium, Anhydrite, Gypsum</t>
+          <t>Arsenic, Gold</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>48.55534</v>
+        <v>49.86141</v>
       </c>
       <c r="W51" t="n">
-        <v>-58.66751</v>
+        <v>-56.85295</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mount Margaret Pond Vein</t>
+          <t>Deer Cove Talc Zone</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>001L/14/Fl 039</t>
+          <t>012I/01/Tlc001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Magnesium, Talc</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>46.95861</v>
+        <v>50.01534</v>
       </c>
       <c r="W53" t="n">
-        <v>-55.38707</v>
+        <v>-56.04949</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ackley City</t>
+          <t>Copper Creek BV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>001M/11/Mo 002</t>
+          <t>012H/16/Cu 040</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Molybdenum</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4369,14 +4369,14 @@
         <v>36</v>
       </c>
       <c r="V54" t="n">
-        <v>47.69347</v>
+        <v>49.91887</v>
       </c>
       <c r="W54" t="n">
-        <v>-55.20716</v>
+        <v>-56.20986</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Copper Creek BV</t>
+          <t>Ackley City</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>012H/16/Cu 040</t>
+          <t>001M/11/Mo 002</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Zinc, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>36</v>
       </c>
       <c r="V56" t="n">
-        <v>49.91887</v>
+        <v>47.69347</v>
       </c>
       <c r="W56" t="n">
-        <v>-56.20986</v>
+        <v>-55.20716</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jaclyn Main - Golden Promise</t>
+          <t>Strickland - Main Zone</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>012A/16/Au 002</t>
+          <t>011O/16/Zn 001</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Lead, Copper, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>35</v>
       </c>
       <c r="V57" t="n">
-        <v>48.90572</v>
+        <v>47.80818</v>
       </c>
       <c r="W57" t="n">
-        <v>-56.15002</v>
+        <v>-58.29993</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4602,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hope Brook</t>
+          <t>Voisey's Bay, Ovoid</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>011O/09/Au 003</t>
+          <t>014D/08/Ni 001</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4657,14 +4657,14 @@
         <v>35</v>
       </c>
       <c r="V58" t="n">
-        <v>47.73806</v>
+        <v>56.33134</v>
       </c>
       <c r="W58" t="n">
-        <v>-58.09531</v>
+        <v>-62.09706</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
         </is>
       </c>
     </row>
@@ -4674,29 +4674,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Strickland - Main Zone</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>011O/16/Zn 001</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I59" t="b">
@@ -4729,14 +4729,14 @@
         <v>35</v>
       </c>
       <c r="V59" t="n">
-        <v>47.80818</v>
+        <v>47.4438</v>
       </c>
       <c r="W59" t="n">
-        <v>-58.29993</v>
+        <v>-54.4169</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Ovoid</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>014D/08/Ni 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>35</v>
       </c>
       <c r="V60" t="n">
-        <v>56.33134</v>
+        <v>47.4063</v>
       </c>
       <c r="W60" t="n">
-        <v>-62.09706</v>
+        <v>-52.70699</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -4818,24 +4818,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Argyle</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>012H/16/Au 083</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>47.4063</v>
+        <v>49.97838</v>
       </c>
       <c r="W61" t="n">
-        <v>-52.70699</v>
+        <v>-56.05952</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
         </is>
       </c>
     </row>
@@ -4890,29 +4890,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Strickland - Copper Zone</t>
+          <t>Sleepy Hollow</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>011O/16/Cu 001</t>
+          <t>002E/12/Cu 031</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I62" t="b">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>47.80365</v>
+        <v>49.59747</v>
       </c>
       <c r="W62" t="n">
-        <v>-58.30275</v>
+        <v>-55.94735</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
         </is>
       </c>
     </row>
@@ -4962,29 +4962,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Jaclyn Main - Golden Promise</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>012A/16/Au 002</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I63" t="b">
@@ -5017,14 +5017,14 @@
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>47.4438</v>
+        <v>48.90572</v>
       </c>
       <c r="W63" t="n">
-        <v>-54.4169</v>
+        <v>-56.15002</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -5034,29 +5034,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>H Brook Showing</t>
+          <t>Hope Brook</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>011O/15/Au 004</t>
+          <t>011O/09/Au 003</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>47.7624</v>
+        <v>47.73806</v>
       </c>
       <c r="W64" t="n">
-        <v>-58.91357</v>
+        <v>-58.09531</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -5106,24 +5106,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Betts Cove Mine</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>002E/13/Cu 002</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>49.81179</v>
+        <v>48.5353</v>
       </c>
       <c r="W65" t="n">
-        <v>-55.80608</v>
+        <v>-58.48804</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tilt Cove Mine</t>
+          <t>Ming West</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>002E/13/Cu 001</t>
+          <t>012H/16/Cu 029</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Silver, Zinc, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U66" t="n">
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>49.88214</v>
+        <v>49.9148</v>
       </c>
       <c r="W66" t="n">
-        <v>-55.62813</v>
+        <v>-56.08996</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nugget Pond</t>
+          <t>Terra Nova Mine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>002E/13/Au 001</t>
+          <t>012H/16/Cu 004</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>49.84502</v>
+        <v>49.92133</v>
       </c>
       <c r="W67" t="n">
-        <v>-55.77536</v>
+        <v>-56.22896</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -5322,24 +5322,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Pine Cove</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>012H/16/Au 023</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>48.5353</v>
+        <v>49.96066</v>
       </c>
       <c r="W68" t="n">
-        <v>-58.48804</v>
+        <v>-56.13074</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
         </is>
       </c>
     </row>
@@ -5394,24 +5394,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>Tilt Cove Mine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>002E/13/Cu 001</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Gold, Nickel, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>49.19579</v>
+        <v>49.88214</v>
       </c>
       <c r="W69" t="n">
-        <v>-57.84974</v>
+        <v>-55.62813</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5466,29 +5466,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>H Brook Showing</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>011O/15/Au 004</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>52.961</v>
+        <v>47.7624</v>
       </c>
       <c r="W70" t="n">
-        <v>-66.81446</v>
+        <v>-58.91357</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Argyle</t>
+          <t>Betts Cove Mine</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>012H/16/Au 083</t>
+          <t>002E/13/Cu 002</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5593,14 +5593,14 @@
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>49.97838</v>
+        <v>49.81179</v>
       </c>
       <c r="W71" t="n">
-        <v>-56.05952</v>
+        <v>-55.80608</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ming West</t>
+          <t>Nugget Pond</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>012H/16/Cu 029</t>
+          <t>002E/13/Au 001</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5656,23 +5656,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>49.9148</v>
+        <v>49.84502</v>
       </c>
       <c r="W72" t="n">
-        <v>-56.08996</v>
+        <v>-55.77536</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Terra Nova Mine</t>
+          <t>Goldenville</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>012H/16/Cu 004</t>
+          <t>012H/16/Au 033</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Iron, Gold</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5728,23 +5728,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T73" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U73" t="n">
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>49.92133</v>
+        <v>49.99193</v>
       </c>
       <c r="W73" t="n">
-        <v>-56.22896</v>
+        <v>-56.05735</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Goldenville</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>012H/16/Au 033</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Iron, Gold</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5800,23 +5800,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T74" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U74" t="n">
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>49.99193</v>
+        <v>49.19579</v>
       </c>
       <c r="W74" t="n">
-        <v>-56.05735</v>
+        <v>-57.84974</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -5826,29 +5826,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Turk's Gut</t>
+          <t>Strickland - Copper Zone</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>001N/11/Cu 001</t>
+          <t>011O/16/Cu 001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>47.50226</v>
+        <v>47.80365</v>
       </c>
       <c r="W75" t="n">
-        <v>-53.20074</v>
+        <v>-58.30275</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sleepy Hollow</t>
+          <t>Turk's Gut</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>002E/12/Cu 031</t>
+          <t>001N/11/Cu 001</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>49.59747</v>
+        <v>47.50226</v>
       </c>
       <c r="W76" t="n">
-        <v>-55.94735</v>
+        <v>-53.20074</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pine Cove</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>012H/16/Au 023</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>49.96066</v>
+        <v>52.961</v>
       </c>
       <c r="W77" t="n">
-        <v>-56.13074</v>
+        <v>-66.81446</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -6042,12 +6042,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Miles Cove Mine</t>
+          <t>Tilt Cove/East Mine/Upper Dump</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>002E/12/Cu 012</t>
+          <t>002E/13/Au 028</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Silver, Nickel, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6097,14 +6097,14 @@
         <v>34</v>
       </c>
       <c r="V78" t="n">
-        <v>49.53936</v>
+        <v>49.88512</v>
       </c>
       <c r="W78" t="n">
-        <v>-55.79062</v>
+        <v>-55.62192</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Stog'er Tight</t>
+          <t>Crescent Lake Mine</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>012H/16/Au 041</t>
+          <t>002E/05/Cu 013</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
+          <t>Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>34</v>
       </c>
       <c r="V79" t="n">
-        <v>49.9661</v>
+        <v>49.48531</v>
       </c>
       <c r="W79" t="n">
-        <v>-56.07765</v>
+        <v>-55.84455</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FCu%20013</t>
         </is>
       </c>
     </row>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Crescent Lake Mine</t>
+          <t>Stog'er Tight</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>002E/05/Cu 013</t>
+          <t>012H/16/Au 041</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Copper</t>
+          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6313,14 +6313,14 @@
         <v>34</v>
       </c>
       <c r="V81" t="n">
-        <v>49.48531</v>
+        <v>49.9661</v>
       </c>
       <c r="W81" t="n">
-        <v>-55.84455</v>
+        <v>-56.07765</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FCu%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tilt Cove/East Mine/Upper Dump</t>
+          <t>Miles Cove Mine</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>002E/13/Au 028</t>
+          <t>002E/12/Cu 012</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Zinc, Gold</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6385,14 +6385,14 @@
         <v>34</v>
       </c>
       <c r="V82" t="n">
-        <v>49.88512</v>
+        <v>49.53936</v>
       </c>
       <c r="W82" t="n">
-        <v>-55.62192</v>
+        <v>-55.79062</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Upper Drill Brook Mine</t>
+          <t>Blow-Me-Down Chromite #1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>012B/09/Fe 002</t>
+          <t>012G/01/Cr 001</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6520,23 +6520,23 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T84" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U84" t="n">
         <v>33</v>
       </c>
       <c r="V84" t="n">
-        <v>48.53533</v>
+        <v>49.01096</v>
       </c>
       <c r="W84" t="n">
-        <v>-58.48601</v>
+        <v>-58.24371</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blow-Me-Down Chromite #1</t>
+          <t>Upper Drill Brook Mine</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>012G/01/Cr 001</t>
+          <t>012B/09/Fe 002</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6592,23 +6592,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T85" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U85" t="n">
         <v>33</v>
       </c>
       <c r="V85" t="n">
-        <v>49.01096</v>
+        <v>48.53533</v>
       </c>
       <c r="W85" t="n">
-        <v>-58.24371</v>
+        <v>-58.48601</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wabush No. 6</t>
+          <t>Sheps Lake</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>023G/02/Fe 006</t>
+          <t>023J/11/Fe 001</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6673,14 +6673,14 @@
         <v>31</v>
       </c>
       <c r="V86" t="n">
-        <v>53.01798</v>
+        <v>54.73475</v>
       </c>
       <c r="W86" t="n">
-        <v>-66.89297999999999</v>
+        <v>-67.06362</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6690,24 +6690,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Neal 1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>023B/14/Fe 028</t>
+          <t>023B/14/Fe 008</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6745,14 +6745,14 @@
         <v>31</v>
       </c>
       <c r="V87" t="n">
-        <v>52.94868</v>
+        <v>52.95013</v>
       </c>
       <c r="W87" t="n">
-        <v>-67.01146</v>
+        <v>-67.15191</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -6762,24 +6762,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sawyer Lake</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>023I/05/Fe 001</t>
+          <t>023B/14/Fe 020</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>31</v>
       </c>
       <c r="V88" t="n">
-        <v>54.45206</v>
+        <v>52.83351</v>
       </c>
       <c r="W88" t="n">
-        <v>-65.98627</v>
+        <v>-67.0311</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
         </is>
       </c>
     </row>
@@ -6834,24 +6834,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Howells River West Zone A</t>
+          <t>Mills Lake</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>023J/14/Fe 001</t>
+          <t>023B/14/Fe 002</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>31</v>
       </c>
       <c r="V89" t="n">
-        <v>54.90958</v>
+        <v>52.79808</v>
       </c>
       <c r="W89" t="n">
-        <v>-67.26052</v>
+        <v>-67.00413</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -6906,24 +6906,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sheps Lake</t>
+          <t>Howells River West Zone A</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>023J/11/Fe 001</t>
+          <t>023J/14/Fe 001</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>31</v>
       </c>
       <c r="V90" t="n">
-        <v>54.73475</v>
+        <v>54.90958</v>
       </c>
       <c r="W90" t="n">
-        <v>-67.06362</v>
+        <v>-67.26052</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Block 103 - Greenbush Zone</t>
+          <t>Duley No. 2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>023J/14/Fe 043</t>
+          <t>023B/15/Fe 008</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>31</v>
       </c>
       <c r="V91" t="n">
-        <v>54.97234</v>
+        <v>52.87214</v>
       </c>
       <c r="W91" t="n">
-        <v>-67.25158</v>
+        <v>-66.99635000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Elizabeth No. 2</t>
+          <t>Howells River West Zone B</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>023J/15/Fe 032</t>
+          <t>023J/14/Fe 002</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7105,14 +7105,14 @@
         <v>31</v>
       </c>
       <c r="V92" t="n">
-        <v>54.77182</v>
+        <v>54.87235</v>
       </c>
       <c r="W92" t="n">
-        <v>-66.88666000000001</v>
+        <v>-67.21584</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Howells River North</t>
+          <t>Wabush No. 8</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>023O/03/Fe 007</t>
+          <t>023B/15/Fe 005</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>31</v>
       </c>
       <c r="V93" t="n">
-        <v>55.01179</v>
+        <v>52.9791</v>
       </c>
       <c r="W93" t="n">
-        <v>-67.37214</v>
+        <v>-66.90604999999999</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -7194,24 +7194,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lorraine No. 4</t>
+          <t>Sawyer Lake</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>023G/02/Fe 008</t>
+          <t>023I/05/Fe 001</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7249,14 +7249,14 @@
         <v>31</v>
       </c>
       <c r="V94" t="n">
-        <v>53.08316</v>
+        <v>54.45206</v>
       </c>
       <c r="W94" t="n">
-        <v>-66.87726000000001</v>
+        <v>-65.98627</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -7266,12 +7266,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kivivic No 4</t>
+          <t>Timmins No 8</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>023O/03/Fe 004</t>
+          <t>023J/14/Fe 026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>31</v>
       </c>
       <c r="V95" t="n">
-        <v>55.04865</v>
+        <v>54.89589</v>
       </c>
       <c r="W95" t="n">
-        <v>-67.28158000000001</v>
+        <v>-67.07944000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kivivic No 3</t>
+          <t>Mile 2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>023O/03/Fe 003</t>
+          <t>023B/15/Fe 011</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7393,14 +7393,14 @@
         <v>31</v>
       </c>
       <c r="V96" t="n">
-        <v>55.05061</v>
+        <v>52.97907</v>
       </c>
       <c r="W96" t="n">
-        <v>-67.26130000000001</v>
+        <v>-66.88907</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Houston 3</t>
+          <t>Wabush No. 1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>023J/10/Fe 010</t>
+          <t>023B/15/Fe 002</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7465,14 +7465,14 @@
         <v>31</v>
       </c>
       <c r="V97" t="n">
-        <v>54.69887</v>
+        <v>52.9599</v>
       </c>
       <c r="W97" t="n">
-        <v>-66.64483</v>
+        <v>-66.9704</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>023B/14/Fe 020</t>
+          <t>023B/14/Fe 028</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>31</v>
       </c>
       <c r="V98" t="n">
-        <v>52.83351</v>
+        <v>52.94868</v>
       </c>
       <c r="W98" t="n">
-        <v>-67.0311</v>
+        <v>-67.01146</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Howells River West Zone B</t>
+          <t>Houston 3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>023J/14/Fe 002</t>
+          <t>023J/10/Fe 010</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>31</v>
       </c>
       <c r="V99" t="n">
-        <v>54.87235</v>
+        <v>54.69887</v>
       </c>
       <c r="W99" t="n">
-        <v>-67.21584</v>
+        <v>-66.64483</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -7626,24 +7626,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Neal 1</t>
+          <t>Kivivic No 5</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>023B/14/Fe 008</t>
+          <t>023O/03/Fe 005</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>31</v>
       </c>
       <c r="V100" t="n">
-        <v>52.95013</v>
+        <v>55.06664</v>
       </c>
       <c r="W100" t="n">
-        <v>-67.15191</v>
+        <v>-67.29537000000001</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -7698,24 +7698,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Duley No. 1</t>
+          <t>Kivivic No 4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>023B/14/Fe 001</t>
+          <t>023O/03/Fe 004</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7753,14 +7753,14 @@
         <v>31</v>
       </c>
       <c r="V101" t="n">
-        <v>52.87237</v>
+        <v>55.04865</v>
       </c>
       <c r="W101" t="n">
-        <v>-67.05874</v>
+        <v>-67.28158000000001</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -7770,24 +7770,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mills Lake</t>
+          <t>Kivivic No 3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>023B/14/Fe 002</t>
+          <t>023O/03/Fe 003</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7825,14 +7825,14 @@
         <v>31</v>
       </c>
       <c r="V102" t="n">
-        <v>52.79808</v>
+        <v>55.05061</v>
       </c>
       <c r="W102" t="n">
-        <v>-67.00413</v>
+        <v>-67.26130000000001</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kivivic No 5</t>
+          <t>Houston 1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>023O/03/Fe 005</t>
+          <t>023J/10/Fe 008</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>31</v>
       </c>
       <c r="V103" t="n">
-        <v>55.06664</v>
+        <v>54.70748</v>
       </c>
       <c r="W103" t="n">
-        <v>-67.29537000000001</v>
+        <v>-66.65615</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -7914,12 +7914,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Redmond 5</t>
+          <t>Houston 2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>023J/10/Fe 005</t>
+          <t>023J/10/Fe 009</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -7969,14 +7969,14 @@
         <v>31</v>
       </c>
       <c r="V104" t="n">
-        <v>54.70854</v>
+        <v>54.71245</v>
       </c>
       <c r="W104" t="n">
-        <v>-66.79174999999999</v>
+        <v>-66.66257</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Houston 1</t>
+          <t>Redmond 5</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>023J/10/Fe 008</t>
+          <t>023J/10/Fe 005</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8041,14 +8041,14 @@
         <v>31</v>
       </c>
       <c r="V105" t="n">
-        <v>54.70748</v>
+        <v>54.70854</v>
       </c>
       <c r="W105" t="n">
-        <v>-66.65615</v>
+        <v>-66.79174999999999</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Houston 2</t>
+          <t>Duley No. 1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>023J/10/Fe 009</t>
+          <t>023B/14/Fe 001</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8113,14 +8113,14 @@
         <v>31</v>
       </c>
       <c r="V106" t="n">
-        <v>54.71245</v>
+        <v>52.87237</v>
       </c>
       <c r="W106" t="n">
-        <v>-66.66257</v>
+        <v>-67.05874</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Timmins No 7</t>
+          <t>Howse</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>023J/14/Fe 025</t>
+          <t>023J/14/Fe 028</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8185,14 +8185,14 @@
         <v>31</v>
       </c>
       <c r="V107" t="n">
-        <v>54.89246</v>
+        <v>54.9089</v>
       </c>
       <c r="W107" t="n">
-        <v>-67.07259000000001</v>
+        <v>-67.14075</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Timmins No 5</t>
+          <t>Howells River North</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>023J/14/Fe 024</t>
+          <t>023O/03/Fe 007</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8257,14 +8257,14 @@
         <v>31</v>
       </c>
       <c r="V108" t="n">
-        <v>54.86384</v>
+        <v>55.01179</v>
       </c>
       <c r="W108" t="n">
-        <v>-67.09327</v>
+        <v>-67.37214</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Duley No. 2</t>
+          <t>Elizabeth No. 2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>023B/15/Fe 008</t>
+          <t>023J/15/Fe 032</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>31</v>
       </c>
       <c r="V109" t="n">
-        <v>52.87214</v>
+        <v>54.77182</v>
       </c>
       <c r="W109" t="n">
-        <v>-66.99635000000001</v>
+        <v>-66.88666000000001</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mile 2</t>
+          <t>Block 103 - Greenbush Zone</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>023B/15/Fe 011</t>
+          <t>023J/14/Fe 043</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -8401,14 +8401,14 @@
         <v>31</v>
       </c>
       <c r="V110" t="n">
-        <v>52.97907</v>
+        <v>54.97234</v>
       </c>
       <c r="W110" t="n">
-        <v>-66.88907</v>
+        <v>-67.25158</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
         </is>
       </c>
     </row>
@@ -8418,24 +8418,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Wabush No. 8</t>
+          <t>Attikamagen Deposit</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>023B/15/Fe 005</t>
+          <t>023J/16/Fe 001</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>31</v>
       </c>
       <c r="V111" t="n">
-        <v>52.9791</v>
+        <v>54.80989</v>
       </c>
       <c r="W111" t="n">
-        <v>-66.90604999999999</v>
+        <v>-66.47658</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Wabush No. 4</t>
+          <t>Canning</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>023B/15/Fe 004</t>
+          <t>023B/15/Fe 007</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8545,14 +8545,14 @@
         <v>31</v>
       </c>
       <c r="V112" t="n">
-        <v>52.95373</v>
+        <v>52.9469</v>
       </c>
       <c r="W112" t="n">
-        <v>-66.94092000000001</v>
+        <v>-66.95802999999999</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timmins No 8</t>
+          <t>Timmins No 5</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>023J/14/Fe 026</t>
+          <t>023J/14/Fe 024</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8617,14 +8617,14 @@
         <v>31</v>
       </c>
       <c r="V113" t="n">
-        <v>54.89589</v>
+        <v>54.86384</v>
       </c>
       <c r="W113" t="n">
-        <v>-67.07944000000001</v>
+        <v>-67.09327</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ferriman No 7</t>
+          <t>Timmins No 7</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>023J/15/Fe 014</t>
+          <t>023J/14/Fe 025</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8689,14 +8689,14 @@
         <v>31</v>
       </c>
       <c r="V114" t="n">
-        <v>54.81281</v>
+        <v>54.89246</v>
       </c>
       <c r="W114" t="n">
-        <v>-66.94580999999999</v>
+        <v>-67.07259000000001</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ruth Lake No 2</t>
+          <t>Wabush No. 4</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>023J/15/Fe 011</t>
+          <t>023B/15/Fe 004</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -8761,14 +8761,14 @@
         <v>31</v>
       </c>
       <c r="V115" t="n">
-        <v>54.79747</v>
+        <v>52.95373</v>
       </c>
       <c r="W115" t="n">
-        <v>-66.87487</v>
+        <v>-66.94092000000001</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wabush No. 1</t>
+          <t>Joyce Lake</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>023B/15/Fe 002</t>
+          <t>023J/15/Fe 030</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>31</v>
       </c>
       <c r="V116" t="n">
-        <v>52.9599</v>
+        <v>54.8993</v>
       </c>
       <c r="W116" t="n">
-        <v>-66.9704</v>
+        <v>-66.53366</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
         </is>
       </c>
     </row>
@@ -8850,29 +8850,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bishop North</t>
+          <t>Ruth Lake No 2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>012B/08/Fe 001</t>
+          <t>023J/15/Fe 011</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I117" t="b">
@@ -8905,14 +8905,14 @@
         <v>31</v>
       </c>
       <c r="V117" t="n">
-        <v>48.40317</v>
+        <v>54.79747</v>
       </c>
       <c r="W117" t="n">
-        <v>-58.3315</v>
+        <v>-66.87487</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8922,29 +8922,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Indian Head Mine</t>
+          <t>Wabush No. 6</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>012B/10/Fe 001</t>
+          <t>023G/02/Fe 006</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I118" t="b">
@@ -8977,14 +8977,14 @@
         <v>31</v>
       </c>
       <c r="V118" t="n">
-        <v>48.52416</v>
+        <v>53.01798</v>
       </c>
       <c r="W118" t="n">
-        <v>-58.5148</v>
+        <v>-66.89297999999999</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -8994,24 +8994,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Howse</t>
+          <t>Ruth Lake No 8</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>023J/14/Fe 028</t>
+          <t>023J/15/Fe 009</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9049,14 +9049,14 @@
         <v>31</v>
       </c>
       <c r="V119" t="n">
-        <v>54.9089</v>
+        <v>54.78104</v>
       </c>
       <c r="W119" t="n">
-        <v>-67.14075</v>
+        <v>-66.86577</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ruth Lake No 8</t>
+          <t>Wabush No. 7</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>023J/15/Fe 009</t>
+          <t>023G/02/Fe 007</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9121,14 +9121,14 @@
         <v>31</v>
       </c>
       <c r="V120" t="n">
-        <v>54.78104</v>
+        <v>53.02512</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.86577</v>
+        <v>-66.90531</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Knob Lake 1</t>
+          <t>Julienne Lake</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>023J/15/Fe 013</t>
+          <t>023G/02/Fe 009</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9193,14 +9193,14 @@
         <v>31</v>
       </c>
       <c r="V121" t="n">
-        <v>54.7766</v>
+        <v>53.13733</v>
       </c>
       <c r="W121" t="n">
-        <v>-66.80589000000001</v>
+        <v>-66.78360000000001</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9210,29 +9210,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bishop South</t>
+          <t>Lorraine No. 4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>012B/08/Fe 002</t>
+          <t>023G/02/Fe 008</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I122" t="b">
@@ -9265,14 +9265,14 @@
         <v>31</v>
       </c>
       <c r="V122" t="n">
-        <v>48.39996</v>
+        <v>53.08316</v>
       </c>
       <c r="W122" t="n">
-        <v>-58.33683</v>
+        <v>-66.87726000000001</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -9282,24 +9282,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Goethite Bay North</t>
+          <t>Ferriman No 7</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>023G/02/Fe 041</t>
+          <t>023J/15/Fe 014</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9337,14 +9337,14 @@
         <v>31</v>
       </c>
       <c r="V123" t="n">
-        <v>53.18717</v>
+        <v>54.81281</v>
       </c>
       <c r="W123" t="n">
-        <v>-66.74445</v>
+        <v>-66.94580999999999</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
         </is>
       </c>
     </row>
@@ -9354,24 +9354,24 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Elizabeth No. 1</t>
+          <t>Knob Lake 1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>023J/15/Fe 031</t>
+          <t>023J/15/Fe 013</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9409,14 +9409,14 @@
         <v>31</v>
       </c>
       <c r="V124" t="n">
-        <v>54.78743</v>
+        <v>54.7766</v>
       </c>
       <c r="W124" t="n">
-        <v>-66.90081000000001</v>
+        <v>-66.80589000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
         </is>
       </c>
     </row>
@@ -9426,29 +9426,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Howells Lake</t>
+          <t>Bishop South</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>023O/03/Fe 006</t>
+          <t>012B/08/Fe 002</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I125" t="b">
@@ -9481,14 +9481,14 @@
         <v>31</v>
       </c>
       <c r="V125" t="n">
-        <v>55.06346</v>
+        <v>48.39996</v>
       </c>
       <c r="W125" t="n">
-        <v>-67.40528</v>
+        <v>-58.33683</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -9498,29 +9498,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Attikamagen Deposit</t>
+          <t>Bishop North</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>023J/16/Fe 001</t>
+          <t>012B/08/Fe 001</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I126" t="b">
@@ -9553,14 +9553,14 @@
         <v>31</v>
       </c>
       <c r="V126" t="n">
-        <v>54.80989</v>
+        <v>48.40317</v>
       </c>
       <c r="W126" t="n">
-        <v>-66.47658</v>
+        <v>-58.3315</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9570,29 +9570,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Wabush No. 7</t>
+          <t>Indian Head Mine</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>023G/02/Fe 007</t>
+          <t>012B/10/Fe 001</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I127" t="b">
@@ -9625,14 +9625,14 @@
         <v>31</v>
       </c>
       <c r="V127" t="n">
-        <v>53.02512</v>
+        <v>48.52416</v>
       </c>
       <c r="W127" t="n">
-        <v>-66.90531</v>
+        <v>-58.5148</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Joyce Lake</t>
+          <t>Goethite Bay North</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>023J/15/Fe 030</t>
+          <t>023G/02/Fe 041</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>31</v>
       </c>
       <c r="V128" t="n">
-        <v>54.8993</v>
+        <v>53.18717</v>
       </c>
       <c r="W128" t="n">
-        <v>-66.53366</v>
+        <v>-66.74445</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
         </is>
       </c>
     </row>
@@ -9714,24 +9714,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Julienne Lake</t>
+          <t>Elizabeth No. 1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>023G/02/Fe 009</t>
+          <t>023J/15/Fe 031</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9769,14 +9769,14 @@
         <v>31</v>
       </c>
       <c r="V129" t="n">
-        <v>53.13733</v>
+        <v>54.78743</v>
       </c>
       <c r="W129" t="n">
-        <v>-66.78360000000001</v>
+        <v>-66.90081000000001</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
         </is>
       </c>
     </row>
@@ -9786,24 +9786,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Canning</t>
+          <t>Howells Lake</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>023B/15/Fe 007</t>
+          <t>023O/03/Fe 006</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9841,14 +9841,14 @@
         <v>31</v>
       </c>
       <c r="V130" t="n">
-        <v>52.9469</v>
+        <v>55.06346</v>
       </c>
       <c r="W130" t="n">
-        <v>-66.95802999999999</v>
+        <v>-67.40528</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Parsons Pond Cart Track</t>
+          <t>Parsons Pond No 4</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>012I/04/Btm001</t>
+          <t>012H/13/Btm004</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Oil Shale</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9913,14 +9913,14 @@
         <v>30</v>
       </c>
       <c r="V131" t="n">
-        <v>50.00564</v>
+        <v>49.99787</v>
       </c>
       <c r="W131" t="n">
-        <v>-57.63187</v>
+        <v>-57.63818</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
         </is>
       </c>
     </row>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Blue Beach Mine</t>
+          <t>Parsons Pond No 1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>001L/14/Fl 001</t>
+          <t>012H/13/Btm001</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9976,23 +9976,23 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T132" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U132" t="n">
         <v>30</v>
       </c>
       <c r="V132" t="n">
-        <v>46.91553</v>
+        <v>49.99228</v>
       </c>
       <c r="W132" t="n">
-        <v>-55.40729</v>
+        <v>-57.58928</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Iron Springs Mine</t>
+          <t>Parsons Pond No 2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>001L/14/Fl 008</t>
+          <t>012H/13/Btm002</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10057,14 +10057,14 @@
         <v>30</v>
       </c>
       <c r="V133" t="n">
-        <v>46.88701</v>
+        <v>49.97421</v>
       </c>
       <c r="W133" t="n">
-        <v>-55.421</v>
+        <v>-57.60538</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Salt Cove Valley Vein</t>
+          <t>Parsons Pond No 3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>001L/14/Fl 015</t>
+          <t>012H/13/Btm003</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10129,14 +10129,14 @@
         <v>30</v>
       </c>
       <c r="V134" t="n">
-        <v>46.87774</v>
+        <v>49.97912</v>
       </c>
       <c r="W134" t="n">
-        <v>-55.43387</v>
+        <v>-57.64547</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
         </is>
       </c>
     </row>
@@ -10146,12 +10146,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Black Duck Mine</t>
+          <t>Parsons Pond Cart Track</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>001L/14/Fl 010</t>
+          <t>012I/04/Btm001</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil Shale</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10192,23 +10192,23 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T135" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U135" t="n">
         <v>30</v>
       </c>
       <c r="V135" t="n">
-        <v>46.93201</v>
+        <v>50.00564</v>
       </c>
       <c r="W135" t="n">
-        <v>-55.38881</v>
+        <v>-57.63187</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AGS Vein</t>
+          <t>La Manche</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>001L/14/Fl 013</t>
+          <t>001N/12/Pb 001</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Fluorine</t>
+          <t>Zinc, Silver, Barium, Lead</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10273,14 +10273,14 @@
         <v>30</v>
       </c>
       <c r="V136" t="n">
-        <v>46.91489</v>
+        <v>47.6889</v>
       </c>
       <c r="W136" t="n">
-        <v>-55.48584</v>
+        <v>-53.93901</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>La Manche</t>
+          <t>Mine Hill</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>001N/12/Pb 001</t>
+          <t>001N/07/Pph004</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Barium, Lead</t>
+          <t>Pyrophyllite</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>30</v>
       </c>
       <c r="V137" t="n">
-        <v>47.6889</v>
+        <v>47.48</v>
       </c>
       <c r="W137" t="n">
-        <v>-53.93901</v>
+        <v>-52.95479</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
         </is>
       </c>
     </row>
@@ -10362,12 +10362,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Collier Point</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>001N/12/Ba 001</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Barium</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>30</v>
       </c>
       <c r="V138" t="n">
-        <v>53.469</v>
+        <v>47.59126</v>
       </c>
       <c r="W138" t="n">
-        <v>-64.91218000000001</v>
+        <v>-53.69011</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mine Hill</t>
+          <t>Middle Arm Brook</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>001N/07/Pph004</t>
+          <t>012H/16/Vir001</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pyrophyllite</t>
+          <t>Virginite</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>30</v>
       </c>
       <c r="V139" t="n">
-        <v>47.48</v>
+        <v>49.80048</v>
       </c>
       <c r="W139" t="n">
-        <v>-52.95479</v>
+        <v>-56.31995</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
         </is>
       </c>
     </row>
@@ -10506,24 +10506,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Silver Cliff</t>
+          <t>Daniel's Harbour Mine-K Zone</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>001N/05/Pb 003</t>
+          <t>012I/06/Zn 010</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Barium, Copper, Zinc, Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>30</v>
       </c>
       <c r="V140" t="n">
-        <v>47.30144</v>
+        <v>50.2935</v>
       </c>
       <c r="W140" t="n">
-        <v>-53.94444</v>
+        <v>-57.46875</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F05%2FPb%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
         </is>
       </c>
     </row>
@@ -10578,12 +10578,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Bluff Head Mine</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/15/Cr 001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Asbestos, Chromium</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10633,14 +10633,14 @@
         <v>30</v>
       </c>
       <c r="V141" t="n">
-        <v>53.40462</v>
+        <v>48.77717</v>
       </c>
       <c r="W141" t="n">
-        <v>-65.08734</v>
+        <v>-58.59931</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -10650,24 +10650,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Collier Point</t>
+          <t>Pilley's Island Mine</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>001N/12/Ba 001</t>
+          <t>002E/12/Cu 001</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Barium</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10705,14 +10705,14 @@
         <v>30</v>
       </c>
       <c r="V142" t="n">
-        <v>47.59126</v>
+        <v>49.50863</v>
       </c>
       <c r="W142" t="n">
-        <v>-53.69011</v>
+        <v>-55.71872</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -10722,12 +10722,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Tarefare Mine</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>001L/14/Fl 006</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10777,14 +10777,14 @@
         <v>30</v>
       </c>
       <c r="V143" t="n">
-        <v>48.56074</v>
+        <v>46.8912</v>
       </c>
       <c r="W143" t="n">
-        <v>-58.8161</v>
+        <v>-55.43112</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pilley's Island Mine</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>002E/12/Cu 001</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>30</v>
       </c>
       <c r="V144" t="n">
-        <v>49.50863</v>
+        <v>53.469</v>
       </c>
       <c r="W144" t="n">
-        <v>-55.71872</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -10866,12 +10866,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Silver Cliff</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>001N/05/Pb 003</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Barium, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10921,14 +10921,14 @@
         <v>30</v>
       </c>
       <c r="V145" t="n">
-        <v>48.50411</v>
+        <v>47.30144</v>
       </c>
       <c r="W145" t="n">
-        <v>-58.53451</v>
+        <v>-53.94444</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F05%2FPb%20003</t>
         </is>
       </c>
     </row>
@@ -10938,12 +10938,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Bluff Head Mine</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>012B/15/Cr 001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Asbestos, Chromium</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>30</v>
       </c>
       <c r="V146" t="n">
-        <v>48.77717</v>
+        <v>48.56074</v>
       </c>
       <c r="W146" t="n">
-        <v>-58.59931</v>
+        <v>-58.8161</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -11010,24 +11010,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cross Cove</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>002E/10/Sb 001</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11065,14 +11065,14 @@
         <v>30</v>
       </c>
       <c r="V147" t="n">
-        <v>49.57534</v>
+        <v>53.40462</v>
       </c>
       <c r="W147" t="n">
-        <v>-54.86876</v>
+        <v>-65.08734</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>York Harbour Mine</t>
+          <t>Goose Cove</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>012G/01/Cu 002</t>
+          <t>002M/05/Cu 001</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
+          <t>Zinc, Nickel, Iron, Copper</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11137,14 +11137,14 @@
         <v>30</v>
       </c>
       <c r="V148" t="n">
-        <v>49.05208</v>
+        <v>51.31009</v>
       </c>
       <c r="W148" t="n">
-        <v>-58.30769</v>
+        <v>-55.62342</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -11154,24 +11154,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lord &amp; Lady Gulch Mine</t>
+          <t>York Harbour Mine</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>001L/14/Fl 005</t>
+          <t>012G/01/Cu 002</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11209,14 +11209,14 @@
         <v>30</v>
       </c>
       <c r="V149" t="n">
-        <v>46.87554</v>
+        <v>49.05208</v>
       </c>
       <c r="W149" t="n">
-        <v>-55.4111</v>
+        <v>-58.30769</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Goose Cove</t>
+          <t>Cross Cove</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>002M/05/Cu 001</t>
+          <t>002E/10/Sb 001</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11243,7 +11243,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Zinc, Nickel, Iron, Copper</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11281,14 +11281,14 @@
         <v>30</v>
       </c>
       <c r="V150" t="n">
-        <v>51.31009</v>
+        <v>49.57534</v>
       </c>
       <c r="W150" t="n">
-        <v>-55.62342</v>
+        <v>-54.86876</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Hares Ears Vein</t>
+          <t>Lord &amp; Lady Gulch Mine</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>001L/14/Fl 007</t>
+          <t>001L/14/Fl 005</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11353,14 +11353,14 @@
         <v>30</v>
       </c>
       <c r="V151" t="n">
-        <v>46.88814</v>
+        <v>46.87554</v>
       </c>
       <c r="W151" t="n">
-        <v>-55.41178</v>
+        <v>-55.4111</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
         </is>
       </c>
     </row>
@@ -11370,12 +11370,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Tarefare Mine</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>001L/14/Fl 006</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11425,14 +11425,14 @@
         <v>30</v>
       </c>
       <c r="V152" t="n">
-        <v>46.8912</v>
+        <v>48.50411</v>
       </c>
       <c r="W152" t="n">
-        <v>-55.43112</v>
+        <v>-58.53451</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Director Mine</t>
+          <t>Southern Cross Veins</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>001L/14/Fl 009</t>
+          <t>001L/14/Fl 020</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -11497,14 +11497,14 @@
         <v>30</v>
       </c>
       <c r="V153" t="n">
-        <v>46.90681</v>
+        <v>46.88974</v>
       </c>
       <c r="W153" t="n">
-        <v>-55.42107</v>
+        <v>-55.42958</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11514,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Doctors Pond Veins</t>
+          <t>Little Salt Cove</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>001L/14/Fl 036</t>
+          <t>001L/14/Fl 016</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11569,14 +11569,14 @@
         <v>30</v>
       </c>
       <c r="V154" t="n">
-        <v>46.92769</v>
+        <v>46.87654</v>
       </c>
       <c r="W154" t="n">
-        <v>-55.37593</v>
+        <v>-55.43141</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Borney Lake</t>
+          <t>Hares Ears Vein</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>002D/14/Stn001</t>
+          <t>001L/14/Fl 007</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11641,14 +11641,14 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>48.9264</v>
+        <v>46.88814</v>
       </c>
       <c r="W155" t="n">
-        <v>-55.44535</v>
+        <v>-55.41178</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
         </is>
       </c>
     </row>
@@ -11658,12 +11658,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Baie Verte Mine</t>
+          <t>Iron Springs Mine</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>012H/16/Asb008</t>
+          <t>001L/14/Fl 008</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Magnesium, Asbestos</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11713,14 +11713,14 @@
         <v>30</v>
       </c>
       <c r="V156" t="n">
-        <v>49.97974</v>
+        <v>46.88701</v>
       </c>
       <c r="W156" t="n">
-        <v>-56.19399</v>
+        <v>-55.421</v>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
         </is>
       </c>
     </row>
@@ -11730,24 +11730,24 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Little Salt Cove</t>
+          <t>AGS Vein</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>001L/14/Fl 016</t>
+          <t>001L/14/Fl 013</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Zinc, Lead, Copper, Fluorine</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11785,14 +11785,14 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>46.87654</v>
+        <v>46.91489</v>
       </c>
       <c r="W157" t="n">
-        <v>-55.43141</v>
+        <v>-55.48584</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Southern Cross Veins</t>
+          <t>Salt Cove Valley Vein</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>001L/14/Fl 020</t>
+          <t>001L/14/Fl 015</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -11857,14 +11857,14 @@
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>46.88974</v>
+        <v>46.87774</v>
       </c>
       <c r="W158" t="n">
-        <v>-55.42958</v>
+        <v>-55.43387</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20015</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Scrape Vein</t>
+          <t>Director Mine</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>001L/14/Fl 035</t>
+          <t>001L/14/Fl 009</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -11929,14 +11929,14 @@
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>46.92547</v>
+        <v>46.90681</v>
       </c>
       <c r="W159" t="n">
-        <v>-55.37193</v>
+        <v>-55.42107</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Parsons Pond No 2</t>
+          <t>Black Duck Mine</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>012H/13/Btm002</t>
+          <t>001L/14/Fl 010</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12001,14 +12001,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>49.97421</v>
+        <v>46.93201</v>
       </c>
       <c r="W160" t="n">
-        <v>-57.60538</v>
+        <v>-55.38881</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Parsons Pond No 4</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>012H/13/Btm004</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12064,23 +12064,23 @@
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T161" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U161" t="n">
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>49.99787</v>
+        <v>48.30663</v>
       </c>
       <c r="W161" t="n">
-        <v>-57.63818</v>
+        <v>-58.68165</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -12090,24 +12090,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Parsons Pond No 1</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>012H/13/Btm001</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12136,23 +12136,23 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T162" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U162" t="n">
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>49.99228</v>
+        <v>49.45488</v>
       </c>
       <c r="W162" t="n">
-        <v>-57.58928</v>
+        <v>-55.49811</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -12162,24 +12162,24 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-K Zone</t>
+          <t>Scrape Vein</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>012I/06/Zn 010</t>
+          <t>001L/14/Fl 035</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12217,14 +12217,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>50.2935</v>
+        <v>46.92547</v>
       </c>
       <c r="W163" t="n">
-        <v>-57.46875</v>
+        <v>-55.37193</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Parsons Pond No 3</t>
+          <t>Doctors Pond Veins</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>012H/13/Btm003</t>
+          <t>001L/14/Fl 036</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12289,14 +12289,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>49.97912</v>
+        <v>46.92769</v>
       </c>
       <c r="W164" t="n">
-        <v>-57.64547</v>
+        <v>-55.37593</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Middle Arm Brook</t>
+          <t>Borney Lake</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>012H/16/Vir001</t>
+          <t>002D/14/Stn001</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Virginite</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -12361,14 +12361,14 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>49.80048</v>
+        <v>48.9264</v>
       </c>
       <c r="W165" t="n">
-        <v>-56.31995</v>
+        <v>-55.44535</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
         </is>
       </c>
     </row>
@@ -12378,24 +12378,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Blue Beach Mine</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>001L/14/Fl 001</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12433,14 +12433,14 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>49.45488</v>
+        <v>46.91553</v>
       </c>
       <c r="W166" t="n">
-        <v>-55.49811</v>
+        <v>-55.40729</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Baie Verte Mine</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>012H/16/Asb008</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Magnesium, Asbestos</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12505,14 +12505,14 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>48.30663</v>
+        <v>49.97974</v>
       </c>
       <c r="W167" t="n">
-        <v>-58.68165</v>
+        <v>-56.19399</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
         </is>
       </c>
     </row>
@@ -12594,12 +12594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-J Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>012I/06/Zn 009</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12649,14 +12649,14 @@
         <v>29</v>
       </c>
       <c r="V169" t="n">
-        <v>50.30247</v>
+        <v>50.31118</v>
       </c>
       <c r="W169" t="n">
-        <v>-57.47459</v>
+        <v>-57.43009</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-B Zone</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 002</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -12721,14 +12721,14 @@
         <v>29</v>
       </c>
       <c r="V170" t="n">
-        <v>50.27283</v>
+        <v>50.2975</v>
       </c>
       <c r="W170" t="n">
-        <v>-57.46448</v>
+        <v>-57.45784</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -12738,12 +12738,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Browning Mine</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>012H/10/Au 001</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Gold</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12793,14 +12793,14 @@
         <v>29</v>
       </c>
       <c r="V171" t="n">
-        <v>49.71799</v>
+        <v>50.27283</v>
       </c>
       <c r="W171" t="n">
-        <v>-56.92565</v>
+        <v>-57.46448</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-M Zone</t>
+          <t>Daniel's Harbour Mine-F Zone</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>012I/06/Zn 012</t>
+          <t>012I/06/Zn 006</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -12937,14 +12937,14 @@
         <v>29</v>
       </c>
       <c r="V173" t="n">
-        <v>50.29514</v>
+        <v>50.29437</v>
       </c>
       <c r="W173" t="n">
-        <v>-57.44013</v>
+        <v>-57.45374</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12954,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-A Zone</t>
+          <t>Daniel's Harbour Mine-G Zone</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>012I/06/Zn 001</t>
+          <t>012I/06/Zn 007</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -13009,14 +13009,14 @@
         <v>29</v>
       </c>
       <c r="V174" t="n">
-        <v>50.29576</v>
+        <v>50.29448</v>
       </c>
       <c r="W174" t="n">
-        <v>-57.46512</v>
+        <v>-57.44714</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-E Zone</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 005</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13081,14 +13081,14 @@
         <v>29</v>
       </c>
       <c r="V175" t="n">
-        <v>50.31118</v>
+        <v>50.31067</v>
       </c>
       <c r="W175" t="n">
-        <v>-57.43009</v>
+        <v>-57.44799</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
         </is>
       </c>
     </row>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-D Zone</t>
+          <t>Daniel's Harbour Mine-H Zone</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>012I/06/Zn 004</t>
+          <t>012I/06/Zn 008</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13153,14 +13153,14 @@
         <v>29</v>
       </c>
       <c r="V176" t="n">
-        <v>50.30795</v>
+        <v>50.29179</v>
       </c>
       <c r="W176" t="n">
-        <v>-57.45218</v>
+        <v>-57.44599</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-C Zone</t>
+          <t>Daniel's Harbour Mine-A Zone</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>012I/06/Zn 003</t>
+          <t>012I/06/Zn 001</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13225,14 +13225,14 @@
         <v>29</v>
       </c>
       <c r="V177" t="n">
-        <v>50.30435</v>
+        <v>50.29576</v>
       </c>
       <c r="W177" t="n">
-        <v>-57.45355</v>
+        <v>-57.46512</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-E Zone</t>
+          <t>Daniel's Harbour Mine-D Zone</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>012I/06/Zn 005</t>
+          <t>012I/06/Zn 004</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13297,14 +13297,14 @@
         <v>29</v>
       </c>
       <c r="V178" t="n">
-        <v>50.31067</v>
+        <v>50.30795</v>
       </c>
       <c r="W178" t="n">
-        <v>-57.44799</v>
+        <v>-57.45218</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
         </is>
       </c>
     </row>
@@ -13314,12 +13314,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-G Zone</t>
+          <t>Daniel's Harbour Mine-C Zone</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>012I/06/Zn 007</t>
+          <t>012I/06/Zn 003</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -13369,14 +13369,14 @@
         <v>29</v>
       </c>
       <c r="V179" t="n">
-        <v>50.29448</v>
+        <v>50.30435</v>
       </c>
       <c r="W179" t="n">
-        <v>-57.44714</v>
+        <v>-57.45355</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
         </is>
       </c>
     </row>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-B Zone</t>
+          <t>Daniel's Harbour Mine-L Zone</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>012I/06/Zn 002</t>
+          <t>012I/06/Zn 011</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Lead, Dolomite, Zinc</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13441,14 +13441,14 @@
         <v>29</v>
       </c>
       <c r="V180" t="n">
-        <v>50.2975</v>
+        <v>50.27686</v>
       </c>
       <c r="W180" t="n">
-        <v>-57.45784</v>
+        <v>-57.46788</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
         </is>
       </c>
     </row>
@@ -13458,12 +13458,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-H Zone</t>
+          <t>Daniel's Harbour Mine-J Zone</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>012I/06/Zn 008</t>
+          <t>012I/06/Zn 009</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13513,14 +13513,14 @@
         <v>29</v>
       </c>
       <c r="V181" t="n">
-        <v>50.29179</v>
+        <v>50.30247</v>
       </c>
       <c r="W181" t="n">
-        <v>-57.44599</v>
+        <v>-57.47459</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
         </is>
       </c>
     </row>
@@ -13530,12 +13530,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-F Zone</t>
+          <t>Daniel's Harbour Mine-M Zone</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>012I/06/Zn 006</t>
+          <t>012I/06/Zn 012</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13585,14 +13585,14 @@
         <v>29</v>
       </c>
       <c r="V182" t="n">
-        <v>50.29437</v>
+        <v>50.29514</v>
       </c>
       <c r="W182" t="n">
-        <v>-57.45374</v>
+        <v>-57.44013</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-L Zone</t>
+          <t>Browning Mine</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>012I/06/Zn 011</t>
+          <t>012H/10/Au 001</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13619,7 +13619,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lead, Dolomite, Zinc</t>
+          <t>Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13657,14 +13657,14 @@
         <v>29</v>
       </c>
       <c r="V183" t="n">
-        <v>50.27686</v>
+        <v>49.71799</v>
       </c>
       <c r="W183" t="n">
-        <v>-57.46788</v>
+        <v>-56.92565</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Gull Island Formation</t>
+          <t>Timmins No 6</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>001N/10/Fe 003</t>
+          <t>023J/14/Fe 021</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13801,14 +13801,14 @@
         <v>26</v>
       </c>
       <c r="V185" t="n">
-        <v>47.65193</v>
+        <v>54.90148</v>
       </c>
       <c r="W185" t="n">
-        <v>-52.95654</v>
+        <v>-67.09757999999999</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Dominion Formation</t>
+          <t>Timmins No 4</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>001N/10/Fe 001</t>
+          <t>023J/14/Fe 023</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -13873,14 +13873,14 @@
         <v>26</v>
       </c>
       <c r="V186" t="n">
-        <v>47.64164</v>
+        <v>54.89884</v>
       </c>
       <c r="W186" t="n">
-        <v>-52.95309</v>
+        <v>-67.10881000000001</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Scotia Formation</t>
+          <t>Fleming No 3</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>001N/10/Fe 002</t>
+          <t>023J/14/Fe 022</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13945,14 +13945,14 @@
         <v>26</v>
       </c>
       <c r="V187" t="n">
-        <v>47.64169</v>
+        <v>54.85836</v>
       </c>
       <c r="W187" t="n">
-        <v>-52.97639</v>
+        <v>-67.03167999999999</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
         </is>
       </c>
     </row>
@@ -13962,24 +13962,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Redmond No 2</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>023J/10/Fe 002</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14017,14 +14017,14 @@
         <v>26</v>
       </c>
       <c r="V188" t="n">
-        <v>54.69738</v>
+        <v>47.53392</v>
       </c>
       <c r="W188" t="n">
-        <v>-66.77224</v>
+        <v>-53.18293</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Grey Copper Mine</t>
+          <t>Dominion Formation</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>002E/11/Cu 001</t>
+          <t>001N/10/Fe 001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Iron, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14089,14 +14089,14 @@
         <v>26</v>
       </c>
       <c r="V189" t="n">
-        <v>49.5173</v>
+        <v>47.64164</v>
       </c>
       <c r="W189" t="n">
-        <v>-55.2721</v>
+        <v>-52.95309</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14106,24 +14106,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Redmond No 2</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>023J/10/Fe 002</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14161,14 +14161,14 @@
         <v>26</v>
       </c>
       <c r="V190" t="n">
-        <v>49.50376</v>
+        <v>54.69738</v>
       </c>
       <c r="W190" t="n">
-        <v>-55.21553</v>
+        <v>-66.77224</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14178,24 +14178,24 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Gull Island Formation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>001N/10/Fe 003</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -14233,14 +14233,14 @@
         <v>26</v>
       </c>
       <c r="V191" t="n">
-        <v>47.53392</v>
+        <v>47.65193</v>
       </c>
       <c r="W191" t="n">
-        <v>-53.18293</v>
+        <v>-52.95654</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -14250,12 +14250,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cliff Mine</t>
+          <t>Scotia Formation</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>012B/09/Fe 001</t>
+          <t>001N/10/Fe 002</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -14305,14 +14305,14 @@
         <v>26</v>
       </c>
       <c r="V192" t="n">
-        <v>48.54434</v>
+        <v>47.64169</v>
       </c>
       <c r="W192" t="n">
-        <v>-58.49915</v>
+        <v>-52.97639</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Skindles Mine</t>
+          <t>Timmins No 1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>012B/09/Fe 004</t>
+          <t>023J/14/Fe 018</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14377,14 +14377,14 @@
         <v>26</v>
       </c>
       <c r="V193" t="n">
-        <v>48.54069</v>
+        <v>54.88449</v>
       </c>
       <c r="W193" t="n">
-        <v>-58.48888</v>
+        <v>-67.08575</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
         </is>
       </c>
     </row>
@@ -14394,24 +14394,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Timmins No 2</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>023J/15/Fe 010</t>
+          <t>023J/14/Fe 019</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14449,14 +14449,14 @@
         <v>26</v>
       </c>
       <c r="V194" t="n">
-        <v>54.77437</v>
+        <v>54.89421</v>
       </c>
       <c r="W194" t="n">
-        <v>-66.82881</v>
+        <v>-67.08716</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14466,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ruth Lake No 7</t>
+          <t>Skindles Mine</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>023J/15/Fe 006</t>
+          <t>012B/09/Fe 004</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
         <v>26</v>
       </c>
       <c r="V195" t="n">
-        <v>54.80557</v>
+        <v>48.54069</v>
       </c>
       <c r="W195" t="n">
-        <v>-66.90618000000001</v>
+        <v>-58.48888</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14538,24 +14538,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Ruth Lake No 5</t>
+          <t>Cliff Mine</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>023J/15/Fe 007</t>
+          <t>012B/09/Fe 001</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14593,14 +14593,14 @@
         <v>26</v>
       </c>
       <c r="V196" t="n">
-        <v>54.80503</v>
+        <v>48.54434</v>
       </c>
       <c r="W196" t="n">
-        <v>-66.88023</v>
+        <v>-58.49915</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ruth Lake No 6</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>023J/15/Fe 008</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -14665,14 +14665,14 @@
         <v>26</v>
       </c>
       <c r="V197" t="n">
-        <v>54.80104</v>
+        <v>49.50376</v>
       </c>
       <c r="W197" t="n">
-        <v>-66.87327999999999</v>
+        <v>-55.21553</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14682,12 +14682,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ruth Lake No 9</t>
+          <t>Grey Copper Mine</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>023J/15/Fe 005</t>
+          <t>002E/11/Cu 001</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Iron, Copper</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14737,14 +14737,14 @@
         <v>26</v>
       </c>
       <c r="V198" t="n">
-        <v>54.80033</v>
+        <v>49.5173</v>
       </c>
       <c r="W198" t="n">
-        <v>-66.89447</v>
+        <v>-55.2721</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14754,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ruth Lake No 1</t>
+          <t>Lorraine Mine</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>023J/15/Fe 002</t>
+          <t>023G/02/Fe 004</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14809,14 +14809,14 @@
         <v>26</v>
       </c>
       <c r="V199" t="n">
-        <v>54.79145</v>
+        <v>53.06833</v>
       </c>
       <c r="W199" t="n">
-        <v>-66.85449</v>
+        <v>-66.94949</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14826,24 +14826,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Wishart No 1 (Wishart Mine)</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>023J/15/Fe 003</t>
+          <t>023J/15/Fe 010</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14881,14 +14881,14 @@
         <v>26</v>
       </c>
       <c r="V200" t="n">
-        <v>54.76166</v>
+        <v>54.77437</v>
       </c>
       <c r="W200" t="n">
-        <v>-66.88793</v>
+        <v>-66.82881</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Wishart No 2 (Wishart Mine)</t>
+          <t>Smallwood Mine</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>023J/15/Fe 004</t>
+          <t>023G/02/Fe 001</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14953,14 +14953,14 @@
         <v>26</v>
       </c>
       <c r="V201" t="n">
-        <v>54.7654</v>
+        <v>53.03718</v>
       </c>
       <c r="W201" t="n">
-        <v>-66.9067</v>
+        <v>-66.93694000000001</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14970,12 +14970,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ruth Lake No 3</t>
+          <t>Ruth Lake No 1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>023J/15/Fe 001</t>
+          <t>023J/15/Fe 002</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
         <v>26</v>
       </c>
       <c r="V202" t="n">
-        <v>54.80404</v>
+        <v>54.79145</v>
       </c>
       <c r="W202" t="n">
-        <v>-66.87016</v>
+        <v>-66.85449</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -15042,24 +15042,24 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Lorraine Mine</t>
+          <t>Wishart No 1 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>023G/02/Fe 004</t>
+          <t>023J/15/Fe 003</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15097,14 +15097,14 @@
         <v>26</v>
       </c>
       <c r="V203" t="n">
-        <v>53.06833</v>
+        <v>54.76166</v>
       </c>
       <c r="W203" t="n">
-        <v>-66.94949</v>
+        <v>-66.88793</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -15114,12 +15114,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Smallwood Mine</t>
+          <t>Ruth Lake No 3</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>023G/02/Fe 001</t>
+          <t>023J/15/Fe 001</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -15169,14 +15169,14 @@
         <v>26</v>
       </c>
       <c r="V204" t="n">
-        <v>53.03718</v>
+        <v>54.80404</v>
       </c>
       <c r="W204" t="n">
-        <v>-66.93694000000001</v>
+        <v>-66.87016</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15186,24 +15186,24 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Timmins No 1</t>
+          <t>Wishart No 2 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>023J/14/Fe 018</t>
+          <t>023J/15/Fe 004</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -15241,14 +15241,14 @@
         <v>26</v>
       </c>
       <c r="V205" t="n">
-        <v>54.88449</v>
+        <v>54.7654</v>
       </c>
       <c r="W205" t="n">
-        <v>-67.08575</v>
+        <v>-66.9067</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Timmins No 2</t>
+          <t>Ruth Lake No 9</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>023J/14/Fe 019</t>
+          <t>023J/15/Fe 005</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -15313,14 +15313,14 @@
         <v>26</v>
       </c>
       <c r="V206" t="n">
-        <v>54.89421</v>
+        <v>54.80033</v>
       </c>
       <c r="W206" t="n">
-        <v>-67.08716</v>
+        <v>-66.89447</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15330,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timmins No 6</t>
+          <t>Ruth Lake No 7</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>023J/14/Fe 021</t>
+          <t>023J/15/Fe 006</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15385,14 +15385,14 @@
         <v>26</v>
       </c>
       <c r="V207" t="n">
-        <v>54.90148</v>
+        <v>54.80557</v>
       </c>
       <c r="W207" t="n">
-        <v>-67.09757999999999</v>
+        <v>-66.90618000000001</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -15402,24 +15402,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Fleming No 3</t>
+          <t>Ruth Lake No 5</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>023J/14/Fe 022</t>
+          <t>023J/15/Fe 007</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15457,14 +15457,14 @@
         <v>26</v>
       </c>
       <c r="V208" t="n">
-        <v>54.85836</v>
+        <v>54.80503</v>
       </c>
       <c r="W208" t="n">
-        <v>-67.03167999999999</v>
+        <v>-66.88023</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -15474,24 +15474,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Timmins No 4</t>
+          <t>Ruth Lake No 6</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>023J/14/Fe 023</t>
+          <t>023J/15/Fe 008</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15529,14 +15529,14 @@
         <v>26</v>
       </c>
       <c r="V209" t="n">
-        <v>54.89884</v>
+        <v>54.80104</v>
       </c>
       <c r="W209" t="n">
-        <v>-67.10881000000001</v>
+        <v>-66.87327999999999</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Two Tom Lake</t>
+          <t>Horseshoe Zone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>013L/01/REE001</t>
+          <t>002E/02/Au 039</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>44</v>
       </c>
       <c r="V2" t="n">
-        <v>54.21359</v>
+        <v>49.01341</v>
       </c>
       <c r="W2" t="n">
-        <v>-62.14192</v>
+        <v>-54.81741</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deer Cove Main Zone</t>
+          <t>Deep Fox</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>012I/01/Au 001</t>
+          <t>003D/05/Ree007</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>50.01619</v>
+        <v>52.3805</v>
       </c>
       <c r="W3" t="n">
-        <v>-56.04389</v>
+        <v>-55.64987</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Far Eastern Deeps</t>
+          <t>Mart Lake Graphite</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>014D/08/Ni 013</t>
+          <t>023B/14/Gf 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper, Zinc, Silver, Graphite</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>56.32109</v>
+        <v>52.8283</v>
       </c>
       <c r="W4" t="n">
-        <v>-62.06064</v>
+        <v>-67.01484000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Windowglass Hill - Main Zone</t>
+          <t>Deer Cove Main Zone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>011O/10/Au 001</t>
+          <t>012I/01/Au 001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,14 +841,14 @@
         <v>44</v>
       </c>
       <c r="V5" t="n">
-        <v>47.74279</v>
+        <v>50.01619</v>
       </c>
       <c r="W5" t="n">
-        <v>-58.95727</v>
+        <v>-56.04389</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Keats</t>
+          <t>Windowglass Hill - Main Zone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>002D/15/Au 010</t>
+          <t>011O/10/Au 001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>44</v>
       </c>
       <c r="V6" t="n">
-        <v>48.97891</v>
+        <v>47.74279</v>
       </c>
       <c r="W6" t="n">
-        <v>-54.8402</v>
+        <v>-58.95727</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Keats South</t>
+          <t>Bull Road Showing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>002D/15/Au 060</t>
+          <t>002E/12/Zn 007</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver, Lead, Antimony, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>44</v>
       </c>
       <c r="V7" t="n">
-        <v>48.97791</v>
+        <v>49.51431</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.84407</v>
+        <v>-55.7118</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Saddle Zone</t>
+          <t>Keats</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>002E/02/Au 038</t>
+          <t>002D/15/Au 010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>44</v>
       </c>
       <c r="V8" t="n">
-        <v>49.00899</v>
+        <v>48.97891</v>
       </c>
       <c r="W8" t="n">
-        <v>-54.81554</v>
+        <v>-54.8402</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20010</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deep Fox</t>
+          <t>Keats South</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>003D/05/Ree007</t>
+          <t>002D/15/Au 060</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rare Earth Elements</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>44</v>
       </c>
       <c r="V9" t="n">
-        <v>52.3805</v>
+        <v>48.97791</v>
       </c>
       <c r="W9" t="n">
-        <v>-55.64987</v>
+        <v>-54.84407</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=003D%2F05%2FRee007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F15%2FAu%20060</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Horseshoe Zone</t>
+          <t>Voisey's Bay, South Eastern Deeps</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>002E/02/Au 039</t>
+          <t>014D/08/Ni 017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>49.01341</v>
+        <v>56.31756</v>
       </c>
       <c r="W10" t="n">
-        <v>-54.81741</v>
+        <v>-62.06953</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Moly Brook</t>
+          <t>Area 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>011P/11/Mo 001</t>
+          <t>013K/07/U  007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Copper, Vanadium, Uranium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1273,14 +1273,14 @@
         <v>44</v>
       </c>
       <c r="V11" t="n">
-        <v>47.61683</v>
+        <v>54.46751</v>
       </c>
       <c r="W11" t="n">
-        <v>-57.1034</v>
+        <v>-60.98105</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bull Road Showing</t>
+          <t>Moly Brook</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>002E/12/Zn 007</t>
+          <t>011P/11/Mo 001</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Antimony, Zinc</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>44</v>
       </c>
       <c r="V12" t="n">
-        <v>49.51431</v>
+        <v>47.61683</v>
       </c>
       <c r="W12" t="n">
-        <v>-55.7118</v>
+        <v>-57.1034</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FMo%20001</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Voisey's Bay, North Eastern Deeps</t>
+          <t>Voisey's Bay, Far Eastern Deeps</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>014D/08/Ni 011</t>
+          <t>014D/08/Ni 013</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1417,14 +1417,14 @@
         <v>44</v>
       </c>
       <c r="V13" t="n">
-        <v>56.32929</v>
+        <v>56.32109</v>
       </c>
       <c r="W13" t="n">
-        <v>-62.07733</v>
+        <v>-62.06064</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20013</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mart Lake Graphite</t>
+          <t>Voisey's Bay, North Eastern Deeps</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>023B/14/Gf 001</t>
+          <t>014D/08/Ni 011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Graphite</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>44</v>
       </c>
       <c r="V14" t="n">
-        <v>52.8283</v>
+        <v>56.32929</v>
       </c>
       <c r="W14" t="n">
-        <v>-67.01484000000001</v>
+        <v>-62.07733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FGf%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20011</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Area 1</t>
+          <t>Voisey's Bay, Southeast Extension</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>013K/07/U  007</t>
+          <t>014D/08/Ni 012</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Vanadium, Uranium</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1561,14 +1561,14 @@
         <v>44</v>
       </c>
       <c r="V15" t="n">
-        <v>54.46751</v>
+        <v>56.32489</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.98105</v>
+        <v>-62.08804</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F07%2FU%20%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20012</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Southeast Extension</t>
+          <t>Saddle Zone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>014D/08/Ni 012</t>
+          <t>002E/02/Au 038</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>44</v>
       </c>
       <c r="V16" t="n">
-        <v>56.32489</v>
+        <v>49.00899</v>
       </c>
       <c r="W16" t="n">
-        <v>-62.08804</v>
+        <v>-54.81554</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F02%2FAu%20038</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Voisey's Bay, South Eastern Deeps</t>
+          <t>Two Tom Lake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>014D/08/Ni 017</t>
+          <t>013L/01/REE001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Rare Earth Elements</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>44</v>
       </c>
       <c r="V17" t="n">
-        <v>56.31756</v>
+        <v>54.21359</v>
       </c>
       <c r="W17" t="n">
-        <v>-62.06953</v>
+        <v>-62.14192</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20017</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FREE001</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Strickland - Silver Hill Zone</t>
+          <t>Road Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>011O/16/Zn 002</t>
+          <t>012H/15/Au 011</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1777,14 +1777,14 @@
         <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>47.81</v>
+        <v>49.88465</v>
       </c>
       <c r="W18" t="n">
-        <v>-58.2985</v>
+        <v>-56.83885</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit 41 Zone</t>
+          <t>Apsy Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>011O/15/Au 002</t>
+          <t>012H/15/Au 014</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>43</v>
       </c>
       <c r="V19" t="n">
-        <v>47.75858</v>
+        <v>49.89471</v>
       </c>
       <c r="W19" t="n">
-        <v>-58.92331</v>
+        <v>-56.82917</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Point Leamington Deposit</t>
+          <t>Cape Ray Gold Deposit #4 Zone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>002E/05/Zn 001</t>
+          <t>011O/15/Au 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead, Zinc</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>43</v>
       </c>
       <c r="V22" t="n">
-        <v>49.27672</v>
+        <v>47.76081</v>
       </c>
       <c r="W22" t="n">
-        <v>-55.63152</v>
+        <v>-58.91872</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apsy Zone</t>
+          <t>Cape Ray Gold Deposit 41 Zone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>012H/15/Au 014</t>
+          <t>011O/15/Au 002</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Silver, Copper, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>43</v>
       </c>
       <c r="V23" t="n">
-        <v>49.89471</v>
+        <v>47.75858</v>
       </c>
       <c r="W23" t="n">
-        <v>-56.82917</v>
+        <v>-58.92331</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Road Zone</t>
+          <t>Point Leamington Deposit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>012H/15/Au 011</t>
+          <t>002E/05/Zn 001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Silver, Copper, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>43</v>
       </c>
       <c r="V24" t="n">
-        <v>49.88465</v>
+        <v>49.27672</v>
       </c>
       <c r="W24" t="n">
-        <v>-56.83885</v>
+        <v>-55.63152</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>51 Zone</t>
+          <t>Strickland - Silver Hill Zone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>011O/15/Au 003</t>
+          <t>011O/16/Zn 002</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Zinc, Gold</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>47.75077</v>
+        <v>47.81</v>
       </c>
       <c r="W25" t="n">
-        <v>-58.93823</v>
+        <v>-58.2985</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cape Ray Gold Deposit #4 Zone</t>
+          <t>51 Zone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>011O/15/Au 001</t>
+          <t>011O/15/Au 003</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2353,14 +2353,14 @@
         <v>43</v>
       </c>
       <c r="V26" t="n">
-        <v>47.76081</v>
+        <v>47.75077</v>
       </c>
       <c r="W26" t="n">
-        <v>-58.91872</v>
+        <v>-58.93823</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rainbow Deposit</t>
+          <t>Gear Lake</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>013J/12/U  008</t>
+          <t>013J/13/U  010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2416,23 +2416,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>42</v>
       </c>
       <c r="V27" t="n">
-        <v>54.56417</v>
+        <v>54.94329</v>
       </c>
       <c r="W27" t="n">
-        <v>-59.99369</v>
+        <v>-59.54386</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Michelin Deposit</t>
+          <t>Nash Lake (Main Zone)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>013J/12/U  001</t>
+          <t>013J/13/U  006</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2497,14 +2497,14 @@
         <v>42</v>
       </c>
       <c r="V28" t="n">
-        <v>54.58562</v>
+        <v>54.91032</v>
       </c>
       <c r="W28" t="n">
-        <v>-59.98056</v>
+        <v>-59.62004</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gear Lake</t>
+          <t>Aillik Prospect</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>013J/13/U  010</t>
+          <t>013O/03/Mo 003</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Uranium, Fluorine, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>42</v>
       </c>
       <c r="V29" t="n">
-        <v>54.94329</v>
+        <v>55.21102</v>
       </c>
       <c r="W29" t="n">
-        <v>-59.54386</v>
+        <v>-59.16645</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013O%2F03%2FMo%20003</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aillik Prospect</t>
+          <t>Kitts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>013O/03/Mo 003</t>
+          <t>013J/14/U  001</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Uranium, Fluorine, Copper, Molybdenum</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2632,23 +2632,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U30" t="n">
         <v>42</v>
       </c>
       <c r="V30" t="n">
-        <v>55.21102</v>
+        <v>54.99779</v>
       </c>
       <c r="W30" t="n">
-        <v>-59.16645</v>
+        <v>-59.4872</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013O%2F03%2FMo%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kitts</t>
+          <t>Jacques Lake</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>013J/14/U  001</t>
+          <t>013J/12/U  018</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2704,23 +2704,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T31" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U31" t="n">
         <v>42</v>
       </c>
       <c r="V31" t="n">
-        <v>54.99779</v>
+        <v>54.71754</v>
       </c>
       <c r="W31" t="n">
-        <v>-59.4872</v>
+        <v>-59.59268</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F14%2FU%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Two Time</t>
+          <t>Michelin Deposit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>013K/11/U  005</t>
+          <t>013J/12/U  001</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2785,14 +2785,14 @@
         <v>42</v>
       </c>
       <c r="V32" t="n">
-        <v>54.56554</v>
+        <v>54.58562</v>
       </c>
       <c r="W32" t="n">
-        <v>-61.17152</v>
+        <v>-59.98056</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20001</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nash Lake (Main Zone)</t>
+          <t>Rainbow Deposit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>013J/13/U  006</t>
+          <t>013J/12/U  008</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2848,23 +2848,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U33" t="n">
         <v>42</v>
       </c>
       <c r="V33" t="n">
-        <v>54.91032</v>
+        <v>54.56417</v>
       </c>
       <c r="W33" t="n">
-        <v>-59.62004</v>
+        <v>-59.99369</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20008</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2874,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jacques Lake</t>
+          <t>Two Time</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>013J/12/U  018</t>
+          <t>013K/11/U  005</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2929,14 +2929,14 @@
         <v>42</v>
       </c>
       <c r="V34" t="n">
-        <v>54.71754</v>
+        <v>54.56554</v>
       </c>
       <c r="W34" t="n">
-        <v>-59.59268</v>
+        <v>-61.17152</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013K%2F11%2FU%20%20005</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mann #1</t>
+          <t>Springer's Hill-Main Showing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>013L/01/Be 001</t>
+          <t>012B/16/Cr 002</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Niobium, Uranium, Zinc, Beryllium</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>41</v>
       </c>
       <c r="V35" t="n">
-        <v>54.23929</v>
+        <v>48.7927</v>
       </c>
       <c r="W35" t="n">
-        <v>-62.3924</v>
+        <v>-58.44526</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Springer's Hill-Main Showing</t>
+          <t>Mann #1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>012B/16/Cr 002</t>
+          <t>013L/01/Be 001</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Niobium, Uranium, Zinc, Beryllium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>41</v>
       </c>
       <c r="V36" t="n">
-        <v>48.7927</v>
+        <v>54.23929</v>
       </c>
       <c r="W36" t="n">
-        <v>-58.44526</v>
+        <v>-62.3924</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F16%2FCr%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013L%2F01%2FBe%20001</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Norsk South Block</t>
+          <t>Lewis Brook Mine</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>012B/10/Dol004</t>
+          <t>012B/15/Asb001</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>37</v>
       </c>
       <c r="V39" t="n">
-        <v>48.52445</v>
+        <v>48.77071</v>
       </c>
       <c r="W39" t="n">
-        <v>-58.99684</v>
+        <v>-58.56548</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Burnt Lake North (Main Zone)</t>
+          <t>Beaver Dam</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>013J/12/U  012</t>
+          <t>012H/15/Au 018</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fluorine, Zinc, Lead, Molybdenum, Gold, Silver, Uranium</t>
+          <t>Arsenic, Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>37</v>
       </c>
       <c r="V40" t="n">
-        <v>54.63965</v>
+        <v>49.86141</v>
       </c>
       <c r="W40" t="n">
-        <v>-59.70939</v>
+        <v>-56.85295</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Round Pond Deposit</t>
+          <t>Strange Lake</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>012P/08/Zn 015</t>
+          <t>024A/08/Ree001</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fluorine, Lead, Zinc</t>
+          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>37</v>
       </c>
       <c r="V41" t="n">
-        <v>51.25735</v>
+        <v>56.31656</v>
       </c>
       <c r="W41" t="n">
-        <v>-56.26701</v>
+        <v>-64.12678</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Norsk North Block</t>
+          <t>Grey River Tungsten</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>012B/10/Dol003</t>
+          <t>011P/11/W  001</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Magnesium, Dolomite</t>
+          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>37</v>
       </c>
       <c r="V42" t="n">
-        <v>48.53397</v>
+        <v>47.59343</v>
       </c>
       <c r="W42" t="n">
-        <v>-58.9773</v>
+        <v>-57.10342</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Porcupine Strand North Beach</t>
+          <t>Inda Lake</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>013I/03/Ti 001</t>
+          <t>013J/13/U  009</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
+          <t>Molybdenum, Copper, Uranium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>37</v>
       </c>
       <c r="V43" t="n">
-        <v>54.03818</v>
+        <v>54.92456</v>
       </c>
       <c r="W43" t="n">
-        <v>-57.31912</v>
+        <v>-59.5807</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mount Margaret Pond Vein</t>
+          <t>Burnt Lake North (Main Zone)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>001L/14/Fl 039</t>
+          <t>013J/12/U  012</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Fluorine, Zinc, Lead, Molybdenum, Gold, Silver, Uranium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>37</v>
       </c>
       <c r="V44" t="n">
-        <v>46.95861</v>
+        <v>54.63965</v>
       </c>
       <c r="W44" t="n">
-        <v>-55.38707</v>
+        <v>-59.70939</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20039</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F12%2FU%20%20012</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Inda Lake</t>
+          <t>Round Pond Deposit</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>013J/13/U  009</t>
+          <t>012P/08/Zn 015</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Uranium</t>
+          <t>Fluorine, Lead, Zinc</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>37</v>
       </c>
       <c r="V45" t="n">
-        <v>54.92456</v>
+        <v>51.25735</v>
       </c>
       <c r="W45" t="n">
-        <v>-59.5807</v>
+        <v>-56.26701</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013J%2F13%2FU%20%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012P%2F08%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Romaines Brook</t>
+          <t>Norsk North Block</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>012B/10/Gyp001</t>
+          <t>012B/10/Dol003</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Magnesium, Anhydrite, Gypsum</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>37</v>
       </c>
       <c r="V46" t="n">
-        <v>48.55534</v>
+        <v>48.53397</v>
       </c>
       <c r="W46" t="n">
-        <v>-58.66751</v>
+        <v>-58.9773</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol003</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Norsk South Block</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>012B/10/Dol004</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Magnesium, Dolomite</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3865,14 +3865,14 @@
         <v>37</v>
       </c>
       <c r="V47" t="n">
-        <v>48.39536</v>
+        <v>48.52445</v>
       </c>
       <c r="W47" t="n">
-        <v>-58.42046</v>
+        <v>-58.99684</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FDol004</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lewis Brook Mine</t>
+          <t>Porcupine Strand North Beach</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>012B/15/Asb001</t>
+          <t>013I/03/Ti 001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Garnet, Iron, Niobium, Tantalum, Titanium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>37</v>
       </c>
       <c r="V48" t="n">
-        <v>48.77071</v>
+        <v>54.03818</v>
       </c>
       <c r="W48" t="n">
-        <v>-58.56548</v>
+        <v>-57.31912</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FAsb001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013I%2F03%2FTi%20001</t>
         </is>
       </c>
     </row>
@@ -3954,24 +3954,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Grey River Tungsten</t>
+          <t>Deer Cove Talc Zone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>011P/11/W  001</t>
+          <t>012I/01/Tlc001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Zinc, Lead, Bismuth, Silver, Gold, Tungsten</t>
+          <t>Magnesium, Talc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4009,14 +4009,14 @@
         <v>37</v>
       </c>
       <c r="V49" t="n">
-        <v>47.59343</v>
+        <v>50.01534</v>
       </c>
       <c r="W49" t="n">
-        <v>-57.10342</v>
+        <v>-56.04949</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011P%2F11%2FW%20%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Strange Lake</t>
+          <t>Sheep Brook</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>024A/08/Ree001</t>
+          <t>012B/08/Gyp001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zirconium, Beryllium, Niobium, Uranium, Thorium, Fluorine, Titanium, Yttrium, Rare Earth Elements</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>56.31656</v>
+        <v>48.39536</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.12678</v>
+        <v>-58.42046</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=024A%2F08%2FRee001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Beaver Dam</t>
+          <t>Romaines Brook</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>012H/15/Au 018</t>
+          <t>012B/10/Gyp001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Arsenic, Gold</t>
+          <t>Magnesium, Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>49.86141</v>
+        <v>48.55534</v>
       </c>
       <c r="W51" t="n">
-        <v>-56.85295</v>
+        <v>-58.66751</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F15%2FAu%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FGyp001</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deer Cove Talc Zone</t>
+          <t>Mount Margaret Pond Vein</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012I/01/Tlc001</t>
+          <t>001L/14/Fl 039</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Magnesium, Talc</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>50.01534</v>
+        <v>46.95861</v>
       </c>
       <c r="W53" t="n">
-        <v>-56.04949</v>
+        <v>-55.38707</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F01%2FTlc001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20039</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Copper Creek BV</t>
+          <t>Ackley City</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>012H/16/Cu 040</t>
+          <t>001M/11/Mo 002</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Zinc, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4369,14 +4369,14 @@
         <v>36</v>
       </c>
       <c r="V54" t="n">
-        <v>49.91887</v>
+        <v>47.69347</v>
       </c>
       <c r="W54" t="n">
-        <v>-56.20986</v>
+        <v>-55.20716</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ackley City</t>
+          <t>Copper Creek BV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>001M/11/Mo 002</t>
+          <t>012H/16/Cu 040</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Molybdenum</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>36</v>
       </c>
       <c r="V56" t="n">
-        <v>47.69347</v>
+        <v>49.91887</v>
       </c>
       <c r="W56" t="n">
-        <v>-55.20716</v>
+        <v>-56.20986</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F11%2FMo%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20040</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Strickland - Main Zone</t>
+          <t>Jaclyn Main - Golden Promise</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>011O/16/Zn 001</t>
+          <t>012A/16/Au 002</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lead, Copper, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>35</v>
       </c>
       <c r="V57" t="n">
-        <v>47.80818</v>
+        <v>48.90572</v>
       </c>
       <c r="W57" t="n">
-        <v>-58.29993</v>
+        <v>-56.15002</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4602,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Voisey's Bay, Ovoid</t>
+          <t>Hope Brook</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>014D/08/Ni 001</t>
+          <t>011O/09/Au 003</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Nickel</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4657,14 +4657,14 @@
         <v>35</v>
       </c>
       <c r="V58" t="n">
-        <v>56.33134</v>
+        <v>47.73806</v>
       </c>
       <c r="W58" t="n">
-        <v>-62.09706</v>
+        <v>-58.09531</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
         </is>
       </c>
     </row>
@@ -4674,29 +4674,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Strickland - Main Zone</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>011O/16/Zn 001</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Copper, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I59" t="b">
@@ -4729,14 +4729,14 @@
         <v>35</v>
       </c>
       <c r="V59" t="n">
-        <v>47.4438</v>
+        <v>47.80818</v>
       </c>
       <c r="W59" t="n">
-        <v>-54.4169</v>
+        <v>-58.29993</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Voisey's Bay, Ovoid</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>014D/08/Ni 001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Cobalt, Nickel</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>35</v>
       </c>
       <c r="V60" t="n">
-        <v>47.4063</v>
+        <v>56.33134</v>
       </c>
       <c r="W60" t="n">
-        <v>-52.70699</v>
+        <v>-62.09706</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=014D%2F08%2FNi%20001</t>
         </is>
       </c>
     </row>
@@ -4818,24 +4818,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Argyle</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>012H/16/Au 083</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>49.97838</v>
+        <v>47.4063</v>
       </c>
       <c r="W61" t="n">
-        <v>-56.05952</v>
+        <v>-52.70699</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -4890,29 +4890,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sleepy Hollow</t>
+          <t>Strickland - Copper Zone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>002E/12/Cu 031</t>
+          <t>011O/16/Cu 001</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I62" t="b">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>49.59747</v>
+        <v>47.80365</v>
       </c>
       <c r="W62" t="n">
-        <v>-55.94735</v>
+        <v>-58.30275</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -4962,29 +4962,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jaclyn Main - Golden Promise</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>012A/16/Au 002</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I63" t="b">
@@ -5017,14 +5017,14 @@
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>48.90572</v>
+        <v>47.4438</v>
       </c>
       <c r="W63" t="n">
-        <v>-56.15002</v>
+        <v>-54.4169</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012A%2F16%2FAu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5034,29 +5034,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hope Brook</t>
+          <t>H Brook Showing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>011O/09/Au 003</t>
+          <t>011O/15/Au 004</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>47.73806</v>
+        <v>47.7624</v>
       </c>
       <c r="W64" t="n">
-        <v>-58.09531</v>
+        <v>-58.91357</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F09%2FAu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
         </is>
       </c>
     </row>
@@ -5106,24 +5106,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Betts Cove Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>002E/13/Cu 002</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>48.5353</v>
+        <v>49.81179</v>
       </c>
       <c r="W65" t="n">
-        <v>-58.48804</v>
+        <v>-55.80608</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ming West</t>
+          <t>Tilt Cove Mine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>012H/16/Cu 029</t>
+          <t>002E/13/Cu 001</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Nickel, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>49.9148</v>
+        <v>49.88214</v>
       </c>
       <c r="W66" t="n">
-        <v>-56.08996</v>
+        <v>-55.62813</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Terra Nova Mine</t>
+          <t>Nugget Pond</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>012H/16/Cu 004</t>
+          <t>002E/13/Au 001</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>49.92133</v>
+        <v>49.84502</v>
       </c>
       <c r="W67" t="n">
-        <v>-56.22896</v>
+        <v>-55.77536</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -5322,24 +5322,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pine Cove</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>012H/16/Au 023</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>49.96066</v>
+        <v>48.5353</v>
       </c>
       <c r="W68" t="n">
-        <v>-56.13074</v>
+        <v>-58.48804</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -5394,24 +5394,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tilt Cove Mine</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>002E/13/Cu 001</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Silver, Zinc, Copper</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>49.88214</v>
+        <v>49.19579</v>
       </c>
       <c r="W69" t="n">
-        <v>-55.62813</v>
+        <v>-57.84974</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -5466,29 +5466,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>H Brook Showing</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>011O/15/Au 004</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>47.7624</v>
+        <v>52.961</v>
       </c>
       <c r="W70" t="n">
-        <v>-58.91357</v>
+        <v>-66.81446</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F15%2FAu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Betts Cove Mine</t>
+          <t>Argyle</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>002E/13/Cu 002</t>
+          <t>012H/16/Au 083</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5593,14 +5593,14 @@
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>49.81179</v>
+        <v>49.97838</v>
       </c>
       <c r="W71" t="n">
-        <v>-55.80608</v>
+        <v>-56.05952</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20083</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nugget Pond</t>
+          <t>Ming West</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>002E/13/Au 001</t>
+          <t>012H/16/Cu 029</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5656,23 +5656,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U72" t="n">
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>49.84502</v>
+        <v>49.9148</v>
       </c>
       <c r="W72" t="n">
-        <v>-55.77536</v>
+        <v>-56.08996</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20029</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Goldenville</t>
+          <t>Terra Nova Mine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>012H/16/Au 033</t>
+          <t>012H/16/Cu 004</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Copper, Iron, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5728,23 +5728,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>49.99193</v>
+        <v>49.92133</v>
       </c>
       <c r="W73" t="n">
-        <v>-56.05735</v>
+        <v>-56.22896</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>Goldenville</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>012H/16/Au 033</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Copper, Iron, Gold</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5800,23 +5800,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U74" t="n">
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>49.19579</v>
+        <v>49.99193</v>
       </c>
       <c r="W74" t="n">
-        <v>-57.84974</v>
+        <v>-56.05735</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20033</t>
         </is>
       </c>
     </row>
@@ -5826,29 +5826,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Strickland - Copper Zone</t>
+          <t>Turk's Gut</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>011O/16/Cu 001</t>
+          <t>001N/11/Cu 001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>47.80365</v>
+        <v>47.50226</v>
       </c>
       <c r="W75" t="n">
-        <v>-58.30275</v>
+        <v>-53.20074</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=011O%2F16%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Turk's Gut</t>
+          <t>Sleepy Hollow</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>001N/11/Cu 001</t>
+          <t>002E/12/Cu 031</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>47.50226</v>
+        <v>49.59747</v>
       </c>
       <c r="W76" t="n">
-        <v>-53.20074</v>
+        <v>-55.94735</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20031</t>
         </is>
       </c>
     </row>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>Pine Cove</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>012H/16/Au 023</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>52.961</v>
+        <v>49.96066</v>
       </c>
       <c r="W77" t="n">
-        <v>-66.81446</v>
+        <v>-56.13074</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20023</t>
         </is>
       </c>
     </row>
@@ -6042,12 +6042,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tilt Cove/East Mine/Upper Dump</t>
+          <t>Miles Cove Mine</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>002E/13/Au 028</t>
+          <t>002E/12/Cu 012</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Silver, Nickel, Copper, Zinc, Gold</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6097,14 +6097,14 @@
         <v>34</v>
       </c>
       <c r="V78" t="n">
-        <v>49.88512</v>
+        <v>49.53936</v>
       </c>
       <c r="W78" t="n">
-        <v>-55.62192</v>
+        <v>-55.79062</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Crescent Lake Mine</t>
+          <t>Stog'er Tight</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>002E/05/Cu 013</t>
+          <t>012H/16/Au 041</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Copper</t>
+          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>34</v>
       </c>
       <c r="V79" t="n">
-        <v>49.48531</v>
+        <v>49.9661</v>
       </c>
       <c r="W79" t="n">
-        <v>-55.84455</v>
+        <v>-56.07765</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FCu%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
         </is>
       </c>
     </row>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Stog'er Tight</t>
+          <t>Crescent Lake Mine</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>012H/16/Au 041</t>
+          <t>002E/05/Cu 013</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Silver, Copper, Molybdenum, Zinc, Gold</t>
+          <t>Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6313,14 +6313,14 @@
         <v>34</v>
       </c>
       <c r="V81" t="n">
-        <v>49.9661</v>
+        <v>49.48531</v>
       </c>
       <c r="W81" t="n">
-        <v>-56.07765</v>
+        <v>-55.84455</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAu%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F05%2FCu%20013</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Miles Cove Mine</t>
+          <t>Tilt Cove/East Mine/Upper Dump</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>002E/12/Cu 012</t>
+          <t>002E/13/Au 028</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Silver, Nickel, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6385,14 +6385,14 @@
         <v>34</v>
       </c>
       <c r="V82" t="n">
-        <v>49.53936</v>
+        <v>49.88512</v>
       </c>
       <c r="W82" t="n">
-        <v>-55.79062</v>
+        <v>-55.62192</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F13%2FAu%20028</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blow-Me-Down Chromite #1</t>
+          <t>Upper Drill Brook Mine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>012G/01/Cr 001</t>
+          <t>012B/09/Fe 002</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6520,23 +6520,23 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T84" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U84" t="n">
         <v>33</v>
       </c>
       <c r="V84" t="n">
-        <v>49.01096</v>
+        <v>48.53533</v>
       </c>
       <c r="W84" t="n">
-        <v>-58.24371</v>
+        <v>-58.48601</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Upper Drill Brook Mine</t>
+          <t>Blow-Me-Down Chromite #1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>012B/09/Fe 002</t>
+          <t>012G/01/Cr 001</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Titanium, Vanadium, Molybdenum, Copper, Iron</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6592,23 +6592,23 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T85" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U85" t="n">
         <v>33</v>
       </c>
       <c r="V85" t="n">
-        <v>48.53533</v>
+        <v>49.01096</v>
       </c>
       <c r="W85" t="n">
-        <v>-58.48601</v>
+        <v>-58.24371</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sheps Lake</t>
+          <t>Wabush No. 6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>023J/11/Fe 001</t>
+          <t>023G/02/Fe 006</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6673,14 +6673,14 @@
         <v>31</v>
       </c>
       <c r="V86" t="n">
-        <v>54.73475</v>
+        <v>53.01798</v>
       </c>
       <c r="W86" t="n">
-        <v>-67.06362</v>
+        <v>-66.89297999999999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -6690,24 +6690,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Neal 1</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>023B/14/Fe 008</t>
+          <t>023B/14/Fe 028</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6745,14 +6745,14 @@
         <v>31</v>
       </c>
       <c r="V87" t="n">
-        <v>52.95013</v>
+        <v>52.94868</v>
       </c>
       <c r="W87" t="n">
-        <v>-67.15191</v>
+        <v>-67.01146</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -6762,24 +6762,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sawyer Lake</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>023B/14/Fe 020</t>
+          <t>023I/05/Fe 001</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>31</v>
       </c>
       <c r="V88" t="n">
-        <v>52.83351</v>
+        <v>54.45206</v>
       </c>
       <c r="W88" t="n">
-        <v>-67.0311</v>
+        <v>-65.98627</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6834,24 +6834,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mills Lake</t>
+          <t>Howells River West Zone A</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>023B/14/Fe 002</t>
+          <t>023J/14/Fe 001</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>31</v>
       </c>
       <c r="V89" t="n">
-        <v>52.79808</v>
+        <v>54.90958</v>
       </c>
       <c r="W89" t="n">
-        <v>-67.00413</v>
+        <v>-67.26052</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6906,24 +6906,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Howells River West Zone A</t>
+          <t>Sheps Lake</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>023J/14/Fe 001</t>
+          <t>023J/11/Fe 001</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>31</v>
       </c>
       <c r="V90" t="n">
-        <v>54.90958</v>
+        <v>54.73475</v>
       </c>
       <c r="W90" t="n">
-        <v>-67.26052</v>
+        <v>-67.06362</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Duley No. 2</t>
+          <t>Block 103 - Greenbush Zone</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>023B/15/Fe 008</t>
+          <t>023J/14/Fe 043</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>31</v>
       </c>
       <c r="V91" t="n">
-        <v>52.87214</v>
+        <v>54.97234</v>
       </c>
       <c r="W91" t="n">
-        <v>-66.99635000000001</v>
+        <v>-67.25158</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Howells River West Zone B</t>
+          <t>Elizabeth No. 2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>023J/14/Fe 002</t>
+          <t>023J/15/Fe 032</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7105,14 +7105,14 @@
         <v>31</v>
       </c>
       <c r="V92" t="n">
-        <v>54.87235</v>
+        <v>54.77182</v>
       </c>
       <c r="W92" t="n">
-        <v>-67.21584</v>
+        <v>-66.88666000000001</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
         </is>
       </c>
     </row>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wabush No. 8</t>
+          <t>Howells River North</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>023B/15/Fe 005</t>
+          <t>023O/03/Fe 007</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>31</v>
       </c>
       <c r="V93" t="n">
-        <v>52.9791</v>
+        <v>55.01179</v>
       </c>
       <c r="W93" t="n">
-        <v>-66.90604999999999</v>
+        <v>-67.37214</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -7194,24 +7194,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sawyer Lake</t>
+          <t>Lorraine No. 4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>023I/05/Fe 001</t>
+          <t>023G/02/Fe 008</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7249,14 +7249,14 @@
         <v>31</v>
       </c>
       <c r="V94" t="n">
-        <v>54.45206</v>
+        <v>53.08316</v>
       </c>
       <c r="W94" t="n">
-        <v>-65.98627</v>
+        <v>-66.87726000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023I%2F05%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -7266,12 +7266,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timmins No 8</t>
+          <t>Kivivic No 4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>023J/14/Fe 026</t>
+          <t>023O/03/Fe 004</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>31</v>
       </c>
       <c r="V95" t="n">
-        <v>54.89589</v>
+        <v>55.04865</v>
       </c>
       <c r="W95" t="n">
-        <v>-67.07944000000001</v>
+        <v>-67.28158000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mile 2</t>
+          <t>Kivivic No 3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>023B/15/Fe 011</t>
+          <t>023O/03/Fe 003</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7393,14 +7393,14 @@
         <v>31</v>
       </c>
       <c r="V96" t="n">
-        <v>52.97907</v>
+        <v>55.05061</v>
       </c>
       <c r="W96" t="n">
-        <v>-66.88907</v>
+        <v>-67.26130000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wabush No. 1</t>
+          <t>Houston 3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>023B/15/Fe 002</t>
+          <t>023J/10/Fe 010</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7465,14 +7465,14 @@
         <v>31</v>
       </c>
       <c r="V97" t="n">
-        <v>52.9599</v>
+        <v>54.69887</v>
       </c>
       <c r="W97" t="n">
-        <v>-66.9704</v>
+        <v>-66.64483</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>023B/14/Fe 028</t>
+          <t>023B/14/Fe 020</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>31</v>
       </c>
       <c r="V98" t="n">
-        <v>52.94868</v>
+        <v>52.83351</v>
       </c>
       <c r="W98" t="n">
-        <v>-67.01146</v>
+        <v>-67.0311</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20020</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Houston 3</t>
+          <t>Howells River West Zone B</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>023J/10/Fe 010</t>
+          <t>023J/14/Fe 002</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>31</v>
       </c>
       <c r="V99" t="n">
-        <v>54.69887</v>
+        <v>54.87235</v>
       </c>
       <c r="W99" t="n">
-        <v>-66.64483</v>
+        <v>-67.21584</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7626,24 +7626,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kivivic No 5</t>
+          <t>Neal 1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>023O/03/Fe 005</t>
+          <t>023B/14/Fe 008</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>31</v>
       </c>
       <c r="V100" t="n">
-        <v>55.06664</v>
+        <v>52.95013</v>
       </c>
       <c r="W100" t="n">
-        <v>-67.29537000000001</v>
+        <v>-67.15191</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -7698,24 +7698,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kivivic No 4</t>
+          <t>Duley No. 1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>023O/03/Fe 004</t>
+          <t>023B/14/Fe 001</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7753,14 +7753,14 @@
         <v>31</v>
       </c>
       <c r="V101" t="n">
-        <v>55.04865</v>
+        <v>52.87237</v>
       </c>
       <c r="W101" t="n">
-        <v>-67.28158000000001</v>
+        <v>-67.05874</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -7770,24 +7770,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kivivic No 3</t>
+          <t>Mills Lake</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>023O/03/Fe 003</t>
+          <t>023B/14/Fe 002</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7825,14 +7825,14 @@
         <v>31</v>
       </c>
       <c r="V102" t="n">
-        <v>55.05061</v>
+        <v>52.79808</v>
       </c>
       <c r="W102" t="n">
-        <v>-67.26130000000001</v>
+        <v>-67.00413</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Houston 1</t>
+          <t>Kivivic No 5</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>023J/10/Fe 008</t>
+          <t>023O/03/Fe 005</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>31</v>
       </c>
       <c r="V103" t="n">
-        <v>54.70748</v>
+        <v>55.06664</v>
       </c>
       <c r="W103" t="n">
-        <v>-66.65615</v>
+        <v>-67.29537000000001</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -7914,12 +7914,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Houston 2</t>
+          <t>Redmond 5</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>023J/10/Fe 009</t>
+          <t>023J/10/Fe 005</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -7969,14 +7969,14 @@
         <v>31</v>
       </c>
       <c r="V104" t="n">
-        <v>54.71245</v>
+        <v>54.70854</v>
       </c>
       <c r="W104" t="n">
-        <v>-66.66257</v>
+        <v>-66.79174999999999</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Redmond 5</t>
+          <t>Houston 1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>023J/10/Fe 005</t>
+          <t>023J/10/Fe 008</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8041,14 +8041,14 @@
         <v>31</v>
       </c>
       <c r="V105" t="n">
-        <v>54.70854</v>
+        <v>54.70748</v>
       </c>
       <c r="W105" t="n">
-        <v>-66.79174999999999</v>
+        <v>-66.65615</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Duley No. 1</t>
+          <t>Houston 2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>023B/14/Fe 001</t>
+          <t>023J/10/Fe 009</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8113,14 +8113,14 @@
         <v>31</v>
       </c>
       <c r="V106" t="n">
-        <v>52.87237</v>
+        <v>54.71245</v>
       </c>
       <c r="W106" t="n">
-        <v>-67.05874</v>
+        <v>-66.66257</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F14%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Howse</t>
+          <t>Timmins No 7</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>023J/14/Fe 028</t>
+          <t>023J/14/Fe 025</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8185,14 +8185,14 @@
         <v>31</v>
       </c>
       <c r="V107" t="n">
-        <v>54.9089</v>
+        <v>54.89246</v>
       </c>
       <c r="W107" t="n">
-        <v>-67.14075</v>
+        <v>-67.07259000000001</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Howells River North</t>
+          <t>Timmins No 5</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>023O/03/Fe 007</t>
+          <t>023J/14/Fe 024</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8257,14 +8257,14 @@
         <v>31</v>
       </c>
       <c r="V108" t="n">
-        <v>55.01179</v>
+        <v>54.86384</v>
       </c>
       <c r="W108" t="n">
-        <v>-67.37214</v>
+        <v>-67.09327</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Elizabeth No. 2</t>
+          <t>Duley No. 2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>023J/15/Fe 032</t>
+          <t>023B/15/Fe 008</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>31</v>
       </c>
       <c r="V109" t="n">
-        <v>54.77182</v>
+        <v>52.87214</v>
       </c>
       <c r="W109" t="n">
-        <v>-66.88666000000001</v>
+        <v>-66.99635000000001</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20032</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Block 103 - Greenbush Zone</t>
+          <t>Mile 2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>023J/14/Fe 043</t>
+          <t>023B/15/Fe 011</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -8401,14 +8401,14 @@
         <v>31</v>
       </c>
       <c r="V110" t="n">
-        <v>54.97234</v>
+        <v>52.97907</v>
       </c>
       <c r="W110" t="n">
-        <v>-67.25158</v>
+        <v>-66.88907</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20043</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8418,24 +8418,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Attikamagen Deposit</t>
+          <t>Wabush No. 8</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>023J/16/Fe 001</t>
+          <t>023B/15/Fe 005</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>31</v>
       </c>
       <c r="V111" t="n">
-        <v>54.80989</v>
+        <v>52.9791</v>
       </c>
       <c r="W111" t="n">
-        <v>-66.47658</v>
+        <v>-66.90604999999999</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Canning</t>
+          <t>Wabush No. 4</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>023B/15/Fe 007</t>
+          <t>023B/15/Fe 004</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8545,14 +8545,14 @@
         <v>31</v>
       </c>
       <c r="V112" t="n">
-        <v>52.9469</v>
+        <v>52.95373</v>
       </c>
       <c r="W112" t="n">
-        <v>-66.95802999999999</v>
+        <v>-66.94092000000001</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timmins No 5</t>
+          <t>Timmins No 8</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>023J/14/Fe 024</t>
+          <t>023J/14/Fe 026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8617,14 +8617,14 @@
         <v>31</v>
       </c>
       <c r="V113" t="n">
-        <v>54.86384</v>
+        <v>54.89589</v>
       </c>
       <c r="W113" t="n">
-        <v>-67.09327</v>
+        <v>-67.07944000000001</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20024</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20026</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timmins No 7</t>
+          <t>Ferriman No 7</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>023J/14/Fe 025</t>
+          <t>023J/15/Fe 014</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8689,14 +8689,14 @@
         <v>31</v>
       </c>
       <c r="V114" t="n">
-        <v>54.89246</v>
+        <v>54.81281</v>
       </c>
       <c r="W114" t="n">
-        <v>-67.07259000000001</v>
+        <v>-66.94580999999999</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20025</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wabush No. 4</t>
+          <t>Ruth Lake No 2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>023B/15/Fe 004</t>
+          <t>023J/15/Fe 011</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -8761,14 +8761,14 @@
         <v>31</v>
       </c>
       <c r="V115" t="n">
-        <v>52.95373</v>
+        <v>54.79747</v>
       </c>
       <c r="W115" t="n">
-        <v>-66.94092000000001</v>
+        <v>-66.87487</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Joyce Lake</t>
+          <t>Wabush No. 1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>023J/15/Fe 030</t>
+          <t>023B/15/Fe 002</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>31</v>
       </c>
       <c r="V116" t="n">
-        <v>54.8993</v>
+        <v>52.9599</v>
       </c>
       <c r="W116" t="n">
-        <v>-66.53366</v>
+        <v>-66.9704</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -8850,29 +8850,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ruth Lake No 2</t>
+          <t>Bishop North</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>023J/15/Fe 011</t>
+          <t>012B/08/Fe 001</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I117" t="b">
@@ -8905,14 +8905,14 @@
         <v>31</v>
       </c>
       <c r="V117" t="n">
-        <v>54.79747</v>
+        <v>48.40317</v>
       </c>
       <c r="W117" t="n">
-        <v>-66.87487</v>
+        <v>-58.3315</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8922,29 +8922,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Wabush No. 6</t>
+          <t>Indian Head Mine</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>023G/02/Fe 006</t>
+          <t>012B/10/Fe 001</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I118" t="b">
@@ -8977,14 +8977,14 @@
         <v>31</v>
       </c>
       <c r="V118" t="n">
-        <v>53.01798</v>
+        <v>48.52416</v>
       </c>
       <c r="W118" t="n">
-        <v>-66.89297999999999</v>
+        <v>-58.5148</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -8994,24 +8994,24 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ruth Lake No 8</t>
+          <t>Howse</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>023J/15/Fe 009</t>
+          <t>023J/14/Fe 028</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9049,14 +9049,14 @@
         <v>31</v>
       </c>
       <c r="V119" t="n">
-        <v>54.78104</v>
+        <v>54.9089</v>
       </c>
       <c r="W119" t="n">
-        <v>-66.86577</v>
+        <v>-67.14075</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20028</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Wabush No. 7</t>
+          <t>Ruth Lake No 8</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>023G/02/Fe 007</t>
+          <t>023J/15/Fe 009</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9121,14 +9121,14 @@
         <v>31</v>
       </c>
       <c r="V120" t="n">
-        <v>53.02512</v>
+        <v>54.78104</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.90531</v>
+        <v>-66.86577</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Julienne Lake</t>
+          <t>Knob Lake 1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>023G/02/Fe 009</t>
+          <t>023J/15/Fe 013</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9193,14 +9193,14 @@
         <v>31</v>
       </c>
       <c r="V121" t="n">
-        <v>53.13733</v>
+        <v>54.7766</v>
       </c>
       <c r="W121" t="n">
-        <v>-66.78360000000001</v>
+        <v>-66.80589000000001</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
         </is>
       </c>
     </row>
@@ -9210,29 +9210,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Lorraine No. 4</t>
+          <t>Bishop South</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>023G/02/Fe 008</t>
+          <t>012B/08/Fe 002</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Vanadium, Titanium, Iron</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I122" t="b">
@@ -9265,14 +9265,14 @@
         <v>31</v>
       </c>
       <c r="V122" t="n">
-        <v>53.08316</v>
+        <v>48.39996</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.87726000000001</v>
+        <v>-58.33683</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -9282,24 +9282,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ferriman No 7</t>
+          <t>Goethite Bay North</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>023J/15/Fe 014</t>
+          <t>023G/02/Fe 041</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9337,14 +9337,14 @@
         <v>31</v>
       </c>
       <c r="V123" t="n">
-        <v>54.81281</v>
+        <v>53.18717</v>
       </c>
       <c r="W123" t="n">
-        <v>-66.94580999999999</v>
+        <v>-66.74445</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
         </is>
       </c>
     </row>
@@ -9354,24 +9354,24 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Knob Lake 1</t>
+          <t>Elizabeth No. 1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>023J/15/Fe 013</t>
+          <t>023J/15/Fe 031</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9409,14 +9409,14 @@
         <v>31</v>
       </c>
       <c r="V124" t="n">
-        <v>54.7766</v>
+        <v>54.78743</v>
       </c>
       <c r="W124" t="n">
-        <v>-66.80589000000001</v>
+        <v>-66.90081000000001</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
         </is>
       </c>
     </row>
@@ -9426,29 +9426,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bishop South</t>
+          <t>Howells Lake</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>012B/08/Fe 002</t>
+          <t>023O/03/Fe 006</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I125" t="b">
@@ -9481,14 +9481,14 @@
         <v>31</v>
       </c>
       <c r="V125" t="n">
-        <v>48.39996</v>
+        <v>55.06346</v>
       </c>
       <c r="W125" t="n">
-        <v>-58.33683</v>
+        <v>-67.40528</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -9498,29 +9498,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bishop North</t>
+          <t>Attikamagen Deposit</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>012B/08/Fe 001</t>
+          <t>023J/16/Fe 001</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I126" t="b">
@@ -9553,14 +9553,14 @@
         <v>31</v>
       </c>
       <c r="V126" t="n">
-        <v>48.40317</v>
+        <v>54.80989</v>
       </c>
       <c r="W126" t="n">
-        <v>-58.3315</v>
+        <v>-66.47658</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F16%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -9570,29 +9570,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Indian Head Mine</t>
+          <t>Wabush No. 7</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>012B/10/Fe 001</t>
+          <t>023G/02/Fe 007</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Vanadium, Titanium, Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Developed Prospect</t>
         </is>
       </c>
       <c r="I127" t="b">
@@ -9625,14 +9625,14 @@
         <v>31</v>
       </c>
       <c r="V127" t="n">
-        <v>48.52416</v>
+        <v>53.02512</v>
       </c>
       <c r="W127" t="n">
-        <v>-58.5148</v>
+        <v>-66.90531</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Goethite Bay North</t>
+          <t>Joyce Lake</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>023G/02/Fe 041</t>
+          <t>023J/15/Fe 030</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>31</v>
       </c>
       <c r="V128" t="n">
-        <v>53.18717</v>
+        <v>54.8993</v>
       </c>
       <c r="W128" t="n">
-        <v>-66.74445</v>
+        <v>-66.53366</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20041</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20030</t>
         </is>
       </c>
     </row>
@@ -9714,24 +9714,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Elizabeth No. 1</t>
+          <t>Julienne Lake</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>023J/15/Fe 031</t>
+          <t>023G/02/Fe 009</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9769,14 +9769,14 @@
         <v>31</v>
       </c>
       <c r="V129" t="n">
-        <v>54.78743</v>
+        <v>53.13733</v>
       </c>
       <c r="W129" t="n">
-        <v>-66.90081000000001</v>
+        <v>-66.78360000000001</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20031</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20009</t>
         </is>
       </c>
     </row>
@@ -9786,24 +9786,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Howells Lake</t>
+          <t>Canning</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>023O/03/Fe 006</t>
+          <t>023B/15/Fe 007</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9841,14 +9841,14 @@
         <v>31</v>
       </c>
       <c r="V130" t="n">
-        <v>55.06346</v>
+        <v>52.9469</v>
       </c>
       <c r="W130" t="n">
-        <v>-67.40528</v>
+        <v>-66.95802999999999</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023O%2F03%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Parsons Pond No 4</t>
+          <t>Parsons Pond Cart Track</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>012H/13/Btm004</t>
+          <t>012I/04/Btm001</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Oil Shale</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9913,14 +9913,14 @@
         <v>30</v>
       </c>
       <c r="V131" t="n">
-        <v>49.99787</v>
+        <v>50.00564</v>
       </c>
       <c r="W131" t="n">
-        <v>-57.63818</v>
+        <v>-57.63187</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Parsons Pond No 1</t>
+          <t>Blue Beach Mine</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>012H/13/Btm001</t>
+          <t>001L/14/Fl 001</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9976,23 +9976,23 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T132" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U132" t="n">
         <v>30</v>
       </c>
       <c r="V132" t="n">
-        <v>49.99228</v>
+        <v>46.91553</v>
       </c>
       <c r="W132" t="n">
-        <v>-57.58928</v>
+        <v>-55.40729</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
         </is>
       </c>
     </row>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Parsons Pond No 2</t>
+          <t>Iron Springs Mine</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>012H/13/Btm002</t>
+          <t>001L/14/Fl 008</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10057,14 +10057,14 @@
         <v>30</v>
       </c>
       <c r="V133" t="n">
-        <v>49.97421</v>
+        <v>46.88701</v>
       </c>
       <c r="W133" t="n">
-        <v>-57.60538</v>
+        <v>-55.421</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Parsons Pond No 3</t>
+          <t>Salt Cove Valley Vein</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>012H/13/Btm003</t>
+          <t>001L/14/Fl 015</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10129,14 +10129,14 @@
         <v>30</v>
       </c>
       <c r="V134" t="n">
-        <v>49.97912</v>
+        <v>46.87774</v>
       </c>
       <c r="W134" t="n">
-        <v>-57.64547</v>
+        <v>-55.43387</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20015</t>
         </is>
       </c>
     </row>
@@ -10146,12 +10146,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Parsons Pond Cart Track</t>
+          <t>Black Duck Mine</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>012I/04/Btm001</t>
+          <t>001L/14/Fl 010</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Oil Shale</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10192,23 +10192,23 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T135" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U135" t="n">
         <v>30</v>
       </c>
       <c r="V135" t="n">
-        <v>50.00564</v>
+        <v>46.93201</v>
       </c>
       <c r="W135" t="n">
-        <v>-57.63187</v>
+        <v>-55.38881</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F04%2FBtm001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
         </is>
       </c>
     </row>
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>La Manche</t>
+          <t>AGS Vein</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>001N/12/Pb 001</t>
+          <t>001L/14/Fl 013</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Barium, Lead</t>
+          <t>Zinc, Lead, Copper, Fluorine</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10273,14 +10273,14 @@
         <v>30</v>
       </c>
       <c r="V136" t="n">
-        <v>47.6889</v>
+        <v>46.91489</v>
       </c>
       <c r="W136" t="n">
-        <v>-53.93901</v>
+        <v>-55.48584</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mine Hill</t>
+          <t>La Manche</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>001N/07/Pph004</t>
+          <t>001N/12/Pb 001</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pyrophyllite</t>
+          <t>Zinc, Silver, Barium, Lead</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>30</v>
       </c>
       <c r="V137" t="n">
-        <v>47.48</v>
+        <v>47.6889</v>
       </c>
       <c r="W137" t="n">
-        <v>-52.95479</v>
+        <v>-53.93901</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -10362,12 +10362,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Collier Point</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>001N/12/Ba 001</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Barium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>30</v>
       </c>
       <c r="V138" t="n">
-        <v>47.59126</v>
+        <v>53.469</v>
       </c>
       <c r="W138" t="n">
-        <v>-53.69011</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Middle Arm Brook</t>
+          <t>Mine Hill</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>012H/16/Vir001</t>
+          <t>001N/07/Pph004</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Virginite</t>
+          <t>Pyrophyllite</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>30</v>
       </c>
       <c r="V139" t="n">
-        <v>49.80048</v>
+        <v>47.48</v>
       </c>
       <c r="W139" t="n">
-        <v>-56.31995</v>
+        <v>-52.95479</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FPph004</t>
         </is>
       </c>
     </row>
@@ -10506,24 +10506,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-K Zone</t>
+          <t>Silver Cliff</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>012I/06/Zn 010</t>
+          <t>001N/05/Pb 003</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Barium, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>30</v>
       </c>
       <c r="V140" t="n">
-        <v>50.2935</v>
+        <v>47.30144</v>
       </c>
       <c r="W140" t="n">
-        <v>-57.46875</v>
+        <v>-53.94444</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F05%2FPb%20003</t>
         </is>
       </c>
     </row>
@@ -10578,12 +10578,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Bluff Head Mine</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>012B/15/Cr 001</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Asbestos, Chromium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10633,14 +10633,14 @@
         <v>30</v>
       </c>
       <c r="V141" t="n">
-        <v>48.77717</v>
+        <v>53.40462</v>
       </c>
       <c r="W141" t="n">
-        <v>-58.59931</v>
+        <v>-65.08734</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -10650,24 +10650,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Pilley's Island Mine</t>
+          <t>Collier Point</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>002E/12/Cu 001</t>
+          <t>001N/12/Ba 001</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Barium</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10705,14 +10705,14 @@
         <v>30</v>
       </c>
       <c r="V142" t="n">
-        <v>49.50863</v>
+        <v>47.59126</v>
       </c>
       <c r="W142" t="n">
-        <v>-55.71872</v>
+        <v>-53.69011</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F12%2FBa%20001</t>
         </is>
       </c>
     </row>
@@ -10722,12 +10722,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tarefare Mine</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>001L/14/Fl 006</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10777,14 +10777,14 @@
         <v>30</v>
       </c>
       <c r="V143" t="n">
-        <v>46.8912</v>
+        <v>48.56074</v>
       </c>
       <c r="W143" t="n">
-        <v>-55.43112</v>
+        <v>-58.8161</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Pilley's Island Mine</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>002E/12/Cu 001</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>30</v>
       </c>
       <c r="V144" t="n">
-        <v>53.469</v>
+        <v>49.50863</v>
       </c>
       <c r="W144" t="n">
-        <v>-64.91218000000001</v>
+        <v>-55.71872</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F12%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -10866,12 +10866,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Silver Cliff</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>001N/05/Pb 003</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Barium, Copper, Zinc, Lead</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10921,14 +10921,14 @@
         <v>30</v>
       </c>
       <c r="V145" t="n">
-        <v>47.30144</v>
+        <v>48.50411</v>
       </c>
       <c r="W145" t="n">
-        <v>-53.94444</v>
+        <v>-58.53451</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F05%2FPb%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -10938,12 +10938,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Bluff Head Mine</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>012B/15/Cr 001</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Asbestos, Chromium</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>30</v>
       </c>
       <c r="V146" t="n">
-        <v>48.56074</v>
+        <v>48.77717</v>
       </c>
       <c r="W146" t="n">
-        <v>-58.8161</v>
+        <v>-58.59931</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F15%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -11010,24 +11010,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Cross Cove</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>002E/10/Sb 001</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11065,14 +11065,14 @@
         <v>30</v>
       </c>
       <c r="V147" t="n">
-        <v>53.40462</v>
+        <v>49.57534</v>
       </c>
       <c r="W147" t="n">
-        <v>-65.08734</v>
+        <v>-54.86876</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Goose Cove</t>
+          <t>York Harbour Mine</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>002M/05/Cu 001</t>
+          <t>012G/01/Cu 002</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Zinc, Nickel, Iron, Copper</t>
+          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11137,14 +11137,14 @@
         <v>30</v>
       </c>
       <c r="V148" t="n">
-        <v>51.31009</v>
+        <v>49.05208</v>
       </c>
       <c r="W148" t="n">
-        <v>-55.62342</v>
+        <v>-58.30769</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
         </is>
       </c>
     </row>
@@ -11154,24 +11154,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>York Harbour Mine</t>
+          <t>Lord &amp; Lady Gulch Mine</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>012G/01/Cu 002</t>
+          <t>001L/14/Fl 005</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Cobalt, Copper</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11209,14 +11209,14 @@
         <v>30</v>
       </c>
       <c r="V149" t="n">
-        <v>49.05208</v>
+        <v>46.87554</v>
       </c>
       <c r="W149" t="n">
-        <v>-58.30769</v>
+        <v>-55.4111</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012G%2F01%2FCu%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
         </is>
       </c>
     </row>
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cross Cove</t>
+          <t>Goose Cove</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>002E/10/Sb 001</t>
+          <t>002M/05/Cu 001</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11243,7 +11243,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Antimony</t>
+          <t>Zinc, Nickel, Iron, Copper</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11281,14 +11281,14 @@
         <v>30</v>
       </c>
       <c r="V150" t="n">
-        <v>49.57534</v>
+        <v>51.31009</v>
       </c>
       <c r="W150" t="n">
-        <v>-54.86876</v>
+        <v>-55.62342</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F10%2FSb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002M%2F05%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lord &amp; Lady Gulch Mine</t>
+          <t>Hares Ears Vein</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>001L/14/Fl 005</t>
+          <t>001L/14/Fl 007</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11353,14 +11353,14 @@
         <v>30</v>
       </c>
       <c r="V151" t="n">
-        <v>46.87554</v>
+        <v>46.88814</v>
       </c>
       <c r="W151" t="n">
-        <v>-55.4111</v>
+        <v>-55.41178</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
         </is>
       </c>
     </row>
@@ -11370,12 +11370,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Tarefare Mine</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>001L/14/Fl 006</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11425,14 +11425,14 @@
         <v>30</v>
       </c>
       <c r="V152" t="n">
-        <v>48.50411</v>
+        <v>46.8912</v>
       </c>
       <c r="W152" t="n">
-        <v>-58.53451</v>
+        <v>-55.43112</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20006</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Southern Cross Veins</t>
+          <t>Director Mine</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>001L/14/Fl 020</t>
+          <t>001L/14/Fl 009</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -11497,14 +11497,14 @@
         <v>30</v>
       </c>
       <c r="V153" t="n">
-        <v>46.88974</v>
+        <v>46.90681</v>
       </c>
       <c r="W153" t="n">
-        <v>-55.42958</v>
+        <v>-55.42107</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11514,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Little Salt Cove</t>
+          <t>Doctors Pond Veins</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>001L/14/Fl 016</t>
+          <t>001L/14/Fl 036</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11569,14 +11569,14 @@
         <v>30</v>
       </c>
       <c r="V154" t="n">
-        <v>46.87654</v>
+        <v>46.92769</v>
       </c>
       <c r="W154" t="n">
-        <v>-55.43141</v>
+        <v>-55.37593</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Hares Ears Vein</t>
+          <t>Borney Lake</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>001L/14/Fl 007</t>
+          <t>002D/14/Stn001</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11641,14 +11641,14 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>46.88814</v>
+        <v>48.9264</v>
       </c>
       <c r="W155" t="n">
-        <v>-55.41178</v>
+        <v>-55.44535</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
         </is>
       </c>
     </row>
@@ -11658,12 +11658,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Iron Springs Mine</t>
+          <t>Baie Verte Mine</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>001L/14/Fl 008</t>
+          <t>012H/16/Asb008</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Magnesium, Asbestos</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11713,14 +11713,14 @@
         <v>30</v>
       </c>
       <c r="V156" t="n">
-        <v>46.88701</v>
+        <v>49.97974</v>
       </c>
       <c r="W156" t="n">
-        <v>-55.421</v>
+        <v>-56.19399</v>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
         </is>
       </c>
     </row>
@@ -11730,24 +11730,24 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>AGS Vein</t>
+          <t>Little Salt Cove</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>001L/14/Fl 013</t>
+          <t>001L/14/Fl 016</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Copper, Fluorine</t>
+          <t>Fluorine</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11785,14 +11785,14 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>46.91489</v>
+        <v>46.87654</v>
       </c>
       <c r="W157" t="n">
-        <v>-55.48584</v>
+        <v>-55.43141</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20013</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20016</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11802,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Salt Cove Valley Vein</t>
+          <t>Southern Cross Veins</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>001L/14/Fl 015</t>
+          <t>001L/14/Fl 020</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -11857,14 +11857,14 @@
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>46.87774</v>
+        <v>46.88974</v>
       </c>
       <c r="W158" t="n">
-        <v>-55.43387</v>
+        <v>-55.42958</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20020</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Director Mine</t>
+          <t>Scrape Vein</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>001L/14/Fl 009</t>
+          <t>001L/14/Fl 035</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -11929,14 +11929,14 @@
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>46.90681</v>
+        <v>46.92547</v>
       </c>
       <c r="W159" t="n">
-        <v>-55.42107</v>
+        <v>-55.37193</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Black Duck Mine</t>
+          <t>Parsons Pond No 2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>001L/14/Fl 010</t>
+          <t>012H/13/Btm002</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12001,14 +12001,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>46.93201</v>
+        <v>49.97421</v>
       </c>
       <c r="W160" t="n">
-        <v>-55.38881</v>
+        <v>-57.60538</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm002</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Parsons Pond No 4</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>012H/13/Btm004</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12064,23 +12064,23 @@
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T161" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U161" t="n">
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>48.30663</v>
+        <v>49.99787</v>
       </c>
       <c r="W161" t="n">
-        <v>-58.68165</v>
+        <v>-57.63818</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm004</t>
         </is>
       </c>
     </row>
@@ -12090,24 +12090,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Parsons Pond No 1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>012H/13/Btm001</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12136,23 +12136,23 @@
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T162" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U162" t="n">
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>49.45488</v>
+        <v>49.99228</v>
       </c>
       <c r="W162" t="n">
-        <v>-55.49811</v>
+        <v>-57.58928</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm001</t>
         </is>
       </c>
     </row>
@@ -12162,24 +12162,24 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Scrape Vein</t>
+          <t>Daniel's Harbour Mine-K Zone</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>001L/14/Fl 035</t>
+          <t>012I/06/Zn 010</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12217,14 +12217,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>46.92547</v>
+        <v>50.2935</v>
       </c>
       <c r="W163" t="n">
-        <v>-55.37193</v>
+        <v>-57.46875</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20035</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20010</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Doctors Pond Veins</t>
+          <t>Parsons Pond No 3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>001L/14/Fl 036</t>
+          <t>012H/13/Btm003</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12289,14 +12289,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>46.92769</v>
+        <v>49.97912</v>
       </c>
       <c r="W164" t="n">
-        <v>-55.37593</v>
+        <v>-57.64547</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20036</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F13%2FBtm003</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Borney Lake</t>
+          <t>Middle Arm Brook</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>002D/14/Stn001</t>
+          <t>012H/16/Vir001</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Virginite</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -12361,14 +12361,14 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>48.9264</v>
+        <v>49.80048</v>
       </c>
       <c r="W165" t="n">
-        <v>-55.44535</v>
+        <v>-56.31995</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002D%2F14%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FVir001</t>
         </is>
       </c>
     </row>
@@ -12378,24 +12378,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Blue Beach Mine</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>001L/14/Fl 001</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fluorine</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12433,14 +12433,14 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>46.91553</v>
+        <v>49.45488</v>
       </c>
       <c r="W166" t="n">
-        <v>-55.40729</v>
+        <v>-55.49811</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001L%2F14%2FFl%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12450,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baie Verte Mine</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>012H/16/Asb008</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Magnesium, Asbestos</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12505,14 +12505,14 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>49.97974</v>
+        <v>48.30663</v>
       </c>
       <c r="W167" t="n">
-        <v>-56.19399</v>
+        <v>-58.68165</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F16%2FAsb008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -12594,12 +12594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-J Zone</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 009</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12649,14 +12649,14 @@
         <v>29</v>
       </c>
       <c r="V169" t="n">
-        <v>50.31118</v>
+        <v>50.30247</v>
       </c>
       <c r="W169" t="n">
-        <v>-57.43009</v>
+        <v>-57.47459</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-B Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>012I/06/Zn 002</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -12721,14 +12721,14 @@
         <v>29</v>
       </c>
       <c r="V170" t="n">
-        <v>50.2975</v>
+        <v>50.27283</v>
       </c>
       <c r="W170" t="n">
-        <v>-57.45784</v>
+        <v>-57.46448</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -12738,12 +12738,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Browning Mine</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012H/10/Au 001</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12793,14 +12793,14 @@
         <v>29</v>
       </c>
       <c r="V171" t="n">
-        <v>50.27283</v>
+        <v>49.71799</v>
       </c>
       <c r="W171" t="n">
-        <v>-57.46448</v>
+        <v>-56.92565</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
         </is>
       </c>
     </row>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-F Zone</t>
+          <t>Daniel's Harbour Mine-M Zone</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>012I/06/Zn 006</t>
+          <t>012I/06/Zn 012</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -12937,14 +12937,14 @@
         <v>29</v>
       </c>
       <c r="V173" t="n">
-        <v>50.29437</v>
+        <v>50.29514</v>
       </c>
       <c r="W173" t="n">
-        <v>-57.45374</v>
+        <v>-57.44013</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12954,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-G Zone</t>
+          <t>Daniel's Harbour Mine-A Zone</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>012I/06/Zn 007</t>
+          <t>012I/06/Zn 001</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -13009,14 +13009,14 @@
         <v>29</v>
       </c>
       <c r="V174" t="n">
-        <v>50.29448</v>
+        <v>50.29576</v>
       </c>
       <c r="W174" t="n">
-        <v>-57.44714</v>
+        <v>-57.46512</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-E Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>012I/06/Zn 005</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13081,14 +13081,14 @@
         <v>29</v>
       </c>
       <c r="V175" t="n">
-        <v>50.31067</v>
+        <v>50.31118</v>
       </c>
       <c r="W175" t="n">
-        <v>-57.44799</v>
+        <v>-57.43009</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-H Zone</t>
+          <t>Daniel's Harbour Mine-D Zone</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>012I/06/Zn 008</t>
+          <t>012I/06/Zn 004</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13153,14 +13153,14 @@
         <v>29</v>
       </c>
       <c r="V176" t="n">
-        <v>50.29179</v>
+        <v>50.30795</v>
       </c>
       <c r="W176" t="n">
-        <v>-57.44599</v>
+        <v>-57.45218</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-A Zone</t>
+          <t>Daniel's Harbour Mine-C Zone</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>012I/06/Zn 001</t>
+          <t>012I/06/Zn 003</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13225,14 +13225,14 @@
         <v>29</v>
       </c>
       <c r="V177" t="n">
-        <v>50.29576</v>
+        <v>50.30435</v>
       </c>
       <c r="W177" t="n">
-        <v>-57.46512</v>
+        <v>-57.45355</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-D Zone</t>
+          <t>Daniel's Harbour Mine-E Zone</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>012I/06/Zn 004</t>
+          <t>012I/06/Zn 005</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13297,14 +13297,14 @@
         <v>29</v>
       </c>
       <c r="V178" t="n">
-        <v>50.30795</v>
+        <v>50.31067</v>
       </c>
       <c r="W178" t="n">
-        <v>-57.45218</v>
+        <v>-57.44799</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20005</t>
         </is>
       </c>
     </row>
@@ -13314,12 +13314,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-C Zone</t>
+          <t>Daniel's Harbour Mine-G Zone</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>012I/06/Zn 003</t>
+          <t>012I/06/Zn 007</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -13369,14 +13369,14 @@
         <v>29</v>
       </c>
       <c r="V179" t="n">
-        <v>50.30435</v>
+        <v>50.29448</v>
       </c>
       <c r="W179" t="n">
-        <v>-57.45355</v>
+        <v>-57.44714</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20007</t>
         </is>
       </c>
     </row>
@@ -13386,12 +13386,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-L Zone</t>
+          <t>Daniel's Harbour Mine-B Zone</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>012I/06/Zn 011</t>
+          <t>012I/06/Zn 002</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lead, Dolomite, Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13441,14 +13441,14 @@
         <v>29</v>
       </c>
       <c r="V180" t="n">
-        <v>50.27686</v>
+        <v>50.2975</v>
       </c>
       <c r="W180" t="n">
-        <v>-57.46788</v>
+        <v>-57.45784</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20002</t>
         </is>
       </c>
     </row>
@@ -13458,12 +13458,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-J Zone</t>
+          <t>Daniel's Harbour Mine-H Zone</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>012I/06/Zn 009</t>
+          <t>012I/06/Zn 008</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13513,14 +13513,14 @@
         <v>29</v>
       </c>
       <c r="V181" t="n">
-        <v>50.30247</v>
+        <v>50.29179</v>
       </c>
       <c r="W181" t="n">
-        <v>-57.47459</v>
+        <v>-57.44599</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20009</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20008</t>
         </is>
       </c>
     </row>
@@ -13530,12 +13530,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-M Zone</t>
+          <t>Daniel's Harbour Mine-F Zone</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>012I/06/Zn 012</t>
+          <t>012I/06/Zn 006</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13585,14 +13585,14 @@
         <v>29</v>
       </c>
       <c r="V182" t="n">
-        <v>50.29514</v>
+        <v>50.29437</v>
       </c>
       <c r="W182" t="n">
-        <v>-57.44013</v>
+        <v>-57.45374</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20012</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20006</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Browning Mine</t>
+          <t>Daniel's Harbour Mine-L Zone</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>012H/10/Au 001</t>
+          <t>012I/06/Zn 011</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13619,7 +13619,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Gold</t>
+          <t>Lead, Dolomite, Zinc</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13657,14 +13657,14 @@
         <v>29</v>
       </c>
       <c r="V183" t="n">
-        <v>49.71799</v>
+        <v>50.27686</v>
       </c>
       <c r="W183" t="n">
-        <v>-56.92565</v>
+        <v>-57.46788</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F10%2FAu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20011</t>
         </is>
       </c>
     </row>
@@ -13746,12 +13746,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Timmins No 6</t>
+          <t>Gull Island Formation</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>023J/14/Fe 021</t>
+          <t>001N/10/Fe 003</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13801,14 +13801,14 @@
         <v>26</v>
       </c>
       <c r="V185" t="n">
-        <v>54.90148</v>
+        <v>47.65193</v>
       </c>
       <c r="W185" t="n">
-        <v>-67.09757999999999</v>
+        <v>-52.95654</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Timmins No 4</t>
+          <t>Dominion Formation</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>023J/14/Fe 023</t>
+          <t>001N/10/Fe 001</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -13873,14 +13873,14 @@
         <v>26</v>
       </c>
       <c r="V186" t="n">
-        <v>54.89884</v>
+        <v>47.64164</v>
       </c>
       <c r="W186" t="n">
-        <v>-67.10881000000001</v>
+        <v>-52.95309</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fleming No 3</t>
+          <t>Scotia Formation</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>023J/14/Fe 022</t>
+          <t>001N/10/Fe 002</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13945,14 +13945,14 @@
         <v>26</v>
       </c>
       <c r="V187" t="n">
-        <v>54.85836</v>
+        <v>47.64169</v>
       </c>
       <c r="W187" t="n">
-        <v>-67.03167999999999</v>
+        <v>-52.97639</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -13962,24 +13962,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Redmond No 2</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>023J/10/Fe 002</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14017,14 +14017,14 @@
         <v>26</v>
       </c>
       <c r="V188" t="n">
-        <v>47.53392</v>
+        <v>54.69738</v>
       </c>
       <c r="W188" t="n">
-        <v>-53.18293</v>
+        <v>-66.77224</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dominion Formation</t>
+          <t>Grey Copper Mine</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>001N/10/Fe 001</t>
+          <t>002E/11/Cu 001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Iron, Copper</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14089,14 +14089,14 @@
         <v>26</v>
       </c>
       <c r="V189" t="n">
-        <v>47.64164</v>
+        <v>49.5173</v>
       </c>
       <c r="W189" t="n">
-        <v>-52.95309</v>
+        <v>-55.2721</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -14106,24 +14106,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Redmond No 2</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>023J/10/Fe 002</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14161,14 +14161,14 @@
         <v>26</v>
       </c>
       <c r="V190" t="n">
-        <v>54.69738</v>
+        <v>49.50376</v>
       </c>
       <c r="W190" t="n">
-        <v>-66.77224</v>
+        <v>-55.21553</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14178,24 +14178,24 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Gull Island Formation</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>001N/10/Fe 003</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -14233,14 +14233,14 @@
         <v>26</v>
       </c>
       <c r="V191" t="n">
-        <v>47.65193</v>
+        <v>47.53392</v>
       </c>
       <c r="W191" t="n">
-        <v>-52.95654</v>
+        <v>-53.18293</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -14250,12 +14250,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Scotia Formation</t>
+          <t>Cliff Mine</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>001N/10/Fe 002</t>
+          <t>012B/09/Fe 001</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -14305,14 +14305,14 @@
         <v>26</v>
       </c>
       <c r="V192" t="n">
-        <v>47.64169</v>
+        <v>48.54434</v>
       </c>
       <c r="W192" t="n">
-        <v>-52.97639</v>
+        <v>-58.49915</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F10%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Timmins No 1</t>
+          <t>Skindles Mine</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>023J/14/Fe 018</t>
+          <t>012B/09/Fe 004</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14377,14 +14377,14 @@
         <v>26</v>
       </c>
       <c r="V193" t="n">
-        <v>54.88449</v>
+        <v>48.54069</v>
       </c>
       <c r="W193" t="n">
-        <v>-67.08575</v>
+        <v>-58.48888</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14394,24 +14394,24 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Timmins No 2</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>023J/14/Fe 019</t>
+          <t>023J/15/Fe 010</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14449,14 +14449,14 @@
         <v>26</v>
       </c>
       <c r="V194" t="n">
-        <v>54.89421</v>
+        <v>54.77437</v>
       </c>
       <c r="W194" t="n">
-        <v>-67.08716</v>
+        <v>-66.82881</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14466,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Skindles Mine</t>
+          <t>Ruth Lake No 7</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>012B/09/Fe 004</t>
+          <t>023J/15/Fe 006</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
         <v>26</v>
       </c>
       <c r="V195" t="n">
-        <v>48.54069</v>
+        <v>54.80557</v>
       </c>
       <c r="W195" t="n">
-        <v>-58.48888</v>
+        <v>-66.90618000000001</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
         </is>
       </c>
     </row>
@@ -14538,24 +14538,24 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Cliff Mine</t>
+          <t>Ruth Lake No 5</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>012B/09/Fe 001</t>
+          <t>023J/15/Fe 007</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14593,14 +14593,14 @@
         <v>26</v>
       </c>
       <c r="V196" t="n">
-        <v>48.54434</v>
+        <v>54.80503</v>
       </c>
       <c r="W196" t="n">
-        <v>-58.49915</v>
+        <v>-66.88023</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Ruth Lake No 6</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>023J/15/Fe 008</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -14665,14 +14665,14 @@
         <v>26</v>
       </c>
       <c r="V197" t="n">
-        <v>49.50376</v>
+        <v>54.80104</v>
       </c>
       <c r="W197" t="n">
-        <v>-55.21553</v>
+        <v>-66.87327999999999</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
         </is>
       </c>
     </row>
@@ -14682,12 +14682,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Grey Copper Mine</t>
+          <t>Ruth Lake No 9</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>002E/11/Cu 001</t>
+          <t>023J/15/Fe 005</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Iron, Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14737,14 +14737,14 @@
         <v>26</v>
       </c>
       <c r="V198" t="n">
-        <v>49.5173</v>
+        <v>54.80033</v>
       </c>
       <c r="W198" t="n">
-        <v>-55.2721</v>
+        <v>-66.89447</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14754,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lorraine Mine</t>
+          <t>Ruth Lake No 1</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>023G/02/Fe 004</t>
+          <t>023J/15/Fe 002</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14809,14 +14809,14 @@
         <v>26</v>
       </c>
       <c r="V199" t="n">
-        <v>53.06833</v>
+        <v>54.79145</v>
       </c>
       <c r="W199" t="n">
-        <v>-66.94949</v>
+        <v>-66.85449</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
         </is>
       </c>
     </row>
@@ -14826,24 +14826,24 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Wishart No 1 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>023J/15/Fe 010</t>
+          <t>023J/15/Fe 003</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14881,14 +14881,14 @@
         <v>26</v>
       </c>
       <c r="V200" t="n">
-        <v>54.77437</v>
+        <v>54.76166</v>
       </c>
       <c r="W200" t="n">
-        <v>-66.82881</v>
+        <v>-66.88793</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20010</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Smallwood Mine</t>
+          <t>Wishart No 2 (Wishart Mine)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>023G/02/Fe 001</t>
+          <t>023J/15/Fe 004</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14953,14 +14953,14 @@
         <v>26</v>
       </c>
       <c r="V201" t="n">
-        <v>53.03718</v>
+        <v>54.7654</v>
       </c>
       <c r="W201" t="n">
-        <v>-66.93694000000001</v>
+        <v>-66.9067</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -14970,12 +14970,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ruth Lake No 1</t>
+          <t>Ruth Lake No 3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>023J/15/Fe 002</t>
+          <t>023J/15/Fe 001</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -15025,14 +15025,14 @@
         <v>26</v>
       </c>
       <c r="V202" t="n">
-        <v>54.79145</v>
+        <v>54.80404</v>
       </c>
       <c r="W202" t="n">
-        <v>-66.85449</v>
+        <v>-66.87016</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20002</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15042,24 +15042,24 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Wishart No 1 (Wishart Mine)</t>
+          <t>Lorraine Mine</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>023J/15/Fe 003</t>
+          <t>023G/02/Fe 004</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15097,14 +15097,14 @@
         <v>26</v>
       </c>
       <c r="V203" t="n">
-        <v>54.76166</v>
+        <v>53.06833</v>
       </c>
       <c r="W203" t="n">
-        <v>-66.88793</v>
+        <v>-66.94949</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20004</t>
         </is>
       </c>
     </row>
@@ -15114,12 +15114,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Ruth Lake No 3</t>
+          <t>Smallwood Mine</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>023J/15/Fe 001</t>
+          <t>023G/02/Fe 001</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -15169,14 +15169,14 @@
         <v>26</v>
       </c>
       <c r="V204" t="n">
-        <v>54.80404</v>
+        <v>53.03718</v>
       </c>
       <c r="W204" t="n">
-        <v>-66.87016</v>
+        <v>-66.93694000000001</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023G%2F02%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -15186,24 +15186,24 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Wishart No 2 (Wishart Mine)</t>
+          <t>Timmins No 1</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>023J/15/Fe 004</t>
+          <t>023J/14/Fe 018</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -15241,14 +15241,14 @@
         <v>26</v>
       </c>
       <c r="V205" t="n">
-        <v>54.7654</v>
+        <v>54.88449</v>
       </c>
       <c r="W205" t="n">
-        <v>-66.9067</v>
+        <v>-67.08575</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20018</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ruth Lake No 9</t>
+          <t>Timmins No 2</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>023J/15/Fe 005</t>
+          <t>023J/14/Fe 019</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -15313,14 +15313,14 @@
         <v>26</v>
       </c>
       <c r="V206" t="n">
-        <v>54.80033</v>
+        <v>54.89421</v>
       </c>
       <c r="W206" t="n">
-        <v>-66.89447</v>
+        <v>-67.08716</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20005</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20019</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15330,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Ruth Lake No 7</t>
+          <t>Timmins No 6</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>023J/15/Fe 006</t>
+          <t>023J/14/Fe 021</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15385,14 +15385,14 @@
         <v>26</v>
       </c>
       <c r="V207" t="n">
-        <v>54.80557</v>
+        <v>54.90148</v>
       </c>
       <c r="W207" t="n">
-        <v>-66.90618000000001</v>
+        <v>-67.09757999999999</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20006</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20021</t>
         </is>
       </c>
     </row>
@@ -15402,24 +15402,24 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ruth Lake No 5</t>
+          <t>Fleming No 3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>023J/15/Fe 007</t>
+          <t>023J/14/Fe 022</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15457,14 +15457,14 @@
         <v>26</v>
       </c>
       <c r="V208" t="n">
-        <v>54.80503</v>
+        <v>54.85836</v>
       </c>
       <c r="W208" t="n">
-        <v>-66.88023</v>
+        <v>-67.03167999999999</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20007</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20022</t>
         </is>
       </c>
     </row>
@@ -15474,24 +15474,24 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Ruth Lake No 6</t>
+          <t>Timmins No 4</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>023J/15/Fe 008</t>
+          <t>023J/14/Fe 023</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15529,14 +15529,14 @@
         <v>26</v>
       </c>
       <c r="V209" t="n">
-        <v>54.80104</v>
+        <v>54.89884</v>
       </c>
       <c r="W209" t="n">
-        <v>-66.87327999999999</v>
+        <v>-67.10881000000001</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F15%2FFe%20008</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023J%2F14%2FFe%20023</t>
         </is>
       </c>
     </row>
